--- a/Facturi_Neincasate.xlsx
+++ b/Facturi_Neincasate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="494">
   <si>
     <t>denumire client</t>
   </si>
@@ -1493,13 +1493,16 @@
   </si>
   <si>
     <t>Calin (G7 Depozit)</t>
+  </si>
+  <si>
+    <t>DMEG 8290</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1511,6 +1514,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1551,7 +1560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1561,6 +1570,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1856,7 +1873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E376"/>
+  <dimension ref="A1:E377"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.28515625" customWidth="1"/>
@@ -4520,16 +4537,16 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>44</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C157" s="3">
-        <v>180.85</v>
-      </c>
-      <c r="D157" s="3">
-        <v>180.85</v>
+        <v>43</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="C157" s="5">
+        <v>-10410.31</v>
+      </c>
+      <c r="D157" s="5">
+        <v>-10410.31</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>489</v>
@@ -4540,13 +4557,13 @@
         <v>44</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C158" s="3">
-        <v>1378.14</v>
+        <v>180.85</v>
       </c>
       <c r="D158" s="3">
-        <v>1378.14</v>
+        <v>180.85</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>489</v>
@@ -4554,33 +4571,33 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C159" s="3">
-        <v>1147.04</v>
+        <v>1378.14</v>
       </c>
       <c r="D159" s="3">
-        <v>1147.04</v>
+        <v>1378.14</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C160" s="3">
-        <v>1270.68</v>
+        <v>1147.04</v>
       </c>
       <c r="D160" s="3">
-        <v>461.97</v>
+        <v>1147.04</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>490</v>
@@ -4591,13 +4608,13 @@
         <v>46</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C161" s="3">
-        <v>1169.94</v>
+        <v>1270.68</v>
       </c>
       <c r="D161" s="3">
-        <v>1169.94</v>
+        <v>461.97</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>490</v>
@@ -4608,13 +4625,13 @@
         <v>46</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C162" s="3">
-        <v>443.82</v>
+        <v>1169.94</v>
       </c>
       <c r="D162" s="3">
-        <v>443.82</v>
+        <v>1169.94</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>490</v>
@@ -4625,13 +4642,13 @@
         <v>46</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C163" s="3">
-        <v>848.28</v>
+        <v>443.82</v>
       </c>
       <c r="D163" s="3">
-        <v>848.28</v>
+        <v>443.82</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>490</v>
@@ -4642,13 +4659,13 @@
         <v>46</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C164" s="3">
-        <v>1908.79</v>
+        <v>848.28</v>
       </c>
       <c r="D164" s="3">
-        <v>1908.79</v>
+        <v>848.28</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>490</v>
@@ -4659,13 +4676,13 @@
         <v>46</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C165" s="3">
-        <v>3337.92</v>
+        <v>1908.79</v>
       </c>
       <c r="D165" s="3">
-        <v>3337.92</v>
+        <v>1908.79</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>490</v>
@@ -4676,13 +4693,13 @@
         <v>46</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C166" s="3">
-        <v>949.96</v>
+        <v>3337.92</v>
       </c>
       <c r="D166" s="3">
-        <v>949.96</v>
+        <v>3337.92</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>490</v>
@@ -4693,13 +4710,13 @@
         <v>46</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C167" s="3">
-        <v>1343.4</v>
+        <v>949.96</v>
       </c>
       <c r="D167" s="3">
-        <v>1343.4</v>
+        <v>949.96</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>490</v>
@@ -4710,13 +4727,13 @@
         <v>46</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C168" s="3">
-        <v>452.3</v>
+        <v>1343.4</v>
       </c>
       <c r="D168" s="3">
-        <v>452.3</v>
+        <v>1343.4</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>490</v>
@@ -4727,13 +4744,13 @@
         <v>46</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C169" s="3">
-        <v>1697.98</v>
+        <v>452.3</v>
       </c>
       <c r="D169" s="3">
-        <v>1697.98</v>
+        <v>452.3</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>490</v>
@@ -4741,33 +4758,33 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C170" s="3">
-        <v>234.16</v>
+        <v>1697.98</v>
       </c>
       <c r="D170" s="3">
-        <v>234.16</v>
+        <v>1697.98</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C171" s="3">
-        <v>4089.68</v>
+        <v>234.16</v>
       </c>
       <c r="D171" s="3">
-        <v>2589.6799999999998</v>
+        <v>234.16</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>489</v>
@@ -4775,36 +4792,36 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C172" s="3">
-        <v>628.79999999999995</v>
+        <v>4089.68</v>
       </c>
       <c r="D172" s="3">
-        <v>262.77999999999997</v>
+        <v>2589.6799999999998</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C173" s="3">
-        <v>2232.1999999999998</v>
+        <v>628.79999999999995</v>
       </c>
       <c r="D173" s="3">
-        <v>1802.77</v>
+        <v>262.77999999999997</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -4812,13 +4829,13 @@
         <v>50</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C174" s="3">
-        <v>591.96</v>
+        <v>2232.1999999999998</v>
       </c>
       <c r="D174" s="3">
-        <v>591.96</v>
+        <v>1802.77</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>490</v>
@@ -4829,13 +4846,13 @@
         <v>50</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C175" s="3">
-        <v>1182.92</v>
+        <v>591.96</v>
       </c>
       <c r="D175" s="3">
-        <v>1182.92</v>
+        <v>591.96</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>490</v>
@@ -4846,13 +4863,13 @@
         <v>50</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C176" s="3">
-        <v>1045.79</v>
+        <v>1182.92</v>
       </c>
       <c r="D176" s="3">
-        <v>1045.79</v>
+        <v>1182.92</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>490</v>
@@ -4863,13 +4880,13 @@
         <v>50</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C177" s="3">
-        <v>1170.74</v>
+        <v>1045.79</v>
       </c>
       <c r="D177" s="3">
-        <v>1170.74</v>
+        <v>1045.79</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>490</v>
@@ -4880,13 +4897,13 @@
         <v>50</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C178" s="3">
-        <v>1356.94</v>
+        <v>1170.74</v>
       </c>
       <c r="D178" s="3">
-        <v>1356.94</v>
+        <v>1170.74</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>490</v>
@@ -4894,19 +4911,19 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C179" s="3">
-        <v>1727.3</v>
+        <v>1356.94</v>
       </c>
       <c r="D179" s="3">
-        <v>1094.17</v>
+        <v>1356.94</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -4914,13 +4931,13 @@
         <v>51</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C180" s="3">
-        <v>465.46</v>
+        <v>1727.3</v>
       </c>
       <c r="D180" s="3">
-        <v>465.46</v>
+        <v>1094.17</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>489</v>
@@ -4931,13 +4948,13 @@
         <v>51</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C181" s="3">
-        <v>5074.25</v>
+        <v>465.46</v>
       </c>
       <c r="D181" s="3">
-        <v>5074.25</v>
+        <v>465.46</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>489</v>
@@ -4945,36 +4962,36 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C182" s="3">
-        <v>403.05</v>
+        <v>5074.25</v>
       </c>
       <c r="D182" s="3">
-        <v>403.05</v>
+        <v>5074.25</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C183" s="3">
-        <v>922.4</v>
+        <v>403.05</v>
       </c>
       <c r="D183" s="3">
-        <v>422.4</v>
+        <v>403.05</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -4982,13 +4999,13 @@
         <v>53</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C184" s="3">
-        <v>586.17999999999995</v>
+        <v>922.4</v>
       </c>
       <c r="D184" s="3">
-        <v>586.17999999999995</v>
+        <v>422.4</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>489</v>
@@ -4999,13 +5016,13 @@
         <v>53</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C185" s="3">
-        <v>443.82</v>
+        <v>586.17999999999995</v>
       </c>
       <c r="D185" s="3">
-        <v>443.82</v>
+        <v>586.17999999999995</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>489</v>
@@ -5013,19 +5030,19 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C186" s="3">
-        <v>62.92</v>
+        <v>443.82</v>
       </c>
       <c r="D186" s="3">
-        <v>59.76</v>
+        <v>443.82</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -5033,13 +5050,13 @@
         <v>54</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C187" s="3">
-        <v>1357.87</v>
+        <v>62.92</v>
       </c>
       <c r="D187" s="3">
-        <v>1357.87</v>
+        <v>59.76</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>490</v>
@@ -5050,13 +5067,13 @@
         <v>54</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C188" s="3">
-        <v>446.71</v>
+        <v>1357.87</v>
       </c>
       <c r="D188" s="3">
-        <v>446.71</v>
+        <v>1357.87</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>490</v>
@@ -5064,16 +5081,16 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C189" s="3">
-        <v>634.15</v>
+        <v>446.71</v>
       </c>
       <c r="D189" s="3">
-        <v>634.15</v>
+        <v>446.71</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>490</v>
@@ -5081,16 +5098,16 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C190" s="3">
-        <v>1854.68</v>
+        <v>634.15</v>
       </c>
       <c r="D190" s="3">
-        <v>598.82000000000005</v>
+        <v>634.15</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>490</v>
@@ -5098,16 +5115,16 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C191" s="3">
-        <v>271.16000000000003</v>
+        <v>1854.68</v>
       </c>
       <c r="D191" s="3">
-        <v>271.16000000000003</v>
+        <v>598.82000000000005</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>490</v>
@@ -5115,16 +5132,16 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C192" s="3">
-        <v>5049.43</v>
+        <v>271.16000000000003</v>
       </c>
       <c r="D192" s="3">
-        <v>100</v>
+        <v>271.16000000000003</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>490</v>
@@ -5132,19 +5149,19 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C193" s="3">
-        <v>8148.44</v>
+        <v>5049.43</v>
       </c>
       <c r="D193" s="3">
-        <v>4148.4399999999996</v>
+        <v>100</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -5152,13 +5169,13 @@
         <v>59</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C194" s="3">
-        <v>2326.6</v>
+        <v>8148.44</v>
       </c>
       <c r="D194" s="3">
-        <v>2326.6</v>
+        <v>4148.4399999999996</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>489</v>
@@ -5166,16 +5183,16 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C195" s="3">
-        <v>196.96</v>
+        <v>2326.6</v>
       </c>
       <c r="D195" s="3">
-        <v>13.94</v>
+        <v>2326.6</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>489</v>
@@ -5186,13 +5203,13 @@
         <v>60</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C196" s="3">
-        <v>632.58000000000004</v>
+        <v>196.96</v>
       </c>
       <c r="D196" s="3">
-        <v>632.58000000000004</v>
+        <v>13.94</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>489</v>
@@ -5203,13 +5220,13 @@
         <v>60</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C197" s="3">
-        <v>188.74</v>
+        <v>632.58000000000004</v>
       </c>
       <c r="D197" s="3">
-        <v>188.74</v>
+        <v>632.58000000000004</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>489</v>
@@ -5220,13 +5237,13 @@
         <v>60</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C198" s="3">
-        <v>822.61</v>
+        <v>188.74</v>
       </c>
       <c r="D198" s="3">
-        <v>822.61</v>
+        <v>188.74</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>489</v>
@@ -5234,16 +5251,16 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C199" s="3">
-        <v>6571.11</v>
+        <v>822.61</v>
       </c>
       <c r="D199" s="3">
-        <v>1565.07</v>
+        <v>822.61</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>489</v>
@@ -5254,13 +5271,13 @@
         <v>61</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C200" s="3">
-        <v>67.39</v>
+        <v>6571.11</v>
       </c>
       <c r="D200" s="3">
-        <v>67.39</v>
+        <v>1565.07</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>489</v>
@@ -5271,13 +5288,13 @@
         <v>61</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C201" s="3">
-        <v>235.12</v>
+        <v>67.39</v>
       </c>
       <c r="D201" s="3">
-        <v>235.12</v>
+        <v>67.39</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>489</v>
@@ -5288,13 +5305,13 @@
         <v>61</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C202" s="3">
-        <v>7257.6</v>
+        <v>235.12</v>
       </c>
       <c r="D202" s="3">
-        <v>7257.6</v>
+        <v>235.12</v>
       </c>
       <c r="E202" s="3" t="s">
         <v>489</v>
@@ -5305,13 +5322,13 @@
         <v>61</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C203" s="3">
-        <v>6111.13</v>
+        <v>7257.6</v>
       </c>
       <c r="D203" s="3">
-        <v>6111.13</v>
+        <v>7257.6</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>489</v>
@@ -5322,13 +5339,13 @@
         <v>61</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C204" s="3">
-        <v>185.97</v>
+        <v>6111.13</v>
       </c>
       <c r="D204" s="3">
-        <v>185.97</v>
+        <v>6111.13</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>489</v>
@@ -5339,13 +5356,13 @@
         <v>61</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C205" s="3">
-        <v>204.69</v>
+        <v>185.97</v>
       </c>
       <c r="D205" s="3">
-        <v>204.69</v>
+        <v>185.97</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>489</v>
@@ -5356,13 +5373,13 @@
         <v>61</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C206" s="3">
-        <v>341.16</v>
+        <v>204.69</v>
       </c>
       <c r="D206" s="3">
-        <v>341.16</v>
+        <v>204.69</v>
       </c>
       <c r="E206" s="3" t="s">
         <v>489</v>
@@ -5373,13 +5390,13 @@
         <v>61</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C207" s="3">
-        <v>204.66</v>
+        <v>341.16</v>
       </c>
       <c r="D207" s="3">
-        <v>204.66</v>
+        <v>341.16</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>489</v>
@@ -5390,13 +5407,13 @@
         <v>61</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C208" s="3">
-        <v>2520.7800000000002</v>
+        <v>204.66</v>
       </c>
       <c r="D208" s="3">
-        <v>2520.7800000000002</v>
+        <v>204.66</v>
       </c>
       <c r="E208" s="3" t="s">
         <v>489</v>
@@ -5404,16 +5421,16 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C209" s="3">
-        <v>448.44</v>
+        <v>2520.7800000000002</v>
       </c>
       <c r="D209" s="3">
-        <v>448.44</v>
+        <v>2520.7800000000002</v>
       </c>
       <c r="E209" s="3" t="s">
         <v>489</v>
@@ -5421,19 +5438,19 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C210" s="3">
-        <v>1109.76</v>
+        <v>448.44</v>
       </c>
       <c r="D210" s="3">
-        <v>289.12</v>
+        <v>448.44</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -5441,13 +5458,13 @@
         <v>63</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C211" s="3">
-        <v>243.15</v>
+        <v>1109.76</v>
       </c>
       <c r="D211" s="3">
-        <v>243.15</v>
+        <v>289.12</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>490</v>
@@ -5458,13 +5475,13 @@
         <v>63</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C212" s="3">
-        <v>467.73</v>
+        <v>243.15</v>
       </c>
       <c r="D212" s="3">
-        <v>467.73</v>
+        <v>243.15</v>
       </c>
       <c r="E212" s="3" t="s">
         <v>490</v>
@@ -5475,13 +5492,13 @@
         <v>63</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C213" s="3">
-        <v>1591.95</v>
+        <v>467.73</v>
       </c>
       <c r="D213" s="3">
-        <v>1591.95</v>
+        <v>467.73</v>
       </c>
       <c r="E213" s="3" t="s">
         <v>490</v>
@@ -5489,19 +5506,19 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C214" s="3">
-        <v>507.56</v>
+        <v>1591.95</v>
       </c>
       <c r="D214" s="3">
-        <v>507.56</v>
+        <v>1591.95</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -5509,13 +5526,13 @@
         <v>64</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C215" s="3">
-        <v>659.4</v>
+        <v>507.56</v>
       </c>
       <c r="D215" s="3">
-        <v>659.4</v>
+        <v>507.56</v>
       </c>
       <c r="E215" s="3" t="s">
         <v>489</v>
@@ -5523,19 +5540,19 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C216" s="3">
-        <v>298.19</v>
+        <v>659.4</v>
       </c>
       <c r="D216" s="3">
-        <v>70.8</v>
+        <v>659.4</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -5543,13 +5560,13 @@
         <v>65</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C217" s="3">
-        <v>143.43</v>
+        <v>298.19</v>
       </c>
       <c r="D217" s="3">
-        <v>143.43</v>
+        <v>70.8</v>
       </c>
       <c r="E217" s="3" t="s">
         <v>490</v>
@@ -5560,13 +5577,13 @@
         <v>65</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C218" s="3">
-        <v>666.99</v>
+        <v>143.43</v>
       </c>
       <c r="D218" s="3">
-        <v>666.99</v>
+        <v>143.43</v>
       </c>
       <c r="E218" s="3" t="s">
         <v>490</v>
@@ -5577,13 +5594,13 @@
         <v>65</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C219" s="3">
-        <v>570.26</v>
+        <v>666.99</v>
       </c>
       <c r="D219" s="3">
-        <v>570.26</v>
+        <v>666.99</v>
       </c>
       <c r="E219" s="3" t="s">
         <v>490</v>
@@ -5594,13 +5611,13 @@
         <v>65</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C220" s="3">
-        <v>97.98</v>
+        <v>570.26</v>
       </c>
       <c r="D220" s="3">
-        <v>97.98</v>
+        <v>570.26</v>
       </c>
       <c r="E220" s="3" t="s">
         <v>490</v>
@@ -5611,13 +5628,13 @@
         <v>65</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C221" s="3">
-        <v>321.5</v>
+        <v>97.98</v>
       </c>
       <c r="D221" s="3">
-        <v>321.5</v>
+        <v>97.98</v>
       </c>
       <c r="E221" s="3" t="s">
         <v>490</v>
@@ -5628,13 +5645,13 @@
         <v>65</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C222" s="3">
-        <v>436.49</v>
+        <v>321.5</v>
       </c>
       <c r="D222" s="3">
-        <v>436.49</v>
+        <v>321.5</v>
       </c>
       <c r="E222" s="3" t="s">
         <v>490</v>
@@ -5642,16 +5659,16 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C223" s="3">
-        <v>8550.85</v>
+        <v>436.49</v>
       </c>
       <c r="D223" s="3">
-        <v>6550.4</v>
+        <v>436.49</v>
       </c>
       <c r="E223" s="3" t="s">
         <v>490</v>
@@ -5662,13 +5679,13 @@
         <v>66</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C224" s="3">
-        <v>6602.62</v>
+        <v>8550.85</v>
       </c>
       <c r="D224" s="3">
-        <v>6602.62</v>
+        <v>6550.4</v>
       </c>
       <c r="E224" s="3" t="s">
         <v>490</v>
@@ -5676,33 +5693,33 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C225" s="3">
-        <v>188.76</v>
+        <v>6602.62</v>
       </c>
       <c r="D225" s="3">
-        <v>188.76</v>
+        <v>6602.62</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:5">
       <c r="A226" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C226" s="3">
-        <v>981.11</v>
+        <v>188.76</v>
       </c>
       <c r="D226" s="3">
-        <v>981.11</v>
+        <v>188.76</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>489</v>
@@ -5710,16 +5727,16 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C227" s="3">
-        <v>686.99</v>
+        <v>981.11</v>
       </c>
       <c r="D227" s="3">
-        <v>686.99</v>
+        <v>981.11</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>489</v>
@@ -5727,16 +5744,16 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C228" s="3">
-        <v>2755.5</v>
+        <v>686.99</v>
       </c>
       <c r="D228" s="3">
-        <v>2654.72</v>
+        <v>686.99</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>489</v>
@@ -5747,13 +5764,13 @@
         <v>70</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C229" s="3">
-        <v>1051.1400000000001</v>
+        <v>2755.5</v>
       </c>
       <c r="D229" s="3">
-        <v>1051.1400000000001</v>
+        <v>2654.72</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>489</v>
@@ -5764,13 +5781,13 @@
         <v>70</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C230" s="3">
-        <v>50.64</v>
+        <v>1051.1400000000001</v>
       </c>
       <c r="D230" s="3">
-        <v>50.64</v>
+        <v>1051.1400000000001</v>
       </c>
       <c r="E230" s="3" t="s">
         <v>489</v>
@@ -5781,13 +5798,13 @@
         <v>70</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C231" s="3">
-        <v>380.31</v>
+        <v>50.64</v>
       </c>
       <c r="D231" s="3">
-        <v>380.31</v>
+        <v>50.64</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>489</v>
@@ -5798,13 +5815,13 @@
         <v>70</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C232" s="3">
-        <v>367.8</v>
+        <v>380.31</v>
       </c>
       <c r="D232" s="3">
-        <v>367.8</v>
+        <v>380.31</v>
       </c>
       <c r="E232" s="3" t="s">
         <v>489</v>
@@ -5815,13 +5832,13 @@
         <v>70</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C233" s="3">
-        <v>185.97</v>
+        <v>367.8</v>
       </c>
       <c r="D233" s="3">
-        <v>185.97</v>
+        <v>367.8</v>
       </c>
       <c r="E233" s="3" t="s">
         <v>489</v>
@@ -5832,13 +5849,13 @@
         <v>70</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C234" s="3">
-        <v>288.83999999999997</v>
+        <v>185.97</v>
       </c>
       <c r="D234" s="3">
-        <v>288.83999999999997</v>
+        <v>185.97</v>
       </c>
       <c r="E234" s="3" t="s">
         <v>489</v>
@@ -5849,13 +5866,13 @@
         <v>70</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C235" s="3">
-        <v>412.7</v>
+        <v>288.83999999999997</v>
       </c>
       <c r="D235" s="3">
-        <v>412.7</v>
+        <v>288.83999999999997</v>
       </c>
       <c r="E235" s="3" t="s">
         <v>489</v>
@@ -5863,16 +5880,16 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C236" s="3">
-        <v>886.1</v>
+        <v>412.7</v>
       </c>
       <c r="D236" s="3">
-        <v>638.34</v>
+        <v>412.7</v>
       </c>
       <c r="E236" s="3" t="s">
         <v>489</v>
@@ -5883,13 +5900,13 @@
         <v>71</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C237" s="3">
-        <v>239.52</v>
+        <v>886.1</v>
       </c>
       <c r="D237" s="3">
-        <v>239.52</v>
+        <v>638.34</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>489</v>
@@ -5900,13 +5917,13 @@
         <v>71</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C238" s="3">
-        <v>498.92</v>
+        <v>239.52</v>
       </c>
       <c r="D238" s="3">
-        <v>498.92</v>
+        <v>239.52</v>
       </c>
       <c r="E238" s="3" t="s">
         <v>489</v>
@@ -5917,13 +5934,13 @@
         <v>71</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C239" s="3">
-        <v>286.82</v>
+        <v>498.92</v>
       </c>
       <c r="D239" s="3">
-        <v>286.82</v>
+        <v>498.92</v>
       </c>
       <c r="E239" s="3" t="s">
         <v>489</v>
@@ -5931,19 +5948,19 @@
     </row>
     <row r="240" spans="1:5">
       <c r="A240" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C240" s="3">
-        <v>2283.4499999999998</v>
+        <v>286.82</v>
       </c>
       <c r="D240" s="3">
-        <v>2283.4499999999998</v>
+        <v>286.82</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -5951,13 +5968,13 @@
         <v>72</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C241" s="3">
-        <v>809.77</v>
+        <v>2283.4499999999998</v>
       </c>
       <c r="D241" s="3">
-        <v>809.77</v>
+        <v>2283.4499999999998</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>490</v>
@@ -5965,19 +5982,19 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C242" s="3">
-        <v>377.4</v>
+        <v>809.77</v>
       </c>
       <c r="D242" s="3">
-        <v>377.4</v>
+        <v>809.77</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -5985,13 +6002,13 @@
         <v>73</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C243" s="3">
-        <v>698.2</v>
+        <v>377.4</v>
       </c>
       <c r="D243" s="3">
-        <v>698.2</v>
+        <v>377.4</v>
       </c>
       <c r="E243" s="3" t="s">
         <v>489</v>
@@ -6002,13 +6019,13 @@
         <v>73</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C244" s="3">
-        <v>904.49</v>
+        <v>698.2</v>
       </c>
       <c r="D244" s="3">
-        <v>904.49</v>
+        <v>698.2</v>
       </c>
       <c r="E244" s="3" t="s">
         <v>489</v>
@@ -6019,13 +6036,13 @@
         <v>73</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C245" s="3">
-        <v>1206.99</v>
+        <v>904.49</v>
       </c>
       <c r="D245" s="3">
-        <v>1206.99</v>
+        <v>904.49</v>
       </c>
       <c r="E245" s="3" t="s">
         <v>489</v>
@@ -6036,13 +6053,13 @@
         <v>73</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C246" s="3">
-        <v>1622.56</v>
+        <v>1206.99</v>
       </c>
       <c r="D246" s="3">
-        <v>1622.56</v>
+        <v>1206.99</v>
       </c>
       <c r="E246" s="3" t="s">
         <v>489</v>
@@ -6050,19 +6067,19 @@
     </row>
     <row r="247" spans="1:5">
       <c r="A247" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C247" s="3">
-        <v>1525.12</v>
+        <v>1622.56</v>
       </c>
       <c r="D247" s="3">
-        <v>1525.12</v>
+        <v>1622.56</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -6070,13 +6087,13 @@
         <v>74</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C248" s="3">
-        <v>2037.99</v>
+        <v>1525.12</v>
       </c>
       <c r="D248" s="3">
-        <v>2037.99</v>
+        <v>1525.12</v>
       </c>
       <c r="E248" s="3" t="s">
         <v>490</v>
@@ -6084,19 +6101,19 @@
     </row>
     <row r="249" spans="1:5">
       <c r="A249" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C249" s="3">
-        <v>2373.4299999999998</v>
+        <v>2037.99</v>
       </c>
       <c r="D249" s="3">
-        <v>1703.6</v>
+        <v>2037.99</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -6104,13 +6121,13 @@
         <v>75</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C250" s="3">
-        <v>2372.73</v>
+        <v>2373.4299999999998</v>
       </c>
       <c r="D250" s="3">
-        <v>2372.73</v>
+        <v>1703.6</v>
       </c>
       <c r="E250" s="3" t="s">
         <v>489</v>
@@ -6121,13 +6138,13 @@
         <v>75</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C251" s="3">
-        <v>216</v>
+        <v>2372.73</v>
       </c>
       <c r="D251" s="3">
-        <v>216</v>
+        <v>2372.73</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>489</v>
@@ -6138,13 +6155,13 @@
         <v>75</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C252" s="3">
-        <v>251.63</v>
+        <v>216</v>
       </c>
       <c r="D252" s="3">
-        <v>251.63</v>
+        <v>216</v>
       </c>
       <c r="E252" s="3" t="s">
         <v>489</v>
@@ -6152,16 +6169,16 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C253" s="3">
-        <v>448.44</v>
+        <v>251.63</v>
       </c>
       <c r="D253" s="3">
-        <v>448.44</v>
+        <v>251.63</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>489</v>
@@ -6169,67 +6186,67 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C254" s="3">
-        <v>905.46</v>
+        <v>448.44</v>
       </c>
       <c r="D254" s="3">
-        <v>905.46</v>
+        <v>448.44</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="255" spans="1:5">
       <c r="A255" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C255" s="3">
-        <v>522.57000000000005</v>
+        <v>905.46</v>
       </c>
       <c r="D255" s="3">
-        <v>522.57000000000005</v>
+        <v>905.46</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="256" spans="1:5">
       <c r="A256" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C256" s="3">
-        <v>924.1</v>
+        <v>522.57000000000005</v>
       </c>
       <c r="D256" s="3">
-        <v>924.1</v>
+        <v>522.57000000000005</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="257" spans="1:5">
       <c r="A257" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C257" s="3">
-        <v>3762.77</v>
+        <v>924.1</v>
       </c>
       <c r="D257" s="3">
-        <v>825.34</v>
+        <v>924.1</v>
       </c>
       <c r="E257" s="3" t="s">
         <v>490</v>
@@ -6240,13 +6257,13 @@
         <v>80</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C258" s="3">
-        <v>2087.52</v>
+        <v>3762.77</v>
       </c>
       <c r="D258" s="3">
-        <v>2087.52</v>
+        <v>825.34</v>
       </c>
       <c r="E258" s="3" t="s">
         <v>490</v>
@@ -6257,13 +6274,13 @@
         <v>80</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C259" s="3">
-        <v>267.10000000000002</v>
+        <v>2087.52</v>
       </c>
       <c r="D259" s="3">
-        <v>267.10000000000002</v>
+        <v>2087.52</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>490</v>
@@ -6274,13 +6291,13 @@
         <v>80</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C260" s="3">
-        <v>4118.0200000000004</v>
+        <v>267.10000000000002</v>
       </c>
       <c r="D260" s="3">
-        <v>4118.0200000000004</v>
+        <v>267.10000000000002</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>490</v>
@@ -6288,19 +6305,19 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C261" s="3">
-        <v>5017.9799999999996</v>
+        <v>4118.0200000000004</v>
       </c>
       <c r="D261" s="3">
-        <v>5017.9799999999996</v>
+        <v>4118.0200000000004</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -6308,13 +6325,13 @@
         <v>81</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C262" s="3">
-        <v>9692.1299999999992</v>
+        <v>5017.9799999999996</v>
       </c>
       <c r="D262" s="3">
-        <v>9692.1299999999992</v>
+        <v>5017.9799999999996</v>
       </c>
       <c r="E262" s="3" t="s">
         <v>489</v>
@@ -6322,16 +6339,16 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C263" s="3">
-        <v>627.24</v>
+        <v>9692.1299999999992</v>
       </c>
       <c r="D263" s="3">
-        <v>627.24</v>
+        <v>9692.1299999999992</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>489</v>
@@ -6342,13 +6359,13 @@
         <v>82</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C264" s="3">
-        <v>401.12</v>
+        <v>627.24</v>
       </c>
       <c r="D264" s="3">
-        <v>401.12</v>
+        <v>627.24</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>489</v>
@@ -6359,13 +6376,13 @@
         <v>82</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C265" s="3">
-        <v>508</v>
+        <v>401.12</v>
       </c>
       <c r="D265" s="3">
-        <v>508</v>
+        <v>401.12</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>489</v>
@@ -6373,19 +6390,19 @@
     </row>
     <row r="266" spans="1:5">
       <c r="A266" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C266" s="3">
-        <v>36000</v>
+        <v>508</v>
       </c>
       <c r="D266" s="3">
-        <v>16800</v>
+        <v>508</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -6393,13 +6410,13 @@
         <v>83</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C267" s="3">
-        <v>1072.2</v>
+        <v>36000</v>
       </c>
       <c r="D267" s="3">
-        <v>594.21</v>
+        <v>16800</v>
       </c>
       <c r="E267" s="3" t="s">
         <v>490</v>
@@ -6410,13 +6427,13 @@
         <v>83</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C268" s="3">
-        <v>416.84</v>
+        <v>1072.2</v>
       </c>
       <c r="D268" s="3">
-        <v>416.84</v>
+        <v>594.21</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>490</v>
@@ -6427,13 +6444,13 @@
         <v>83</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C269" s="3">
-        <v>729.12</v>
+        <v>416.84</v>
       </c>
       <c r="D269" s="3">
-        <v>729.12</v>
+        <v>416.84</v>
       </c>
       <c r="E269" s="3" t="s">
         <v>490</v>
@@ -6444,13 +6461,13 @@
         <v>83</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C270" s="3">
-        <v>356.73</v>
+        <v>729.12</v>
       </c>
       <c r="D270" s="3">
-        <v>356.73</v>
+        <v>729.12</v>
       </c>
       <c r="E270" s="3" t="s">
         <v>490</v>
@@ -6461,13 +6478,13 @@
         <v>83</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C271" s="3">
-        <v>651.4</v>
+        <v>356.73</v>
       </c>
       <c r="D271" s="3">
-        <v>651.4</v>
+        <v>356.73</v>
       </c>
       <c r="E271" s="3" t="s">
         <v>490</v>
@@ -6478,13 +6495,13 @@
         <v>83</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C272" s="3">
-        <v>764.3</v>
+        <v>651.4</v>
       </c>
       <c r="D272" s="3">
-        <v>764.3</v>
+        <v>651.4</v>
       </c>
       <c r="E272" s="3" t="s">
         <v>490</v>
@@ -6495,13 +6512,13 @@
         <v>83</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C273" s="3">
-        <v>729.12</v>
+        <v>764.3</v>
       </c>
       <c r="D273" s="3">
-        <v>729.12</v>
+        <v>764.3</v>
       </c>
       <c r="E273" s="3" t="s">
         <v>490</v>
@@ -6512,13 +6529,13 @@
         <v>83</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C274" s="3">
-        <v>216.35</v>
+        <v>729.12</v>
       </c>
       <c r="D274" s="3">
-        <v>216.35</v>
+        <v>729.12</v>
       </c>
       <c r="E274" s="3" t="s">
         <v>490</v>
@@ -6529,13 +6546,13 @@
         <v>83</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C275" s="3">
-        <v>597.20000000000005</v>
+        <v>216.35</v>
       </c>
       <c r="D275" s="3">
-        <v>597.20000000000005</v>
+        <v>216.35</v>
       </c>
       <c r="E275" s="3" t="s">
         <v>490</v>
@@ -6546,13 +6563,13 @@
         <v>83</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C276" s="3">
-        <v>5600.79</v>
+        <v>597.20000000000005</v>
       </c>
       <c r="D276" s="3">
-        <v>5600.79</v>
+        <v>597.20000000000005</v>
       </c>
       <c r="E276" s="3" t="s">
         <v>490</v>
@@ -6563,13 +6580,13 @@
         <v>83</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C277" s="3">
-        <v>652.29999999999995</v>
+        <v>5600.79</v>
       </c>
       <c r="D277" s="3">
-        <v>652.29999999999995</v>
+        <v>5600.79</v>
       </c>
       <c r="E277" s="3" t="s">
         <v>490</v>
@@ -6580,13 +6597,13 @@
         <v>83</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C278" s="3">
-        <v>2042.43</v>
+        <v>652.29999999999995</v>
       </c>
       <c r="D278" s="3">
-        <v>2042.43</v>
+        <v>652.29999999999995</v>
       </c>
       <c r="E278" s="3" t="s">
         <v>490</v>
@@ -6597,13 +6614,13 @@
         <v>83</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C279" s="3">
-        <v>870.5</v>
+        <v>2042.43</v>
       </c>
       <c r="D279" s="3">
-        <v>870.5</v>
+        <v>2042.43</v>
       </c>
       <c r="E279" s="3" t="s">
         <v>490</v>
@@ -6614,13 +6631,13 @@
         <v>83</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C280" s="3">
-        <v>1009.8</v>
+        <v>870.5</v>
       </c>
       <c r="D280" s="3">
-        <v>1009.8</v>
+        <v>870.5</v>
       </c>
       <c r="E280" s="3" t="s">
         <v>490</v>
@@ -6631,13 +6648,13 @@
         <v>83</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C281" s="3">
-        <v>870.5</v>
+        <v>1009.8</v>
       </c>
       <c r="D281" s="3">
-        <v>870.5</v>
+        <v>1009.8</v>
       </c>
       <c r="E281" s="3" t="s">
         <v>490</v>
@@ -6648,13 +6665,13 @@
         <v>83</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C282" s="3">
-        <v>596.72</v>
+        <v>870.5</v>
       </c>
       <c r="D282" s="3">
-        <v>596.72</v>
+        <v>870.5</v>
       </c>
       <c r="E282" s="3" t="s">
         <v>490</v>
@@ -6665,13 +6682,13 @@
         <v>83</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C283" s="3">
-        <v>736.72</v>
+        <v>596.72</v>
       </c>
       <c r="D283" s="3">
-        <v>736.72</v>
+        <v>596.72</v>
       </c>
       <c r="E283" s="3" t="s">
         <v>490</v>
@@ -6682,13 +6699,13 @@
         <v>83</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C284" s="3">
-        <v>716.1</v>
+        <v>736.72</v>
       </c>
       <c r="D284" s="3">
-        <v>716.1</v>
+        <v>736.72</v>
       </c>
       <c r="E284" s="3" t="s">
         <v>490</v>
@@ -6699,13 +6716,13 @@
         <v>83</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C285" s="3">
-        <v>564.66</v>
+        <v>716.1</v>
       </c>
       <c r="D285" s="3">
-        <v>564.66</v>
+        <v>716.1</v>
       </c>
       <c r="E285" s="3" t="s">
         <v>490</v>
@@ -6716,13 +6733,13 @@
         <v>83</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C286" s="3">
-        <v>651.29999999999995</v>
+        <v>564.66</v>
       </c>
       <c r="D286" s="3">
-        <v>651.29999999999995</v>
+        <v>564.66</v>
       </c>
       <c r="E286" s="3" t="s">
         <v>490</v>
@@ -6733,13 +6750,13 @@
         <v>83</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C287" s="3">
-        <v>898.02</v>
+        <v>651.29999999999995</v>
       </c>
       <c r="D287" s="3">
-        <v>898.02</v>
+        <v>651.29999999999995</v>
       </c>
       <c r="E287" s="3" t="s">
         <v>490</v>
@@ -6750,7 +6767,7 @@
         <v>83</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C288" s="3">
         <v>898.02</v>
@@ -6764,50 +6781,50 @@
     </row>
     <row r="289" spans="1:5">
       <c r="A289" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C289" s="3">
-        <v>13080.39</v>
+        <v>898.02</v>
       </c>
       <c r="D289" s="3">
-        <v>3528.34</v>
+        <v>898.02</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="290" spans="1:5">
       <c r="A290" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C290" s="3">
-        <v>358.62</v>
+        <v>13080.39</v>
       </c>
       <c r="D290" s="3">
-        <v>358.62</v>
+        <v>3528.34</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="291" spans="1:5">
       <c r="A291" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C291" s="3">
-        <v>748.1</v>
+        <v>358.62</v>
       </c>
       <c r="D291" s="3">
-        <v>248.1</v>
+        <v>358.62</v>
       </c>
       <c r="E291" s="3" t="s">
         <v>490</v>
@@ -6818,13 +6835,13 @@
         <v>86</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C292" s="3">
-        <v>432.76</v>
+        <v>748.1</v>
       </c>
       <c r="D292" s="3">
-        <v>432.76</v>
+        <v>248.1</v>
       </c>
       <c r="E292" s="3" t="s">
         <v>490</v>
@@ -6832,19 +6849,19 @@
     </row>
     <row r="293" spans="1:5">
       <c r="A293" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C293" s="3">
-        <v>578.61</v>
+        <v>432.76</v>
       </c>
       <c r="D293" s="3">
-        <v>578.61</v>
+        <v>432.76</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -6852,13 +6869,13 @@
         <v>87</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C294" s="3">
-        <v>6604.2</v>
+        <v>578.61</v>
       </c>
       <c r="D294" s="3">
-        <v>6604.2</v>
+        <v>578.61</v>
       </c>
       <c r="E294" s="3" t="s">
         <v>489</v>
@@ -6869,13 +6886,13 @@
         <v>87</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C295" s="3">
-        <v>535.79999999999995</v>
+        <v>6604.2</v>
       </c>
       <c r="D295" s="3">
-        <v>535.79999999999995</v>
+        <v>6604.2</v>
       </c>
       <c r="E295" s="3" t="s">
         <v>489</v>
@@ -6886,13 +6903,13 @@
         <v>87</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C296" s="3">
-        <v>6604.2</v>
+        <v>535.79999999999995</v>
       </c>
       <c r="D296" s="3">
-        <v>6604.2</v>
+        <v>535.79999999999995</v>
       </c>
       <c r="E296" s="3" t="s">
         <v>489</v>
@@ -6903,13 +6920,13 @@
         <v>87</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C297" s="3">
-        <v>2201.4</v>
+        <v>6604.2</v>
       </c>
       <c r="D297" s="3">
-        <v>2201.4</v>
+        <v>6604.2</v>
       </c>
       <c r="E297" s="3" t="s">
         <v>489</v>
@@ -6920,13 +6937,13 @@
         <v>87</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C298" s="3">
-        <v>1135.75</v>
+        <v>2201.4</v>
       </c>
       <c r="D298" s="3">
-        <v>1135.75</v>
+        <v>2201.4</v>
       </c>
       <c r="E298" s="3" t="s">
         <v>489</v>
@@ -6934,19 +6951,19 @@
     </row>
     <row r="299" spans="1:5">
       <c r="A299" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C299" s="3">
-        <v>8680.93</v>
+        <v>1135.75</v>
       </c>
       <c r="D299" s="3">
-        <v>5694.93</v>
+        <v>1135.75</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -6954,13 +6971,13 @@
         <v>88</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C300" s="3">
-        <v>9512.7099999999991</v>
+        <v>8680.93</v>
       </c>
       <c r="D300" s="3">
-        <v>9512.7099999999991</v>
+        <v>5694.93</v>
       </c>
       <c r="E300" s="3" t="s">
         <v>490</v>
@@ -6971,13 +6988,13 @@
         <v>88</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C301" s="3">
-        <v>6835.49</v>
+        <v>9512.7099999999991</v>
       </c>
       <c r="D301" s="3">
-        <v>6835.49</v>
+        <v>9512.7099999999991</v>
       </c>
       <c r="E301" s="3" t="s">
         <v>490</v>
@@ -6988,13 +7005,13 @@
         <v>88</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C302" s="3">
-        <v>374.52</v>
+        <v>6835.49</v>
       </c>
       <c r="D302" s="3">
-        <v>374.52</v>
+        <v>6835.49</v>
       </c>
       <c r="E302" s="3" t="s">
         <v>490</v>
@@ -7002,19 +7019,19 @@
     </row>
     <row r="303" spans="1:5">
       <c r="A303" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C303" s="3">
-        <v>432.76</v>
+        <v>374.52</v>
       </c>
       <c r="D303" s="3">
-        <v>46.38</v>
+        <v>374.52</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -7022,13 +7039,13 @@
         <v>89</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C304" s="3">
-        <v>656.44</v>
+        <v>432.76</v>
       </c>
       <c r="D304" s="3">
-        <v>656.44</v>
+        <v>46.38</v>
       </c>
       <c r="E304" s="3" t="s">
         <v>489</v>
@@ -7039,13 +7056,13 @@
         <v>89</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C305" s="3">
-        <v>142.41</v>
+        <v>656.44</v>
       </c>
       <c r="D305" s="3">
-        <v>142.41</v>
+        <v>656.44</v>
       </c>
       <c r="E305" s="3" t="s">
         <v>489</v>
@@ -7056,13 +7073,13 @@
         <v>89</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C306" s="3">
-        <v>409.44</v>
+        <v>142.41</v>
       </c>
       <c r="D306" s="3">
-        <v>409.44</v>
+        <v>142.41</v>
       </c>
       <c r="E306" s="3" t="s">
         <v>489</v>
@@ -7073,13 +7090,13 @@
         <v>89</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C307" s="3">
-        <v>461.93</v>
+        <v>409.44</v>
       </c>
       <c r="D307" s="3">
-        <v>461.93</v>
+        <v>409.44</v>
       </c>
       <c r="E307" s="3" t="s">
         <v>489</v>
@@ -7090,13 +7107,13 @@
         <v>89</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C308" s="3">
-        <v>146.88</v>
+        <v>461.93</v>
       </c>
       <c r="D308" s="3">
-        <v>146.88</v>
+        <v>461.93</v>
       </c>
       <c r="E308" s="3" t="s">
         <v>489</v>
@@ -7107,13 +7124,13 @@
         <v>89</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C309" s="3">
-        <v>804.28</v>
+        <v>146.88</v>
       </c>
       <c r="D309" s="3">
-        <v>804.28</v>
+        <v>146.88</v>
       </c>
       <c r="E309" s="3" t="s">
         <v>489</v>
@@ -7121,16 +7138,16 @@
     </row>
     <row r="310" spans="1:5">
       <c r="A310" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C310" s="3">
-        <v>1949.41</v>
+        <v>804.28</v>
       </c>
       <c r="D310" s="3">
-        <v>1583.6</v>
+        <v>804.28</v>
       </c>
       <c r="E310" s="3" t="s">
         <v>489</v>
@@ -7138,16 +7155,16 @@
     </row>
     <row r="311" spans="1:5">
       <c r="A311" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C311" s="3">
-        <v>1120.58</v>
+        <v>1949.41</v>
       </c>
       <c r="D311" s="3">
-        <v>1101.81</v>
+        <v>1583.6</v>
       </c>
       <c r="E311" s="3" t="s">
         <v>489</v>
@@ -7158,13 +7175,13 @@
         <v>91</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C312" s="3">
-        <v>356.1</v>
+        <v>1120.58</v>
       </c>
       <c r="D312" s="3">
-        <v>356.1</v>
+        <v>1101.81</v>
       </c>
       <c r="E312" s="3" t="s">
         <v>489</v>
@@ -7172,19 +7189,19 @@
     </row>
     <row r="313" spans="1:5">
       <c r="A313" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C313" s="3">
-        <v>3087.07</v>
+        <v>356.1</v>
       </c>
       <c r="D313" s="3">
-        <v>3087.07</v>
+        <v>356.1</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -7192,16 +7209,16 @@
         <v>92</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C314" s="3">
-        <v>2644.48</v>
+        <v>3087.07</v>
       </c>
       <c r="D314" s="3">
-        <v>2644.48</v>
+        <v>3087.07</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -7209,16 +7226,16 @@
         <v>92</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C315" s="3">
-        <v>2931.2</v>
+        <v>2644.48</v>
       </c>
       <c r="D315" s="3">
-        <v>2931.2</v>
+        <v>2644.48</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -7226,13 +7243,13 @@
         <v>92</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C316" s="3">
-        <v>2741.2</v>
+        <v>2931.2</v>
       </c>
       <c r="D316" s="3">
-        <v>2741.2</v>
+        <v>2931.2</v>
       </c>
       <c r="E316" s="3" t="s">
         <v>491</v>
@@ -7240,19 +7257,19 @@
     </row>
     <row r="317" spans="1:5">
       <c r="A317" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C317" s="3">
-        <v>3766.49</v>
+        <v>2741.2</v>
       </c>
       <c r="D317" s="3">
-        <v>1067.8599999999999</v>
+        <v>2741.2</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -7260,13 +7277,13 @@
         <v>93</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C318" s="3">
-        <v>269.85000000000002</v>
+        <v>3766.49</v>
       </c>
       <c r="D318" s="3">
-        <v>269.85000000000002</v>
+        <v>1067.8599999999999</v>
       </c>
       <c r="E318" s="3" t="s">
         <v>490</v>
@@ -7277,13 +7294,13 @@
         <v>93</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C319" s="3">
-        <v>733.35</v>
+        <v>269.85000000000002</v>
       </c>
       <c r="D319" s="3">
-        <v>733.35</v>
+        <v>269.85000000000002</v>
       </c>
       <c r="E319" s="3" t="s">
         <v>490</v>
@@ -7294,13 +7311,13 @@
         <v>93</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C320" s="3">
-        <v>10808.11</v>
+        <v>733.35</v>
       </c>
       <c r="D320" s="3">
-        <v>10808.11</v>
+        <v>733.35</v>
       </c>
       <c r="E320" s="3" t="s">
         <v>490</v>
@@ -7308,16 +7325,16 @@
     </row>
     <row r="321" spans="1:5">
       <c r="A321" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C321" s="3">
-        <v>2640.58</v>
+        <v>10808.11</v>
       </c>
       <c r="D321" s="3">
-        <v>1889.67</v>
+        <v>10808.11</v>
       </c>
       <c r="E321" s="3" t="s">
         <v>490</v>
@@ -7325,16 +7342,16 @@
     </row>
     <row r="322" spans="1:5">
       <c r="A322" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C322" s="3">
-        <v>4631.03</v>
+        <v>2640.58</v>
       </c>
       <c r="D322" s="3">
-        <v>4631.03</v>
+        <v>1889.67</v>
       </c>
       <c r="E322" s="3" t="s">
         <v>490</v>
@@ -7345,13 +7362,13 @@
         <v>95</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C323" s="3">
-        <v>1578.85</v>
+        <v>4631.03</v>
       </c>
       <c r="D323" s="3">
-        <v>1578.85</v>
+        <v>4631.03</v>
       </c>
       <c r="E323" s="3" t="s">
         <v>490</v>
@@ -7359,36 +7376,36 @@
     </row>
     <row r="324" spans="1:5">
       <c r="A324" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C324" s="3">
-        <v>3745.59</v>
+        <v>1578.85</v>
       </c>
       <c r="D324" s="3">
-        <v>3745.59</v>
+        <v>1578.85</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="325" spans="1:5">
       <c r="A325" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C325" s="3">
-        <v>1138.77</v>
+        <v>3745.59</v>
       </c>
       <c r="D325" s="3">
-        <v>1138.77</v>
+        <v>3745.59</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -7396,13 +7413,13 @@
         <v>97</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C326" s="3">
-        <v>1217.72</v>
+        <v>1138.77</v>
       </c>
       <c r="D326" s="3">
-        <v>1217.72</v>
+        <v>1138.77</v>
       </c>
       <c r="E326" s="3" t="s">
         <v>490</v>
@@ -7413,13 +7430,13 @@
         <v>97</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C327" s="3">
-        <v>706.5</v>
+        <v>1217.72</v>
       </c>
       <c r="D327" s="3">
-        <v>706.5</v>
+        <v>1217.72</v>
       </c>
       <c r="E327" s="3" t="s">
         <v>490</v>
@@ -7427,33 +7444,33 @@
     </row>
     <row r="328" spans="1:5">
       <c r="A328" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C328" s="3">
-        <v>1893.52</v>
+        <v>706.5</v>
       </c>
       <c r="D328" s="3">
-        <v>551.6</v>
+        <v>706.5</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="329" spans="1:5">
       <c r="A329" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C329" s="3">
-        <v>1414.7</v>
+        <v>1893.52</v>
       </c>
       <c r="D329" s="3">
-        <v>1414.7</v>
+        <v>551.6</v>
       </c>
       <c r="E329" s="3" t="s">
         <v>489</v>
@@ -7464,13 +7481,13 @@
         <v>99</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C330" s="3">
-        <v>1262.69</v>
+        <v>1414.7</v>
       </c>
       <c r="D330" s="3">
-        <v>1262.69</v>
+        <v>1414.7</v>
       </c>
       <c r="E330" s="3" t="s">
         <v>489</v>
@@ -7478,19 +7495,19 @@
     </row>
     <row r="331" spans="1:5">
       <c r="A331" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C331" s="3">
-        <v>829.15</v>
+        <v>1262.69</v>
       </c>
       <c r="D331" s="3">
-        <v>264.02999999999997</v>
+        <v>1262.69</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -7498,13 +7515,13 @@
         <v>100</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C332" s="3">
-        <v>569.84</v>
+        <v>829.15</v>
       </c>
       <c r="D332" s="3">
-        <v>569.84</v>
+        <v>264.02999999999997</v>
       </c>
       <c r="E332" s="3" t="s">
         <v>490</v>
@@ -7515,13 +7532,13 @@
         <v>100</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C333" s="3">
-        <v>211.45</v>
+        <v>569.84</v>
       </c>
       <c r="D333" s="3">
-        <v>211.45</v>
+        <v>569.84</v>
       </c>
       <c r="E333" s="3" t="s">
         <v>490</v>
@@ -7532,13 +7549,13 @@
         <v>100</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C334" s="3">
-        <v>92.34</v>
+        <v>211.45</v>
       </c>
       <c r="D334" s="3">
-        <v>92.34</v>
+        <v>211.45</v>
       </c>
       <c r="E334" s="3" t="s">
         <v>490</v>
@@ -7549,13 +7566,13 @@
         <v>100</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C335" s="3">
-        <v>318.69</v>
+        <v>92.34</v>
       </c>
       <c r="D335" s="3">
-        <v>318.69</v>
+        <v>92.34</v>
       </c>
       <c r="E335" s="3" t="s">
         <v>490</v>
@@ -7566,13 +7583,13 @@
         <v>100</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C336" s="3">
-        <v>501.26</v>
+        <v>318.69</v>
       </c>
       <c r="D336" s="3">
-        <v>501.26</v>
+        <v>318.69</v>
       </c>
       <c r="E336" s="3" t="s">
         <v>490</v>
@@ -7580,19 +7597,19 @@
     </row>
     <row r="337" spans="1:5">
       <c r="A337" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C337" s="3">
-        <v>10514.78</v>
+        <v>501.26</v>
       </c>
       <c r="D337" s="3">
-        <v>10514.78</v>
+        <v>501.26</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -7600,33 +7617,33 @@
         <v>101</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C338" s="3">
-        <v>1469.88</v>
+        <v>10514.78</v>
       </c>
       <c r="D338" s="3">
-        <v>1469.88</v>
+        <v>10514.78</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="339" spans="1:5">
       <c r="A339" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C339" s="3">
-        <v>307.13</v>
+        <v>1469.88</v>
       </c>
       <c r="D339" s="3">
-        <v>25.48</v>
+        <v>1469.88</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -7634,13 +7651,13 @@
         <v>102</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C340" s="3">
-        <v>112.29</v>
+        <v>307.13</v>
       </c>
       <c r="D340" s="3">
-        <v>112.29</v>
+        <v>25.48</v>
       </c>
       <c r="E340" s="3" t="s">
         <v>489</v>
@@ -7651,13 +7668,13 @@
         <v>102</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C341" s="3">
-        <v>344.22</v>
+        <v>112.29</v>
       </c>
       <c r="D341" s="3">
-        <v>344.22</v>
+        <v>112.29</v>
       </c>
       <c r="E341" s="3" t="s">
         <v>489</v>
@@ -7668,13 +7685,13 @@
         <v>102</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C342" s="3">
-        <v>269.08999999999997</v>
+        <v>344.22</v>
       </c>
       <c r="D342" s="3">
-        <v>269.08999999999997</v>
+        <v>344.22</v>
       </c>
       <c r="E342" s="3" t="s">
         <v>489</v>
@@ -7685,13 +7702,13 @@
         <v>102</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C343" s="3">
-        <v>190.03</v>
+        <v>269.08999999999997</v>
       </c>
       <c r="D343" s="3">
-        <v>190.03</v>
+        <v>269.08999999999997</v>
       </c>
       <c r="E343" s="3" t="s">
         <v>489</v>
@@ -7702,13 +7719,13 @@
         <v>102</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C344" s="3">
-        <v>221.9</v>
+        <v>190.03</v>
       </c>
       <c r="D344" s="3">
-        <v>221.9</v>
+        <v>190.03</v>
       </c>
       <c r="E344" s="3" t="s">
         <v>489</v>
@@ -7719,13 +7736,13 @@
         <v>102</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C345" s="3">
-        <v>442.02</v>
+        <v>221.9</v>
       </c>
       <c r="D345" s="3">
-        <v>442.02</v>
+        <v>221.9</v>
       </c>
       <c r="E345" s="3" t="s">
         <v>489</v>
@@ -7736,13 +7753,13 @@
         <v>102</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C346" s="3">
-        <v>137.36000000000001</v>
+        <v>442.02</v>
       </c>
       <c r="D346" s="3">
-        <v>137.36000000000001</v>
+        <v>442.02</v>
       </c>
       <c r="E346" s="3" t="s">
         <v>489</v>
@@ -7753,13 +7770,13 @@
         <v>102</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C347" s="3">
-        <v>343.39</v>
+        <v>137.36000000000001</v>
       </c>
       <c r="D347" s="3">
-        <v>343.39</v>
+        <v>137.36000000000001</v>
       </c>
       <c r="E347" s="3" t="s">
         <v>489</v>
@@ -7770,13 +7787,13 @@
         <v>102</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C348" s="3">
-        <v>277.12</v>
+        <v>343.39</v>
       </c>
       <c r="D348" s="3">
-        <v>277.12</v>
+        <v>343.39</v>
       </c>
       <c r="E348" s="3" t="s">
         <v>489</v>
@@ -7787,13 +7804,13 @@
         <v>102</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C349" s="3">
-        <v>353.81</v>
+        <v>277.12</v>
       </c>
       <c r="D349" s="3">
-        <v>353.81</v>
+        <v>277.12</v>
       </c>
       <c r="E349" s="3" t="s">
         <v>489</v>
@@ -7801,16 +7818,16 @@
     </row>
     <row r="350" spans="1:5">
       <c r="A350" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C350" s="3">
-        <v>556.46</v>
+        <v>353.81</v>
       </c>
       <c r="D350" s="3">
-        <v>556.46</v>
+        <v>353.81</v>
       </c>
       <c r="E350" s="3" t="s">
         <v>489</v>
@@ -7818,16 +7835,16 @@
     </row>
     <row r="351" spans="1:5">
       <c r="A351" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C351" s="3">
-        <v>188.76</v>
+        <v>556.46</v>
       </c>
       <c r="D351" s="3">
-        <v>188.76</v>
+        <v>556.46</v>
       </c>
       <c r="E351" s="3" t="s">
         <v>489</v>
@@ -7838,13 +7855,13 @@
         <v>104</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C352" s="3">
-        <v>706.71</v>
+        <v>188.76</v>
       </c>
       <c r="D352" s="3">
-        <v>706.71</v>
+        <v>188.76</v>
       </c>
       <c r="E352" s="3" t="s">
         <v>489</v>
@@ -7852,19 +7869,19 @@
     </row>
     <row r="353" spans="1:5">
       <c r="A353" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C353" s="3">
-        <v>467.36</v>
+        <v>706.71</v>
       </c>
       <c r="D353" s="3">
-        <v>9.48</v>
+        <v>706.71</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -7872,13 +7889,13 @@
         <v>105</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C354" s="3">
-        <v>940.25</v>
+        <v>467.36</v>
       </c>
       <c r="D354" s="3">
-        <v>940.25</v>
+        <v>9.48</v>
       </c>
       <c r="E354" s="3" t="s">
         <v>490</v>
@@ -7889,13 +7906,13 @@
         <v>105</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C355" s="3">
-        <v>5748.89</v>
+        <v>940.25</v>
       </c>
       <c r="D355" s="3">
-        <v>5748.89</v>
+        <v>940.25</v>
       </c>
       <c r="E355" s="3" t="s">
         <v>490</v>
@@ -7906,13 +7923,13 @@
         <v>105</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C356" s="3">
-        <v>1213.6300000000001</v>
+        <v>5748.89</v>
       </c>
       <c r="D356" s="3">
-        <v>1213.6300000000001</v>
+        <v>5748.89</v>
       </c>
       <c r="E356" s="3" t="s">
         <v>490</v>
@@ -7923,13 +7940,13 @@
         <v>105</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C357" s="3">
-        <v>798.91</v>
+        <v>1213.6300000000001</v>
       </c>
       <c r="D357" s="3">
-        <v>798.91</v>
+        <v>1213.6300000000001</v>
       </c>
       <c r="E357" s="3" t="s">
         <v>490</v>
@@ -7937,36 +7954,36 @@
     </row>
     <row r="358" spans="1:5">
       <c r="A358" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C358" s="3">
-        <v>440.46</v>
+        <v>798.91</v>
       </c>
       <c r="D358" s="3">
-        <v>436.54</v>
+        <v>798.91</v>
       </c>
       <c r="E358" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="359" spans="1:5">
       <c r="A359" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C359" s="3">
-        <v>1810.19</v>
+        <v>440.46</v>
       </c>
       <c r="D359" s="3">
-        <v>692.04</v>
+        <v>436.54</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -7974,13 +7991,13 @@
         <v>107</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C360" s="3">
-        <v>497.23</v>
+        <v>1810.19</v>
       </c>
       <c r="D360" s="3">
-        <v>497.23</v>
+        <v>692.04</v>
       </c>
       <c r="E360" s="3" t="s">
         <v>490</v>
@@ -7991,13 +8008,13 @@
         <v>107</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C361" s="3">
-        <v>1814.31</v>
+        <v>497.23</v>
       </c>
       <c r="D361" s="3">
-        <v>1814.31</v>
+        <v>497.23</v>
       </c>
       <c r="E361" s="3" t="s">
         <v>490</v>
@@ -8008,13 +8025,13 @@
         <v>107</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C362" s="3">
-        <v>314.64999999999998</v>
+        <v>1814.31</v>
       </c>
       <c r="D362" s="3">
-        <v>314.64999999999998</v>
+        <v>1814.31</v>
       </c>
       <c r="E362" s="3" t="s">
         <v>490</v>
@@ -8025,13 +8042,13 @@
         <v>107</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C363" s="3">
-        <v>531.07000000000005</v>
+        <v>314.64999999999998</v>
       </c>
       <c r="D363" s="3">
-        <v>531.07000000000005</v>
+        <v>314.64999999999998</v>
       </c>
       <c r="E363" s="3" t="s">
         <v>490</v>
@@ -8042,13 +8059,13 @@
         <v>107</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C364" s="3">
-        <v>2070.84</v>
+        <v>531.07000000000005</v>
       </c>
       <c r="D364" s="3">
-        <v>2070.84</v>
+        <v>531.07000000000005</v>
       </c>
       <c r="E364" s="3" t="s">
         <v>490</v>
@@ -8059,13 +8076,13 @@
         <v>107</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C365" s="3">
-        <v>2696.18</v>
+        <v>2070.84</v>
       </c>
       <c r="D365" s="3">
-        <v>2696.18</v>
+        <v>2070.84</v>
       </c>
       <c r="E365" s="3" t="s">
         <v>490</v>
@@ -8076,13 +8093,13 @@
         <v>107</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C366" s="3">
-        <v>3607.99</v>
+        <v>2696.18</v>
       </c>
       <c r="D366" s="3">
-        <v>3607.99</v>
+        <v>2696.18</v>
       </c>
       <c r="E366" s="3" t="s">
         <v>490</v>
@@ -8090,16 +8107,16 @@
     </row>
     <row r="367" spans="1:5">
       <c r="A367" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C367" s="3">
-        <v>3470.57</v>
+        <v>3607.99</v>
       </c>
       <c r="D367" s="3">
-        <v>10.98</v>
+        <v>3607.99</v>
       </c>
       <c r="E367" s="3" t="s">
         <v>490</v>
@@ -8107,16 +8124,16 @@
     </row>
     <row r="368" spans="1:5">
       <c r="A368" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C368" s="3">
-        <v>883.75</v>
+        <v>3470.57</v>
       </c>
       <c r="D368" s="3">
-        <v>314.72000000000003</v>
+        <v>10.98</v>
       </c>
       <c r="E368" s="3" t="s">
         <v>490</v>
@@ -8127,13 +8144,13 @@
         <v>109</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C369" s="3">
-        <v>887.63</v>
+        <v>883.75</v>
       </c>
       <c r="D369" s="3">
-        <v>887.63</v>
+        <v>314.72000000000003</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>490</v>
@@ -8141,19 +8158,19 @@
     </row>
     <row r="370" spans="1:5">
       <c r="A370" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C370" s="3">
-        <v>784.52</v>
+        <v>887.63</v>
       </c>
       <c r="D370" s="3">
-        <v>775.48</v>
+        <v>887.63</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -8161,13 +8178,13 @@
         <v>110</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C371" s="3">
-        <v>3242.51</v>
+        <v>784.52</v>
       </c>
       <c r="D371" s="3">
-        <v>3242.51</v>
+        <v>775.48</v>
       </c>
       <c r="E371" s="3" t="s">
         <v>489</v>
@@ -8178,13 +8195,13 @@
         <v>110</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C372" s="3">
-        <v>188.76</v>
+        <v>3242.51</v>
       </c>
       <c r="D372" s="3">
-        <v>188.76</v>
+        <v>3242.51</v>
       </c>
       <c r="E372" s="3" t="s">
         <v>489</v>
@@ -8192,19 +8209,19 @@
     </row>
     <row r="373" spans="1:5">
       <c r="A373" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C373" s="3">
-        <v>2732.17</v>
+        <v>188.76</v>
       </c>
       <c r="D373" s="3">
-        <v>1732.17</v>
+        <v>188.76</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -8212,13 +8229,13 @@
         <v>111</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C374" s="3">
-        <v>956.4</v>
+        <v>2732.17</v>
       </c>
       <c r="D374" s="3">
-        <v>956.4</v>
+        <v>1732.17</v>
       </c>
       <c r="E374" s="3" t="s">
         <v>490</v>
@@ -8226,16 +8243,16 @@
     </row>
     <row r="375" spans="1:5">
       <c r="A375" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C375" s="3">
-        <v>526.86</v>
+        <v>956.4</v>
       </c>
       <c r="D375" s="3">
-        <v>505.21</v>
+        <v>956.4</v>
       </c>
       <c r="E375" s="3" t="s">
         <v>490</v>
@@ -8243,22 +8260,40 @@
     </row>
     <row r="376" spans="1:5">
       <c r="A376" t="s">
+        <v>112</v>
+      </c>
+      <c r="B376" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C376" s="3">
+        <v>526.86</v>
+      </c>
+      <c r="D376" s="3">
+        <v>505.21</v>
+      </c>
+      <c r="E376" s="3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" t="s">
         <v>113</v>
       </c>
-      <c r="B376" s="3" t="s">
+      <c r="B377" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="C376" s="3">
+      <c r="C377" s="3">
         <v>437.15</v>
       </c>
-      <c r="D376" s="3">
+      <c r="D377" s="3">
         <v>437.15</v>
       </c>
-      <c r="E376" s="3" t="s">
+      <c r="E377" s="3" t="s">
         <v>489</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Facturi_Neincasate.xlsx
+++ b/Facturi_Neincasate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="640">
   <si>
     <t>Denumire client</t>
   </si>
@@ -52,6 +52,9 @@
     <t>ANDREI DARIOANA SYCO SRL VLADOSESTI</t>
   </si>
   <si>
+    <t>ARALAND NATURA S.R.L. DAIA ROMANA</t>
+  </si>
+  <si>
     <t>ATHENA ENERGY CARS S.R.L. DEVA</t>
   </si>
   <si>
@@ -97,6 +100,9 @@
     <t>AUTOSPEED UTIL SRL ORASTIE</t>
   </si>
   <si>
+    <t>AUTOVES TEHNIC S.R.L. ALBA IULIA</t>
+  </si>
+  <si>
     <t>AXF TRANSILVANIA PARTS S.R.L. ALBA IULIA</t>
   </si>
   <si>
@@ -112,6 +118,9 @@
     <t>CCS TECHNIK GARAGE S.R.L. ORASTIE</t>
   </si>
   <si>
+    <t>CRIS AUTOSERVICE S.R.L. BAIA DE ARIES</t>
+  </si>
+  <si>
     <t>CRISOBI  MTX SRL HUNEDOARA</t>
   </si>
   <si>
@@ -127,6 +136,9 @@
     <t>DETAILING STYLE SRL BLAJ</t>
   </si>
   <si>
+    <t>DIESEL TRADING ONE S.R.L. OIEJDEA</t>
+  </si>
+  <si>
     <t>DIROM INTERTRANS SRL ALBA IULIA</t>
   </si>
   <si>
@@ -145,6 +157,9 @@
     <t>ECAT AUTO S.R.L. ABRUD</t>
   </si>
   <si>
+    <t>ECODEP SERVICE SRL SAT DAIA ROMANA  DAIA ROM</t>
+  </si>
+  <si>
     <t>EMINENT EXPERT TOUR SRL HATEG</t>
   </si>
   <si>
@@ -271,6 +286,9 @@
     <t>SEIU GRUP S.R.L. ALBA IULIA</t>
   </si>
   <si>
+    <t>SERCOM AGREGATE SRL OIEJDEA</t>
+  </si>
+  <si>
     <t>SERVICE CONCEPT WEST EXPERT S.R.L. DEVA</t>
   </si>
   <si>
@@ -397,6 +415,9 @@
     <t>DMEG 8940</t>
   </si>
   <si>
+    <t>DMEG 8790</t>
+  </si>
+  <si>
     <t>DMEG 3565</t>
   </si>
   <si>
@@ -571,6 +592,9 @@
     <t>DMEGB 92</t>
   </si>
   <si>
+    <t>DMEG 4588</t>
+  </si>
+  <si>
     <t>DMEG 8305</t>
   </si>
   <si>
@@ -682,6 +706,21 @@
     <t>DMEG 8408</t>
   </si>
   <si>
+    <t>DMEG 8179</t>
+  </si>
+  <si>
+    <t>DMEG 8570</t>
+  </si>
+  <si>
+    <t>DMEG 8485</t>
+  </si>
+  <si>
+    <t>DMEG 8486</t>
+  </si>
+  <si>
+    <t>DMEG 8164</t>
+  </si>
+  <si>
     <t>DMEG 8728</t>
   </si>
   <si>
@@ -721,6 +760,9 @@
     <t>DMEG 8926</t>
   </si>
   <si>
+    <t>DMEG 8701</t>
+  </si>
+  <si>
     <t>DMEG 7500</t>
   </si>
   <si>
@@ -793,6 +835,9 @@
     <t>DMEG 8872</t>
   </si>
   <si>
+    <t>DMEG 5760</t>
+  </si>
+  <si>
     <t>DMEG 7494</t>
   </si>
   <si>
@@ -1210,6 +1255,27 @@
     <t>DMEG 8767</t>
   </si>
   <si>
+    <t>DMEGB 93</t>
+  </si>
+  <si>
+    <t>DMEGB 95</t>
+  </si>
+  <si>
+    <t>DMEGB 96</t>
+  </si>
+  <si>
+    <t>DMEGB 83</t>
+  </si>
+  <si>
+    <t>DMEGB 32</t>
+  </si>
+  <si>
+    <t>DMEG 8659</t>
+  </si>
+  <si>
+    <t>DMEGB 86</t>
+  </si>
+  <si>
     <t>DMEG 8876</t>
   </si>
   <si>
@@ -1255,6 +1321,9 @@
     <t>DMEG 8291</t>
   </si>
   <si>
+    <t>DMEG 8303</t>
+  </si>
+  <si>
     <t>DMEG 8551</t>
   </si>
   <si>
@@ -1423,6 +1492,9 @@
     <t>14.01.26</t>
   </si>
   <si>
+    <t>22.04.26</t>
+  </si>
+  <si>
     <t>04.10.23</t>
   </si>
   <si>
@@ -1504,6 +1576,9 @@
     <t>27.05.26</t>
   </si>
   <si>
+    <t>11.04.24</t>
+  </si>
+  <si>
     <t>12.01.26</t>
   </si>
   <si>
@@ -1546,6 +1621,21 @@
     <t>28.01.26</t>
   </si>
   <si>
+    <t>02.12.25</t>
+  </si>
+  <si>
+    <t>05.03.26</t>
+  </si>
+  <si>
+    <t>13.02.26</t>
+  </si>
+  <si>
+    <t>16.02.26</t>
+  </si>
+  <si>
+    <t>26.11.25</t>
+  </si>
+  <si>
     <t>16.03.26</t>
   </si>
   <si>
@@ -1567,6 +1657,9 @@
     <t>07.04.26</t>
   </si>
   <si>
+    <t>31.03.26</t>
+  </si>
+  <si>
     <t>05.08.25</t>
   </si>
   <si>
@@ -1603,6 +1696,9 @@
     <t>09.01.26</t>
   </si>
   <si>
+    <t>16.10.24</t>
+  </si>
+  <si>
     <t>08.06.25</t>
   </si>
   <si>
@@ -1663,9 +1759,6 @@
     <t>28.04.25</t>
   </si>
   <si>
-    <t>31.03.26</t>
-  </si>
-  <si>
     <t>05.11.25</t>
   </si>
   <si>
@@ -1784,6 +1877,12 @@
   </si>
   <si>
     <t>28.04.26</t>
+  </si>
+  <si>
+    <t>14.11.25</t>
+  </si>
+  <si>
+    <t>20.03.25</t>
   </si>
   <si>
     <t>13.05.26</t>
@@ -2198,10 +2297,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E348"/>
+  <dimension ref="A1:E365"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="53.85546875" customWidth="1"/>
+    <col min="1" max="1" width="53.28515625" customWidth="1"/>
     <col min="2" max="5" width="15.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2227,10 +2326,10 @@
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>451</v>
+        <v>474</v>
       </c>
       <c r="D2" s="3">
         <v>850.85</v>
@@ -2244,10 +2343,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="D3" s="3">
         <v>521.97</v>
@@ -2261,10 +2360,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="D4" s="3">
         <v>2802.73</v>
@@ -2278,10 +2377,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="D5" s="3">
         <v>893.3</v>
@@ -2295,10 +2394,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>455</v>
+        <v>478</v>
       </c>
       <c r="D6" s="3">
         <v>481.94</v>
@@ -2312,10 +2411,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>456</v>
+        <v>479</v>
       </c>
       <c r="D7" s="3">
         <v>1132</v>
@@ -2329,10 +2428,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="D8" s="3">
         <v>840.17</v>
@@ -2346,10 +2445,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="D9" s="3">
         <v>987.25</v>
@@ -2363,10 +2462,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="D10" s="3">
         <v>541.57000000000005</v>
@@ -2380,10 +2479,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="D11" s="3">
         <v>674.47</v>
@@ -2397,10 +2496,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="D12" s="3">
         <v>464.86</v>
@@ -2414,10 +2513,10 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="D13" s="3">
         <v>874.25</v>
@@ -2431,10 +2530,10 @@
         <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="D14" s="3">
         <v>904.6</v>
@@ -2448,10 +2547,10 @@
         <v>7</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="D15" s="3">
         <v>872.99</v>
@@ -2465,10 +2564,10 @@
         <v>8</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="D16" s="3">
         <v>385.48</v>
@@ -2482,10 +2581,10 @@
         <v>8</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>464</v>
+        <v>487</v>
       </c>
       <c r="D17" s="3">
         <v>1418.1</v>
@@ -2499,10 +2598,10 @@
         <v>8</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>465</v>
+        <v>488</v>
       </c>
       <c r="D18" s="3">
         <v>450.74</v>
@@ -2516,10 +2615,10 @@
         <v>9</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="D19" s="3">
         <v>1536.5</v>
@@ -2533,10 +2632,10 @@
         <v>9</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="D20" s="3">
         <v>637.62</v>
@@ -2550,10 +2649,10 @@
         <v>9</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="D21" s="3">
         <v>226.19</v>
@@ -2567,10 +2666,10 @@
         <v>10</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="D22" s="3">
         <v>1842.97</v>
@@ -2584,10 +2683,10 @@
         <v>11</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="D23" s="3">
         <v>1395.14</v>
@@ -2601,10 +2700,10 @@
         <v>11</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="D24" s="3">
         <v>1334.19</v>
@@ -2618,101 +2717,101 @@
         <v>12</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="D25" s="3">
-        <v>220.74</v>
+        <v>545</v>
       </c>
       <c r="E25" s="3">
-        <v>220.74</v>
+        <v>545</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="D26" s="3">
-        <v>304.68</v>
+        <v>220.74</v>
       </c>
       <c r="E26" s="3">
-        <v>304.68</v>
+        <v>220.74</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="D27" s="3">
-        <v>1017.46</v>
+        <v>304.68</v>
       </c>
       <c r="E27" s="3">
-        <v>132.46</v>
+        <v>304.68</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="D28" s="3">
-        <v>216.59</v>
+        <v>1017.46</v>
       </c>
       <c r="E28" s="3">
-        <v>216.59</v>
+        <v>132.46</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
       <c r="D29" s="3">
-        <v>152.68</v>
+        <v>216.59</v>
       </c>
       <c r="E29" s="3">
-        <v>152.68</v>
+        <v>216.59</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="D30" s="3">
-        <v>163.05000000000001</v>
+        <v>152.68</v>
       </c>
       <c r="E30" s="3">
-        <v>163.05000000000001</v>
+        <v>152.68</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2720,101 +2819,101 @@
         <v>13</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="D31" s="3">
-        <v>234.55</v>
+        <v>163.05000000000001</v>
       </c>
       <c r="E31" s="3">
-        <v>234.55</v>
+        <v>163.05000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="D32" s="3">
-        <v>1057.78</v>
+        <v>234.55</v>
       </c>
       <c r="E32" s="3">
-        <v>1057.78</v>
+        <v>234.55</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="D33" s="3">
-        <v>1252.83</v>
+        <v>1057.78</v>
       </c>
       <c r="E33" s="3">
-        <v>1252.83</v>
+        <v>1057.78</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>478</v>
+        <v>501</v>
       </c>
       <c r="D34" s="3">
-        <v>1178.49</v>
+        <v>1252.83</v>
       </c>
       <c r="E34" s="3">
-        <v>1178.49</v>
+        <v>1252.83</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>479</v>
+        <v>502</v>
       </c>
       <c r="D35" s="3">
-        <v>361.76</v>
+        <v>1178.49</v>
       </c>
       <c r="E35" s="3">
-        <v>361.76</v>
+        <v>1178.49</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>480</v>
+        <v>503</v>
       </c>
       <c r="D36" s="3">
-        <v>301.58999999999997</v>
+        <v>361.76</v>
       </c>
       <c r="E36" s="3">
-        <v>301.58999999999997</v>
+        <v>361.76</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2822,16 +2921,16 @@
         <v>14</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>481</v>
+        <v>504</v>
       </c>
       <c r="D37" s="3">
-        <v>7388.44</v>
+        <v>301.58999999999997</v>
       </c>
       <c r="E37" s="3">
-        <v>6957.53</v>
+        <v>301.58999999999997</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2839,50 +2938,50 @@
         <v>15</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>451</v>
+        <v>505</v>
       </c>
       <c r="D38" s="3">
-        <v>813.02</v>
+        <v>7388.44</v>
       </c>
       <c r="E38" s="3">
-        <v>133.22</v>
+        <v>6957.53</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="D39" s="3">
-        <v>323.57</v>
+        <v>813.02</v>
       </c>
       <c r="E39" s="3">
-        <v>323.57</v>
+        <v>133.22</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="D40" s="3">
-        <v>1514.21</v>
+        <v>323.57</v>
       </c>
       <c r="E40" s="3">
-        <v>1514.21</v>
+        <v>323.57</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2890,67 +2989,67 @@
         <v>16</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D41" s="3">
-        <v>279.39999999999998</v>
+        <v>1514.21</v>
       </c>
       <c r="E41" s="3">
-        <v>157.52000000000001</v>
+        <v>1514.21</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>483</v>
+        <v>506</v>
       </c>
       <c r="D42" s="3">
-        <v>615.05999999999995</v>
+        <v>279.39999999999998</v>
       </c>
       <c r="E42" s="3">
-        <v>615.05999999999995</v>
+        <v>157.52000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>484</v>
+        <v>507</v>
       </c>
       <c r="D43" s="3">
-        <v>1835.5</v>
+        <v>615.05999999999995</v>
       </c>
       <c r="E43" s="3">
-        <v>1835.5</v>
+        <v>615.05999999999995</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>485</v>
+        <v>508</v>
       </c>
       <c r="D44" s="3">
-        <v>839.88</v>
+        <v>1835.5</v>
       </c>
       <c r="E44" s="3">
-        <v>839.88</v>
+        <v>1835.5</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2958,16 +3057,16 @@
         <v>17</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>466</v>
+        <v>509</v>
       </c>
       <c r="D45" s="3">
-        <v>2461.4</v>
+        <v>839.88</v>
       </c>
       <c r="E45" s="3">
-        <v>2461.4</v>
+        <v>839.88</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2975,50 +3074,50 @@
         <v>18</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
       <c r="D46" s="3">
-        <v>1213.92</v>
+        <v>2461.4</v>
       </c>
       <c r="E46" s="3">
-        <v>1213.92</v>
+        <v>2461.4</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>454</v>
+        <v>485</v>
       </c>
       <c r="D47" s="3">
-        <v>501.06</v>
+        <v>1213.92</v>
       </c>
       <c r="E47" s="3">
-        <v>501.06</v>
+        <v>1213.92</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="D48" s="3">
-        <v>474.72</v>
+        <v>501.06</v>
       </c>
       <c r="E48" s="3">
-        <v>398.72</v>
+        <v>501.06</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -3026,16 +3125,16 @@
         <v>19</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="D49" s="3">
-        <v>290.61</v>
+        <v>474.72</v>
       </c>
       <c r="E49" s="3">
-        <v>290.61</v>
+        <v>398.72</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -3043,50 +3142,50 @@
         <v>20</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>475</v>
+        <v>510</v>
       </c>
       <c r="D50" s="3">
-        <v>541.84</v>
+        <v>290.61</v>
       </c>
       <c r="E50" s="3">
-        <v>541.84</v>
+        <v>290.61</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="D51" s="3">
-        <v>258.45999999999998</v>
+        <v>541.84</v>
       </c>
       <c r="E51" s="3">
-        <v>258.45999999999998</v>
+        <v>541.84</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>478</v>
+        <v>501</v>
       </c>
       <c r="D52" s="3">
-        <v>420.63</v>
+        <v>258.45999999999998</v>
       </c>
       <c r="E52" s="3">
-        <v>420.63</v>
+        <v>258.45999999999998</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -3094,237 +3193,237 @@
         <v>21</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="D53" s="3">
-        <v>377.96</v>
+        <v>420.63</v>
       </c>
       <c r="E53" s="3">
-        <v>377.96</v>
+        <v>420.63</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>459</v>
+        <v>511</v>
       </c>
       <c r="D54" s="3">
-        <v>724.46</v>
+        <v>377.96</v>
       </c>
       <c r="E54" s="3">
-        <v>84.74</v>
+        <v>377.96</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="D55" s="3">
-        <v>346.81</v>
+        <v>724.46</v>
       </c>
       <c r="E55" s="3">
-        <v>346.81</v>
+        <v>84.74</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="D56" s="3">
-        <v>569.30999999999995</v>
+        <v>346.81</v>
       </c>
       <c r="E56" s="3">
-        <v>569.30999999999995</v>
+        <v>346.81</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>488</v>
+        <v>512</v>
       </c>
       <c r="D57" s="3">
-        <v>904.43</v>
+        <v>569.30999999999995</v>
       </c>
       <c r="E57" s="3">
-        <v>904.43</v>
+        <v>569.30999999999995</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>489</v>
+        <v>512</v>
       </c>
       <c r="D58" s="3">
-        <v>692.5</v>
+        <v>904.43</v>
       </c>
       <c r="E58" s="3">
-        <v>692.5</v>
+        <v>904.43</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="D59" s="3">
-        <v>781.3</v>
+        <v>692.5</v>
       </c>
       <c r="E59" s="3">
-        <v>781.3</v>
+        <v>692.5</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>490</v>
+        <v>514</v>
       </c>
       <c r="D60" s="3">
-        <v>262.82</v>
+        <v>781.3</v>
       </c>
       <c r="E60" s="3">
-        <v>262.82</v>
+        <v>781.3</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>491</v>
+        <v>514</v>
       </c>
       <c r="D61" s="3">
-        <v>188.29</v>
+        <v>262.82</v>
       </c>
       <c r="E61" s="3">
-        <v>188.29</v>
+        <v>262.82</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>466</v>
+        <v>515</v>
       </c>
       <c r="D62" s="3">
-        <v>741.39</v>
+        <v>188.29</v>
       </c>
       <c r="E62" s="3">
-        <v>741.39</v>
+        <v>188.29</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="D63" s="3">
-        <v>793.89</v>
+        <v>741.39</v>
       </c>
       <c r="E63" s="3">
-        <v>793.89</v>
+        <v>741.39</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D64" s="3">
-        <v>341.79</v>
+        <v>793.89</v>
       </c>
       <c r="E64" s="3">
-        <v>341.79</v>
+        <v>793.89</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>492</v>
+        <v>516</v>
       </c>
       <c r="D65" s="3">
-        <v>886.18</v>
+        <v>341.79</v>
       </c>
       <c r="E65" s="3">
-        <v>886.18</v>
+        <v>341.79</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>461</v>
+        <v>516</v>
       </c>
       <c r="D66" s="3">
-        <v>491.37</v>
+        <v>886.18</v>
       </c>
       <c r="E66" s="3">
-        <v>491.37</v>
+        <v>886.18</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3332,84 +3431,84 @@
         <v>22</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>460</v>
+        <v>484</v>
       </c>
       <c r="D67" s="3">
-        <v>180.11</v>
+        <v>491.37</v>
       </c>
       <c r="E67" s="3">
-        <v>180.11</v>
+        <v>491.37</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>451</v>
+        <v>483</v>
       </c>
       <c r="D68" s="3">
-        <v>1763.07</v>
+        <v>180.11</v>
       </c>
       <c r="E68" s="3">
-        <v>1763.07</v>
+        <v>180.11</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="D69" s="3">
-        <v>1717.87</v>
+        <v>1763.07</v>
       </c>
       <c r="E69" s="3">
-        <v>1717.87</v>
+        <v>1763.07</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="D70" s="3">
-        <v>301.89</v>
+        <v>1717.87</v>
       </c>
       <c r="E70" s="3">
-        <v>301.89</v>
+        <v>1717.87</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="D71" s="3">
-        <v>3721.1</v>
+        <v>301.89</v>
       </c>
       <c r="E71" s="3">
-        <v>3721.1</v>
+        <v>301.89</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3417,84 +3516,84 @@
         <v>23</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="D72" s="3">
-        <v>610.37</v>
+        <v>3721.1</v>
       </c>
       <c r="E72" s="3">
-        <v>610.37</v>
+        <v>3721.1</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>464</v>
+        <v>517</v>
       </c>
       <c r="D73" s="3">
-        <v>1018.78</v>
+        <v>610.37</v>
       </c>
       <c r="E73" s="3">
-        <v>1018.78</v>
+        <v>610.37</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D74" s="3">
-        <v>308.06</v>
+        <v>1018.78</v>
       </c>
       <c r="E74" s="3">
-        <v>306.79000000000002</v>
+        <v>1018.78</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>465</v>
+        <v>514</v>
       </c>
       <c r="D75" s="3">
-        <v>1146.32</v>
+        <v>308.06</v>
       </c>
       <c r="E75" s="3">
-        <v>1146.32</v>
+        <v>306.79000000000002</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="D76" s="3">
-        <v>710.23</v>
+        <v>1146.32</v>
       </c>
       <c r="E76" s="3">
-        <v>710.23</v>
+        <v>1146.32</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3502,16 +3601,16 @@
         <v>24</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>454</v>
+        <v>481</v>
       </c>
       <c r="D77" s="3">
-        <v>272.35000000000002</v>
+        <v>710.23</v>
       </c>
       <c r="E77" s="3">
-        <v>272.35000000000002</v>
+        <v>710.23</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3519,33 +3618,33 @@
         <v>25</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="D78" s="3">
-        <v>377.52</v>
+        <v>272.35000000000002</v>
       </c>
       <c r="E78" s="3">
-        <v>372.92</v>
+        <v>272.35000000000002</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>495</v>
+        <v>518</v>
       </c>
       <c r="D79" s="3">
-        <v>414.95</v>
+        <v>377.52</v>
       </c>
       <c r="E79" s="3">
-        <v>414.95</v>
+        <v>372.92</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -3553,50 +3652,50 @@
         <v>26</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>486</v>
+        <v>519</v>
       </c>
       <c r="D80" s="3">
-        <v>661.9</v>
+        <v>414.95</v>
       </c>
       <c r="E80" s="3">
-        <v>661.9</v>
+        <v>414.95</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
       <c r="D81" s="3">
-        <v>1084.03</v>
+        <v>661.9</v>
       </c>
       <c r="E81" s="3">
-        <v>1084.03</v>
+        <v>661.9</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>494</v>
+        <v>518</v>
       </c>
       <c r="D82" s="3">
-        <v>1518.6</v>
+        <v>1084.03</v>
       </c>
       <c r="E82" s="3">
-        <v>1518.6</v>
+        <v>1084.03</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -3604,271 +3703,271 @@
         <v>27</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>496</v>
+        <v>518</v>
       </c>
       <c r="D83" s="3">
-        <v>1045.26</v>
+        <v>1518.6</v>
       </c>
       <c r="E83" s="3">
-        <v>1045.26</v>
+        <v>1518.6</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>497</v>
+        <v>520</v>
       </c>
       <c r="D84" s="3">
-        <v>149.36000000000001</v>
+        <v>1128.3</v>
       </c>
       <c r="E84" s="3">
-        <v>149.36000000000001</v>
+        <v>1128.3</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>498</v>
+        <v>521</v>
       </c>
       <c r="D85" s="3">
-        <v>2018.53</v>
+        <v>1045.26</v>
       </c>
       <c r="E85" s="3">
-        <v>2018.53</v>
+        <v>1045.26</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>499</v>
+        <v>522</v>
       </c>
       <c r="D86" s="3">
-        <v>4758.71</v>
+        <v>149.36000000000001</v>
       </c>
       <c r="E86" s="3">
-        <v>2990.86</v>
+        <v>149.36000000000001</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>499</v>
+        <v>523</v>
       </c>
       <c r="D87" s="3">
-        <v>4946.04</v>
+        <v>2018.53</v>
       </c>
       <c r="E87" s="3">
-        <v>4946.04</v>
+        <v>2018.53</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="D88" s="3">
-        <v>3164.86</v>
+        <v>4758.71</v>
       </c>
       <c r="E88" s="3">
-        <v>3164.86</v>
+        <v>2990.86</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>456</v>
+        <v>524</v>
       </c>
       <c r="D89" s="3">
-        <v>65.459999999999994</v>
+        <v>4946.04</v>
       </c>
       <c r="E89" s="3">
-        <v>65.459999999999994</v>
+        <v>4946.04</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>482</v>
+        <v>524</v>
       </c>
       <c r="D90" s="3">
-        <v>239.26</v>
+        <v>3164.86</v>
       </c>
       <c r="E90" s="3">
-        <v>239.26</v>
+        <v>3164.86</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>500</v>
+        <v>479</v>
       </c>
       <c r="D91" s="3">
-        <v>490.77</v>
+        <v>65.459999999999994</v>
       </c>
       <c r="E91" s="3">
-        <v>490.77</v>
+        <v>65.459999999999994</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="D92" s="3">
-        <v>334.17</v>
+        <v>239.26</v>
       </c>
       <c r="E92" s="3">
-        <v>334.17</v>
+        <v>239.26</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>483</v>
+        <v>525</v>
       </c>
       <c r="D93" s="3">
-        <v>541.19000000000005</v>
+        <v>490.77</v>
       </c>
       <c r="E93" s="3">
-        <v>541.19000000000005</v>
+        <v>490.77</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="D94" s="3">
-        <v>411.95</v>
+        <v>334.17</v>
       </c>
       <c r="E94" s="3">
-        <v>411.95</v>
+        <v>334.17</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>484</v>
+        <v>507</v>
       </c>
       <c r="D95" s="3">
-        <v>384.88</v>
+        <v>541.19000000000005</v>
       </c>
       <c r="E95" s="3">
-        <v>384.88</v>
+        <v>541.19000000000005</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>503</v>
+        <v>527</v>
       </c>
       <c r="D96" s="3">
-        <v>1541.08</v>
+        <v>411.95</v>
       </c>
       <c r="E96" s="3">
-        <v>640.17999999999995</v>
+        <v>411.95</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D97" s="3">
-        <v>363.47</v>
+        <v>384.88</v>
       </c>
       <c r="E97" s="3">
-        <v>363.47</v>
+        <v>384.88</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>486</v>
+        <v>528</v>
       </c>
       <c r="D98" s="3">
-        <v>880.98</v>
+        <v>1541.08</v>
       </c>
       <c r="E98" s="3">
-        <v>880.98</v>
+        <v>640.17999999999995</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -3876,373 +3975,373 @@
         <v>30</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>486</v>
+        <v>529</v>
       </c>
       <c r="D99" s="3">
-        <v>782.1</v>
+        <v>363.47</v>
       </c>
       <c r="E99" s="3">
-        <v>782.1</v>
+        <v>363.47</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>451</v>
+        <v>510</v>
       </c>
       <c r="D100" s="3">
-        <v>585.54999999999995</v>
+        <v>880.98</v>
       </c>
       <c r="E100" s="3">
-        <v>585.54999999999995</v>
+        <v>880.98</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="D101" s="3">
-        <v>1810.44</v>
+        <v>782.1</v>
       </c>
       <c r="E101" s="3">
-        <v>186.23</v>
+        <v>782.1</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>505</v>
+        <v>474</v>
       </c>
       <c r="D102" s="3">
-        <v>215.71</v>
+        <v>585.54999999999995</v>
       </c>
       <c r="E102" s="3">
-        <v>215.71</v>
+        <v>585.54999999999995</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="D103" s="3">
-        <v>527.85</v>
+        <v>1810.44</v>
       </c>
       <c r="E103" s="3">
-        <v>527.85</v>
+        <v>186.23</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>454</v>
+        <v>530</v>
       </c>
       <c r="D104" s="3">
-        <v>257.2</v>
+        <v>215.71</v>
       </c>
       <c r="E104" s="3">
-        <v>257.2</v>
+        <v>215.71</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>466</v>
+        <v>514</v>
       </c>
       <c r="D105" s="3">
-        <v>930.59</v>
+        <v>527.85</v>
       </c>
       <c r="E105" s="3">
-        <v>930.59</v>
+        <v>527.85</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="D106" s="3">
-        <v>620.75</v>
+        <v>257.2</v>
       </c>
       <c r="E106" s="3">
-        <v>620.75</v>
+        <v>257.2</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D107" s="3">
-        <v>339.56</v>
+        <v>930.59</v>
       </c>
       <c r="E107" s="3">
-        <v>339.56</v>
+        <v>930.59</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>461</v>
+        <v>490</v>
       </c>
       <c r="D108" s="3">
-        <v>320.11</v>
+        <v>620.75</v>
       </c>
       <c r="E108" s="3">
-        <v>320.11</v>
+        <v>620.75</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>487</v>
+        <v>516</v>
       </c>
       <c r="D109" s="3">
-        <v>308.89999999999998</v>
+        <v>339.56</v>
       </c>
       <c r="E109" s="3">
-        <v>308.89999999999998</v>
+        <v>339.56</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="D110" s="3">
-        <v>598.35</v>
+        <v>320.11</v>
       </c>
       <c r="E110" s="3">
-        <v>598.35</v>
+        <v>320.11</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>459</v>
+        <v>511</v>
       </c>
       <c r="D111" s="3">
-        <v>442.72</v>
+        <v>308.89999999999998</v>
       </c>
       <c r="E111" s="3">
-        <v>442.72</v>
+        <v>308.89999999999998</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>489</v>
+        <v>531</v>
       </c>
       <c r="D112" s="3">
-        <v>613.28</v>
+        <v>598.35</v>
       </c>
       <c r="E112" s="3">
-        <v>613.28</v>
+        <v>598.35</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="D113" s="3">
-        <v>2644.4</v>
+        <v>442.72</v>
       </c>
       <c r="E113" s="3">
-        <v>2644.4</v>
+        <v>442.72</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D114" s="3">
-        <v>662.82</v>
+        <v>613.28</v>
       </c>
       <c r="E114" s="3">
-        <v>430.48</v>
+        <v>613.28</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>490</v>
+        <v>530</v>
       </c>
       <c r="D115" s="3">
-        <v>354.69</v>
+        <v>2644.4</v>
       </c>
       <c r="E115" s="3">
-        <v>354.69</v>
+        <v>2644.4</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>466</v>
+        <v>532</v>
       </c>
       <c r="D116" s="3">
-        <v>403.75</v>
+        <v>662.82</v>
       </c>
       <c r="E116" s="3">
-        <v>403.75</v>
+        <v>430.48</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="D117" s="3">
-        <v>328.34</v>
+        <v>354.69</v>
       </c>
       <c r="E117" s="3">
-        <v>328.34</v>
+        <v>354.69</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D118" s="3">
-        <v>271.16000000000003</v>
+        <v>403.75</v>
       </c>
       <c r="E118" s="3">
-        <v>271.16000000000003</v>
+        <v>403.75</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="D119" s="3">
-        <v>344.97</v>
+        <v>328.34</v>
       </c>
       <c r="E119" s="3">
-        <v>344.97</v>
+        <v>328.34</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>487</v>
+        <v>516</v>
       </c>
       <c r="D120" s="3">
-        <v>1570.56</v>
+        <v>271.16000000000003</v>
       </c>
       <c r="E120" s="3">
-        <v>1570.56</v>
+        <v>271.16000000000003</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -4250,16 +4349,16 @@
         <v>33</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>510</v>
+        <v>534</v>
       </c>
       <c r="D121" s="3">
-        <v>5017.9799999999996</v>
+        <v>344.97</v>
       </c>
       <c r="E121" s="3">
-        <v>5017.9799999999996</v>
+        <v>344.97</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -4267,16 +4366,16 @@
         <v>34</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>511</v>
+        <v>535</v>
       </c>
       <c r="D122" s="3">
-        <v>63.48</v>
+        <v>776.34</v>
       </c>
       <c r="E122" s="3">
-        <v>63.48</v>
+        <v>776.34</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -4284,16 +4383,16 @@
         <v>34</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="D123" s="3">
-        <v>93.8</v>
+        <v>637.61</v>
       </c>
       <c r="E123" s="3">
-        <v>93.8</v>
+        <v>637.61</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -4301,16 +4400,16 @@
         <v>34</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="D124" s="3">
-        <v>852.76</v>
+        <v>505.6</v>
       </c>
       <c r="E124" s="3">
-        <v>852.76</v>
+        <v>505.6</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -4318,16 +4417,16 @@
         <v>34</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>513</v>
+        <v>538</v>
       </c>
       <c r="D125" s="3">
-        <v>4795.4399999999996</v>
+        <v>1067.48</v>
       </c>
       <c r="E125" s="3">
-        <v>498.17</v>
+        <v>1067.48</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -4335,118 +4434,118 @@
         <v>34</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="D126" s="3">
-        <v>1575.72</v>
+        <v>1164.48</v>
       </c>
       <c r="E126" s="3">
-        <v>1575.72</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D127" s="3">
-        <v>467.32</v>
+        <v>1570.56</v>
       </c>
       <c r="E127" s="3">
-        <v>467.32</v>
+        <v>1570.56</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>515</v>
+        <v>540</v>
       </c>
       <c r="D128" s="3">
-        <v>119.58</v>
+        <v>5017.9799999999996</v>
       </c>
       <c r="E128" s="3">
-        <v>119.58</v>
+        <v>5017.9799999999996</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="D129" s="3">
-        <v>989.56</v>
+        <v>63.48</v>
       </c>
       <c r="E129" s="3">
-        <v>989.56</v>
+        <v>63.48</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>477</v>
+        <v>542</v>
       </c>
       <c r="D130" s="3">
-        <v>779.83</v>
+        <v>93.8</v>
       </c>
       <c r="E130" s="3">
-        <v>779.83</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>481</v>
+        <v>542</v>
       </c>
       <c r="D131" s="3">
-        <v>1459.04</v>
+        <v>852.76</v>
       </c>
       <c r="E131" s="3">
-        <v>1392.7</v>
+        <v>852.76</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>479</v>
+        <v>543</v>
       </c>
       <c r="D132" s="3">
-        <v>2896.99</v>
+        <v>4795.4399999999996</v>
       </c>
       <c r="E132" s="3">
-        <v>2896.99</v>
+        <v>498.17</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -4454,16 +4553,16 @@
         <v>37</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="D133" s="3">
-        <v>551.74</v>
+        <v>1575.72</v>
       </c>
       <c r="E133" s="3">
-        <v>551.74</v>
+        <v>1575.72</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -4471,16 +4570,16 @@
         <v>37</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>518</v>
+        <v>544</v>
       </c>
       <c r="D134" s="3">
-        <v>-10410.31</v>
+        <v>467.32</v>
       </c>
       <c r="E134" s="3">
-        <v>-10410.31</v>
+        <v>467.32</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -4488,662 +4587,662 @@
         <v>37</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="D135" s="3">
-        <v>428.78</v>
+        <v>119.58</v>
       </c>
       <c r="E135" s="3">
-        <v>428.78</v>
+        <v>119.58</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="D136" s="3">
-        <v>190.03</v>
+        <v>989.56</v>
       </c>
       <c r="E136" s="3">
-        <v>190.03</v>
+        <v>989.56</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="D137" s="3">
-        <v>5152.92</v>
+        <v>779.83</v>
       </c>
       <c r="E137" s="3">
-        <v>5152.92</v>
+        <v>779.83</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="D138" s="3">
-        <v>5257.39</v>
+        <v>1459.04</v>
       </c>
       <c r="E138" s="3">
-        <v>5257.39</v>
+        <v>1392.7</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="D139" s="3">
-        <v>193.56</v>
+        <v>2896.99</v>
       </c>
       <c r="E139" s="3">
-        <v>193.56</v>
+        <v>2896.99</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>524</v>
+        <v>547</v>
       </c>
       <c r="D140" s="3">
-        <v>5379.19</v>
+        <v>6232.46</v>
       </c>
       <c r="E140" s="3">
-        <v>5346.27</v>
+        <v>6232.46</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>525</v>
+        <v>548</v>
       </c>
       <c r="D141" s="3">
-        <v>301.58</v>
+        <v>551.74</v>
       </c>
       <c r="E141" s="3">
-        <v>301.58</v>
+        <v>551.74</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>526</v>
+        <v>549</v>
       </c>
       <c r="D142" s="3">
-        <v>274.11</v>
+        <v>-10410.31</v>
       </c>
       <c r="E142" s="3">
-        <v>274.11</v>
+        <v>-10410.31</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>516</v>
+        <v>550</v>
       </c>
       <c r="D143" s="3">
-        <v>180.85</v>
+        <v>428.78</v>
       </c>
       <c r="E143" s="3">
-        <v>180.85</v>
+        <v>428.78</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>464</v>
+        <v>551</v>
       </c>
       <c r="D144" s="3">
-        <v>1378.14</v>
+        <v>190.03</v>
       </c>
       <c r="E144" s="3">
-        <v>1378.14</v>
+        <v>190.03</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>486</v>
+        <v>552</v>
       </c>
       <c r="D145" s="3">
-        <v>1147.04</v>
+        <v>5152.92</v>
       </c>
       <c r="E145" s="3">
-        <v>1147.04</v>
+        <v>5152.92</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>487</v>
+        <v>553</v>
       </c>
       <c r="D146" s="3">
-        <v>949.96</v>
+        <v>5257.39</v>
       </c>
       <c r="E146" s="3">
-        <v>949.96</v>
+        <v>5257.39</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>527</v>
+        <v>554</v>
       </c>
       <c r="D147" s="3">
-        <v>1169.94</v>
+        <v>193.56</v>
       </c>
       <c r="E147" s="3">
-        <v>631.91</v>
+        <v>193.56</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>506</v>
+        <v>555</v>
       </c>
       <c r="D148" s="3">
-        <v>1908.79</v>
+        <v>5379.19</v>
       </c>
       <c r="E148" s="3">
-        <v>1908.79</v>
+        <v>5346.27</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>528</v>
+        <v>556</v>
       </c>
       <c r="D149" s="3">
-        <v>443.82</v>
+        <v>301.58</v>
       </c>
       <c r="E149" s="3">
-        <v>443.82</v>
+        <v>301.58</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>489</v>
+        <v>557</v>
       </c>
       <c r="D150" s="3">
-        <v>3337.92</v>
+        <v>274.11</v>
       </c>
       <c r="E150" s="3">
-        <v>3337.92</v>
+        <v>274.11</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>505</v>
+        <v>546</v>
       </c>
       <c r="D151" s="3">
-        <v>452.3</v>
+        <v>180.85</v>
       </c>
       <c r="E151" s="3">
-        <v>452.3</v>
+        <v>180.85</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>507</v>
+        <v>487</v>
       </c>
       <c r="D152" s="3">
-        <v>848.28</v>
+        <v>1378.14</v>
       </c>
       <c r="E152" s="3">
-        <v>848.28</v>
+        <v>1378.14</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>461</v>
+        <v>510</v>
       </c>
       <c r="D153" s="3">
-        <v>1697.98</v>
+        <v>1147.04</v>
       </c>
       <c r="E153" s="3">
-        <v>1697.98</v>
+        <v>1147.04</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>458</v>
+        <v>511</v>
       </c>
       <c r="D154" s="3">
-        <v>1343.4</v>
+        <v>949.96</v>
       </c>
       <c r="E154" s="3">
-        <v>1343.4</v>
+        <v>949.96</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>466</v>
+        <v>558</v>
       </c>
       <c r="D155" s="3">
-        <v>234.16</v>
+        <v>1169.94</v>
       </c>
       <c r="E155" s="3">
-        <v>234.16</v>
+        <v>631.91</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>453</v>
+        <v>531</v>
       </c>
       <c r="D156" s="3">
-        <v>4089.68</v>
+        <v>1908.79</v>
       </c>
       <c r="E156" s="3">
-        <v>2589.6799999999998</v>
+        <v>1908.79</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="D157" s="3">
-        <v>1182.92</v>
+        <v>443.82</v>
       </c>
       <c r="E157" s="3">
-        <v>1182.92</v>
+        <v>443.82</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="D158" s="3">
-        <v>1170.74</v>
+        <v>3337.92</v>
       </c>
       <c r="E158" s="3">
-        <v>1170.74</v>
+        <v>3337.92</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D159" s="3">
-        <v>591.96</v>
+        <v>452.3</v>
       </c>
       <c r="E159" s="3">
-        <v>591.96</v>
+        <v>452.3</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>532</v>
       </c>
       <c r="D160" s="3">
-        <v>1045.79</v>
+        <v>848.28</v>
       </c>
       <c r="E160" s="3">
-        <v>1045.79</v>
+        <v>848.28</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>533</v>
+        <v>484</v>
       </c>
       <c r="D161" s="3">
-        <v>2232.1999999999998</v>
+        <v>1697.98</v>
       </c>
       <c r="E161" s="3">
-        <v>1802.77</v>
+        <v>1697.98</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="D162" s="3">
-        <v>1356.94</v>
+        <v>1343.4</v>
       </c>
       <c r="E162" s="3">
-        <v>1356.94</v>
+        <v>1343.4</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
       <c r="D163" s="3">
-        <v>1727.3</v>
+        <v>234.16</v>
       </c>
       <c r="E163" s="3">
-        <v>1094.17</v>
+        <v>234.16</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="D164" s="3">
-        <v>5074.25</v>
+        <v>4089.68</v>
       </c>
       <c r="E164" s="3">
-        <v>5074.25</v>
+        <v>2589.6799999999998</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>458</v>
+        <v>560</v>
       </c>
       <c r="D165" s="3">
-        <v>465.46</v>
+        <v>628.79999999999995</v>
       </c>
       <c r="E165" s="3">
-        <v>465.46</v>
+        <v>262.77999999999997</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>534</v>
+        <v>561</v>
       </c>
       <c r="D166" s="3">
-        <v>586.17999999999995</v>
+        <v>1182.92</v>
       </c>
       <c r="E166" s="3">
-        <v>586.17999999999995</v>
+        <v>1182.92</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>535</v>
+        <v>562</v>
       </c>
       <c r="D167" s="3">
-        <v>922.4</v>
+        <v>1170.74</v>
       </c>
       <c r="E167" s="3">
-        <v>422.4</v>
+        <v>1170.74</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>536</v>
+        <v>563</v>
       </c>
       <c r="D168" s="3">
-        <v>443.82</v>
+        <v>591.96</v>
       </c>
       <c r="E168" s="3">
-        <v>443.82</v>
+        <v>591.96</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>505</v>
+        <v>564</v>
       </c>
       <c r="D169" s="3">
-        <v>62.92</v>
+        <v>1045.79</v>
       </c>
       <c r="E169" s="3">
-        <v>59.76</v>
+        <v>1045.79</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>466</v>
+        <v>565</v>
       </c>
       <c r="D170" s="3">
-        <v>1357.87</v>
+        <v>2232.1999999999998</v>
       </c>
       <c r="E170" s="3">
-        <v>1357.87</v>
+        <v>1802.77</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>461</v>
+        <v>518</v>
       </c>
       <c r="D171" s="3">
-        <v>446.71</v>
+        <v>1356.94</v>
       </c>
       <c r="E171" s="3">
-        <v>446.71</v>
+        <v>1356.94</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="D172" s="3">
-        <v>634.15</v>
+        <v>1727.3</v>
       </c>
       <c r="E172" s="3">
-        <v>634.15</v>
+        <v>1094.17</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>537</v>
+        <v>480</v>
       </c>
       <c r="D173" s="3">
-        <v>1854.68</v>
+        <v>5074.25</v>
       </c>
       <c r="E173" s="3">
-        <v>598.82000000000005</v>
+        <v>5074.25</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -5151,16 +5250,16 @@
         <v>49</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="D174" s="3">
-        <v>271.16000000000003</v>
+        <v>465.46</v>
       </c>
       <c r="E174" s="3">
-        <v>271.16000000000003</v>
+        <v>465.46</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -5168,118 +5267,118 @@
         <v>50</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>493</v>
+        <v>566</v>
       </c>
       <c r="D175" s="3">
-        <v>979.86</v>
+        <v>586.17999999999995</v>
       </c>
       <c r="E175" s="3">
-        <v>979.86</v>
+        <v>586.17999999999995</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>493</v>
+        <v>567</v>
       </c>
       <c r="D176" s="3">
-        <v>5049.43</v>
+        <v>922.4</v>
       </c>
       <c r="E176" s="3">
-        <v>100</v>
+        <v>422.4</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>538</v>
+        <v>568</v>
       </c>
       <c r="D177" s="3">
-        <v>8148.44</v>
+        <v>443.82</v>
       </c>
       <c r="E177" s="3">
-        <v>4148.4399999999996</v>
+        <v>443.82</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="D178" s="3">
-        <v>2326.6</v>
+        <v>62.92</v>
       </c>
       <c r="E178" s="3">
-        <v>2326.6</v>
+        <v>59.76</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>540</v>
+        <v>489</v>
       </c>
       <c r="D179" s="3">
-        <v>188.74</v>
+        <v>1357.87</v>
       </c>
       <c r="E179" s="3">
-        <v>188.74</v>
+        <v>1357.87</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>534</v>
+        <v>484</v>
       </c>
       <c r="D180" s="3">
-        <v>196.96</v>
+        <v>446.71</v>
       </c>
       <c r="E180" s="3">
-        <v>13.94</v>
+        <v>446.71</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="D181" s="3">
-        <v>822.61</v>
+        <v>634.15</v>
       </c>
       <c r="E181" s="3">
-        <v>822.61</v>
+        <v>634.15</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -5287,16 +5386,16 @@
         <v>53</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>536</v>
+        <v>569</v>
       </c>
       <c r="D182" s="3">
-        <v>632.58000000000004</v>
+        <v>1854.68</v>
       </c>
       <c r="E182" s="3">
-        <v>632.58000000000004</v>
+        <v>598.82000000000005</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -5304,16 +5403,16 @@
         <v>54</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="D183" s="3">
-        <v>646.65</v>
+        <v>271.16000000000003</v>
       </c>
       <c r="E183" s="3">
-        <v>-477.93</v>
+        <v>271.16000000000003</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -5321,492 +5420,492 @@
         <v>55</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>542</v>
+        <v>517</v>
       </c>
       <c r="D184" s="3">
-        <v>204.66</v>
+        <v>979.86</v>
       </c>
       <c r="E184" s="3">
-        <v>204.66</v>
+        <v>979.86</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>493</v>
+        <v>517</v>
       </c>
       <c r="D185" s="3">
-        <v>2820.19</v>
+        <v>5049.43</v>
       </c>
       <c r="E185" s="3">
-        <v>2820.19</v>
+        <v>100</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>543</v>
+        <v>570</v>
       </c>
       <c r="D186" s="3">
-        <v>6111.13</v>
+        <v>8148.44</v>
       </c>
       <c r="E186" s="3">
-        <v>6111.13</v>
+        <v>4148.4399999999996</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>544</v>
+        <v>571</v>
       </c>
       <c r="D187" s="3">
-        <v>67.39</v>
+        <v>2326.6</v>
       </c>
       <c r="E187" s="3">
-        <v>67.39</v>
+        <v>2326.6</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>498</v>
+        <v>572</v>
       </c>
       <c r="D188" s="3">
-        <v>185.97</v>
+        <v>188.74</v>
       </c>
       <c r="E188" s="3">
-        <v>185.97</v>
+        <v>188.74</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="D189" s="3">
-        <v>341.16</v>
+        <v>196.96</v>
       </c>
       <c r="E189" s="3">
-        <v>341.16</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>503</v>
+        <v>573</v>
       </c>
       <c r="D190" s="3">
-        <v>235.12</v>
+        <v>822.61</v>
       </c>
       <c r="E190" s="3">
-        <v>235.12</v>
+        <v>822.61</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>546</v>
+        <v>568</v>
       </c>
       <c r="D191" s="3">
-        <v>7257.6</v>
+        <v>632.58000000000004</v>
       </c>
       <c r="E191" s="3">
-        <v>7257.6</v>
+        <v>632.58000000000004</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>547</v>
+        <v>513</v>
       </c>
       <c r="D192" s="3">
-        <v>204.69</v>
+        <v>646.65</v>
       </c>
       <c r="E192" s="3">
-        <v>204.69</v>
+        <v>-477.93</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>548</v>
+        <v>574</v>
       </c>
       <c r="D193" s="3">
-        <v>6571.11</v>
+        <v>204.66</v>
       </c>
       <c r="E193" s="3">
-        <v>1565.07</v>
+        <v>204.66</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>549</v>
+        <v>517</v>
       </c>
       <c r="D194" s="3">
-        <v>2520.7800000000002</v>
+        <v>2820.19</v>
       </c>
       <c r="E194" s="3">
-        <v>2520.7800000000002</v>
+        <v>2820.19</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>464</v>
+        <v>575</v>
       </c>
       <c r="D195" s="3">
-        <v>448.44</v>
+        <v>6111.13</v>
       </c>
       <c r="E195" s="3">
-        <v>448.44</v>
+        <v>6111.13</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>493</v>
+        <v>576</v>
       </c>
       <c r="D196" s="3">
-        <v>1361.17</v>
+        <v>67.39</v>
       </c>
       <c r="E196" s="3">
-        <v>1361.17</v>
+        <v>67.39</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>457</v>
+        <v>523</v>
       </c>
       <c r="D197" s="3">
-        <v>1591.95</v>
+        <v>185.97</v>
       </c>
       <c r="E197" s="3">
-        <v>1091.95</v>
+        <v>185.97</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>493</v>
+        <v>577</v>
       </c>
       <c r="D198" s="3">
-        <v>772.93</v>
+        <v>341.16</v>
       </c>
       <c r="E198" s="3">
-        <v>772.93</v>
+        <v>341.16</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>477</v>
+        <v>528</v>
       </c>
       <c r="D199" s="3">
-        <v>507.56</v>
+        <v>235.12</v>
       </c>
       <c r="E199" s="3">
-        <v>507.56</v>
+        <v>235.12</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>461</v>
+        <v>578</v>
       </c>
       <c r="D200" s="3">
-        <v>659.4</v>
+        <v>7257.6</v>
       </c>
       <c r="E200" s="3">
-        <v>659.4</v>
+        <v>7257.6</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>550</v>
+        <v>579</v>
       </c>
       <c r="D201" s="3">
-        <v>143.43</v>
+        <v>204.69</v>
       </c>
       <c r="E201" s="3">
-        <v>143.43</v>
+        <v>204.69</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>551</v>
+        <v>580</v>
       </c>
       <c r="D202" s="3">
-        <v>666.99</v>
+        <v>6571.11</v>
       </c>
       <c r="E202" s="3">
-        <v>666.99</v>
+        <v>1565.07</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="D203" s="3">
-        <v>570.26</v>
+        <v>2520.7800000000002</v>
       </c>
       <c r="E203" s="3">
-        <v>570.26</v>
+        <v>2520.7800000000002</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>553</v>
+        <v>487</v>
       </c>
       <c r="D204" s="3">
-        <v>97.98</v>
+        <v>448.44</v>
       </c>
       <c r="E204" s="3">
-        <v>97.98</v>
+        <v>448.44</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>554</v>
+        <v>517</v>
       </c>
       <c r="D205" s="3">
-        <v>298.19</v>
+        <v>1361.17</v>
       </c>
       <c r="E205" s="3">
-        <v>70.8</v>
+        <v>1361.17</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="D206" s="3">
-        <v>436.49</v>
+        <v>1591.95</v>
       </c>
       <c r="E206" s="3">
-        <v>436.49</v>
+        <v>1091.95</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="D207" s="3">
-        <v>321.5</v>
+        <v>772.93</v>
       </c>
       <c r="E207" s="3">
-        <v>321.5</v>
+        <v>772.93</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>555</v>
+        <v>501</v>
       </c>
       <c r="D208" s="3">
-        <v>8550.85</v>
+        <v>507.56</v>
       </c>
       <c r="E208" s="3">
-        <v>6550.4</v>
+        <v>507.56</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="D209" s="3">
-        <v>6602.62</v>
+        <v>659.4</v>
       </c>
       <c r="E209" s="3">
-        <v>6602.62</v>
+        <v>659.4</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>453</v>
+        <v>581</v>
       </c>
       <c r="D210" s="3">
-        <v>188.76</v>
+        <v>143.43</v>
       </c>
       <c r="E210" s="3">
-        <v>188.76</v>
+        <v>143.43</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>488</v>
+        <v>582</v>
       </c>
       <c r="D211" s="3">
-        <v>981.11</v>
+        <v>666.99</v>
       </c>
       <c r="E211" s="3">
-        <v>981.11</v>
+        <v>666.99</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>451</v>
+        <v>583</v>
       </c>
       <c r="D212" s="3">
-        <v>686.99</v>
+        <v>570.26</v>
       </c>
       <c r="E212" s="3">
-        <v>686.99</v>
+        <v>570.26</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -5814,16 +5913,16 @@
         <v>64</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>475</v>
+        <v>584</v>
       </c>
       <c r="D213" s="3">
-        <v>412.7</v>
+        <v>97.98</v>
       </c>
       <c r="E213" s="3">
-        <v>412.7</v>
+        <v>97.98</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -5831,16 +5930,16 @@
         <v>64</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>542</v>
+        <v>585</v>
       </c>
       <c r="D214" s="3">
-        <v>367.8</v>
+        <v>298.19</v>
       </c>
       <c r="E214" s="3">
-        <v>367.8</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -5848,16 +5947,16 @@
         <v>64</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D215" s="3">
-        <v>288.83999999999997</v>
+        <v>436.49</v>
       </c>
       <c r="E215" s="3">
-        <v>288.83999999999997</v>
+        <v>436.49</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -5865,390 +5964,390 @@
         <v>64</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>556</v>
+        <v>534</v>
       </c>
       <c r="D216" s="3">
-        <v>2755.5</v>
+        <v>321.5</v>
       </c>
       <c r="E216" s="3">
-        <v>2654.72</v>
+        <v>321.5</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>545</v>
+        <v>586</v>
       </c>
       <c r="D217" s="3">
-        <v>1051.1400000000001</v>
+        <v>8550.85</v>
       </c>
       <c r="E217" s="3">
-        <v>1051.1400000000001</v>
+        <v>6550.4</v>
       </c>
     </row>
     <row r="218" spans="1:5">
       <c r="A218" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="D218" s="3">
-        <v>50.64</v>
+        <v>6602.62</v>
       </c>
       <c r="E218" s="3">
-        <v>50.64</v>
+        <v>6602.62</v>
       </c>
     </row>
     <row r="219" spans="1:5">
       <c r="A219" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>557</v>
+        <v>476</v>
       </c>
       <c r="D219" s="3">
-        <v>380.31</v>
+        <v>188.76</v>
       </c>
       <c r="E219" s="3">
-        <v>380.31</v>
+        <v>188.76</v>
       </c>
     </row>
     <row r="220" spans="1:5">
       <c r="A220" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D220" s="3">
-        <v>185.97</v>
+        <v>981.11</v>
       </c>
       <c r="E220" s="3">
-        <v>185.97</v>
+        <v>981.11</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>556</v>
+        <v>474</v>
       </c>
       <c r="D221" s="3">
-        <v>886.1</v>
+        <v>686.99</v>
       </c>
       <c r="E221" s="3">
-        <v>638.34</v>
+        <v>686.99</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="D222" s="3">
-        <v>286.82</v>
+        <v>412.7</v>
       </c>
       <c r="E222" s="3">
-        <v>286.82</v>
+        <v>412.7</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>545</v>
+        <v>574</v>
       </c>
       <c r="D223" s="3">
-        <v>239.52</v>
+        <v>367.8</v>
       </c>
       <c r="E223" s="3">
-        <v>239.52</v>
+        <v>367.8</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D224" s="3">
-        <v>498.92</v>
+        <v>288.83999999999997</v>
       </c>
       <c r="E224" s="3">
-        <v>498.92</v>
+        <v>288.83999999999997</v>
       </c>
     </row>
     <row r="225" spans="1:5">
       <c r="A225" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>488</v>
+        <v>587</v>
       </c>
       <c r="D225" s="3">
-        <v>2283.4499999999998</v>
+        <v>2755.5</v>
       </c>
       <c r="E225" s="3">
-        <v>2283.4499999999998</v>
+        <v>2654.72</v>
       </c>
     </row>
     <row r="226" spans="1:5">
       <c r="A226" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>466</v>
+        <v>577</v>
       </c>
       <c r="D226" s="3">
-        <v>809.77</v>
+        <v>1051.1400000000001</v>
       </c>
       <c r="E226" s="3">
-        <v>809.77</v>
+        <v>1051.1400000000001</v>
       </c>
     </row>
     <row r="227" spans="1:5">
       <c r="A227" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>462</v>
+        <v>529</v>
       </c>
       <c r="D227" s="3">
-        <v>1622.56</v>
+        <v>50.64</v>
       </c>
       <c r="E227" s="3">
-        <v>1622.56</v>
+        <v>50.64</v>
       </c>
     </row>
     <row r="228" spans="1:5">
       <c r="A228" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>453</v>
+        <v>588</v>
       </c>
       <c r="D228" s="3">
-        <v>698.2</v>
+        <v>380.31</v>
       </c>
       <c r="E228" s="3">
-        <v>698.2</v>
+        <v>380.31</v>
       </c>
     </row>
     <row r="229" spans="1:5">
       <c r="A229" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>454</v>
+        <v>533</v>
       </c>
       <c r="D229" s="3">
-        <v>904.49</v>
+        <v>185.97</v>
       </c>
       <c r="E229" s="3">
-        <v>904.49</v>
+        <v>185.97</v>
       </c>
     </row>
     <row r="230" spans="1:5">
       <c r="A230" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>457</v>
+        <v>587</v>
       </c>
       <c r="D230" s="3">
-        <v>1206.99</v>
+        <v>886.1</v>
       </c>
       <c r="E230" s="3">
-        <v>1206.99</v>
+        <v>638.34</v>
       </c>
     </row>
     <row r="231" spans="1:5">
       <c r="A231" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>458</v>
+        <v>502</v>
       </c>
       <c r="D231" s="3">
-        <v>377.4</v>
+        <v>286.82</v>
       </c>
       <c r="E231" s="3">
-        <v>377.4</v>
+        <v>286.82</v>
       </c>
     </row>
     <row r="232" spans="1:5">
       <c r="A232" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="D232" s="3">
-        <v>2037.99</v>
+        <v>239.52</v>
       </c>
       <c r="E232" s="3">
-        <v>2037.99</v>
+        <v>239.52</v>
       </c>
     </row>
     <row r="233" spans="1:5">
       <c r="A233" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D233" s="3">
-        <v>251.63</v>
+        <v>498.92</v>
       </c>
       <c r="E233" s="3">
-        <v>251.63</v>
+        <v>498.92</v>
       </c>
     </row>
     <row r="234" spans="1:5">
       <c r="A234" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>560</v>
+        <v>512</v>
       </c>
       <c r="D234" s="3">
-        <v>2373.4299999999998</v>
+        <v>2283.4499999999998</v>
       </c>
       <c r="E234" s="3">
-        <v>1703.6</v>
+        <v>2283.4499999999998</v>
       </c>
     </row>
     <row r="235" spans="1:5">
       <c r="A235" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>561</v>
+        <v>489</v>
       </c>
       <c r="D235" s="3">
-        <v>2372.73</v>
+        <v>809.77</v>
       </c>
       <c r="E235" s="3">
-        <v>2372.73</v>
+        <v>809.77</v>
       </c>
     </row>
     <row r="236" spans="1:5">
       <c r="A236" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>562</v>
+        <v>485</v>
       </c>
       <c r="D236" s="3">
-        <v>216</v>
+        <v>1622.56</v>
       </c>
       <c r="E236" s="3">
-        <v>216</v>
+        <v>1622.56</v>
       </c>
     </row>
     <row r="237" spans="1:5">
       <c r="A237" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D237" s="3">
-        <v>448.44</v>
+        <v>698.2</v>
       </c>
       <c r="E237" s="3">
-        <v>448.44</v>
+        <v>698.2</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="A238" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="D238" s="3">
-        <v>905.46</v>
+        <v>904.49</v>
       </c>
       <c r="E238" s="3">
-        <v>905.46</v>
+        <v>904.49</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -6256,50 +6355,50 @@
         <v>72</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="D239" s="3">
-        <v>522.57000000000005</v>
+        <v>1206.99</v>
       </c>
       <c r="E239" s="3">
-        <v>522.57000000000005</v>
+        <v>1206.99</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="D240" s="3">
-        <v>924.1</v>
+        <v>377.4</v>
       </c>
       <c r="E240" s="3">
-        <v>924.1</v>
+        <v>377.4</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>563</v>
+        <v>589</v>
       </c>
       <c r="D241" s="3">
-        <v>3762.77</v>
+        <v>2037.99</v>
       </c>
       <c r="E241" s="3">
-        <v>825.34</v>
+        <v>2037.99</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -6307,16 +6406,16 @@
         <v>74</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>564</v>
+        <v>590</v>
       </c>
       <c r="D242" s="3">
-        <v>2087.52</v>
+        <v>251.63</v>
       </c>
       <c r="E242" s="3">
-        <v>2087.52</v>
+        <v>251.63</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -6324,16 +6423,16 @@
         <v>74</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>565</v>
+        <v>591</v>
       </c>
       <c r="D243" s="3">
-        <v>267.10000000000002</v>
+        <v>2373.4299999999998</v>
       </c>
       <c r="E243" s="3">
-        <v>267.10000000000002</v>
+        <v>1703.6</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -6341,33 +6440,33 @@
         <v>74</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>566</v>
+        <v>592</v>
       </c>
       <c r="D244" s="3">
-        <v>4118.0200000000004</v>
+        <v>2372.73</v>
       </c>
       <c r="E244" s="3">
-        <v>4118.0200000000004</v>
+        <v>2372.73</v>
       </c>
     </row>
     <row r="245" spans="1:5">
       <c r="A245" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>567</v>
+        <v>593</v>
       </c>
       <c r="D245" s="3">
-        <v>5017.9799999999996</v>
+        <v>216</v>
       </c>
       <c r="E245" s="3">
-        <v>5017.9799999999996</v>
+        <v>216</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -6375,16 +6474,16 @@
         <v>75</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>568</v>
+        <v>503</v>
       </c>
       <c r="D246" s="3">
-        <v>9692.1299999999992</v>
+        <v>448.44</v>
       </c>
       <c r="E246" s="3">
-        <v>9692.1299999999992</v>
+        <v>448.44</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -6392,866 +6491,866 @@
         <v>76</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>477</v>
+        <v>518</v>
       </c>
       <c r="D247" s="3">
-        <v>627.24</v>
+        <v>905.46</v>
       </c>
       <c r="E247" s="3">
-        <v>627.24</v>
+        <v>905.46</v>
       </c>
     </row>
     <row r="248" spans="1:5">
       <c r="A248" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="D248" s="3">
-        <v>401.12</v>
+        <v>522.57000000000005</v>
       </c>
       <c r="E248" s="3">
-        <v>401.12</v>
+        <v>522.57000000000005</v>
       </c>
     </row>
     <row r="249" spans="1:5">
       <c r="A249" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>457</v>
+        <v>484</v>
       </c>
       <c r="D249" s="3">
-        <v>508</v>
+        <v>924.1</v>
       </c>
       <c r="E249" s="3">
-        <v>508</v>
+        <v>924.1</v>
       </c>
     </row>
     <row r="250" spans="1:5">
       <c r="A250" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>563</v>
+        <v>594</v>
       </c>
       <c r="D250" s="3">
-        <v>564.66</v>
+        <v>3762.77</v>
       </c>
       <c r="E250" s="3">
-        <v>564.66</v>
+        <v>825.34</v>
       </c>
     </row>
     <row r="251" spans="1:5">
       <c r="A251" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>470</v>
+        <v>595</v>
       </c>
       <c r="D251" s="3">
-        <v>764.3</v>
+        <v>2087.52</v>
       </c>
       <c r="E251" s="3">
-        <v>764.3</v>
+        <v>2087.52</v>
       </c>
     </row>
     <row r="252" spans="1:5">
       <c r="A252" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>569</v>
+        <v>596</v>
       </c>
       <c r="D252" s="3">
-        <v>652.29999999999995</v>
+        <v>267.10000000000002</v>
       </c>
       <c r="E252" s="3">
-        <v>652.29999999999995</v>
+        <v>267.10000000000002</v>
       </c>
     </row>
     <row r="253" spans="1:5">
       <c r="A253" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>570</v>
+        <v>597</v>
       </c>
       <c r="D253" s="3">
-        <v>870.5</v>
+        <v>4118.0200000000004</v>
       </c>
       <c r="E253" s="3">
-        <v>870.5</v>
+        <v>4118.0200000000004</v>
       </c>
     </row>
     <row r="254" spans="1:5">
       <c r="A254" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>570</v>
+        <v>598</v>
       </c>
       <c r="D254" s="3">
-        <v>1009.8</v>
+        <v>5017.9799999999996</v>
       </c>
       <c r="E254" s="3">
-        <v>1009.8</v>
+        <v>5017.9799999999996</v>
       </c>
     </row>
     <row r="255" spans="1:5">
       <c r="A255" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>571</v>
+        <v>599</v>
       </c>
       <c r="D255" s="3">
-        <v>596.72</v>
+        <v>9692.1299999999992</v>
       </c>
       <c r="E255" s="3">
-        <v>596.72</v>
+        <v>9692.1299999999992</v>
       </c>
     </row>
     <row r="256" spans="1:5">
       <c r="A256" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>572</v>
+        <v>501</v>
       </c>
       <c r="D256" s="3">
-        <v>36000</v>
+        <v>627.24</v>
       </c>
       <c r="E256" s="3">
-        <v>16800</v>
+        <v>627.24</v>
       </c>
     </row>
     <row r="257" spans="1:5">
       <c r="A257" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>564</v>
+        <v>502</v>
       </c>
       <c r="D257" s="3">
-        <v>898.02</v>
+        <v>401.12</v>
       </c>
       <c r="E257" s="3">
-        <v>898.02</v>
+        <v>401.12</v>
       </c>
     </row>
     <row r="258" spans="1:5">
       <c r="A258" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>573</v>
+        <v>480</v>
       </c>
       <c r="D258" s="3">
-        <v>729.12</v>
+        <v>508</v>
       </c>
       <c r="E258" s="3">
-        <v>729.12</v>
+        <v>508</v>
       </c>
     </row>
     <row r="259" spans="1:5">
       <c r="A259" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="D259" s="3">
-        <v>216.35</v>
+        <v>564.66</v>
       </c>
       <c r="E259" s="3">
-        <v>216.35</v>
+        <v>564.66</v>
       </c>
     </row>
     <row r="260" spans="1:5">
       <c r="A260" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="D260" s="3">
-        <v>356.73</v>
+        <v>764.3</v>
       </c>
       <c r="E260" s="3">
-        <v>356.73</v>
+        <v>764.3</v>
       </c>
     </row>
     <row r="261" spans="1:5">
       <c r="A261" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>574</v>
+        <v>600</v>
       </c>
       <c r="D261" s="3">
-        <v>716.1</v>
+        <v>652.29999999999995</v>
       </c>
       <c r="E261" s="3">
-        <v>716.1</v>
+        <v>652.29999999999995</v>
       </c>
     </row>
     <row r="262" spans="1:5">
       <c r="A262" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>575</v>
+        <v>601</v>
       </c>
       <c r="D262" s="3">
-        <v>2042.43</v>
+        <v>870.5</v>
       </c>
       <c r="E262" s="3">
-        <v>2042.43</v>
+        <v>870.5</v>
       </c>
     </row>
     <row r="263" spans="1:5">
       <c r="A263" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>576</v>
+        <v>601</v>
       </c>
       <c r="D263" s="3">
-        <v>898.02</v>
+        <v>1009.8</v>
       </c>
       <c r="E263" s="3">
-        <v>898.02</v>
+        <v>1009.8</v>
       </c>
     </row>
     <row r="264" spans="1:5">
       <c r="A264" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="D264" s="3">
-        <v>597.20000000000005</v>
+        <v>596.72</v>
       </c>
       <c r="E264" s="3">
-        <v>597.20000000000005</v>
+        <v>596.72</v>
       </c>
     </row>
     <row r="265" spans="1:5">
       <c r="A265" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="D265" s="3">
-        <v>1072.2</v>
+        <v>36000</v>
       </c>
       <c r="E265" s="3">
-        <v>594.21</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="266" spans="1:5">
       <c r="A266" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="D266" s="3">
-        <v>416.84</v>
+        <v>898.02</v>
       </c>
       <c r="E266" s="3">
-        <v>416.84</v>
+        <v>898.02</v>
       </c>
     </row>
     <row r="267" spans="1:5">
       <c r="A267" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="D267" s="3">
-        <v>651.4</v>
+        <v>729.12</v>
       </c>
       <c r="E267" s="3">
-        <v>651.4</v>
+        <v>729.12</v>
       </c>
     </row>
     <row r="268" spans="1:5">
       <c r="A268" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D268" s="3">
-        <v>5600.79</v>
+        <v>216.35</v>
       </c>
       <c r="E268" s="3">
-        <v>5600.79</v>
+        <v>216.35</v>
       </c>
     </row>
     <row r="269" spans="1:5">
       <c r="A269" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>581</v>
+        <v>497</v>
       </c>
       <c r="D269" s="3">
-        <v>736.72</v>
+        <v>356.73</v>
       </c>
       <c r="E269" s="3">
-        <v>736.72</v>
+        <v>356.73</v>
       </c>
     </row>
     <row r="270" spans="1:5">
       <c r="A270" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>582</v>
+        <v>605</v>
       </c>
       <c r="D270" s="3">
-        <v>870.5</v>
+        <v>716.1</v>
       </c>
       <c r="E270" s="3">
-        <v>870.5</v>
+        <v>716.1</v>
       </c>
     </row>
     <row r="271" spans="1:5">
       <c r="A271" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="D271" s="3">
-        <v>651.29999999999995</v>
+        <v>2042.43</v>
       </c>
       <c r="E271" s="3">
-        <v>651.29999999999995</v>
+        <v>2042.43</v>
       </c>
     </row>
     <row r="272" spans="1:5">
       <c r="A272" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="D272" s="3">
-        <v>729.12</v>
+        <v>898.02</v>
       </c>
       <c r="E272" s="3">
-        <v>729.12</v>
+        <v>898.02</v>
       </c>
     </row>
     <row r="273" spans="1:5">
       <c r="A273" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>560</v>
+        <v>608</v>
       </c>
       <c r="D273" s="3">
-        <v>13080.39</v>
+        <v>597.20000000000005</v>
       </c>
       <c r="E273" s="3">
-        <v>3528.34</v>
+        <v>597.20000000000005</v>
       </c>
     </row>
     <row r="274" spans="1:5">
       <c r="A274" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>459</v>
+        <v>609</v>
       </c>
       <c r="D274" s="3">
-        <v>432.76</v>
+        <v>1072.2</v>
       </c>
       <c r="E274" s="3">
-        <v>432.76</v>
+        <v>594.21</v>
       </c>
     </row>
     <row r="275" spans="1:5">
       <c r="A275" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="D275" s="3">
-        <v>748.1</v>
+        <v>416.84</v>
       </c>
       <c r="E275" s="3">
-        <v>248.1</v>
+        <v>416.84</v>
       </c>
     </row>
     <row r="276" spans="1:5">
       <c r="A276" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D276" s="3">
-        <v>2201.4</v>
+        <v>651.4</v>
       </c>
       <c r="E276" s="3">
-        <v>2201.4</v>
+        <v>651.4</v>
       </c>
     </row>
     <row r="277" spans="1:5">
       <c r="A277" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>518</v>
+        <v>611</v>
       </c>
       <c r="D277" s="3">
-        <v>578.61</v>
+        <v>5600.79</v>
       </c>
       <c r="E277" s="3">
-        <v>578.61</v>
+        <v>5600.79</v>
       </c>
     </row>
     <row r="278" spans="1:5">
       <c r="A278" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>518</v>
+        <v>612</v>
       </c>
       <c r="D278" s="3">
-        <v>6604.2</v>
+        <v>736.72</v>
       </c>
       <c r="E278" s="3">
-        <v>6604.2</v>
+        <v>736.72</v>
       </c>
     </row>
     <row r="279" spans="1:5">
       <c r="A279" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>587</v>
+        <v>613</v>
       </c>
       <c r="D279" s="3">
-        <v>1135.75</v>
+        <v>870.5</v>
       </c>
       <c r="E279" s="3">
-        <v>1135.75</v>
+        <v>870.5</v>
       </c>
     </row>
     <row r="280" spans="1:5">
       <c r="A280" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>504</v>
+        <v>614</v>
       </c>
       <c r="D280" s="3">
-        <v>535.79999999999995</v>
+        <v>651.29999999999995</v>
       </c>
       <c r="E280" s="3">
-        <v>535.79999999999995</v>
+        <v>651.29999999999995</v>
       </c>
     </row>
     <row r="281" spans="1:5">
       <c r="A281" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>557</v>
+        <v>615</v>
       </c>
       <c r="D281" s="3">
-        <v>6604.2</v>
+        <v>729.12</v>
       </c>
       <c r="E281" s="3">
-        <v>6604.2</v>
+        <v>729.12</v>
       </c>
     </row>
     <row r="282" spans="1:5">
       <c r="A282" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>550</v>
+        <v>591</v>
       </c>
       <c r="D282" s="3">
-        <v>8680.93</v>
+        <v>13080.39</v>
       </c>
       <c r="E282" s="3">
-        <v>5694.93</v>
+        <v>3528.34</v>
       </c>
     </row>
     <row r="283" spans="1:5">
       <c r="A283" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>588</v>
+        <v>482</v>
       </c>
       <c r="D283" s="3">
-        <v>6835.49</v>
+        <v>432.76</v>
       </c>
       <c r="E283" s="3">
-        <v>6835.49</v>
+        <v>432.76</v>
       </c>
     </row>
     <row r="284" spans="1:5">
       <c r="A284" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>468</v>
+        <v>616</v>
       </c>
       <c r="D284" s="3">
-        <v>9512.7099999999991</v>
+        <v>748.1</v>
       </c>
       <c r="E284" s="3">
-        <v>9512.7099999999991</v>
+        <v>248.1</v>
       </c>
     </row>
     <row r="285" spans="1:5">
       <c r="A285" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>479</v>
+        <v>617</v>
       </c>
       <c r="D285" s="3">
-        <v>374.52</v>
+        <v>2201.4</v>
       </c>
       <c r="E285" s="3">
-        <v>374.52</v>
+        <v>2201.4</v>
       </c>
     </row>
     <row r="286" spans="1:5">
       <c r="A286" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>462</v>
+        <v>549</v>
       </c>
       <c r="D286" s="3">
-        <v>804.28</v>
+        <v>578.61</v>
       </c>
       <c r="E286" s="3">
-        <v>804.28</v>
+        <v>578.61</v>
       </c>
     </row>
     <row r="287" spans="1:5">
       <c r="A287" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>516</v>
+        <v>549</v>
       </c>
       <c r="D287" s="3">
-        <v>142.41</v>
+        <v>6604.2</v>
       </c>
       <c r="E287" s="3">
-        <v>142.41</v>
+        <v>6604.2</v>
       </c>
     </row>
     <row r="288" spans="1:5">
       <c r="A288" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>488</v>
+        <v>618</v>
       </c>
       <c r="D288" s="3">
-        <v>146.88</v>
+        <v>1135.75</v>
       </c>
       <c r="E288" s="3">
-        <v>146.88</v>
+        <v>1135.75</v>
       </c>
     </row>
     <row r="289" spans="1:5">
       <c r="A289" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="D289" s="3">
-        <v>432.76</v>
+        <v>535.79999999999995</v>
       </c>
       <c r="E289" s="3">
-        <v>46.38</v>
+        <v>535.79999999999995</v>
       </c>
     </row>
     <row r="290" spans="1:5">
       <c r="A290" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>491</v>
+        <v>588</v>
       </c>
       <c r="D290" s="3">
-        <v>656.44</v>
+        <v>6604.2</v>
       </c>
       <c r="E290" s="3">
-        <v>656.44</v>
+        <v>6604.2</v>
       </c>
     </row>
     <row r="291" spans="1:5">
       <c r="A291" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>467</v>
+        <v>581</v>
       </c>
       <c r="D291" s="3">
-        <v>409.44</v>
+        <v>8680.93</v>
       </c>
       <c r="E291" s="3">
-        <v>409.44</v>
+        <v>5694.93</v>
       </c>
     </row>
     <row r="292" spans="1:5">
       <c r="A292" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>589</v>
+        <v>619</v>
       </c>
       <c r="D292" s="3">
-        <v>461.93</v>
+        <v>6835.49</v>
       </c>
       <c r="E292" s="3">
-        <v>461.93</v>
+        <v>6835.49</v>
       </c>
     </row>
     <row r="293" spans="1:5">
       <c r="A293" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>520</v>
+        <v>491</v>
       </c>
       <c r="D293" s="3">
-        <v>1949.41</v>
+        <v>9512.7099999999991</v>
       </c>
       <c r="E293" s="3">
-        <v>1583.6</v>
+        <v>9512.7099999999991</v>
       </c>
     </row>
     <row r="294" spans="1:5">
       <c r="A294" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>451</v>
+        <v>503</v>
       </c>
       <c r="D294" s="3">
-        <v>356.1</v>
+        <v>374.52</v>
       </c>
       <c r="E294" s="3">
-        <v>356.1</v>
+        <v>374.52</v>
       </c>
     </row>
     <row r="295" spans="1:5">
       <c r="A295" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="D295" s="3">
-        <v>1120.58</v>
+        <v>804.28</v>
       </c>
       <c r="E295" s="3">
-        <v>1101.81</v>
+        <v>804.28</v>
       </c>
     </row>
     <row r="296" spans="1:5">
       <c r="A296" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>505</v>
+        <v>546</v>
       </c>
       <c r="D296" s="3">
-        <v>10808.11</v>
+        <v>142.41</v>
       </c>
       <c r="E296" s="3">
-        <v>9879.17</v>
+        <v>142.41</v>
       </c>
     </row>
     <row r="297" spans="1:5">
       <c r="A297" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>467</v>
+        <v>512</v>
       </c>
       <c r="D297" s="3">
-        <v>2640.58</v>
+        <v>146.88</v>
       </c>
       <c r="E297" s="3">
-        <v>1889.67</v>
+        <v>146.88</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -7259,84 +7358,84 @@
         <v>87</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>488</v>
+        <v>522</v>
       </c>
       <c r="D298" s="3">
-        <v>3745.59</v>
+        <v>432.76</v>
       </c>
       <c r="E298" s="3">
-        <v>3745.59</v>
+        <v>46.38</v>
       </c>
     </row>
     <row r="299" spans="1:5">
       <c r="A299" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>460</v>
+        <v>515</v>
       </c>
       <c r="D299" s="3">
-        <v>1138.77</v>
+        <v>656.44</v>
       </c>
       <c r="E299" s="3">
-        <v>1138.77</v>
+        <v>656.44</v>
       </c>
     </row>
     <row r="300" spans="1:5">
       <c r="A300" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>590</v>
+        <v>490</v>
       </c>
       <c r="D300" s="3">
-        <v>1217.72</v>
+        <v>409.44</v>
       </c>
       <c r="E300" s="3">
-        <v>1217.72</v>
+        <v>409.44</v>
       </c>
     </row>
     <row r="301" spans="1:5">
       <c r="A301" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>494</v>
+        <v>620</v>
       </c>
       <c r="D301" s="3">
-        <v>706.5</v>
+        <v>461.93</v>
       </c>
       <c r="E301" s="3">
-        <v>706.5</v>
+        <v>461.93</v>
       </c>
     </row>
     <row r="302" spans="1:5">
       <c r="A302" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>454</v>
+        <v>551</v>
       </c>
       <c r="D302" s="3">
-        <v>1414.7</v>
+        <v>1949.41</v>
       </c>
       <c r="E302" s="3">
-        <v>1414.7</v>
+        <v>1583.6</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -7344,33 +7443,33 @@
         <v>89</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="D303" s="3">
-        <v>1262.69</v>
+        <v>356.1</v>
       </c>
       <c r="E303" s="3">
-        <v>1262.69</v>
+        <v>356.1</v>
       </c>
     </row>
     <row r="304" spans="1:5">
       <c r="A304" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>591</v>
+        <v>514</v>
       </c>
       <c r="D304" s="3">
-        <v>318.69</v>
+        <v>1120.58</v>
       </c>
       <c r="E304" s="3">
-        <v>318.69</v>
+        <v>1101.81</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -7378,16 +7477,16 @@
         <v>90</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>591</v>
+        <v>517</v>
       </c>
       <c r="D305" s="3">
-        <v>501.26</v>
+        <v>2741.2</v>
       </c>
       <c r="E305" s="3">
-        <v>501.26</v>
+        <v>2741.2</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -7395,16 +7494,16 @@
         <v>90</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>592</v>
+        <v>517</v>
       </c>
       <c r="D306" s="3">
-        <v>211.45</v>
+        <v>-2741.2</v>
       </c>
       <c r="E306" s="3">
-        <v>211.45</v>
+        <v>-2741.2</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -7412,16 +7511,16 @@
         <v>90</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>593</v>
+        <v>517</v>
       </c>
       <c r="D307" s="3">
-        <v>92.34</v>
+        <v>2201.4</v>
       </c>
       <c r="E307" s="3">
-        <v>92.34</v>
+        <v>2201.4</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -7429,16 +7528,16 @@
         <v>90</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>594</v>
+        <v>621</v>
       </c>
       <c r="D308" s="3">
-        <v>829.15</v>
+        <v>2931.2</v>
       </c>
       <c r="E308" s="3">
-        <v>264.02999999999997</v>
+        <v>2931.2</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -7446,67 +7545,67 @@
         <v>90</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>594</v>
+        <v>622</v>
       </c>
       <c r="D309" s="3">
-        <v>569.84</v>
+        <v>2644.48</v>
       </c>
       <c r="E309" s="3">
-        <v>569.84</v>
+        <v>2644.48</v>
       </c>
     </row>
     <row r="310" spans="1:5">
       <c r="A310" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D310" s="3">
-        <v>10514.78</v>
+        <v>3087.07</v>
       </c>
       <c r="E310" s="3">
-        <v>10514.78</v>
+        <v>3087.07</v>
       </c>
     </row>
     <row r="311" spans="1:5">
       <c r="A311" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>595</v>
+        <v>568</v>
       </c>
       <c r="D311" s="3">
-        <v>343.39</v>
+        <v>2741.2</v>
       </c>
       <c r="E311" s="3">
-        <v>343.39</v>
+        <v>2741.2</v>
       </c>
     </row>
     <row r="312" spans="1:5">
       <c r="A312" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>596</v>
+        <v>530</v>
       </c>
       <c r="D312" s="3">
-        <v>344.22</v>
+        <v>10808.11</v>
       </c>
       <c r="E312" s="3">
-        <v>344.22</v>
+        <v>9879.17</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -7514,441 +7613,441 @@
         <v>92</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>540</v>
+        <v>490</v>
       </c>
       <c r="D313" s="3">
-        <v>269.08999999999997</v>
+        <v>2640.58</v>
       </c>
       <c r="E313" s="3">
-        <v>269.08999999999997</v>
+        <v>1889.67</v>
       </c>
     </row>
     <row r="314" spans="1:5">
       <c r="A314" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>543</v>
+        <v>512</v>
       </c>
       <c r="D314" s="3">
-        <v>307.13</v>
+        <v>3745.59</v>
       </c>
       <c r="E314" s="3">
-        <v>25.48</v>
+        <v>3745.59</v>
       </c>
     </row>
     <row r="315" spans="1:5">
       <c r="A315" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>556</v>
+        <v>483</v>
       </c>
       <c r="D315" s="3">
-        <v>137.36000000000001</v>
+        <v>1138.77</v>
       </c>
       <c r="E315" s="3">
-        <v>137.36000000000001</v>
+        <v>1138.77</v>
       </c>
     </row>
     <row r="316" spans="1:5">
       <c r="A316" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>597</v>
+        <v>623</v>
       </c>
       <c r="D316" s="3">
-        <v>112.29</v>
+        <v>1217.72</v>
       </c>
       <c r="E316" s="3">
-        <v>112.29</v>
+        <v>1217.72</v>
       </c>
     </row>
     <row r="317" spans="1:5">
       <c r="A317" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="D317" s="3">
-        <v>190.03</v>
+        <v>706.5</v>
       </c>
       <c r="E317" s="3">
-        <v>190.03</v>
+        <v>706.5</v>
       </c>
     </row>
     <row r="318" spans="1:5">
       <c r="A318" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="D318" s="3">
-        <v>353.81</v>
+        <v>1414.7</v>
       </c>
       <c r="E318" s="3">
-        <v>353.81</v>
+        <v>1414.7</v>
       </c>
     </row>
     <row r="319" spans="1:5">
       <c r="A319" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="D319" s="3">
-        <v>-68.67</v>
+        <v>1262.69</v>
       </c>
       <c r="E319" s="3">
-        <v>-68.67</v>
+        <v>1262.69</v>
       </c>
     </row>
     <row r="320" spans="1:5">
       <c r="A320" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>541</v>
+        <v>624</v>
       </c>
       <c r="D320" s="3">
-        <v>221.9</v>
+        <v>318.69</v>
       </c>
       <c r="E320" s="3">
-        <v>221.9</v>
+        <v>318.69</v>
       </c>
     </row>
     <row r="321" spans="1:5">
       <c r="A321" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>492</v>
+        <v>624</v>
       </c>
       <c r="D321" s="3">
-        <v>277.12</v>
+        <v>501.26</v>
       </c>
       <c r="E321" s="3">
-        <v>277.12</v>
+        <v>501.26</v>
       </c>
     </row>
     <row r="322" spans="1:5">
       <c r="A322" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>598</v>
+        <v>625</v>
       </c>
       <c r="D322" s="3">
-        <v>442.02</v>
+        <v>211.45</v>
       </c>
       <c r="E322" s="3">
-        <v>442.02</v>
+        <v>211.45</v>
       </c>
     </row>
     <row r="323" spans="1:5">
       <c r="A323" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>478</v>
+        <v>626</v>
       </c>
       <c r="D323" s="3">
-        <v>556.46</v>
+        <v>92.34</v>
       </c>
       <c r="E323" s="3">
-        <v>556.46</v>
+        <v>92.34</v>
       </c>
     </row>
     <row r="324" spans="1:5">
       <c r="A324" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>462</v>
+        <v>627</v>
       </c>
       <c r="D324" s="3">
-        <v>706.71</v>
+        <v>829.15</v>
       </c>
       <c r="E324" s="3">
-        <v>706.71</v>
+        <v>264.02999999999997</v>
       </c>
     </row>
     <row r="325" spans="1:5">
       <c r="A325" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>453</v>
+        <v>627</v>
       </c>
       <c r="D325" s="3">
-        <v>188.76</v>
+        <v>569.84</v>
       </c>
       <c r="E325" s="3">
-        <v>188.76</v>
+        <v>569.84</v>
       </c>
     </row>
     <row r="326" spans="1:5">
       <c r="A326" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>599</v>
+        <v>549</v>
       </c>
       <c r="D326" s="3">
-        <v>940.25</v>
+        <v>10514.78</v>
       </c>
       <c r="E326" s="3">
-        <v>940.25</v>
+        <v>10514.78</v>
       </c>
     </row>
     <row r="327" spans="1:5">
       <c r="A327" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>600</v>
+        <v>559</v>
       </c>
       <c r="D327" s="3">
-        <v>798.91</v>
+        <v>1469.88</v>
       </c>
       <c r="E327" s="3">
-        <v>798.91</v>
+        <v>1469.88</v>
       </c>
     </row>
     <row r="328" spans="1:5">
       <c r="A328" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>555</v>
+        <v>628</v>
       </c>
       <c r="D328" s="3">
-        <v>5748.89</v>
+        <v>343.39</v>
       </c>
       <c r="E328" s="3">
-        <v>5748.89</v>
+        <v>343.39</v>
       </c>
     </row>
     <row r="329" spans="1:5">
       <c r="A329" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>566</v>
+        <v>629</v>
       </c>
       <c r="D329" s="3">
-        <v>1213.6300000000001</v>
+        <v>344.22</v>
       </c>
       <c r="E329" s="3">
-        <v>1213.6300000000001</v>
+        <v>344.22</v>
       </c>
     </row>
     <row r="330" spans="1:5">
       <c r="A330" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>601</v>
+        <v>572</v>
       </c>
       <c r="D330" s="3">
-        <v>467.36</v>
+        <v>269.08999999999997</v>
       </c>
       <c r="E330" s="3">
-        <v>9.48</v>
+        <v>269.08999999999997</v>
       </c>
     </row>
     <row r="331" spans="1:5">
       <c r="A331" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>602</v>
+        <v>575</v>
       </c>
       <c r="D331" s="3">
-        <v>440.46</v>
+        <v>307.13</v>
       </c>
       <c r="E331" s="3">
-        <v>436.54</v>
+        <v>25.48</v>
       </c>
     </row>
     <row r="332" spans="1:5">
       <c r="A332" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>487</v>
+        <v>587</v>
       </c>
       <c r="D332" s="3">
-        <v>531.07000000000005</v>
+        <v>137.36000000000001</v>
       </c>
       <c r="E332" s="3">
-        <v>531.07000000000005</v>
+        <v>137.36000000000001</v>
       </c>
     </row>
     <row r="333" spans="1:5">
       <c r="A333" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>493</v>
+        <v>630</v>
       </c>
       <c r="D333" s="3">
-        <v>1269.68</v>
+        <v>112.29</v>
       </c>
       <c r="E333" s="3">
-        <v>1269.68</v>
+        <v>112.29</v>
       </c>
     </row>
     <row r="334" spans="1:5">
       <c r="A334" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>488</v>
+        <v>522</v>
       </c>
       <c r="D334" s="3">
-        <v>2070.84</v>
+        <v>190.03</v>
       </c>
       <c r="E334" s="3">
-        <v>2070.84</v>
+        <v>190.03</v>
       </c>
     </row>
     <row r="335" spans="1:5">
       <c r="A335" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="D335" s="3">
-        <v>2696.18</v>
+        <v>353.81</v>
       </c>
       <c r="E335" s="3">
-        <v>2696.18</v>
+        <v>353.81</v>
       </c>
     </row>
     <row r="336" spans="1:5">
       <c r="A336" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>491</v>
+        <v>514</v>
       </c>
       <c r="D336" s="3">
-        <v>1814.31</v>
+        <v>-68.67</v>
       </c>
       <c r="E336" s="3">
-        <v>1803.58</v>
+        <v>-68.67</v>
       </c>
     </row>
     <row r="337" spans="1:5">
       <c r="A337" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>492</v>
+        <v>573</v>
       </c>
       <c r="D337" s="3">
-        <v>314.64999999999998</v>
+        <v>221.9</v>
       </c>
       <c r="E337" s="3">
-        <v>314.64999999999998</v>
+        <v>221.9</v>
       </c>
     </row>
     <row r="338" spans="1:5">
       <c r="A338" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>461</v>
+        <v>516</v>
       </c>
       <c r="D338" s="3">
-        <v>3607.99</v>
+        <v>277.12</v>
       </c>
       <c r="E338" s="3">
-        <v>3607.99</v>
+        <v>277.12</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -7956,16 +8055,16 @@
         <v>98</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>603</v>
+        <v>631</v>
       </c>
       <c r="D339" s="3">
-        <v>3470.57</v>
+        <v>442.02</v>
       </c>
       <c r="E339" s="3">
-        <v>10.98</v>
+        <v>442.02</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -7973,33 +8072,33 @@
         <v>99</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>604</v>
+        <v>502</v>
       </c>
       <c r="D340" s="3">
-        <v>883.75</v>
+        <v>556.46</v>
       </c>
       <c r="E340" s="3">
-        <v>314.72000000000003</v>
+        <v>556.46</v>
       </c>
     </row>
     <row r="341" spans="1:5">
       <c r="A341" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>554</v>
+        <v>485</v>
       </c>
       <c r="D341" s="3">
-        <v>887.63</v>
+        <v>706.71</v>
       </c>
       <c r="E341" s="3">
-        <v>887.63</v>
+        <v>706.71</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -8007,10 +8106,10 @@
         <v>100</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="D342" s="3">
         <v>188.76</v>
@@ -8021,36 +8120,36 @@
     </row>
     <row r="343" spans="1:5">
       <c r="A343" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>454</v>
+        <v>632</v>
       </c>
       <c r="D343" s="3">
-        <v>3242.51</v>
+        <v>940.25</v>
       </c>
       <c r="E343" s="3">
-        <v>3242.51</v>
+        <v>940.25</v>
       </c>
     </row>
     <row r="344" spans="1:5">
       <c r="A344" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>458</v>
+        <v>633</v>
       </c>
       <c r="D344" s="3">
-        <v>784.52</v>
+        <v>798.91</v>
       </c>
       <c r="E344" s="3">
-        <v>775.48</v>
+        <v>798.91</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -8058,16 +8157,16 @@
         <v>101</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>605</v>
+        <v>586</v>
       </c>
       <c r="D345" s="3">
-        <v>2732.17</v>
+        <v>5748.89</v>
       </c>
       <c r="E345" s="3">
-        <v>1732.17</v>
+        <v>5748.89</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -8075,49 +8174,338 @@
         <v>101</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="D346" s="3">
-        <v>956.4</v>
+        <v>1213.6300000000001</v>
       </c>
       <c r="E346" s="3">
-        <v>956.4</v>
+        <v>1213.6300000000001</v>
       </c>
     </row>
     <row r="347" spans="1:5">
       <c r="A347" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>481</v>
+        <v>634</v>
       </c>
       <c r="D347" s="3">
-        <v>526.86</v>
+        <v>467.36</v>
       </c>
       <c r="E347" s="3">
-        <v>505.21</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="348" spans="1:5">
       <c r="A348" t="s">
+        <v>102</v>
+      </c>
+      <c r="B348" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C348" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D348" s="3">
+        <v>440.46</v>
+      </c>
+      <c r="E348" s="3">
+        <v>436.54</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" t="s">
         <v>103</v>
       </c>
-      <c r="B348" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="C348" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="D348" s="3">
+      <c r="B349" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C349" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="D349" s="3">
+        <v>531.07000000000005</v>
+      </c>
+      <c r="E349" s="3">
+        <v>531.07000000000005</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" t="s">
+        <v>103</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C350" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="D350" s="3">
+        <v>1269.68</v>
+      </c>
+      <c r="E350" s="3">
+        <v>1269.68</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" t="s">
+        <v>103</v>
+      </c>
+      <c r="B351" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C351" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D351" s="3">
+        <v>2070.84</v>
+      </c>
+      <c r="E351" s="3">
+        <v>2070.84</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" t="s">
+        <v>103</v>
+      </c>
+      <c r="B352" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C352" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="D352" s="3">
+        <v>2696.18</v>
+      </c>
+      <c r="E352" s="3">
+        <v>2696.18</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" t="s">
+        <v>103</v>
+      </c>
+      <c r="B353" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C353" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D353" s="3">
+        <v>1814.31</v>
+      </c>
+      <c r="E353" s="3">
+        <v>1803.58</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" t="s">
+        <v>103</v>
+      </c>
+      <c r="B354" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C354" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D354" s="3">
+        <v>314.64999999999998</v>
+      </c>
+      <c r="E354" s="3">
+        <v>314.64999999999998</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" t="s">
+        <v>103</v>
+      </c>
+      <c r="B355" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D355" s="3">
+        <v>3607.99</v>
+      </c>
+      <c r="E355" s="3">
+        <v>3607.99</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" t="s">
+        <v>104</v>
+      </c>
+      <c r="B356" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C356" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="D356" s="3">
+        <v>3470.57</v>
+      </c>
+      <c r="E356" s="3">
+        <v>10.98</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" t="s">
+        <v>105</v>
+      </c>
+      <c r="B357" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="D357" s="3">
+        <v>883.75</v>
+      </c>
+      <c r="E357" s="3">
+        <v>314.72000000000003</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" t="s">
+        <v>105</v>
+      </c>
+      <c r="B358" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C358" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="D358" s="3">
+        <v>887.63</v>
+      </c>
+      <c r="E358" s="3">
+        <v>887.63</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" t="s">
+        <v>106</v>
+      </c>
+      <c r="B359" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C359" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="D359" s="3">
+        <v>188.76</v>
+      </c>
+      <c r="E359" s="3">
+        <v>188.76</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" t="s">
+        <v>106</v>
+      </c>
+      <c r="B360" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C360" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D360" s="3">
+        <v>3242.51</v>
+      </c>
+      <c r="E360" s="3">
+        <v>3242.51</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" t="s">
+        <v>106</v>
+      </c>
+      <c r="B361" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C361" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="D361" s="3">
+        <v>784.52</v>
+      </c>
+      <c r="E361" s="3">
+        <v>775.48</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" t="s">
+        <v>107</v>
+      </c>
+      <c r="B362" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C362" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="D362" s="3">
+        <v>2732.17</v>
+      </c>
+      <c r="E362" s="3">
+        <v>1732.17</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" t="s">
+        <v>107</v>
+      </c>
+      <c r="B363" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C363" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="D363" s="3">
+        <v>956.4</v>
+      </c>
+      <c r="E363" s="3">
+        <v>956.4</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" t="s">
+        <v>108</v>
+      </c>
+      <c r="B364" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C364" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="D364" s="3">
+        <v>526.86</v>
+      </c>
+      <c r="E364" s="3">
+        <v>505.21</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" t="s">
+        <v>109</v>
+      </c>
+      <c r="B365" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C365" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D365" s="3">
         <v>437.15</v>
       </c>
-      <c r="E348" s="3">
+      <c r="E365" s="3">
         <v>437.15</v>
       </c>
     </row>

--- a/Facturi_Neincasate.xlsx
+++ b/Facturi_Neincasate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="700">
   <si>
     <t>Denumire client</t>
   </si>
@@ -2111,6 +2111,9 @@
   </si>
   <si>
     <t>09.01.26</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -2118,11 +2121,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="168" formatCode="########0"/>
-    <numFmt numFmtId="169" formatCode="###,###,##0.00"/>
-    <numFmt numFmtId="170" formatCode="########0.00"/>
-    <numFmt numFmtId="171" formatCode="m/d/yy;@"/>
-    <numFmt numFmtId="172" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="########0"/>
+    <numFmt numFmtId="165" formatCode="###,###,##0.00"/>
+    <numFmt numFmtId="166" formatCode="########0.00"/>
+    <numFmt numFmtId="167" formatCode="m/d/yy;@"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -2371,7 +2374,7 @@
     <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2383,28 +2386,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2738,23 +2744,24 @@
   <cols>
     <col min="1" max="1" width="8.85546875" style="1"/>
     <col min="2" max="2" width="43.5703125" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.85546875" style="1"/>
+    <col min="3" max="6" width="8.85546875" style="13"/>
+    <col min="7" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2765,16 +2772,16 @@
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="11">
         <v>1382.19</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="11">
         <v>1382.19</v>
       </c>
     </row>
@@ -2785,16 +2792,16 @@
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="12">
         <v>970.57</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="12">
         <v>970.57</v>
       </c>
     </row>
@@ -2805,16 +2812,16 @@
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="12">
         <v>593.46</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="12">
         <v>593.46</v>
       </c>
     </row>
@@ -2825,16 +2832,16 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="12">
         <v>523.6</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="12">
         <v>523.6</v>
       </c>
     </row>
@@ -2845,16 +2852,16 @@
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="12">
         <v>524.65</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="12">
         <v>524.65</v>
       </c>
     </row>
@@ -2865,16 +2872,16 @@
       <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="11">
         <v>1536.44</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="11">
         <v>1536.44</v>
       </c>
     </row>
@@ -2885,16 +2892,16 @@
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="11">
         <v>2508.38</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="11">
         <v>2508.38</v>
       </c>
     </row>
@@ -2905,16 +2912,16 @@
       <c r="B9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="12">
         <v>483.88</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="12">
         <v>483.88</v>
       </c>
     </row>
@@ -2925,16 +2932,16 @@
       <c r="B10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="12">
         <v>287.20999999999998</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="12">
         <v>287.20999999999998</v>
       </c>
     </row>
@@ -2945,16 +2952,16 @@
       <c r="B11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="11">
         <v>4412.12</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="11">
         <v>3212.12</v>
       </c>
     </row>
@@ -2965,16 +2972,16 @@
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="11">
         <v>1990.1</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="11">
         <v>1990.1</v>
       </c>
     </row>
@@ -2985,16 +2992,16 @@
       <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="12">
         <v>438.87</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="12">
         <v>438.87</v>
       </c>
     </row>
@@ -3005,16 +3012,16 @@
       <c r="B14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="12">
         <v>391.05</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="12">
         <v>391.05</v>
       </c>
     </row>
@@ -3025,16 +3032,16 @@
       <c r="B15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="11">
         <v>1147.69</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="11">
         <v>1147.69</v>
       </c>
     </row>
@@ -3045,16 +3052,16 @@
       <c r="B16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="11">
         <v>1188.72</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="11">
         <v>1188.72</v>
       </c>
     </row>
@@ -3065,16 +3072,16 @@
       <c r="B17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="12">
         <v>729.44</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="12">
         <v>729.44</v>
       </c>
     </row>
@@ -3085,16 +3092,16 @@
       <c r="B18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="12">
         <v>377.1</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="12">
         <v>227.1</v>
       </c>
     </row>
@@ -3105,16 +3112,16 @@
       <c r="B19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="12">
         <v>245.39</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="12">
         <v>245.39</v>
       </c>
     </row>
@@ -3125,16 +3132,16 @@
       <c r="B20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="11">
         <v>1098.57</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="12">
         <v>586.97</v>
       </c>
     </row>
@@ -3145,16 +3152,16 @@
       <c r="B21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="4" t="s">
         <v>36</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="12">
         <v>799.86</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="12">
         <v>799.86</v>
       </c>
     </row>
@@ -3165,16 +3172,16 @@
       <c r="B22" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="12">
         <v>96.83</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="12">
         <v>96.83</v>
       </c>
     </row>
@@ -3185,16 +3192,16 @@
       <c r="B23" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="12">
         <v>512.16999999999996</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="12">
         <v>499.33</v>
       </c>
     </row>
@@ -3205,16 +3212,16 @@
       <c r="B24" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="4" t="s">
         <v>41</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="11">
         <v>1799.67</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="11">
         <v>1799.67</v>
       </c>
     </row>
@@ -3225,16 +3232,16 @@
       <c r="B25" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="4" t="s">
         <v>43</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="12">
         <v>188.7</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="12">
         <v>177.94</v>
       </c>
     </row>
@@ -3245,16 +3252,16 @@
       <c r="B26" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="12">
         <v>393.18</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="12">
         <v>393.18</v>
       </c>
     </row>
@@ -3265,16 +3272,16 @@
       <c r="B27" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="4" t="s">
         <v>47</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="11">
         <v>1311.16</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="11">
         <v>1311.16</v>
       </c>
     </row>
@@ -3285,16 +3292,16 @@
       <c r="B28" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="12">
         <v>109.38</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="12">
         <v>109.38</v>
       </c>
     </row>
@@ -3305,16 +3312,16 @@
       <c r="B29" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="11">
         <v>1961.14</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="11">
         <v>1961.14</v>
       </c>
     </row>
@@ -3325,16 +3332,16 @@
       <c r="B30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="4" t="s">
         <v>51</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="11">
         <v>1140.42</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="11">
         <v>1140.42</v>
       </c>
     </row>
@@ -3345,16 +3352,16 @@
       <c r="B31" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="12">
         <v>607.47</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="12">
         <v>607.47</v>
       </c>
     </row>
@@ -3365,16 +3372,16 @@
       <c r="B32" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="4" t="s">
         <v>53</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="12">
         <v>581.70000000000005</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="12">
         <v>581.70000000000005</v>
       </c>
     </row>
@@ -3385,16 +3392,16 @@
       <c r="B33" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="4" t="s">
         <v>55</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="11">
         <v>8026.77</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="11">
         <v>7434.3</v>
       </c>
     </row>
@@ -3405,16 +3412,16 @@
       <c r="B34" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="11">
         <v>1001.25</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="11">
         <v>1001.25</v>
       </c>
     </row>
@@ -3425,16 +3432,16 @@
       <c r="B35" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="11">
         <v>1001.25</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="11">
         <v>1001.25</v>
       </c>
     </row>
@@ -3445,16 +3452,16 @@
       <c r="B36" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="4" t="s">
         <v>60</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E36" s="12">
         <v>686.22</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="12">
         <v>326.81</v>
       </c>
     </row>
@@ -3465,16 +3472,16 @@
       <c r="B37" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="4" t="s">
         <v>62</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="E37" s="8">
+      <c r="E37" s="12">
         <v>631.30999999999995</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="12">
         <v>631.30999999999995</v>
       </c>
     </row>
@@ -3485,16 +3492,16 @@
       <c r="B38" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="4" t="s">
         <v>63</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="11">
         <v>1260.6600000000001</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="11">
         <v>1260.6600000000001</v>
       </c>
     </row>
@@ -3505,16 +3512,16 @@
       <c r="B39" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="12">
         <v>972.6</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="12">
         <v>972.6</v>
       </c>
     </row>
@@ -3525,16 +3532,16 @@
       <c r="B40" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E40" s="8">
+      <c r="E40" s="12">
         <v>911.42</v>
       </c>
-      <c r="F40" s="8">
+      <c r="F40" s="12">
         <v>911.42</v>
       </c>
     </row>
@@ -3545,16 +3552,16 @@
       <c r="B41" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="4" t="s">
         <v>67</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="11">
         <v>1213.92</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="12">
         <v>600</v>
       </c>
     </row>
@@ -3565,16 +3572,16 @@
       <c r="B42" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E42" s="8">
+      <c r="E42" s="12">
         <v>578.86</v>
       </c>
-      <c r="F42" s="8">
+      <c r="F42" s="12">
         <v>578.86</v>
       </c>
     </row>
@@ -3585,16 +3592,16 @@
       <c r="B43" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="4" t="s">
         <v>69</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E43" s="11">
         <v>1127.1600000000001</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F43" s="11">
         <v>1127.1600000000001</v>
       </c>
     </row>
@@ -3605,16 +3612,16 @@
       <c r="B44" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="4" t="s">
         <v>71</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E44" s="8">
+      <c r="E44" s="12">
         <v>321.92</v>
       </c>
-      <c r="F44" s="8">
+      <c r="F44" s="12">
         <v>321.92</v>
       </c>
     </row>
@@ -3625,16 +3632,16 @@
       <c r="B45" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="4" t="s">
         <v>74</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E45" s="7">
+      <c r="E45" s="11">
         <v>1639.22</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="12">
         <v>82.77</v>
       </c>
     </row>
@@ -3645,16 +3652,16 @@
       <c r="B46" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E46" s="11">
         <v>1241.95</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F46" s="11">
         <v>1241.95</v>
       </c>
     </row>
@@ -3665,16 +3672,16 @@
       <c r="B47" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="4" t="s">
         <v>76</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E47" s="7">
+      <c r="E47" s="11">
         <v>1256.97</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F47" s="11">
         <v>1256.97</v>
       </c>
     </row>
@@ -3685,16 +3692,16 @@
       <c r="B48" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="4" t="s">
         <v>77</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E48" s="11">
         <v>1632.74</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F48" s="11">
         <v>1632.74</v>
       </c>
     </row>
@@ -3705,16 +3712,16 @@
       <c r="B49" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="4" t="s">
         <v>78</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E49" s="8">
+      <c r="E49" s="12">
         <v>995.61</v>
       </c>
-      <c r="F49" s="8">
+      <c r="F49" s="12">
         <v>995.61</v>
       </c>
     </row>
@@ -3725,16 +3732,16 @@
       <c r="B50" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="4" t="s">
         <v>80</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E50" s="8">
+      <c r="E50" s="12">
         <v>124.17</v>
       </c>
-      <c r="F50" s="8">
+      <c r="F50" s="12">
         <v>124.17</v>
       </c>
     </row>
@@ -3745,16 +3752,16 @@
       <c r="B51" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E51" s="8">
+      <c r="E51" s="12">
         <v>353.93</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F51" s="12">
         <v>353.93</v>
       </c>
     </row>
@@ -3765,16 +3772,16 @@
       <c r="B52" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="4" t="s">
         <v>82</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E52" s="8">
+      <c r="E52" s="12">
         <v>719.66</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="12">
         <v>719.66</v>
       </c>
     </row>
@@ -3785,16 +3792,16 @@
       <c r="B53" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="4" t="s">
         <v>83</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E53" s="8">
+      <c r="E53" s="12">
         <v>774.25</v>
       </c>
-      <c r="F53" s="8">
+      <c r="F53" s="12">
         <v>774.25</v>
       </c>
     </row>
@@ -3805,16 +3812,16 @@
       <c r="B54" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E54" s="8">
+      <c r="E54" s="12">
         <v>493.77</v>
       </c>
-      <c r="F54" s="8">
+      <c r="F54" s="12">
         <v>493.77</v>
       </c>
     </row>
@@ -3825,16 +3832,16 @@
       <c r="B55" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="4" t="s">
         <v>86</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E55" s="8">
+      <c r="E55" s="12">
         <v>566.28</v>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="12">
         <v>566.28</v>
       </c>
     </row>
@@ -3845,16 +3852,16 @@
       <c r="B56" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="4" t="s">
         <v>87</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E56" s="8">
+      <c r="E56" s="12">
         <v>991.24</v>
       </c>
-      <c r="F56" s="8">
+      <c r="F56" s="12">
         <v>991.24</v>
       </c>
     </row>
@@ -3865,16 +3872,16 @@
       <c r="B57" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="4" t="s">
         <v>88</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="E57" s="8">
+      <c r="E57" s="12">
         <v>620.66999999999996</v>
       </c>
-      <c r="F57" s="8">
+      <c r="F57" s="12">
         <v>620.66999999999996</v>
       </c>
     </row>
@@ -3885,16 +3892,16 @@
       <c r="B58" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="4" t="s">
         <v>89</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E58" s="8">
+      <c r="E58" s="12">
         <v>760.39</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F58" s="12">
         <v>760.39</v>
       </c>
     </row>
@@ -3905,16 +3912,16 @@
       <c r="B59" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E59" s="8">
+      <c r="E59" s="12">
         <v>311.89999999999998</v>
       </c>
-      <c r="F59" s="8">
+      <c r="F59" s="12">
         <v>304.39</v>
       </c>
     </row>
@@ -3925,16 +3932,16 @@
       <c r="B60" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="4" t="s">
         <v>92</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E60" s="8">
+      <c r="E60" s="12">
         <v>412.14</v>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="12">
         <v>412.14</v>
       </c>
     </row>
@@ -3945,16 +3952,16 @@
       <c r="B61" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="4" t="s">
         <v>93</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E61" s="8">
+      <c r="E61" s="12">
         <v>298.94</v>
       </c>
-      <c r="F61" s="8">
+      <c r="F61" s="12">
         <v>298.94</v>
       </c>
     </row>
@@ -3965,16 +3972,16 @@
       <c r="B62" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="4" t="s">
         <v>94</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E62" s="8">
+      <c r="E62" s="12">
         <v>303.18</v>
       </c>
-      <c r="F62" s="8">
+      <c r="F62" s="12">
         <v>303.18</v>
       </c>
     </row>
@@ -3985,16 +3992,16 @@
       <c r="B63" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="4" t="s">
         <v>96</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E63" s="8">
+      <c r="E63" s="12">
         <v>250.3</v>
       </c>
-      <c r="F63" s="8">
+      <c r="F63" s="12">
         <v>250.3</v>
       </c>
     </row>
@@ -4005,16 +4012,16 @@
       <c r="B64" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="4" t="s">
         <v>97</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E64" s="8">
+      <c r="E64" s="12">
         <v>198.84</v>
       </c>
-      <c r="F64" s="8">
+      <c r="F64" s="12">
         <v>198.84</v>
       </c>
     </row>
@@ -4025,16 +4032,16 @@
       <c r="B65" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E65" s="7">
+      <c r="E65" s="11">
         <v>4758.71</v>
       </c>
-      <c r="F65" s="8">
+      <c r="F65" s="12">
         <v>390.86</v>
       </c>
     </row>
@@ -4045,16 +4052,16 @@
       <c r="B66" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="4" t="s">
         <v>101</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E66" s="7">
+      <c r="E66" s="11">
         <v>4946.04</v>
       </c>
-      <c r="F66" s="7">
+      <c r="F66" s="11">
         <v>4946.04</v>
       </c>
     </row>
@@ -4065,16 +4072,16 @@
       <c r="B67" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="4" t="s">
         <v>102</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E67" s="7">
+      <c r="E67" s="11">
         <v>3164.86</v>
       </c>
-      <c r="F67" s="7">
+      <c r="F67" s="11">
         <v>3164.86</v>
       </c>
     </row>
@@ -4085,16 +4092,16 @@
       <c r="B68" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="4" t="s">
         <v>103</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E68" s="7">
+      <c r="E68" s="11">
         <v>2018.53</v>
       </c>
-      <c r="F68" s="7">
+      <c r="F68" s="11">
         <v>2018.53</v>
       </c>
     </row>
@@ -4105,16 +4112,16 @@
       <c r="B69" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="4" t="s">
         <v>105</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E69" s="8">
+      <c r="E69" s="12">
         <v>149.36000000000001</v>
       </c>
-      <c r="F69" s="8">
+      <c r="F69" s="12">
         <v>149.36000000000001</v>
       </c>
     </row>
@@ -4125,16 +4132,16 @@
       <c r="B70" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="4" t="s">
         <v>107</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="E70" s="7">
+      <c r="E70" s="11">
         <v>1045.26</v>
       </c>
-      <c r="F70" s="7">
+      <c r="F70" s="11">
         <v>1045.26</v>
       </c>
     </row>
@@ -4145,16 +4152,16 @@
       <c r="B71" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="4" t="s">
         <v>108</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E71" s="8">
+      <c r="E71" s="12">
         <v>65.459999999999994</v>
       </c>
-      <c r="F71" s="8">
+      <c r="F71" s="12">
         <v>65.459999999999994</v>
       </c>
     </row>
@@ -4165,16 +4172,16 @@
       <c r="B72" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="4" t="s">
         <v>111</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E72" s="7">
+      <c r="E72" s="11">
         <v>1541.08</v>
       </c>
-      <c r="F72" s="8">
+      <c r="F72" s="12">
         <v>340.18</v>
       </c>
     </row>
@@ -4185,16 +4192,16 @@
       <c r="B73" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="4" t="s">
         <v>113</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="E73" s="8">
+      <c r="E73" s="12">
         <v>334.17</v>
       </c>
-      <c r="F73" s="8">
+      <c r="F73" s="12">
         <v>334.17</v>
       </c>
     </row>
@@ -4205,16 +4212,16 @@
       <c r="B74" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="4" t="s">
         <v>114</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="E74" s="8">
+      <c r="E74" s="12">
         <v>239.26</v>
       </c>
-      <c r="F74" s="8">
+      <c r="F74" s="12">
         <v>239.26</v>
       </c>
     </row>
@@ -4225,16 +4232,16 @@
       <c r="B75" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="4" t="s">
         <v>115</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="E75" s="8">
+      <c r="E75" s="12">
         <v>490.77</v>
       </c>
-      <c r="F75" s="8">
+      <c r="F75" s="12">
         <v>490.77</v>
       </c>
     </row>
@@ -4245,16 +4252,16 @@
       <c r="B76" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="4" t="s">
         <v>116</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E76" s="8">
+      <c r="E76" s="12">
         <v>384.88</v>
       </c>
-      <c r="F76" s="8">
+      <c r="F76" s="12">
         <v>384.88</v>
       </c>
     </row>
@@ -4265,16 +4272,16 @@
       <c r="B77" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="4" t="s">
         <v>118</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="E77" s="8">
+      <c r="E77" s="12">
         <v>541.19000000000005</v>
       </c>
-      <c r="F77" s="8">
+      <c r="F77" s="12">
         <v>541.19000000000005</v>
       </c>
     </row>
@@ -4285,16 +4292,16 @@
       <c r="B78" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="4" t="s">
         <v>119</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E78" s="8">
+      <c r="E78" s="12">
         <v>411.95</v>
       </c>
-      <c r="F78" s="8">
+      <c r="F78" s="12">
         <v>411.95</v>
       </c>
     </row>
@@ -4305,16 +4312,16 @@
       <c r="B79" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="4" t="s">
         <v>121</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E79" s="8">
+      <c r="E79" s="12">
         <v>363.47</v>
       </c>
-      <c r="F79" s="8">
+      <c r="F79" s="12">
         <v>363.47</v>
       </c>
     </row>
@@ -4325,16 +4332,16 @@
       <c r="B80" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="4" t="s">
         <v>123</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E80" s="7">
+      <c r="E80" s="11">
         <v>-1186.45</v>
       </c>
-      <c r="F80" s="7">
+      <c r="F80" s="11">
         <v>-1186.45</v>
       </c>
     </row>
@@ -4345,16 +4352,16 @@
       <c r="B81" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="4" t="s">
         <v>126</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E81" s="8">
+      <c r="E81" s="12">
         <v>952.17</v>
       </c>
-      <c r="F81" s="8">
+      <c r="F81" s="12">
         <v>952.17</v>
       </c>
     </row>
@@ -4365,16 +4372,16 @@
       <c r="B82" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E82" s="7">
+      <c r="E82" s="11">
         <v>1019.52</v>
       </c>
-      <c r="F82" s="7">
+      <c r="F82" s="11">
         <v>1000</v>
       </c>
     </row>
@@ -4385,16 +4392,16 @@
       <c r="B83" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="4" t="s">
         <v>130</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E83" s="8">
+      <c r="E83" s="12">
         <v>842.01</v>
       </c>
-      <c r="F83" s="8">
+      <c r="F83" s="12">
         <v>842.01</v>
       </c>
     </row>
@@ -4405,16 +4412,16 @@
       <c r="B84" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="4" t="s">
         <v>132</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E84" s="8">
+      <c r="E84" s="12">
         <v>777.09</v>
       </c>
-      <c r="F84" s="8">
+      <c r="F84" s="12">
         <v>777.09</v>
       </c>
     </row>
@@ -4425,16 +4432,16 @@
       <c r="B85" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E85" s="7">
+      <c r="E85" s="11">
         <v>2416.3200000000002</v>
       </c>
-      <c r="F85" s="7">
+      <c r="F85" s="11">
         <v>2416.3200000000002</v>
       </c>
     </row>
@@ -4445,16 +4452,16 @@
       <c r="B86" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E86" s="7">
+      <c r="E86" s="11">
         <v>1483.41</v>
       </c>
-      <c r="F86" s="7">
+      <c r="F86" s="11">
         <v>1483.41</v>
       </c>
     </row>
@@ -4465,16 +4472,16 @@
       <c r="B87" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="4" t="s">
         <v>138</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E87" s="8">
+      <c r="E87" s="12">
         <v>568.25</v>
       </c>
-      <c r="F87" s="8">
+      <c r="F87" s="12">
         <v>568.25</v>
       </c>
     </row>
@@ -4485,16 +4492,16 @@
       <c r="B88" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="4" t="s">
         <v>140</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E88" s="7">
+      <c r="E88" s="11">
         <v>1521.12</v>
       </c>
-      <c r="F88" s="7">
+      <c r="F88" s="11">
         <v>1244.72</v>
       </c>
     </row>
@@ -4505,16 +4512,16 @@
       <c r="B89" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="4" t="s">
         <v>141</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E89" s="8">
+      <c r="E89" s="12">
         <v>890.95</v>
       </c>
-      <c r="F89" s="8">
+      <c r="F89" s="12">
         <v>890.95</v>
       </c>
     </row>
@@ -4525,16 +4532,16 @@
       <c r="B90" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="4" t="s">
         <v>142</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="E90" s="8">
+      <c r="E90" s="12">
         <v>418.2</v>
       </c>
-      <c r="F90" s="8">
+      <c r="F90" s="12">
         <v>418.2</v>
       </c>
     </row>
@@ -4545,16 +4552,16 @@
       <c r="B91" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="4" t="s">
         <v>144</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E91" s="7">
+      <c r="E91" s="11">
         <v>4445.34</v>
       </c>
-      <c r="F91" s="7">
+      <c r="F91" s="11">
         <v>4445.34</v>
       </c>
     </row>
@@ -4565,16 +4572,16 @@
       <c r="B92" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="4" t="s">
         <v>145</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E92" s="7">
+      <c r="E92" s="11">
         <v>7737.85</v>
       </c>
-      <c r="F92" s="7">
+      <c r="F92" s="11">
         <v>7737.85</v>
       </c>
     </row>
@@ -4585,16 +4592,16 @@
       <c r="B93" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="4" t="s">
         <v>147</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="E93" s="7">
+      <c r="E93" s="11">
         <v>5379.19</v>
       </c>
-      <c r="F93" s="7">
+      <c r="F93" s="11">
         <v>5346.27</v>
       </c>
     </row>
@@ -4605,16 +4612,16 @@
       <c r="B94" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="4" t="s">
         <v>149</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="E94" s="8">
+      <c r="E94" s="12">
         <v>301.58</v>
       </c>
-      <c r="F94" s="8">
+      <c r="F94" s="12">
         <v>301.58</v>
       </c>
     </row>
@@ -4625,16 +4632,16 @@
       <c r="B95" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="4" t="s">
         <v>151</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E95" s="8">
+      <c r="E95" s="12">
         <v>428.78</v>
       </c>
-      <c r="F95" s="8">
+      <c r="F95" s="12">
         <v>428.78</v>
       </c>
     </row>
@@ -4645,16 +4652,16 @@
       <c r="B96" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="4" t="s">
         <v>153</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E96" s="7">
+      <c r="E96" s="11">
         <v>5152.92</v>
       </c>
-      <c r="F96" s="7">
+      <c r="F96" s="11">
         <v>5152.92</v>
       </c>
     </row>
@@ -4665,16 +4672,16 @@
       <c r="B97" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="4" t="s">
         <v>155</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E97" s="8">
+      <c r="E97" s="12">
         <v>193.56</v>
       </c>
-      <c r="F97" s="8">
+      <c r="F97" s="12">
         <v>193.56</v>
       </c>
     </row>
@@ -4685,16 +4692,16 @@
       <c r="B98" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="4" t="s">
         <v>157</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E98" s="8">
+      <c r="E98" s="12">
         <v>274.11</v>
       </c>
-      <c r="F98" s="8">
+      <c r="F98" s="12">
         <v>274.11</v>
       </c>
     </row>
@@ -4705,16 +4712,16 @@
       <c r="B99" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="4" t="s">
         <v>159</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="E99" s="8">
+      <c r="E99" s="12">
         <v>551.74</v>
       </c>
-      <c r="F99" s="8">
+      <c r="F99" s="12">
         <v>551.74</v>
       </c>
     </row>
@@ -4725,16 +4732,16 @@
       <c r="B100" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="4" t="s">
         <v>160</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E100" s="7">
+      <c r="E100" s="11">
         <v>5257.39</v>
       </c>
-      <c r="F100" s="7">
+      <c r="F100" s="11">
         <v>5257.39</v>
       </c>
     </row>
@@ -4745,16 +4752,16 @@
       <c r="B101" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="4" t="s">
         <v>162</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E101" s="8">
+      <c r="E101" s="12">
         <v>190.03</v>
       </c>
-      <c r="F101" s="8">
+      <c r="F101" s="12">
         <v>190.03</v>
       </c>
     </row>
@@ -4765,16 +4772,16 @@
       <c r="B102" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="E102" s="7">
+      <c r="E102" s="11">
         <v>-10410.31</v>
       </c>
-      <c r="F102" s="7">
+      <c r="F102" s="11">
         <v>-10410.31</v>
       </c>
     </row>
@@ -4785,16 +4792,16 @@
       <c r="B103" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E103" s="7">
+      <c r="E103" s="11">
         <v>2059.4</v>
       </c>
-      <c r="F103" s="7">
+      <c r="F103" s="11">
         <v>2056.79</v>
       </c>
     </row>
@@ -4805,16 +4812,16 @@
       <c r="B104" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="E104" s="8">
+      <c r="E104" s="12">
         <v>684.26</v>
       </c>
-      <c r="F104" s="8">
+      <c r="F104" s="12">
         <v>684.26</v>
       </c>
     </row>
@@ -4825,16 +4832,16 @@
       <c r="B105" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="4" t="s">
         <v>169</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E105" s="8">
+      <c r="E105" s="12">
         <v>398.08</v>
       </c>
-      <c r="F105" s="8">
+      <c r="F105" s="12">
         <v>398.08</v>
       </c>
     </row>
@@ -4845,16 +4852,16 @@
       <c r="B106" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="4" t="s">
         <v>171</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E106" s="7">
+      <c r="E106" s="11">
         <v>3684.84</v>
       </c>
-      <c r="F106" s="7">
+      <c r="F106" s="11">
         <v>3684.84</v>
       </c>
     </row>
@@ -4865,16 +4872,16 @@
       <c r="B107" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="4" t="s">
         <v>172</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="E107" s="7">
+      <c r="E107" s="11">
         <v>1778.88</v>
       </c>
-      <c r="F107" s="7">
+      <c r="F107" s="11">
         <v>1778.88</v>
       </c>
     </row>
@@ -4885,16 +4892,16 @@
       <c r="B108" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="4" t="s">
         <v>174</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E108" s="7">
+      <c r="E108" s="11">
         <v>2808.73</v>
       </c>
-      <c r="F108" s="7">
+      <c r="F108" s="11">
         <v>2382.98</v>
       </c>
     </row>
@@ -4905,16 +4912,16 @@
       <c r="B109" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="4" t="s">
         <v>175</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E109" s="8">
+      <c r="E109" s="12">
         <v>284.56</v>
       </c>
-      <c r="F109" s="8">
+      <c r="F109" s="12">
         <v>284.56</v>
       </c>
     </row>
@@ -4925,16 +4932,16 @@
       <c r="B110" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="4" t="s">
         <v>176</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E110" s="8">
+      <c r="E110" s="12">
         <v>960.11</v>
       </c>
-      <c r="F110" s="8">
+      <c r="F110" s="12">
         <v>960.11</v>
       </c>
     </row>
@@ -4945,16 +4952,16 @@
       <c r="B111" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C111" s="4" t="s">
         <v>177</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E111" s="7">
+      <c r="E111" s="11">
         <v>3627.02</v>
       </c>
-      <c r="F111" s="7">
+      <c r="F111" s="11">
         <v>3627.02</v>
       </c>
     </row>
@@ -4965,16 +4972,16 @@
       <c r="B112" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="4" t="s">
         <v>179</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="E112" s="7">
+      <c r="E112" s="11">
         <v>8148.44</v>
       </c>
-      <c r="F112" s="7">
+      <c r="F112" s="11">
         <v>4148.4399999999996</v>
       </c>
     </row>
@@ -4985,16 +4992,16 @@
       <c r="B113" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="4" t="s">
         <v>180</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="E113" s="7">
+      <c r="E113" s="11">
         <v>2326.6</v>
       </c>
-      <c r="F113" s="7">
+      <c r="F113" s="11">
         <v>2326.6</v>
       </c>
     </row>
@@ -5005,16 +5012,16 @@
       <c r="B114" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="4" t="s">
         <v>183</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="E114" s="8">
+      <c r="E114" s="12">
         <v>188.76</v>
       </c>
-      <c r="F114" s="8">
+      <c r="F114" s="12">
         <v>188.76</v>
       </c>
     </row>
@@ -5025,16 +5032,16 @@
       <c r="B115" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="4" t="s">
         <v>184</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E115" s="8">
+      <c r="E115" s="12">
         <v>530</v>
       </c>
-      <c r="F115" s="8">
+      <c r="F115" s="12">
         <v>530</v>
       </c>
     </row>
@@ -5045,16 +5052,16 @@
       <c r="B116" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="4" t="s">
         <v>187</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E116" s="8">
+      <c r="E116" s="12">
         <v>730.11</v>
       </c>
-      <c r="F116" s="8">
+      <c r="F116" s="12">
         <v>287.98</v>
       </c>
     </row>
@@ -5065,16 +5072,16 @@
       <c r="B117" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="4" t="s">
         <v>189</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E117" s="8">
+      <c r="E117" s="12">
         <v>461.38</v>
       </c>
-      <c r="F117" s="8">
+      <c r="F117" s="12">
         <v>461.38</v>
       </c>
     </row>
@@ -5085,16 +5092,16 @@
       <c r="B118" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="4" t="s">
         <v>190</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E118" s="8">
+      <c r="E118" s="12">
         <v>316.27</v>
       </c>
-      <c r="F118" s="8">
+      <c r="F118" s="12">
         <v>316.27</v>
       </c>
     </row>
@@ -5105,16 +5112,16 @@
       <c r="B119" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C119" s="4" t="s">
         <v>191</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E119" s="8">
+      <c r="E119" s="12">
         <v>262.48</v>
       </c>
-      <c r="F119" s="8">
+      <c r="F119" s="12">
         <v>262.48</v>
       </c>
     </row>
@@ -5125,16 +5132,16 @@
       <c r="B120" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C120" s="4" t="s">
         <v>192</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E120" s="8">
+      <c r="E120" s="12">
         <v>219.43</v>
       </c>
-      <c r="F120" s="8">
+      <c r="F120" s="12">
         <v>219.43</v>
       </c>
     </row>
@@ -5145,16 +5152,16 @@
       <c r="B121" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="4" t="s">
         <v>193</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E121" s="8">
+      <c r="E121" s="12">
         <v>261.86</v>
       </c>
-      <c r="F121" s="8">
+      <c r="F121" s="12">
         <v>261.86</v>
       </c>
     </row>
@@ -5165,16 +5172,16 @@
       <c r="B122" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="4" t="s">
         <v>194</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E122" s="8">
+      <c r="E122" s="12">
         <v>455.71</v>
       </c>
-      <c r="F122" s="8">
+      <c r="F122" s="12">
         <v>455.71</v>
       </c>
     </row>
@@ -5185,16 +5192,16 @@
       <c r="B123" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C123" s="4" t="s">
         <v>196</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E123" s="7">
+      <c r="E123" s="11">
         <v>2520.7800000000002</v>
       </c>
-      <c r="F123" s="7">
+      <c r="F123" s="11">
         <v>2513.7600000000002</v>
       </c>
     </row>
@@ -5205,16 +5212,16 @@
       <c r="B124" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" s="4" t="s">
         <v>198</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E124" s="7">
+      <c r="E124" s="11">
         <v>2820.19</v>
       </c>
-      <c r="F124" s="7">
+      <c r="F124" s="11">
         <v>2820.19</v>
       </c>
     </row>
@@ -5225,16 +5232,16 @@
       <c r="B125" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C125" s="4" t="s">
         <v>199</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E125" s="7">
+      <c r="E125" s="11">
         <v>5665.62</v>
       </c>
-      <c r="F125" s="7">
+      <c r="F125" s="11">
         <v>5665.62</v>
       </c>
     </row>
@@ -5245,16 +5252,16 @@
       <c r="B126" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="4" t="s">
         <v>201</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E126" s="8">
+      <c r="E126" s="12">
         <v>168.97</v>
       </c>
-      <c r="F126" s="8">
+      <c r="F126" s="12">
         <v>168.97</v>
       </c>
     </row>
@@ -5265,16 +5272,16 @@
       <c r="B127" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C127" s="4" t="s">
         <v>202</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E127" s="7">
+      <c r="E127" s="11">
         <v>8875.52</v>
       </c>
-      <c r="F127" s="7">
+      <c r="F127" s="11">
         <v>8875.52</v>
       </c>
     </row>
@@ -5285,16 +5292,16 @@
       <c r="B128" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" s="4" t="s">
         <v>203</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="E128" s="8">
+      <c r="E128" s="12">
         <v>537.76</v>
       </c>
-      <c r="F128" s="8">
+      <c r="F128" s="12">
         <v>537.76</v>
       </c>
     </row>
@@ -5305,16 +5312,16 @@
       <c r="B129" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C129" s="4" t="s">
         <v>204</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E129" s="8">
+      <c r="E129" s="12">
         <v>168.97</v>
       </c>
-      <c r="F129" s="8">
+      <c r="F129" s="12">
         <v>168.97</v>
       </c>
     </row>
@@ -5325,16 +5332,16 @@
       <c r="B130" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C130" s="4" t="s">
         <v>206</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="E130" s="8">
+      <c r="E130" s="12">
         <v>341.65</v>
       </c>
-      <c r="F130" s="8">
+      <c r="F130" s="12">
         <v>340.09</v>
       </c>
     </row>
@@ -5345,16 +5352,16 @@
       <c r="B131" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C131" s="4" t="s">
         <v>208</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E131" s="8">
+      <c r="E131" s="12">
         <v>378.31</v>
       </c>
-      <c r="F131" s="8">
+      <c r="F131" s="12">
         <v>378.31</v>
       </c>
     </row>
@@ -5365,16 +5372,16 @@
       <c r="B132" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C132" s="4" t="s">
         <v>210</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E132" s="8">
+      <c r="E132" s="12">
         <v>768.27</v>
       </c>
-      <c r="F132" s="8">
+      <c r="F132" s="12">
         <v>30.48</v>
       </c>
     </row>
@@ -5385,16 +5392,16 @@
       <c r="B133" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C133" s="4" t="s">
         <v>211</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E133" s="8">
+      <c r="E133" s="12">
         <v>753.53</v>
       </c>
-      <c r="F133" s="8">
+      <c r="F133" s="12">
         <v>753.53</v>
       </c>
     </row>
@@ -5405,16 +5412,16 @@
       <c r="B134" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C134" s="4" t="s">
         <v>212</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E134" s="8">
+      <c r="E134" s="12">
         <v>206.07</v>
       </c>
-      <c r="F134" s="8">
+      <c r="F134" s="12">
         <v>206.07</v>
       </c>
     </row>
@@ -5425,16 +5432,16 @@
       <c r="B135" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" s="4" t="s">
         <v>213</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E135" s="7">
+      <c r="E135" s="11">
         <v>1224.3</v>
       </c>
-      <c r="F135" s="7">
+      <c r="F135" s="11">
         <v>1224.3</v>
       </c>
     </row>
@@ -5445,16 +5452,16 @@
       <c r="B136" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="C136" s="4" t="s">
         <v>215</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E136" s="7">
+      <c r="E136" s="11">
         <v>1533.02</v>
       </c>
-      <c r="F136" s="7">
+      <c r="F136" s="11">
         <v>1533.02</v>
       </c>
     </row>
@@ -5465,16 +5472,16 @@
       <c r="B137" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="C137" s="4" t="s">
         <v>217</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E137" s="8">
+      <c r="E137" s="12">
         <v>286.82</v>
       </c>
-      <c r="F137" s="8">
+      <c r="F137" s="12">
         <v>-36.4</v>
       </c>
     </row>
@@ -5485,16 +5492,16 @@
       <c r="B138" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="C138" s="4" t="s">
         <v>219</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E138" s="8">
+      <c r="E138" s="12">
         <v>328.58</v>
       </c>
-      <c r="F138" s="8">
+      <c r="F138" s="12">
         <v>328.58</v>
       </c>
     </row>
@@ -5505,16 +5512,16 @@
       <c r="B139" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C139" s="2" t="s">
+      <c r="C139" s="4" t="s">
         <v>220</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E139" s="8">
+      <c r="E139" s="12">
         <v>675.45</v>
       </c>
-      <c r="F139" s="8">
+      <c r="F139" s="12">
         <v>675.45</v>
       </c>
     </row>
@@ -5525,16 +5532,16 @@
       <c r="B140" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C140" s="4" t="s">
         <v>221</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E140" s="8">
+      <c r="E140" s="12">
         <v>384.17</v>
       </c>
-      <c r="F140" s="8">
+      <c r="F140" s="12">
         <v>384.17</v>
       </c>
     </row>
@@ -5545,16 +5552,16 @@
       <c r="B141" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C141" s="4" t="s">
         <v>222</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E141" s="8">
+      <c r="E141" s="12">
         <v>483.88</v>
       </c>
-      <c r="F141" s="8">
+      <c r="F141" s="12">
         <v>483.88</v>
       </c>
     </row>
@@ -5565,16 +5572,16 @@
       <c r="B142" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="C142" s="4" t="s">
         <v>223</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E142" s="8">
+      <c r="E142" s="12">
         <v>569.72</v>
       </c>
-      <c r="F142" s="8">
+      <c r="F142" s="12">
         <v>569.72</v>
       </c>
     </row>
@@ -5585,16 +5592,16 @@
       <c r="B143" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C143" s="4" t="s">
         <v>224</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E143" s="8">
+      <c r="E143" s="12">
         <v>-129.77000000000001</v>
       </c>
-      <c r="F143" s="8">
+      <c r="F143" s="12">
         <v>-129.77000000000001</v>
       </c>
     </row>
@@ -5605,16 +5612,16 @@
       <c r="B144" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C144" s="4" t="s">
         <v>227</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E144" s="7">
+      <c r="E144" s="11">
         <v>1379.09</v>
       </c>
-      <c r="F144" s="7">
+      <c r="F144" s="11">
         <v>1379.09</v>
       </c>
     </row>
@@ -5625,16 +5632,16 @@
       <c r="B145" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="4" t="s">
         <v>229</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E145" s="7">
+      <c r="E145" s="11">
         <v>1486.44</v>
       </c>
-      <c r="F145" s="7">
+      <c r="F145" s="11">
         <v>1486.44</v>
       </c>
     </row>
@@ -5645,16 +5652,16 @@
       <c r="B146" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C146" s="4" t="s">
         <v>230</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E146" s="8">
+      <c r="E146" s="12">
         <v>512.16999999999996</v>
       </c>
-      <c r="F146" s="8">
+      <c r="F146" s="12">
         <v>512.16999999999996</v>
       </c>
     </row>
@@ -5665,16 +5672,16 @@
       <c r="B147" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C147" s="4" t="s">
         <v>231</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E147" s="7">
+      <c r="E147" s="11">
         <v>1894.18</v>
       </c>
-      <c r="F147" s="7">
+      <c r="F147" s="11">
         <v>1894.18</v>
       </c>
     </row>
@@ -5685,16 +5692,16 @@
       <c r="B148" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="C148" s="4" t="s">
         <v>232</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="E148" s="8">
+      <c r="E148" s="12">
         <v>576.96</v>
       </c>
-      <c r="F148" s="8">
+      <c r="F148" s="12">
         <v>576.96</v>
       </c>
     </row>
@@ -5705,16 +5712,16 @@
       <c r="B149" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="C149" s="4" t="s">
         <v>233</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E149" s="8">
+      <c r="E149" s="12">
         <v>881.9</v>
       </c>
-      <c r="F149" s="8">
+      <c r="F149" s="12">
         <v>881.9</v>
       </c>
     </row>
@@ -5725,16 +5732,16 @@
       <c r="B150" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="C150" s="4" t="s">
         <v>235</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E150" s="7">
+      <c r="E150" s="11">
         <v>2372.73</v>
       </c>
-      <c r="F150" s="7">
+      <c r="F150" s="11">
         <v>2126.33</v>
       </c>
     </row>
@@ -5745,16 +5752,16 @@
       <c r="B151" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="C151" s="4" t="s">
         <v>237</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E151" s="8">
+      <c r="E151" s="12">
         <v>216</v>
       </c>
-      <c r="F151" s="8">
+      <c r="F151" s="12">
         <v>216</v>
       </c>
     </row>
@@ -5765,16 +5772,16 @@
       <c r="B152" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="C152" s="4" t="s">
         <v>239</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="E152" s="8">
+      <c r="E152" s="12">
         <v>251.63</v>
       </c>
-      <c r="F152" s="8">
+      <c r="F152" s="12">
         <v>251.63</v>
       </c>
     </row>
@@ -5785,16 +5792,16 @@
       <c r="B153" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C153" s="2" t="s">
+      <c r="C153" s="4" t="s">
         <v>241</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E153" s="8">
+      <c r="E153" s="12">
         <v>245.39</v>
       </c>
-      <c r="F153" s="8">
+      <c r="F153" s="12">
         <v>245.39</v>
       </c>
     </row>
@@ -5805,16 +5812,16 @@
       <c r="B154" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C154" s="4" t="s">
         <v>243</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E154" s="8">
+      <c r="E154" s="12">
         <v>458.57</v>
       </c>
-      <c r="F154" s="8">
+      <c r="F154" s="12">
         <v>395.77</v>
       </c>
     </row>
@@ -5825,16 +5832,16 @@
       <c r="B155" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C155" s="2" t="s">
+      <c r="C155" s="4" t="s">
         <v>244</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E155" s="7">
+      <c r="E155" s="11">
         <v>1551.64</v>
       </c>
-      <c r="F155" s="7">
+      <c r="F155" s="11">
         <v>1551.64</v>
       </c>
     </row>
@@ -5845,16 +5852,16 @@
       <c r="B156" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C156" s="2" t="s">
+      <c r="C156" s="4" t="s">
         <v>245</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E156" s="8">
+      <c r="E156" s="12">
         <v>328.76</v>
       </c>
-      <c r="F156" s="8">
+      <c r="F156" s="12">
         <v>328.76</v>
       </c>
     </row>
@@ -5865,16 +5872,16 @@
       <c r="B157" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C157" s="2" t="s">
+      <c r="C157" s="4" t="s">
         <v>247</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E157" s="8">
+      <c r="E157" s="12">
         <v>343.26</v>
       </c>
-      <c r="F157" s="8">
+      <c r="F157" s="12">
         <v>343.26</v>
       </c>
     </row>
@@ -5885,16 +5892,16 @@
       <c r="B158" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="C158" s="4" t="s">
         <v>248</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E158" s="8">
+      <c r="E158" s="12">
         <v>173.03</v>
       </c>
-      <c r="F158" s="8">
+      <c r="F158" s="12">
         <v>173.03</v>
       </c>
     </row>
@@ -5905,16 +5912,16 @@
       <c r="B159" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="C159" s="4" t="s">
         <v>249</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E159" s="7">
+      <c r="E159" s="11">
         <v>1185.02</v>
       </c>
-      <c r="F159" s="7">
+      <c r="F159" s="11">
         <v>1185.02</v>
       </c>
     </row>
@@ -5925,16 +5932,16 @@
       <c r="B160" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="C160" s="4" t="s">
         <v>250</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="E160" s="8">
+      <c r="E160" s="12">
         <v>172.87</v>
       </c>
-      <c r="F160" s="8">
+      <c r="F160" s="12">
         <v>172.87</v>
       </c>
     </row>
@@ -5945,16 +5952,16 @@
       <c r="B161" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C161" s="2" t="s">
+      <c r="C161" s="4" t="s">
         <v>252</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E161" s="8">
+      <c r="E161" s="12">
         <v>672.76</v>
       </c>
-      <c r="F161" s="8">
+      <c r="F161" s="12">
         <v>672.76</v>
       </c>
     </row>
@@ -5965,16 +5972,16 @@
       <c r="B162" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C162" s="4" t="s">
         <v>253</v>
       </c>
       <c r="D162" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="E162" s="8">
+      <c r="E162" s="12">
         <v>795.21</v>
       </c>
-      <c r="F162" s="8">
+      <c r="F162" s="12">
         <v>795.21</v>
       </c>
     </row>
@@ -5985,16 +5992,16 @@
       <c r="B163" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="C163" s="4" t="s">
         <v>254</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E163" s="8">
+      <c r="E163" s="12">
         <v>603.02</v>
       </c>
-      <c r="F163" s="8">
+      <c r="F163" s="12">
         <v>603.02</v>
       </c>
     </row>
@@ -6005,16 +6012,16 @@
       <c r="B164" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="C164" s="4" t="s">
         <v>255</v>
       </c>
       <c r="D164" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E164" s="8">
+      <c r="E164" s="12">
         <v>316.20999999999998</v>
       </c>
-      <c r="F164" s="8">
+      <c r="F164" s="12">
         <v>316.20999999999998</v>
       </c>
     </row>
@@ -6025,16 +6032,16 @@
       <c r="B165" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="C165" s="4" t="s">
         <v>257</v>
       </c>
       <c r="D165" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E165" s="7">
+      <c r="E165" s="11">
         <v>2491.89</v>
       </c>
-      <c r="F165" s="7">
+      <c r="F165" s="11">
         <v>2491.89</v>
       </c>
     </row>
@@ -6045,16 +6052,16 @@
       <c r="B166" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C166" s="2" t="s">
+      <c r="C166" s="4" t="s">
         <v>258</v>
       </c>
       <c r="D166" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E166" s="8">
+      <c r="E166" s="12">
         <v>401.14</v>
       </c>
-      <c r="F166" s="8">
+      <c r="F166" s="12">
         <v>401.14</v>
       </c>
     </row>
@@ -6065,16 +6072,16 @@
       <c r="B167" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C167" s="2" t="s">
+      <c r="C167" s="4" t="s">
         <v>259</v>
       </c>
       <c r="D167" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E167" s="8">
+      <c r="E167" s="12">
         <v>603.80999999999995</v>
       </c>
-      <c r="F167" s="8">
+      <c r="F167" s="12">
         <v>603.80999999999995</v>
       </c>
     </row>
@@ -6085,16 +6092,16 @@
       <c r="B168" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C168" s="2" t="s">
+      <c r="C168" s="4" t="s">
         <v>260</v>
       </c>
       <c r="D168" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E168" s="8">
+      <c r="E168" s="12">
         <v>401.14</v>
       </c>
-      <c r="F168" s="8">
+      <c r="F168" s="12">
         <v>401.14</v>
       </c>
     </row>
@@ -6105,16 +6112,16 @@
       <c r="B169" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C169" s="2" t="s">
+      <c r="C169" s="4" t="s">
         <v>261</v>
       </c>
       <c r="D169" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E169" s="8">
+      <c r="E169" s="12">
         <v>429.91</v>
       </c>
-      <c r="F169" s="8">
+      <c r="F169" s="12">
         <v>429.91</v>
       </c>
     </row>
@@ -6125,16 +6132,16 @@
       <c r="B170" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C170" s="2" t="s">
+      <c r="C170" s="4" t="s">
         <v>263</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="E170" s="7">
+      <c r="E170" s="11">
         <v>13080.39</v>
       </c>
-      <c r="F170" s="7">
+      <c r="F170" s="11">
         <v>3528.34</v>
       </c>
     </row>
@@ -6145,16 +6152,16 @@
       <c r="B171" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C171" s="2" t="s">
+      <c r="C171" s="4" t="s">
         <v>266</v>
       </c>
       <c r="D171" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="E171" s="7">
+      <c r="E171" s="11">
         <v>10726.46</v>
       </c>
-      <c r="F171" s="7">
+      <c r="F171" s="11">
         <v>10726.46</v>
       </c>
     </row>
@@ -6165,16 +6172,16 @@
       <c r="B172" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C172" s="2" t="s">
+      <c r="C172" s="4" t="s">
         <v>267</v>
       </c>
       <c r="D172" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E172" s="7">
+      <c r="E172" s="11">
         <v>2086.77</v>
       </c>
-      <c r="F172" s="7">
+      <c r="F172" s="11">
         <v>2086.77</v>
       </c>
     </row>
@@ -6185,16 +6192,16 @@
       <c r="B173" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C173" s="2" t="s">
+      <c r="C173" s="4" t="s">
         <v>268</v>
       </c>
       <c r="D173" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="E173" s="7">
+      <c r="E173" s="11">
         <v>1100.7</v>
       </c>
-      <c r="F173" s="7">
+      <c r="F173" s="11">
         <v>1100.7</v>
       </c>
     </row>
@@ -6205,16 +6212,16 @@
       <c r="B174" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C174" s="2" t="s">
+      <c r="C174" s="4" t="s">
         <v>269</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E174" s="7">
+      <c r="E174" s="11">
         <v>2201.4</v>
       </c>
-      <c r="F174" s="7">
+      <c r="F174" s="11">
         <v>2201.4</v>
       </c>
     </row>
@@ -6225,16 +6232,16 @@
       <c r="B175" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C175" s="2" t="s">
+      <c r="C175" s="4" t="s">
         <v>270</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E175" s="8">
+      <c r="E175" s="12">
         <v>376.95</v>
       </c>
-      <c r="F175" s="8">
+      <c r="F175" s="12">
         <v>376.95</v>
       </c>
     </row>
@@ -6245,16 +6252,16 @@
       <c r="B176" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C176" s="2" t="s">
+      <c r="C176" s="4" t="s">
         <v>271</v>
       </c>
       <c r="D176" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E176" s="8">
+      <c r="E176" s="12">
         <v>295.83</v>
       </c>
-      <c r="F176" s="8">
+      <c r="F176" s="12">
         <v>295.83</v>
       </c>
     </row>
@@ -6265,16 +6272,16 @@
       <c r="B177" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C177" s="2" t="s">
+      <c r="C177" s="4" t="s">
         <v>273</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E177" s="8">
+      <c r="E177" s="12">
         <v>178.12</v>
       </c>
-      <c r="F177" s="8">
+      <c r="F177" s="12">
         <v>172.82</v>
       </c>
     </row>
@@ -6285,16 +6292,16 @@
       <c r="B178" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C178" s="2" t="s">
+      <c r="C178" s="4" t="s">
         <v>274</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E178" s="8">
+      <c r="E178" s="12">
         <v>161.83000000000001</v>
       </c>
-      <c r="F178" s="8">
+      <c r="F178" s="12">
         <v>161.83000000000001</v>
       </c>
     </row>
@@ -6305,16 +6312,16 @@
       <c r="B179" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C179" s="2" t="s">
+      <c r="C179" s="4" t="s">
         <v>275</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E179" s="8">
+      <c r="E179" s="12">
         <v>466.44</v>
       </c>
-      <c r="F179" s="8">
+      <c r="F179" s="12">
         <v>466.44</v>
       </c>
     </row>
@@ -6325,16 +6332,16 @@
       <c r="B180" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C180" s="2" t="s">
+      <c r="C180" s="4" t="s">
         <v>276</v>
       </c>
       <c r="D180" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="E180" s="8">
+      <c r="E180" s="12">
         <v>311.14999999999998</v>
       </c>
-      <c r="F180" s="8">
+      <c r="F180" s="12">
         <v>311.14999999999998</v>
       </c>
     </row>
@@ -6345,16 +6352,16 @@
       <c r="B181" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C181" s="2" t="s">
+      <c r="C181" s="4" t="s">
         <v>277</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E181" s="8">
+      <c r="E181" s="12">
         <v>391.05</v>
       </c>
-      <c r="F181" s="8">
+      <c r="F181" s="12">
         <v>391.05</v>
       </c>
     </row>
@@ -6365,16 +6372,16 @@
       <c r="B182" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C182" s="2" t="s">
+      <c r="C182" s="4" t="s">
         <v>278</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E182" s="8">
+      <c r="E182" s="12">
         <v>418.15</v>
       </c>
-      <c r="F182" s="8">
+      <c r="F182" s="12">
         <v>418.15</v>
       </c>
     </row>
@@ -6385,16 +6392,16 @@
       <c r="B183" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C183" s="2" t="s">
+      <c r="C183" s="4" t="s">
         <v>279</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E183" s="8">
+      <c r="E183" s="12">
         <v>93.82</v>
       </c>
-      <c r="F183" s="8">
+      <c r="F183" s="12">
         <v>93.82</v>
       </c>
     </row>
@@ -6405,16 +6412,16 @@
       <c r="B184" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C184" s="2" t="s">
+      <c r="C184" s="4" t="s">
         <v>280</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="E184" s="8">
+      <c r="E184" s="12">
         <v>404.89</v>
       </c>
-      <c r="F184" s="8">
+      <c r="F184" s="12">
         <v>404.89</v>
       </c>
     </row>
@@ -6425,16 +6432,16 @@
       <c r="B185" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C185" s="2" t="s">
+      <c r="C185" s="4" t="s">
         <v>282</v>
       </c>
       <c r="D185" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="E185" s="8">
+      <c r="E185" s="12">
         <v>398.26</v>
       </c>
-      <c r="F185" s="8">
+      <c r="F185" s="12">
         <v>398.26</v>
       </c>
     </row>
@@ -6445,16 +6452,16 @@
       <c r="B186" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C186" s="2" t="s">
+      <c r="C186" s="4" t="s">
         <v>284</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E186" s="7">
+      <c r="E186" s="11">
         <v>1949.41</v>
       </c>
-      <c r="F186" s="7">
+      <c r="F186" s="11">
         <v>1583.6</v>
       </c>
     </row>
@@ -6465,16 +6472,16 @@
       <c r="B187" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C187" s="2" t="s">
+      <c r="C187" s="4" t="s">
         <v>286</v>
       </c>
       <c r="D187" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="E187" s="8">
+      <c r="E187" s="12">
         <v>356.1</v>
       </c>
-      <c r="F187" s="8">
+      <c r="F187" s="12">
         <v>356.1</v>
       </c>
     </row>
@@ -6485,16 +6492,16 @@
       <c r="B188" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C188" s="2" t="s">
+      <c r="C188" s="4" t="s">
         <v>287</v>
       </c>
       <c r="D188" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E188" s="8">
+      <c r="E188" s="12">
         <v>467.44</v>
       </c>
-      <c r="F188" s="8">
+      <c r="F188" s="12">
         <v>467.44</v>
       </c>
     </row>
@@ -6505,16 +6512,16 @@
       <c r="B189" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C189" s="2" t="s">
+      <c r="C189" s="4" t="s">
         <v>288</v>
       </c>
       <c r="D189" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E189" s="8">
+      <c r="E189" s="12">
         <v>271.20999999999998</v>
       </c>
-      <c r="F189" s="8">
+      <c r="F189" s="12">
         <v>271.20999999999998</v>
       </c>
     </row>
@@ -6525,16 +6532,16 @@
       <c r="B190" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C190" s="2" t="s">
+      <c r="C190" s="4" t="s">
         <v>290</v>
       </c>
       <c r="D190" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E190" s="7">
+      <c r="E190" s="11">
         <v>3153.65</v>
       </c>
-      <c r="F190" s="7">
+      <c r="F190" s="11">
         <v>3153.65</v>
       </c>
     </row>
@@ -6545,16 +6552,16 @@
       <c r="B191" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C191" s="2" t="s">
+      <c r="C191" s="4" t="s">
         <v>291</v>
       </c>
       <c r="D191" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E191" s="7">
+      <c r="E191" s="11">
         <v>2741.2</v>
       </c>
-      <c r="F191" s="7">
+      <c r="F191" s="11">
         <v>2741.2</v>
       </c>
     </row>
@@ -6565,16 +6572,16 @@
       <c r="B192" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C192" s="2" t="s">
+      <c r="C192" s="4" t="s">
         <v>292</v>
       </c>
       <c r="D192" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E192" s="8">
+      <c r="E192" s="12">
         <v>734.31</v>
       </c>
-      <c r="F192" s="8">
+      <c r="F192" s="12">
         <v>734.31</v>
       </c>
     </row>
@@ -6585,16 +6592,16 @@
       <c r="B193" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C193" s="2" t="s">
+      <c r="C193" s="4" t="s">
         <v>293</v>
       </c>
       <c r="D193" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E193" s="7">
+      <c r="E193" s="11">
         <v>2820.19</v>
       </c>
-      <c r="F193" s="7">
+      <c r="F193" s="11">
         <v>2820.19</v>
       </c>
     </row>
@@ -6605,16 +6612,16 @@
       <c r="B194" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C194" s="2" t="s">
+      <c r="C194" s="4" t="s">
         <v>294</v>
       </c>
       <c r="D194" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E194" s="7">
+      <c r="E194" s="11">
         <v>2741.2</v>
       </c>
-      <c r="F194" s="7">
+      <c r="F194" s="11">
         <v>2741.2</v>
       </c>
     </row>
@@ -6625,16 +6632,16 @@
       <c r="B195" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C195" s="2" t="s">
+      <c r="C195" s="4" t="s">
         <v>296</v>
       </c>
       <c r="D195" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="E195" s="7">
+      <c r="E195" s="11">
         <v>3744.87</v>
       </c>
-      <c r="F195" s="7">
+      <c r="F195" s="11">
         <v>3744.87</v>
       </c>
     </row>
@@ -6645,16 +6652,16 @@
       <c r="B196" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C196" s="2" t="s">
+      <c r="C196" s="4" t="s">
         <v>297</v>
       </c>
       <c r="D196" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E196" s="8">
+      <c r="E196" s="12">
         <v>960.45</v>
       </c>
-      <c r="F196" s="8">
+      <c r="F196" s="12">
         <v>960.45</v>
       </c>
     </row>
@@ -6665,16 +6672,16 @@
       <c r="B197" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C197" s="2" t="s">
+      <c r="C197" s="4" t="s">
         <v>299</v>
       </c>
       <c r="D197" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E197" s="8">
+      <c r="E197" s="12">
         <v>836.17</v>
       </c>
-      <c r="F197" s="8">
+      <c r="F197" s="12">
         <v>836.17</v>
       </c>
     </row>
@@ -6685,16 +6692,16 @@
       <c r="B198" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C198" s="2" t="s">
+      <c r="C198" s="4" t="s">
         <v>300</v>
       </c>
       <c r="D198" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E198" s="8">
+      <c r="E198" s="12">
         <v>738.85</v>
       </c>
-      <c r="F198" s="8">
+      <c r="F198" s="12">
         <v>738.85</v>
       </c>
     </row>
@@ -6705,16 +6712,16 @@
       <c r="B199" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C199" s="2" t="s">
+      <c r="C199" s="4" t="s">
         <v>302</v>
       </c>
       <c r="D199" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="E199" s="7">
+      <c r="E199" s="11">
         <v>10514.78</v>
       </c>
-      <c r="F199" s="7">
+      <c r="F199" s="11">
         <v>5514.78</v>
       </c>
     </row>
@@ -6725,16 +6732,16 @@
       <c r="B200" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C200" s="2" t="s">
+      <c r="C200" s="4" t="s">
         <v>303</v>
       </c>
       <c r="D200" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="E200" s="7">
+      <c r="E200" s="11">
         <v>1142.45</v>
       </c>
-      <c r="F200" s="7">
+      <c r="F200" s="11">
         <v>1142.45</v>
       </c>
     </row>
@@ -6745,16 +6752,16 @@
       <c r="B201" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C201" s="2" t="s">
+      <c r="C201" s="4" t="s">
         <v>305</v>
       </c>
       <c r="D201" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="E201" s="8">
+      <c r="E201" s="12">
         <v>311.89999999999998</v>
       </c>
-      <c r="F201" s="8">
+      <c r="F201" s="12">
         <v>309.94</v>
       </c>
     </row>
@@ -6765,16 +6772,16 @@
       <c r="B202" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C202" s="2" t="s">
+      <c r="C202" s="4" t="s">
         <v>306</v>
       </c>
       <c r="D202" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="E202" s="8">
+      <c r="E202" s="12">
         <v>360.13</v>
       </c>
-      <c r="F202" s="8">
+      <c r="F202" s="12">
         <v>360.13</v>
       </c>
     </row>
@@ -6785,16 +6792,16 @@
       <c r="B203" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C203" s="2" t="s">
+      <c r="C203" s="4" t="s">
         <v>308</v>
       </c>
       <c r="D203" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E203" s="8">
+      <c r="E203" s="12">
         <v>419.75</v>
       </c>
-      <c r="F203" s="8">
+      <c r="F203" s="12">
         <v>419.75</v>
       </c>
     </row>
@@ -6805,16 +6812,16 @@
       <c r="B204" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C204" s="2" t="s">
+      <c r="C204" s="4" t="s">
         <v>309</v>
       </c>
       <c r="D204" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="E204" s="8">
+      <c r="E204" s="12">
         <v>316.56</v>
       </c>
-      <c r="F204" s="8">
+      <c r="F204" s="12">
         <v>316.56</v>
       </c>
     </row>
@@ -6825,16 +6832,16 @@
       <c r="B205" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C205" s="2" t="s">
+      <c r="C205" s="4" t="s">
         <v>310</v>
       </c>
       <c r="D205" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="E205" s="8">
+      <c r="E205" s="12">
         <v>537.76</v>
       </c>
-      <c r="F205" s="8">
+      <c r="F205" s="12">
         <v>537.76</v>
       </c>
     </row>
@@ -6845,16 +6852,16 @@
       <c r="B206" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C206" s="2" t="s">
+      <c r="C206" s="4" t="s">
         <v>313</v>
       </c>
       <c r="D206" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E206" s="8">
+      <c r="E206" s="12">
         <v>173.03</v>
       </c>
-      <c r="F206" s="8">
+      <c r="F206" s="12">
         <v>173.03</v>
       </c>
     </row>
@@ -6865,16 +6872,16 @@
       <c r="B207" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C207" s="2" t="s">
+      <c r="C207" s="4" t="s">
         <v>315</v>
       </c>
       <c r="D207" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E207" s="8">
+      <c r="E207" s="12">
         <v>266.61</v>
       </c>
-      <c r="F207" s="8">
+      <c r="F207" s="12">
         <v>266.61</v>
       </c>
     </row>
@@ -6885,16 +6892,16 @@
       <c r="B208" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C208" s="2" t="s">
+      <c r="C208" s="4" t="s">
         <v>316</v>
       </c>
       <c r="D208" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E208" s="7">
+      <c r="E208" s="11">
         <v>1263.77</v>
       </c>
-      <c r="F208" s="7">
+      <c r="F208" s="11">
         <v>1263.77</v>
       </c>
     </row>
@@ -6905,16 +6912,16 @@
       <c r="B209" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C209" s="2" t="s">
+      <c r="C209" s="4" t="s">
         <v>317</v>
       </c>
       <c r="D209" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E209" s="7">
+      <c r="E209" s="11">
         <v>1263.92</v>
       </c>
-      <c r="F209" s="7">
+      <c r="F209" s="11">
         <v>1263.92</v>
       </c>
     </row>
@@ -6925,16 +6932,16 @@
       <c r="B210" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C210" s="2" t="s">
+      <c r="C210" s="4" t="s">
         <v>318</v>
       </c>
       <c r="D210" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E210" s="8">
+      <c r="E210" s="12">
         <v>188.76</v>
       </c>
-      <c r="F210" s="8">
+      <c r="F210" s="12">
         <v>188.76</v>
       </c>
     </row>
@@ -6945,16 +6952,16 @@
       <c r="B211" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C211" s="2" t="s">
+      <c r="C211" s="4" t="s">
         <v>319</v>
       </c>
       <c r="D211" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E211" s="8">
+      <c r="E211" s="12">
         <v>323.64999999999998</v>
       </c>
-      <c r="F211" s="8">
+      <c r="F211" s="12">
         <v>323.64999999999998</v>
       </c>
     </row>
@@ -6965,16 +6972,16 @@
       <c r="B212" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="C212" s="2" t="s">
+      <c r="C212" s="4" t="s">
         <v>321</v>
       </c>
       <c r="D212" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E212" s="7">
+      <c r="E212" s="11">
         <v>1781.89</v>
       </c>
-      <c r="F212" s="7">
+      <c r="F212" s="11">
         <v>1566.69</v>
       </c>
     </row>
@@ -6985,16 +6992,16 @@
       <c r="B213" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="C213" s="2" t="s">
+      <c r="C213" s="4" t="s">
         <v>322</v>
       </c>
       <c r="D213" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="E213" s="7">
+      <c r="E213" s="11">
         <v>1170.03</v>
       </c>
-      <c r="F213" s="7">
+      <c r="F213" s="11">
         <v>1170.03</v>
       </c>
     </row>
@@ -7005,16 +7012,16 @@
       <c r="B214" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="C214" s="2" t="s">
+      <c r="C214" s="4" t="s">
         <v>323</v>
       </c>
       <c r="D214" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E214" s="7">
+      <c r="E214" s="11">
         <v>1548.06</v>
       </c>
-      <c r="F214" s="7">
+      <c r="F214" s="11">
         <v>1548.06</v>
       </c>
     </row>
@@ -7025,16 +7032,16 @@
       <c r="B215" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="C215" s="2" t="s">
+      <c r="C215" s="4" t="s">
         <v>324</v>
       </c>
       <c r="D215" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E215" s="8">
+      <c r="E215" s="12">
         <v>162.1</v>
       </c>
-      <c r="F215" s="8">
+      <c r="F215" s="12">
         <v>162.1</v>
       </c>
     </row>
@@ -7042,16 +7049,16 @@
       <c r="B216" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="C216" s="2" t="s">
+      <c r="C216" s="4" t="s">
         <v>355</v>
       </c>
       <c r="D216" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="E216" s="7">
+      <c r="E216" s="11">
         <v>1395.04</v>
       </c>
-      <c r="F216" s="8">
+      <c r="F216" s="12">
         <v>911.88</v>
       </c>
     </row>
@@ -7059,16 +7066,16 @@
       <c r="B217" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="C217" s="2" t="s">
+      <c r="C217" s="4" t="s">
         <v>357</v>
       </c>
       <c r="D217" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="E217" s="8">
+      <c r="E217" s="12">
         <v>222.3</v>
       </c>
-      <c r="F217" s="8">
+      <c r="F217" s="12">
         <v>222.3</v>
       </c>
     </row>
@@ -7076,36 +7083,36 @@
       <c r="B218" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="C218" s="2" t="s">
+      <c r="C218" s="4" t="s">
         <v>358</v>
       </c>
       <c r="D218" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E218" s="8">
+      <c r="E218" s="12">
         <v>589.88</v>
       </c>
-      <c r="F218" s="8">
+      <c r="F218" s="12">
         <v>589.88</v>
       </c>
     </row>
     <row r="219" spans="1:6">
-      <c r="A219" s="9" t="s">
+      <c r="A219" s="7" t="s">
         <v>325</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C219" s="2" t="s">
+      <c r="C219" s="4" t="s">
         <v>360</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E219" s="7">
+      <c r="E219" s="11">
         <v>5995.83</v>
       </c>
-      <c r="F219" s="7">
+      <c r="F219" s="11">
         <v>5995.83</v>
       </c>
     </row>
@@ -7113,16 +7120,16 @@
       <c r="B220" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C220" s="2" t="s">
+      <c r="C220" s="4" t="s">
         <v>362</v>
       </c>
       <c r="D220" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E220" s="8">
+      <c r="E220" s="12">
         <v>421.28</v>
       </c>
-      <c r="F220" s="8">
+      <c r="F220" s="12">
         <v>17.61</v>
       </c>
     </row>
@@ -7130,16 +7137,16 @@
       <c r="B221" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C221" s="2" t="s">
+      <c r="C221" s="4" t="s">
         <v>363</v>
       </c>
       <c r="D221" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="E221" s="8">
+      <c r="E221" s="12">
         <v>222.65</v>
       </c>
-      <c r="F221" s="8">
+      <c r="F221" s="12">
         <v>222.65</v>
       </c>
     </row>
@@ -7147,16 +7154,16 @@
       <c r="B222" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C222" s="2" t="s">
+      <c r="C222" s="4" t="s">
         <v>365</v>
       </c>
       <c r="D222" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="E222" s="8">
+      <c r="E222" s="12">
         <v>351.09</v>
       </c>
-      <c r="F222" s="8">
+      <c r="F222" s="12">
         <v>351.09</v>
       </c>
     </row>
@@ -7164,16 +7171,16 @@
       <c r="B223" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="C223" s="2" t="s">
+      <c r="C223" s="4" t="s">
         <v>367</v>
       </c>
       <c r="D223" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="E223" s="7">
+      <c r="E223" s="11">
         <v>2219.77</v>
       </c>
-      <c r="F223" s="7">
+      <c r="F223" s="11">
         <v>1719.77</v>
       </c>
     </row>
@@ -7181,16 +7188,16 @@
       <c r="B224" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="C224" s="2" t="s">
+      <c r="C224" s="4" t="s">
         <v>369</v>
       </c>
       <c r="D224" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E224" s="8">
+      <c r="E224" s="12">
         <v>838.68</v>
       </c>
-      <c r="F224" s="8">
+      <c r="F224" s="12">
         <v>838.68</v>
       </c>
     </row>
@@ -7198,16 +7205,16 @@
       <c r="B225" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="C225" s="2" t="s">
+      <c r="C225" s="4" t="s">
         <v>370</v>
       </c>
       <c r="D225" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E225" s="7">
+      <c r="E225" s="11">
         <v>3440.81</v>
       </c>
-      <c r="F225" s="7">
+      <c r="F225" s="11">
         <v>3440.81</v>
       </c>
     </row>
@@ -7215,16 +7222,16 @@
       <c r="B226" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="C226" s="2" t="s">
+      <c r="C226" s="4" t="s">
         <v>371</v>
       </c>
       <c r="D226" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="E226" s="8">
+      <c r="E226" s="12">
         <v>353.93</v>
       </c>
-      <c r="F226" s="8">
+      <c r="F226" s="12">
         <v>353.93</v>
       </c>
     </row>
@@ -7232,16 +7239,16 @@
       <c r="B227" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="C227" s="2" t="s">
+      <c r="C227" s="4" t="s">
         <v>373</v>
       </c>
       <c r="D227" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="E227" s="8">
+      <c r="E227" s="12">
         <v>750.28</v>
       </c>
-      <c r="F227" s="8">
+      <c r="F227" s="12">
         <v>750.28</v>
       </c>
     </row>
@@ -7249,16 +7256,16 @@
       <c r="B228" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="C228" s="2" t="s">
+      <c r="C228" s="4" t="s">
         <v>374</v>
       </c>
       <c r="D228" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="E228" s="8">
+      <c r="E228" s="12">
         <v>210.36</v>
       </c>
-      <c r="F228" s="8">
+      <c r="F228" s="12">
         <v>210.36</v>
       </c>
     </row>
@@ -7266,16 +7273,16 @@
       <c r="B229" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C229" s="2" t="s">
+      <c r="C229" s="4" t="s">
         <v>376</v>
       </c>
       <c r="D229" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E229" s="8">
+      <c r="E229" s="12">
         <v>377.52</v>
       </c>
-      <c r="F229" s="8">
+      <c r="F229" s="12">
         <v>377.52</v>
       </c>
     </row>
@@ -7283,16 +7290,16 @@
       <c r="B230" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C230" s="2" t="s">
+      <c r="C230" s="4" t="s">
         <v>378</v>
       </c>
       <c r="D230" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="E230" s="7">
+      <c r="E230" s="11">
         <v>1017.46</v>
       </c>
-      <c r="F230" s="8">
+      <c r="F230" s="12">
         <v>132.46</v>
       </c>
     </row>
@@ -7300,16 +7307,16 @@
       <c r="B231" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C231" s="2" t="s">
+      <c r="C231" s="4" t="s">
         <v>380</v>
       </c>
       <c r="D231" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="E231" s="8">
+      <c r="E231" s="12">
         <v>152.68</v>
       </c>
-      <c r="F231" s="8">
+      <c r="F231" s="12">
         <v>152.68</v>
       </c>
     </row>
@@ -7317,16 +7324,16 @@
       <c r="B232" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C232" s="2" t="s">
+      <c r="C232" s="4" t="s">
         <v>382</v>
       </c>
       <c r="D232" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="E232" s="8">
+      <c r="E232" s="12">
         <v>163.05000000000001</v>
       </c>
-      <c r="F232" s="8">
+      <c r="F232" s="12">
         <v>163.05000000000001</v>
       </c>
     </row>
@@ -7334,16 +7341,16 @@
       <c r="B233" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C233" s="2" t="s">
+      <c r="C233" s="4" t="s">
         <v>384</v>
       </c>
       <c r="D233" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="E233" s="8">
+      <c r="E233" s="12">
         <v>220.74</v>
       </c>
-      <c r="F233" s="8">
+      <c r="F233" s="12">
         <v>220.74</v>
       </c>
     </row>
@@ -7351,16 +7358,16 @@
       <c r="B234" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C234" s="2" t="s">
+      <c r="C234" s="4" t="s">
         <v>386</v>
       </c>
       <c r="D234" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="E234" s="8">
+      <c r="E234" s="12">
         <v>304.68</v>
       </c>
-      <c r="F234" s="8">
+      <c r="F234" s="12">
         <v>304.68</v>
       </c>
     </row>
@@ -7368,16 +7375,16 @@
       <c r="B235" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C235" s="2" t="s">
+      <c r="C235" s="4" t="s">
         <v>388</v>
       </c>
       <c r="D235" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="E235" s="8">
+      <c r="E235" s="12">
         <v>216.59</v>
       </c>
-      <c r="F235" s="8">
+      <c r="F235" s="12">
         <v>216.59</v>
       </c>
     </row>
@@ -7385,16 +7392,16 @@
       <c r="B236" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C236" s="2" t="s">
+      <c r="C236" s="4" t="s">
         <v>391</v>
       </c>
       <c r="D236" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E236" s="7">
+      <c r="E236" s="11">
         <v>3826.5</v>
       </c>
-      <c r="F236" s="7">
+      <c r="F236" s="11">
         <v>3826.5</v>
       </c>
     </row>
@@ -7402,16 +7409,16 @@
       <c r="B237" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C237" s="2" t="s">
+      <c r="C237" s="4" t="s">
         <v>393</v>
       </c>
       <c r="D237" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="E237" s="7">
+      <c r="E237" s="11">
         <v>1514.21</v>
       </c>
-      <c r="F237" s="8">
+      <c r="F237" s="12">
         <v>471</v>
       </c>
     </row>
@@ -7419,16 +7426,16 @@
       <c r="B238" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C238" s="2" t="s">
+      <c r="C238" s="4" t="s">
         <v>395</v>
       </c>
       <c r="D238" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="E238" s="7">
+      <c r="E238" s="11">
         <v>2931.42</v>
       </c>
-      <c r="F238" s="7">
+      <c r="F238" s="11">
         <v>2931.42</v>
       </c>
     </row>
@@ -7436,16 +7443,16 @@
       <c r="B239" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C239" s="2" t="s">
+      <c r="C239" s="4" t="s">
         <v>396</v>
       </c>
       <c r="D239" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E239" s="7">
+      <c r="E239" s="11">
         <v>2924.9</v>
       </c>
-      <c r="F239" s="7">
+      <c r="F239" s="11">
         <v>2924.9</v>
       </c>
     </row>
@@ -7453,16 +7460,16 @@
       <c r="B240" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C240" s="2" t="s">
+      <c r="C240" s="4" t="s">
         <v>398</v>
       </c>
       <c r="D240" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="E240" s="7">
+      <c r="E240" s="11">
         <v>7246.34</v>
       </c>
-      <c r="F240" s="7">
+      <c r="F240" s="11">
         <v>7246.34</v>
       </c>
     </row>
@@ -7470,16 +7477,16 @@
       <c r="B241" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C241" s="2" t="s">
+      <c r="C241" s="4" t="s">
         <v>400</v>
       </c>
       <c r="D241" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E241" s="8">
+      <c r="E241" s="12">
         <v>98.01</v>
       </c>
-      <c r="F241" s="8">
+      <c r="F241" s="12">
         <v>98.01</v>
       </c>
     </row>
@@ -7490,16 +7497,16 @@
       <c r="B242" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C242" s="2" t="s">
+      <c r="C242" s="4" t="s">
         <v>401</v>
       </c>
       <c r="D242" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="E242" s="7">
+      <c r="E242" s="11">
         <v>1578.01</v>
       </c>
-      <c r="F242" s="7">
+      <c r="F242" s="11">
         <v>1578.01</v>
       </c>
     </row>
@@ -7507,16 +7514,16 @@
       <c r="B243" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C243" s="2" t="s">
+      <c r="C243" s="4" t="s">
         <v>402</v>
       </c>
       <c r="D243" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="E243" s="8">
+      <c r="E243" s="12">
         <v>361.77</v>
       </c>
-      <c r="F243" s="8">
+      <c r="F243" s="12">
         <v>361.77</v>
       </c>
     </row>
@@ -7524,16 +7531,16 @@
       <c r="B244" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C244" s="2" t="s">
+      <c r="C244" s="4" t="s">
         <v>404</v>
       </c>
       <c r="D244" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E244" s="7">
+      <c r="E244" s="11">
         <v>1156.58</v>
       </c>
-      <c r="F244" s="7">
+      <c r="F244" s="11">
         <v>1156.58</v>
       </c>
     </row>
@@ -7541,16 +7548,16 @@
       <c r="B245" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C245" s="2" t="s">
+      <c r="C245" s="4" t="s">
         <v>406</v>
       </c>
       <c r="D245" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="E245" s="8">
+      <c r="E245" s="12">
         <v>741.39</v>
       </c>
-      <c r="F245" s="8">
+      <c r="F245" s="12">
         <v>71.41</v>
       </c>
     </row>
@@ -7558,16 +7565,16 @@
       <c r="B246" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C246" s="2" t="s">
+      <c r="C246" s="4" t="s">
         <v>408</v>
       </c>
       <c r="D246" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="E246" s="8">
+      <c r="E246" s="12">
         <v>491.37</v>
       </c>
-      <c r="F246" s="8">
+      <c r="F246" s="12">
         <v>491.37</v>
       </c>
     </row>
@@ -7575,16 +7582,16 @@
       <c r="B247" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C247" s="2" t="s">
+      <c r="C247" s="4" t="s">
         <v>409</v>
       </c>
       <c r="D247" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="E247" s="7">
+      <c r="E247" s="11">
         <v>1291.47</v>
       </c>
-      <c r="F247" s="7">
+      <c r="F247" s="11">
         <v>1291.47</v>
       </c>
     </row>
@@ -7592,16 +7599,16 @@
       <c r="B248" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C248" s="2" t="s">
+      <c r="C248" s="4" t="s">
         <v>410</v>
       </c>
       <c r="D248" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="E248" s="7">
+      <c r="E248" s="11">
         <v>1055.2</v>
       </c>
-      <c r="F248" s="7">
+      <c r="F248" s="11">
         <v>1055.2</v>
       </c>
     </row>
@@ -7609,16 +7616,16 @@
       <c r="B249" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C249" s="2" t="s">
+      <c r="C249" s="4" t="s">
         <v>411</v>
       </c>
       <c r="D249" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E249" s="8">
+      <c r="E249" s="12">
         <v>490.93</v>
       </c>
-      <c r="F249" s="8">
+      <c r="F249" s="12">
         <v>490.93</v>
       </c>
     </row>
@@ -7626,16 +7633,16 @@
       <c r="B250" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C250" s="2" t="s">
+      <c r="C250" s="4" t="s">
         <v>412</v>
       </c>
       <c r="D250" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="E250" s="8">
+      <c r="E250" s="12">
         <v>800.74</v>
       </c>
-      <c r="F250" s="8">
+      <c r="F250" s="12">
         <v>800.74</v>
       </c>
     </row>
@@ -7643,16 +7650,16 @@
       <c r="B251" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C251" s="2" t="s">
+      <c r="C251" s="4" t="s">
         <v>413</v>
       </c>
       <c r="D251" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="E251" s="8">
+      <c r="E251" s="12">
         <v>523.71</v>
       </c>
-      <c r="F251" s="8">
+      <c r="F251" s="12">
         <v>523.71</v>
       </c>
     </row>
@@ -7660,16 +7667,16 @@
       <c r="B252" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C252" s="2" t="s">
+      <c r="C252" s="4" t="s">
         <v>414</v>
       </c>
       <c r="D252" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E252" s="8">
+      <c r="E252" s="12">
         <v>483.88</v>
       </c>
-      <c r="F252" s="8">
+      <c r="F252" s="12">
         <v>483.88</v>
       </c>
     </row>
@@ -7677,16 +7684,16 @@
       <c r="B253" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C253" s="2" t="s">
+      <c r="C253" s="4" t="s">
         <v>415</v>
       </c>
       <c r="D253" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E253" s="8">
+      <c r="E253" s="12">
         <v>634.45000000000005</v>
       </c>
-      <c r="F253" s="8">
+      <c r="F253" s="12">
         <v>634.45000000000005</v>
       </c>
     </row>
@@ -7694,16 +7701,16 @@
       <c r="B254" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C254" s="2" t="s">
+      <c r="C254" s="4" t="s">
         <v>416</v>
       </c>
       <c r="D254" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E254" s="7">
+      <c r="E254" s="11">
         <v>1258.33</v>
       </c>
-      <c r="F254" s="7">
+      <c r="F254" s="11">
         <v>1258.33</v>
       </c>
     </row>
@@ -7711,16 +7718,16 @@
       <c r="B255" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C255" s="2" t="s">
+      <c r="C255" s="4" t="s">
         <v>417</v>
       </c>
       <c r="D255" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="E255" s="8">
+      <c r="E255" s="12">
         <v>703.97</v>
       </c>
-      <c r="F255" s="8">
+      <c r="F255" s="12">
         <v>703.97</v>
       </c>
     </row>
@@ -7728,16 +7735,16 @@
       <c r="B256" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C256" s="2" t="s">
+      <c r="C256" s="4" t="s">
         <v>418</v>
       </c>
       <c r="D256" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E256" s="8">
+      <c r="E256" s="12">
         <v>522.53</v>
       </c>
-      <c r="F256" s="8">
+      <c r="F256" s="12">
         <v>522.53</v>
       </c>
     </row>
@@ -7745,16 +7752,16 @@
       <c r="B257" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C257" s="2" t="s">
+      <c r="C257" s="4" t="s">
         <v>419</v>
       </c>
       <c r="D257" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E257" s="8">
+      <c r="E257" s="12">
         <v>268.63</v>
       </c>
-      <c r="F257" s="8">
+      <c r="F257" s="12">
         <v>268.63</v>
       </c>
     </row>
@@ -7762,16 +7769,16 @@
       <c r="B258" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="C258" s="2" t="s">
+      <c r="C258" s="4" t="s">
         <v>421</v>
       </c>
       <c r="D258" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="E258" s="7">
+      <c r="E258" s="11">
         <v>1240.21</v>
       </c>
-      <c r="F258" s="7">
+      <c r="F258" s="11">
         <v>1238.3800000000001</v>
       </c>
     </row>
@@ -7779,16 +7786,16 @@
       <c r="B259" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="C259" s="2" t="s">
+      <c r="C259" s="4" t="s">
         <v>422</v>
       </c>
       <c r="D259" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E259" s="8">
+      <c r="E259" s="12">
         <v>537.75</v>
       </c>
-      <c r="F259" s="8">
+      <c r="F259" s="12">
         <v>537.75</v>
       </c>
     </row>
@@ -7796,16 +7803,16 @@
       <c r="B260" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="C260" s="2" t="s">
+      <c r="C260" s="4" t="s">
         <v>423</v>
       </c>
       <c r="D260" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="E260" s="8">
+      <c r="E260" s="12">
         <v>377.52</v>
       </c>
-      <c r="F260" s="8">
+      <c r="F260" s="12">
         <v>377.52</v>
       </c>
     </row>
@@ -7813,16 +7820,16 @@
       <c r="B261" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="C261" s="2" t="s">
+      <c r="C261" s="4" t="s">
         <v>425</v>
       </c>
       <c r="D261" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="E261" s="8">
+      <c r="E261" s="12">
         <v>661.9</v>
       </c>
-      <c r="F261" s="8">
+      <c r="F261" s="12">
         <v>264.52999999999997</v>
       </c>
     </row>
@@ -7830,16 +7837,16 @@
       <c r="B262" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="C262" s="2" t="s">
+      <c r="C262" s="4" t="s">
         <v>427</v>
       </c>
       <c r="D262" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="E262" s="8">
+      <c r="E262" s="12">
         <v>188.76</v>
       </c>
-      <c r="F262" s="8">
+      <c r="F262" s="12">
         <v>188.76</v>
       </c>
     </row>
@@ -7847,16 +7854,16 @@
       <c r="B263" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="C263" s="2" t="s">
+      <c r="C263" s="4" t="s">
         <v>429</v>
       </c>
       <c r="D263" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="E263" s="7">
+      <c r="E263" s="11">
         <v>1603.85</v>
       </c>
-      <c r="F263" s="7">
+      <c r="F263" s="11">
         <v>1603.85</v>
       </c>
     </row>
@@ -7864,16 +7871,16 @@
       <c r="B264" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="C264" s="2" t="s">
+      <c r="C264" s="4" t="s">
         <v>431</v>
       </c>
       <c r="D264" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E264" s="8">
+      <c r="E264" s="12">
         <v>607.19000000000005</v>
       </c>
-      <c r="F264" s="8">
+      <c r="F264" s="12">
         <v>607.19000000000005</v>
       </c>
     </row>
@@ -7881,16 +7888,16 @@
       <c r="B265" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="C265" s="2" t="s">
+      <c r="C265" s="4" t="s">
         <v>432</v>
       </c>
       <c r="D265" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E265" s="8">
+      <c r="E265" s="12">
         <v>250.31</v>
       </c>
-      <c r="F265" s="8">
+      <c r="F265" s="12">
         <v>250.31</v>
       </c>
     </row>
@@ -7898,16 +7905,16 @@
       <c r="B266" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="C266" s="2" t="s">
+      <c r="C266" s="4" t="s">
         <v>433</v>
       </c>
       <c r="D266" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="E266" s="8">
+      <c r="E266" s="12">
         <v>188.76</v>
       </c>
-      <c r="F266" s="8">
+      <c r="F266" s="12">
         <v>188.76</v>
       </c>
     </row>
@@ -7915,16 +7922,16 @@
       <c r="B267" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C267" s="2" t="s">
+      <c r="C267" s="4" t="s">
         <v>435</v>
       </c>
       <c r="D267" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="E267" s="8">
+      <c r="E267" s="12">
         <v>988.66</v>
       </c>
-      <c r="F267" s="8">
+      <c r="F267" s="12">
         <v>595.57000000000005</v>
       </c>
     </row>
@@ -7932,16 +7939,16 @@
       <c r="B268" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C268" s="2" t="s">
+      <c r="C268" s="4" t="s">
         <v>436</v>
       </c>
       <c r="D268" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="E268" s="7">
+      <c r="E268" s="11">
         <v>1769.71</v>
       </c>
-      <c r="F268" s="7">
+      <c r="F268" s="11">
         <v>1769.71</v>
       </c>
     </row>
@@ -7949,16 +7956,16 @@
       <c r="B269" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C269" s="2" t="s">
+      <c r="C269" s="4" t="s">
         <v>437</v>
       </c>
       <c r="D269" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E269" s="8">
+      <c r="E269" s="12">
         <v>640.19000000000005</v>
       </c>
-      <c r="F269" s="8">
+      <c r="F269" s="12">
         <v>640.19000000000005</v>
       </c>
     </row>
@@ -7966,16 +7973,16 @@
       <c r="B270" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C270" s="2" t="s">
+      <c r="C270" s="4" t="s">
         <v>438</v>
       </c>
       <c r="D270" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="E270" s="7">
+      <c r="E270" s="11">
         <v>2376.7199999999998</v>
       </c>
-      <c r="F270" s="7">
+      <c r="F270" s="11">
         <v>2376.7199999999998</v>
       </c>
     </row>
@@ -7983,16 +7990,16 @@
       <c r="B271" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C271" s="2" t="s">
+      <c r="C271" s="4" t="s">
         <v>439</v>
       </c>
       <c r="D271" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="E271" s="7">
+      <c r="E271" s="11">
         <v>1468.04</v>
       </c>
-      <c r="F271" s="7">
+      <c r="F271" s="11">
         <v>1468.04</v>
       </c>
     </row>
@@ -8000,16 +8007,16 @@
       <c r="B272" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C272" s="2" t="s">
+      <c r="C272" s="4" t="s">
         <v>440</v>
       </c>
       <c r="D272" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="E272" s="7">
+      <c r="E272" s="11">
         <v>3705.98</v>
       </c>
-      <c r="F272" s="7">
+      <c r="F272" s="11">
         <v>3705.98</v>
       </c>
     </row>
@@ -8017,16 +8024,16 @@
       <c r="B273" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C273" s="2" t="s">
+      <c r="C273" s="4" t="s">
         <v>441</v>
       </c>
       <c r="D273" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="E273" s="8">
+      <c r="E273" s="12">
         <v>261.86</v>
       </c>
-      <c r="F273" s="8">
+      <c r="F273" s="12">
         <v>261.86</v>
       </c>
     </row>
@@ -8034,16 +8041,16 @@
       <c r="B274" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C274" s="2" t="s">
+      <c r="C274" s="4" t="s">
         <v>442</v>
       </c>
       <c r="D274" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E274" s="8">
+      <c r="E274" s="12">
         <v>772.98</v>
       </c>
-      <c r="F274" s="8">
+      <c r="F274" s="12">
         <v>772.98</v>
       </c>
     </row>
@@ -8051,16 +8058,16 @@
       <c r="B275" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C275" s="2" t="s">
+      <c r="C275" s="4" t="s">
         <v>443</v>
       </c>
       <c r="D275" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="E275" s="8">
+      <c r="E275" s="12">
         <v>731.45</v>
       </c>
-      <c r="F275" s="8">
+      <c r="F275" s="12">
         <v>731.45</v>
       </c>
     </row>
@@ -8068,16 +8075,16 @@
       <c r="B276" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C276" s="2" t="s">
+      <c r="C276" s="4" t="s">
         <v>444</v>
       </c>
       <c r="D276" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="E276" s="7">
+      <c r="E276" s="11">
         <v>1310.6199999999999</v>
       </c>
-      <c r="F276" s="7">
+      <c r="F276" s="11">
         <v>1310.6199999999999</v>
       </c>
     </row>
@@ -8085,16 +8092,16 @@
       <c r="B277" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C277" s="2" t="s">
+      <c r="C277" s="4" t="s">
         <v>445</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E277" s="8">
+      <c r="E277" s="12">
         <v>749.9</v>
       </c>
-      <c r="F277" s="8">
+      <c r="F277" s="12">
         <v>749.9</v>
       </c>
     </row>
@@ -8102,16 +8109,16 @@
       <c r="B278" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C278" s="2" t="s">
+      <c r="C278" s="4" t="s">
         <v>446</v>
       </c>
       <c r="D278" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E278" s="7">
+      <c r="E278" s="11">
         <v>1994.85</v>
       </c>
-      <c r="F278" s="7">
+      <c r="F278" s="11">
         <v>1994.85</v>
       </c>
     </row>
@@ -8119,16 +8126,16 @@
       <c r="B279" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C279" s="2" t="s">
+      <c r="C279" s="4" t="s">
         <v>447</v>
       </c>
       <c r="D279" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="E279" s="7">
+      <c r="E279" s="11">
         <v>1128.19</v>
       </c>
-      <c r="F279" s="7">
+      <c r="F279" s="11">
         <v>1018.05</v>
       </c>
     </row>
@@ -8136,16 +8143,16 @@
       <c r="B280" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C280" s="2" t="s">
+      <c r="C280" s="4" t="s">
         <v>449</v>
       </c>
       <c r="D280" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="E280" s="8">
+      <c r="E280" s="12">
         <v>162.1</v>
       </c>
-      <c r="F280" s="8">
+      <c r="F280" s="12">
         <v>162.1</v>
       </c>
     </row>
@@ -8153,16 +8160,16 @@
       <c r="B281" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C281" s="2" t="s">
+      <c r="C281" s="4" t="s">
         <v>450</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E281" s="8">
+      <c r="E281" s="12">
         <v>252.08</v>
       </c>
-      <c r="F281" s="8">
+      <c r="F281" s="12">
         <v>252.08</v>
       </c>
     </row>
@@ -8170,16 +8177,16 @@
       <c r="B282" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C282" s="2" t="s">
+      <c r="C282" s="4" t="s">
         <v>451</v>
       </c>
       <c r="D282" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="E282" s="8">
+      <c r="E282" s="12">
         <v>797.4</v>
       </c>
-      <c r="F282" s="8">
+      <c r="F282" s="12">
         <v>797.4</v>
       </c>
     </row>
@@ -8187,16 +8194,16 @@
       <c r="B283" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C283" s="2" t="s">
+      <c r="C283" s="4" t="s">
         <v>453</v>
       </c>
       <c r="D283" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="E283" s="8">
+      <c r="E283" s="12">
         <v>349.33</v>
       </c>
-      <c r="F283" s="8">
+      <c r="F283" s="12">
         <v>349.33</v>
       </c>
     </row>
@@ -8204,16 +8211,16 @@
       <c r="B284" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C284" s="2" t="s">
+      <c r="C284" s="4" t="s">
         <v>454</v>
       </c>
       <c r="D284" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E284" s="8">
+      <c r="E284" s="12">
         <v>530.57000000000005</v>
       </c>
-      <c r="F284" s="8">
+      <c r="F284" s="12">
         <v>530.57000000000005</v>
       </c>
     </row>
@@ -8221,16 +8228,16 @@
       <c r="B285" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C285" s="2" t="s">
+      <c r="C285" s="4" t="s">
         <v>455</v>
       </c>
       <c r="D285" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="E285" s="7">
+      <c r="E285" s="11">
         <v>1109.42</v>
       </c>
-      <c r="F285" s="7">
+      <c r="F285" s="11">
         <v>1109.42</v>
       </c>
     </row>
@@ -8238,16 +8245,16 @@
       <c r="B286" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C286" s="2" t="s">
+      <c r="C286" s="4" t="s">
         <v>456</v>
       </c>
       <c r="D286" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E286" s="8">
+      <c r="E286" s="12">
         <v>257.98</v>
       </c>
-      <c r="F286" s="8">
+      <c r="F286" s="12">
         <v>257.98</v>
       </c>
     </row>
@@ -8255,16 +8262,16 @@
       <c r="B287" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C287" s="2" t="s">
+      <c r="C287" s="4" t="s">
         <v>458</v>
       </c>
       <c r="D287" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="E287" s="7">
+      <c r="E287" s="11">
         <v>2644.4</v>
       </c>
-      <c r="F287" s="7">
+      <c r="F287" s="11">
         <v>2437.29</v>
       </c>
     </row>
@@ -8272,16 +8279,16 @@
       <c r="B288" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C288" s="2" t="s">
+      <c r="C288" s="4" t="s">
         <v>460</v>
       </c>
       <c r="D288" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="E288" s="8">
+      <c r="E288" s="12">
         <v>403.75</v>
       </c>
-      <c r="F288" s="8">
+      <c r="F288" s="12">
         <v>403.75</v>
       </c>
     </row>
@@ -8289,16 +8296,16 @@
       <c r="B289" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C289" s="2" t="s">
+      <c r="C289" s="4" t="s">
         <v>461</v>
       </c>
       <c r="D289" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="E289" s="8">
+      <c r="E289" s="12">
         <v>326.95</v>
       </c>
-      <c r="F289" s="8">
+      <c r="F289" s="12">
         <v>326.95</v>
       </c>
     </row>
@@ -8306,16 +8313,16 @@
       <c r="B290" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C290" s="2" t="s">
+      <c r="C290" s="4" t="s">
         <v>462</v>
       </c>
       <c r="D290" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="E290" s="8">
+      <c r="E290" s="12">
         <v>708.92</v>
       </c>
-      <c r="F290" s="8">
+      <c r="F290" s="12">
         <v>708.92</v>
       </c>
     </row>
@@ -8323,16 +8330,16 @@
       <c r="B291" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C291" s="2" t="s">
+      <c r="C291" s="4" t="s">
         <v>463</v>
       </c>
       <c r="D291" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="E291" s="8">
+      <c r="E291" s="12">
         <v>170.36</v>
       </c>
-      <c r="F291" s="8">
+      <c r="F291" s="12">
         <v>170.36</v>
       </c>
     </row>
@@ -8340,16 +8347,16 @@
       <c r="B292" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C292" s="2" t="s">
+      <c r="C292" s="4" t="s">
         <v>464</v>
       </c>
       <c r="D292" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="E292" s="8">
+      <c r="E292" s="12">
         <v>417.37</v>
       </c>
-      <c r="F292" s="8">
+      <c r="F292" s="12">
         <v>417.37</v>
       </c>
     </row>
@@ -8357,16 +8364,16 @@
       <c r="B293" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="C293" s="2" t="s">
+      <c r="C293" s="4" t="s">
         <v>466</v>
       </c>
       <c r="D293" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E293" s="7">
+      <c r="E293" s="11">
         <v>1448.37</v>
       </c>
-      <c r="F293" s="7">
+      <c r="F293" s="11">
         <v>1448.37</v>
       </c>
     </row>
@@ -8374,16 +8381,16 @@
       <c r="B294" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C294" s="2" t="s">
+      <c r="C294" s="4" t="s">
         <v>468</v>
       </c>
       <c r="D294" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="E294" s="7">
+      <c r="E294" s="11">
         <v>4795.4399999999996</v>
       </c>
-      <c r="F294" s="8">
+      <c r="F294" s="12">
         <v>498.17</v>
       </c>
     </row>
@@ -8391,16 +8398,16 @@
       <c r="B295" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C295" s="2" t="s">
+      <c r="C295" s="4" t="s">
         <v>470</v>
       </c>
       <c r="D295" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="E295" s="7">
+      <c r="E295" s="11">
         <v>1575.72</v>
       </c>
-      <c r="F295" s="7">
+      <c r="F295" s="11">
         <v>1575.72</v>
       </c>
     </row>
@@ -8408,16 +8415,16 @@
       <c r="B296" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C296" s="2" t="s">
+      <c r="C296" s="4" t="s">
         <v>471</v>
       </c>
       <c r="D296" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="E296" s="8">
+      <c r="E296" s="12">
         <v>63.48</v>
       </c>
-      <c r="F296" s="8">
+      <c r="F296" s="12">
         <v>63.48</v>
       </c>
     </row>
@@ -8425,16 +8432,16 @@
       <c r="B297" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C297" s="2" t="s">
+      <c r="C297" s="4" t="s">
         <v>473</v>
       </c>
       <c r="D297" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="E297" s="8">
+      <c r="E297" s="12">
         <v>93.8</v>
       </c>
-      <c r="F297" s="8">
+      <c r="F297" s="12">
         <v>93.8</v>
       </c>
     </row>
@@ -8442,16 +8449,16 @@
       <c r="B298" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C298" s="2" t="s">
+      <c r="C298" s="4" t="s">
         <v>475</v>
       </c>
       <c r="D298" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="E298" s="8">
+      <c r="E298" s="12">
         <v>852.76</v>
       </c>
-      <c r="F298" s="8">
+      <c r="F298" s="12">
         <v>852.76</v>
       </c>
     </row>
@@ -8459,16 +8466,16 @@
       <c r="B299" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C299" s="2" t="s">
+      <c r="C299" s="4" t="s">
         <v>476</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="E299" s="8">
+      <c r="E299" s="12">
         <v>119.58</v>
       </c>
-      <c r="F299" s="8">
+      <c r="F299" s="12">
         <v>119.58</v>
       </c>
     </row>
@@ -8476,16 +8483,16 @@
       <c r="B300" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C300" s="2" t="s">
+      <c r="C300" s="4" t="s">
         <v>478</v>
       </c>
       <c r="D300" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="E300" s="8">
+      <c r="E300" s="12">
         <v>467.32</v>
       </c>
-      <c r="F300" s="8">
+      <c r="F300" s="12">
         <v>467.32</v>
       </c>
     </row>
@@ -8493,16 +8500,16 @@
       <c r="B301" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="C301" s="2" t="s">
+      <c r="C301" s="4" t="s">
         <v>481</v>
       </c>
       <c r="D301" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E301" s="8">
+      <c r="E301" s="12">
         <v>439.87</v>
       </c>
-      <c r="F301" s="8">
+      <c r="F301" s="12">
         <v>439.87</v>
       </c>
     </row>
@@ -8510,16 +8517,16 @@
       <c r="B302" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C302" s="2" t="s">
+      <c r="C302" s="4" t="s">
         <v>483</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="E302" s="7">
+      <c r="E302" s="11">
         <v>1697.98</v>
       </c>
-      <c r="F302" s="7">
+      <c r="F302" s="11">
         <v>1614.36</v>
       </c>
     </row>
@@ -8527,16 +8534,16 @@
       <c r="B303" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C303" s="2" t="s">
+      <c r="C303" s="4" t="s">
         <v>484</v>
       </c>
       <c r="D303" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="E303" s="7">
+      <c r="E303" s="11">
         <v>1172.6099999999999</v>
       </c>
-      <c r="F303" s="7">
+      <c r="F303" s="11">
         <v>1172.6099999999999</v>
       </c>
     </row>
@@ -8544,16 +8551,16 @@
       <c r="B304" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C304" s="2" t="s">
+      <c r="C304" s="4" t="s">
         <v>485</v>
       </c>
       <c r="D304" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="E304" s="8">
+      <c r="E304" s="12">
         <v>981.7</v>
       </c>
-      <c r="F304" s="8">
+      <c r="F304" s="12">
         <v>981.7</v>
       </c>
     </row>
@@ -8561,16 +8568,16 @@
       <c r="B305" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C305" s="2" t="s">
+      <c r="C305" s="4" t="s">
         <v>486</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="E305" s="8">
+      <c r="E305" s="12">
         <v>778.34</v>
       </c>
-      <c r="F305" s="8">
+      <c r="F305" s="12">
         <v>778.34</v>
       </c>
     </row>
@@ -8578,16 +8585,16 @@
       <c r="B306" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C306" s="2" t="s">
+      <c r="C306" s="4" t="s">
         <v>487</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E306" s="7">
+      <c r="E306" s="11">
         <v>1052.3699999999999</v>
       </c>
-      <c r="F306" s="7">
+      <c r="F306" s="11">
         <v>1052.3699999999999</v>
       </c>
     </row>
@@ -8595,16 +8602,16 @@
       <c r="B307" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C307" s="2" t="s">
+      <c r="C307" s="4" t="s">
         <v>488</v>
       </c>
       <c r="D307" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="E307" s="7">
+      <c r="E307" s="11">
         <v>1352.99</v>
       </c>
-      <c r="F307" s="7">
+      <c r="F307" s="11">
         <v>1352.99</v>
       </c>
     </row>
@@ -8612,16 +8619,16 @@
       <c r="B308" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C308" s="2" t="s">
+      <c r="C308" s="4" t="s">
         <v>489</v>
       </c>
       <c r="D308" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="E308" s="8">
+      <c r="E308" s="12">
         <v>164.08</v>
       </c>
-      <c r="F308" s="8">
+      <c r="F308" s="12">
         <v>164.08</v>
       </c>
     </row>
@@ -8629,16 +8636,16 @@
       <c r="B309" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C309" s="2" t="s">
+      <c r="C309" s="4" t="s">
         <v>490</v>
       </c>
       <c r="D309" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="E309" s="8">
+      <c r="E309" s="12">
         <v>374.52</v>
       </c>
-      <c r="F309" s="8">
+      <c r="F309" s="12">
         <v>374.52</v>
       </c>
     </row>
@@ -8646,16 +8653,16 @@
       <c r="B310" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C310" s="2" t="s">
+      <c r="C310" s="4" t="s">
         <v>491</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="E310" s="7">
+      <c r="E310" s="11">
         <v>1873.63</v>
       </c>
-      <c r="F310" s="7">
+      <c r="F310" s="11">
         <v>1873.63</v>
       </c>
     </row>
@@ -8663,16 +8670,16 @@
       <c r="B311" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C311" s="2" t="s">
+      <c r="C311" s="4" t="s">
         <v>492</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="E311" s="8">
+      <c r="E311" s="12">
         <v>397.56</v>
       </c>
-      <c r="F311" s="8">
+      <c r="F311" s="12">
         <v>397.56</v>
       </c>
     </row>
@@ -8680,16 +8687,16 @@
       <c r="B312" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C312" s="2" t="s">
+      <c r="C312" s="4" t="s">
         <v>493</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E312" s="7">
+      <c r="E312" s="11">
         <v>1135.22</v>
       </c>
-      <c r="F312" s="7">
+      <c r="F312" s="11">
         <v>1135.22</v>
       </c>
     </row>
@@ -8697,16 +8704,16 @@
       <c r="B313" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C313" s="2" t="s">
+      <c r="C313" s="4" t="s">
         <v>494</v>
       </c>
       <c r="D313" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E313" s="8">
+      <c r="E313" s="12">
         <v>910.84</v>
       </c>
-      <c r="F313" s="8">
+      <c r="F313" s="12">
         <v>910.84</v>
       </c>
     </row>
@@ -8714,16 +8721,16 @@
       <c r="B314" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C314" s="2" t="s">
+      <c r="C314" s="4" t="s">
         <v>495</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="E314" s="7">
+      <c r="E314" s="11">
         <v>1313.79</v>
       </c>
-      <c r="F314" s="7">
+      <c r="F314" s="11">
         <v>1313.79</v>
       </c>
     </row>
@@ -8731,16 +8738,16 @@
       <c r="B315" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C315" s="2" t="s">
+      <c r="C315" s="4" t="s">
         <v>496</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="E315" s="8">
+      <c r="E315" s="12">
         <v>374.52</v>
       </c>
-      <c r="F315" s="8">
+      <c r="F315" s="12">
         <v>374.52</v>
       </c>
     </row>
@@ -8748,16 +8755,16 @@
       <c r="B316" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C316" s="2" t="s">
+      <c r="C316" s="4" t="s">
         <v>497</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E316" s="8">
+      <c r="E316" s="12">
         <v>633.09</v>
       </c>
-      <c r="F316" s="8">
+      <c r="F316" s="12">
         <v>633.09</v>
       </c>
     </row>
@@ -8765,16 +8772,16 @@
       <c r="B317" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C317" s="2" t="s">
+      <c r="C317" s="4" t="s">
         <v>499</v>
       </c>
       <c r="D317" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="E317" s="7">
+      <c r="E317" s="11">
         <v>1182.92</v>
       </c>
-      <c r="F317" s="8">
+      <c r="F317" s="12">
         <v>74.88</v>
       </c>
     </row>
@@ -8782,16 +8789,16 @@
       <c r="B318" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C318" s="2" t="s">
+      <c r="C318" s="4" t="s">
         <v>500</v>
       </c>
       <c r="D318" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="E318" s="7">
+      <c r="E318" s="11">
         <v>1045.79</v>
       </c>
-      <c r="F318" s="7">
+      <c r="F318" s="11">
         <v>1045.79</v>
       </c>
     </row>
@@ -8799,16 +8806,16 @@
       <c r="B319" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C319" s="2" t="s">
+      <c r="C319" s="4" t="s">
         <v>502</v>
       </c>
       <c r="D319" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="E319" s="7">
+      <c r="E319" s="11">
         <v>1170.74</v>
       </c>
-      <c r="F319" s="7">
+      <c r="F319" s="11">
         <v>1170.74</v>
       </c>
     </row>
@@ -8816,16 +8823,16 @@
       <c r="B320" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C320" s="2" t="s">
+      <c r="C320" s="4" t="s">
         <v>504</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="E320" s="7">
+      <c r="E320" s="11">
         <v>1356.94</v>
       </c>
-      <c r="F320" s="7">
+      <c r="F320" s="11">
         <v>1356.94</v>
       </c>
     </row>
@@ -8833,16 +8840,16 @@
       <c r="B321" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C321" s="2" t="s">
+      <c r="C321" s="4" t="s">
         <v>506</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="E321" s="7">
+      <c r="E321" s="11">
         <v>1873.85</v>
       </c>
-      <c r="F321" s="7">
+      <c r="F321" s="11">
         <v>1873.85</v>
       </c>
     </row>
@@ -8850,16 +8857,16 @@
       <c r="B322" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C322" s="2" t="s">
+      <c r="C322" s="4" t="s">
         <v>507</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E322" s="8">
+      <c r="E322" s="12">
         <v>188.76</v>
       </c>
-      <c r="F322" s="8">
+      <c r="F322" s="12">
         <v>188.76</v>
       </c>
     </row>
@@ -8867,16 +8874,16 @@
       <c r="B323" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C323" s="2" t="s">
+      <c r="C323" s="4" t="s">
         <v>508</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="E323" s="7">
+      <c r="E323" s="11">
         <v>1565.58</v>
       </c>
-      <c r="F323" s="7">
+      <c r="F323" s="11">
         <v>1565.58</v>
       </c>
     </row>
@@ -8884,16 +8891,16 @@
       <c r="B324" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="C324" s="2" t="s">
+      <c r="C324" s="4" t="s">
         <v>510</v>
       </c>
       <c r="D324" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E324" s="8">
+      <c r="E324" s="12">
         <v>861.4</v>
       </c>
-      <c r="F324" s="8">
+      <c r="F324" s="12">
         <v>259.48</v>
       </c>
     </row>
@@ -8901,16 +8908,16 @@
       <c r="B325" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="C325" s="2" t="s">
+      <c r="C325" s="4" t="s">
         <v>511</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="E325" s="8">
+      <c r="E325" s="12">
         <v>408.67</v>
       </c>
-      <c r="F325" s="8">
+      <c r="F325" s="12">
         <v>408.67</v>
       </c>
     </row>
@@ -8918,16 +8925,16 @@
       <c r="B326" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="C326" s="2" t="s">
+      <c r="C326" s="4" t="s">
         <v>512</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E326" s="8">
+      <c r="E326" s="12">
         <v>188.76</v>
       </c>
-      <c r="F326" s="8">
+      <c r="F326" s="12">
         <v>188.76</v>
       </c>
     </row>
@@ -8935,16 +8942,16 @@
       <c r="B327" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="C327" s="2" t="s">
+      <c r="C327" s="4" t="s">
         <v>514</v>
       </c>
       <c r="D327" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="E327" s="8">
+      <c r="E327" s="12">
         <v>648.6</v>
       </c>
-      <c r="F327" s="8">
+      <c r="F327" s="12">
         <v>632.75</v>
       </c>
     </row>
@@ -8952,16 +8959,16 @@
       <c r="B328" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="C328" s="2" t="s">
+      <c r="C328" s="4" t="s">
         <v>515</v>
       </c>
       <c r="D328" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="E328" s="8">
+      <c r="E328" s="12">
         <v>557.41999999999996</v>
       </c>
-      <c r="F328" s="8">
+      <c r="F328" s="12">
         <v>557.41999999999996</v>
       </c>
     </row>
@@ -8969,16 +8976,16 @@
       <c r="B329" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="C329" s="2" t="s">
+      <c r="C329" s="4" t="s">
         <v>517</v>
       </c>
       <c r="D329" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="E329" s="7">
+      <c r="E329" s="11">
         <v>1854.68</v>
       </c>
-      <c r="F329" s="8">
+      <c r="F329" s="12">
         <v>598.82000000000005</v>
       </c>
     </row>
@@ -8986,16 +8993,16 @@
       <c r="B330" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="C330" s="2" t="s">
+      <c r="C330" s="4" t="s">
         <v>520</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="E330" s="8">
+      <c r="E330" s="12">
         <v>188.76</v>
       </c>
-      <c r="F330" s="8">
+      <c r="F330" s="12">
         <v>188.76</v>
       </c>
     </row>
@@ -9003,16 +9010,16 @@
       <c r="B331" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="C331" s="2" t="s">
+      <c r="C331" s="4" t="s">
         <v>521</v>
       </c>
       <c r="D331" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="E331" s="8">
+      <c r="E331" s="12">
         <v>514.4</v>
       </c>
-      <c r="F331" s="8">
+      <c r="F331" s="12">
         <v>514.4</v>
       </c>
     </row>
@@ -9020,16 +9027,16 @@
       <c r="B332" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="C332" s="2" t="s">
+      <c r="C332" s="4" t="s">
         <v>522</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="E332" s="8">
+      <c r="E332" s="12">
         <v>631.80999999999995</v>
       </c>
-      <c r="F332" s="8">
+      <c r="F332" s="12">
         <v>631.80999999999995</v>
       </c>
     </row>
@@ -9037,16 +9044,16 @@
       <c r="B333" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="C333" s="2" t="s">
+      <c r="C333" s="4" t="s">
         <v>524</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E333" s="8">
+      <c r="E333" s="12">
         <v>512.16999999999996</v>
       </c>
-      <c r="F333" s="8">
+      <c r="F333" s="12">
         <v>512.16999999999996</v>
       </c>
     </row>
@@ -9054,16 +9061,16 @@
       <c r="B334" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="C334" s="2" t="s">
+      <c r="C334" s="4" t="s">
         <v>525</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E334" s="7">
+      <c r="E334" s="11">
         <v>7003.29</v>
       </c>
-      <c r="F334" s="7">
+      <c r="F334" s="11">
         <v>7003.29</v>
       </c>
     </row>
@@ -9071,16 +9078,16 @@
       <c r="B335" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="C335" s="2" t="s">
+      <c r="C335" s="4" t="s">
         <v>527</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="E335" s="8">
+      <c r="E335" s="12">
         <v>261.86</v>
       </c>
-      <c r="F335" s="8">
+      <c r="F335" s="12">
         <v>-848.73</v>
       </c>
     </row>
@@ -9088,16 +9095,16 @@
       <c r="B336" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="C336" s="2" t="s">
+      <c r="C336" s="4" t="s">
         <v>529</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="E336" s="7">
+      <c r="E336" s="11">
         <v>1578.79</v>
       </c>
-      <c r="F336" s="8">
+      <c r="F336" s="12">
         <v>487.29</v>
       </c>
     </row>
@@ -9105,16 +9112,16 @@
       <c r="B337" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="C337" s="2" t="s">
+      <c r="C337" s="4" t="s">
         <v>530</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E337" s="8">
+      <c r="E337" s="12">
         <v>949.57</v>
       </c>
-      <c r="F337" s="8">
+      <c r="F337" s="12">
         <v>949.57</v>
       </c>
     </row>
@@ -9122,16 +9129,16 @@
       <c r="B338" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="C338" s="2" t="s">
+      <c r="C338" s="4" t="s">
         <v>531</v>
       </c>
       <c r="D338" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E338" s="7">
+      <c r="E338" s="11">
         <v>2272.1799999999998</v>
       </c>
-      <c r="F338" s="7">
+      <c r="F338" s="11">
         <v>2272.1799999999998</v>
       </c>
     </row>
@@ -9139,16 +9146,16 @@
       <c r="B339" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="C339" s="2" t="s">
+      <c r="C339" s="4" t="s">
         <v>532</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="E339" s="8">
+      <c r="E339" s="12">
         <v>164.08</v>
       </c>
-      <c r="F339" s="8">
+      <c r="F339" s="12">
         <v>164.08</v>
       </c>
     </row>
@@ -9156,16 +9163,16 @@
       <c r="B340" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="C340" s="2" t="s">
+      <c r="C340" s="4" t="s">
         <v>533</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E340" s="8">
+      <c r="E340" s="12">
         <v>939.86</v>
       </c>
-      <c r="F340" s="8">
+      <c r="F340" s="12">
         <v>939.86</v>
       </c>
     </row>
@@ -9173,16 +9180,16 @@
       <c r="B341" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="C341" s="2" t="s">
+      <c r="C341" s="4" t="s">
         <v>535</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E341" s="8">
+      <c r="E341" s="12">
         <v>562.69000000000005</v>
       </c>
-      <c r="F341" s="8">
+      <c r="F341" s="12">
         <v>562.69000000000005</v>
       </c>
     </row>
@@ -9190,16 +9197,16 @@
       <c r="B342" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="C342" s="2" t="s">
+      <c r="C342" s="4" t="s">
         <v>536</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E342" s="8">
+      <c r="E342" s="12">
         <v>455.71</v>
       </c>
-      <c r="F342" s="8">
+      <c r="F342" s="12">
         <v>455.71</v>
       </c>
     </row>
@@ -9207,16 +9214,16 @@
       <c r="B343" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="C343" s="2" t="s">
+      <c r="C343" s="4" t="s">
         <v>538</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="E343" s="7">
+      <c r="E343" s="11">
         <v>6600.83</v>
       </c>
-      <c r="F343" s="7">
+      <c r="F343" s="11">
         <v>6553.85</v>
       </c>
     </row>
@@ -9224,16 +9231,16 @@
       <c r="B344" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="C344" s="2" t="s">
+      <c r="C344" s="4" t="s">
         <v>539</v>
       </c>
       <c r="D344" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="E344" s="8">
+      <c r="E344" s="12">
         <v>377.52</v>
       </c>
-      <c r="F344" s="8">
+      <c r="F344" s="12">
         <v>377.52</v>
       </c>
     </row>
@@ -9241,16 +9248,16 @@
       <c r="B345" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="C345" s="2" t="s">
+      <c r="C345" s="4" t="s">
         <v>540</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="E345" s="8">
+      <c r="E345" s="12">
         <v>188.76</v>
       </c>
-      <c r="F345" s="8">
+      <c r="F345" s="12">
         <v>188.76</v>
       </c>
     </row>
@@ -9258,16 +9265,16 @@
       <c r="B346" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="C346" s="2" t="s">
+      <c r="C346" s="4" t="s">
         <v>541</v>
       </c>
       <c r="D346" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E346" s="7">
+      <c r="E346" s="11">
         <v>6789.59</v>
       </c>
-      <c r="F346" s="7">
+      <c r="F346" s="11">
         <v>6789.59</v>
       </c>
     </row>
@@ -9275,16 +9282,16 @@
       <c r="B347" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C347" s="2" t="s">
+      <c r="C347" s="4" t="s">
         <v>543</v>
       </c>
       <c r="D347" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="E347" s="8">
+      <c r="E347" s="12">
         <v>73.14</v>
       </c>
-      <c r="F347" s="8">
+      <c r="F347" s="12">
         <v>59.67</v>
       </c>
     </row>
@@ -9292,16 +9299,16 @@
       <c r="B348" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C348" s="2" t="s">
+      <c r="C348" s="4" t="s">
         <v>544</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="E348" s="8">
+      <c r="E348" s="12">
         <v>998.26</v>
       </c>
-      <c r="F348" s="8">
+      <c r="F348" s="12">
         <v>998.26</v>
       </c>
     </row>
@@ -9309,16 +9316,16 @@
       <c r="B349" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C349" s="2" t="s">
+      <c r="C349" s="4" t="s">
         <v>545</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="E349" s="8">
+      <c r="E349" s="12">
         <v>809.77</v>
       </c>
-      <c r="F349" s="8">
+      <c r="F349" s="12">
         <v>809.77</v>
       </c>
     </row>
@@ -9326,16 +9333,16 @@
       <c r="B350" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C350" s="2" t="s">
+      <c r="C350" s="4" t="s">
         <v>546</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E350" s="7">
+      <c r="E350" s="11">
         <v>1551.24</v>
       </c>
-      <c r="F350" s="7">
+      <c r="F350" s="11">
         <v>1551.24</v>
       </c>
     </row>
@@ -9343,16 +9350,16 @@
       <c r="B351" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C351" s="2" t="s">
+      <c r="C351" s="4" t="s">
         <v>547</v>
       </c>
       <c r="D351" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="E351" s="8">
+      <c r="E351" s="12">
         <v>685.68</v>
       </c>
-      <c r="F351" s="8">
+      <c r="F351" s="12">
         <v>685.68</v>
       </c>
     </row>
@@ -9360,16 +9367,16 @@
       <c r="B352" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="C352" s="2" t="s">
+      <c r="C352" s="4" t="s">
         <v>549</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="E352" s="8">
+      <c r="E352" s="12">
         <v>860.28</v>
       </c>
-      <c r="F352" s="8">
+      <c r="F352" s="12">
         <v>860.28</v>
       </c>
     </row>
@@ -9377,16 +9384,16 @@
       <c r="B353" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="C353" s="2" t="s">
+      <c r="C353" s="4" t="s">
         <v>550</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E353" s="8">
+      <c r="E353" s="12">
         <v>313.39</v>
       </c>
-      <c r="F353" s="8">
+      <c r="F353" s="12">
         <v>313.39</v>
       </c>
     </row>
@@ -9394,16 +9401,16 @@
       <c r="B354" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="C354" s="2" t="s">
+      <c r="C354" s="4" t="s">
         <v>552</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E354" s="7">
+      <c r="E354" s="11">
         <v>1001.25</v>
       </c>
-      <c r="F354" s="7">
+      <c r="F354" s="11">
         <v>1001.25</v>
       </c>
     </row>
@@ -9411,16 +9418,16 @@
       <c r="B355" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="C355" s="2" t="s">
+      <c r="C355" s="4" t="s">
         <v>553</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="E355" s="7">
+      <c r="E355" s="11">
         <v>1263.92</v>
       </c>
-      <c r="F355" s="7">
+      <c r="F355" s="11">
         <v>1263.92</v>
       </c>
     </row>
@@ -9428,16 +9435,16 @@
       <c r="B356" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="C356" s="2" t="s">
+      <c r="C356" s="4" t="s">
         <v>554</v>
       </c>
       <c r="D356" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="E356" s="7">
+      <c r="E356" s="11">
         <v>1062.22</v>
       </c>
-      <c r="F356" s="7">
+      <c r="F356" s="11">
         <v>1062.22</v>
       </c>
     </row>
@@ -9445,16 +9452,16 @@
       <c r="B357" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="C357" s="2" t="s">
+      <c r="C357" s="4" t="s">
         <v>556</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="E357" s="7">
+      <c r="E357" s="11">
         <v>4118.0200000000004</v>
       </c>
-      <c r="F357" s="7">
+      <c r="F357" s="11">
         <v>2097.98</v>
       </c>
     </row>
@@ -9462,16 +9469,16 @@
       <c r="B358" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="C358" s="2" t="s">
+      <c r="C358" s="4" t="s">
         <v>558</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="E358" s="7">
+      <c r="E358" s="11">
         <v>1893.12</v>
       </c>
-      <c r="F358" s="7">
+      <c r="F358" s="11">
         <v>1893.12</v>
       </c>
     </row>
@@ -9479,16 +9486,16 @@
       <c r="B359" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="C359" s="2" t="s">
+      <c r="C359" s="4" t="s">
         <v>559</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E359" s="8">
+      <c r="E359" s="12">
         <v>473.16</v>
       </c>
-      <c r="F359" s="8">
+      <c r="F359" s="12">
         <v>473.16</v>
       </c>
     </row>
@@ -9496,16 +9503,16 @@
       <c r="B360" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="C360" s="2" t="s">
+      <c r="C360" s="4" t="s">
         <v>560</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E360" s="7">
+      <c r="E360" s="11">
         <v>1150.99</v>
       </c>
-      <c r="F360" s="7">
+      <c r="F360" s="11">
         <v>1150.99</v>
       </c>
     </row>
@@ -9513,16 +9520,16 @@
       <c r="B361" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="C361" s="2" t="s">
+      <c r="C361" s="4" t="s">
         <v>561</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E361" s="8">
+      <c r="E361" s="12">
         <v>981.71</v>
       </c>
-      <c r="F361" s="8">
+      <c r="F361" s="12">
         <v>981.71</v>
       </c>
     </row>
@@ -9530,16 +9537,16 @@
       <c r="B362" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="C362" s="2" t="s">
+      <c r="C362" s="4" t="s">
         <v>562</v>
       </c>
       <c r="D362" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E362" s="8">
+      <c r="E362" s="12">
         <v>109.38</v>
       </c>
-      <c r="F362" s="8">
+      <c r="F362" s="12">
         <v>109.38</v>
       </c>
     </row>
@@ -9547,16 +9554,16 @@
       <c r="B363" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="C363" s="2" t="s">
+      <c r="C363" s="4" t="s">
         <v>563</v>
       </c>
       <c r="D363" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E363" s="8">
+      <c r="E363" s="12">
         <v>981.71</v>
       </c>
-      <c r="F363" s="8">
+      <c r="F363" s="12">
         <v>981.71</v>
       </c>
     </row>
@@ -9564,16 +9571,16 @@
       <c r="B364" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C364" s="2" t="s">
+      <c r="C364" s="4" t="s">
         <v>565</v>
       </c>
       <c r="D364" s="6" t="s">
         <v>566</v>
       </c>
-      <c r="E364" s="7">
+      <c r="E364" s="11">
         <v>36000</v>
       </c>
-      <c r="F364" s="7">
+      <c r="F364" s="11">
         <v>16800</v>
       </c>
     </row>
@@ -9581,16 +9588,16 @@
       <c r="B365" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C365" s="2" t="s">
+      <c r="C365" s="4" t="s">
         <v>567</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="E365" s="7">
+      <c r="E365" s="11">
         <v>1072.2</v>
       </c>
-      <c r="F365" s="8">
+      <c r="F365" s="12">
         <v>594.21</v>
       </c>
     </row>
@@ -9598,16 +9605,16 @@
       <c r="B366" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C366" s="2" t="s">
+      <c r="C366" s="4" t="s">
         <v>569</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="E366" s="8">
+      <c r="E366" s="12">
         <v>416.84</v>
       </c>
-      <c r="F366" s="8">
+      <c r="F366" s="12">
         <v>416.84</v>
       </c>
     </row>
@@ -9615,16 +9622,16 @@
       <c r="B367" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C367" s="2" t="s">
+      <c r="C367" s="4" t="s">
         <v>570</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="E367" s="8">
+      <c r="E367" s="12">
         <v>729.12</v>
       </c>
-      <c r="F367" s="8">
+      <c r="F367" s="12">
         <v>729.12</v>
       </c>
     </row>
@@ -9632,16 +9639,16 @@
       <c r="B368" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C368" s="2" t="s">
+      <c r="C368" s="4" t="s">
         <v>572</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="E368" s="8">
+      <c r="E368" s="12">
         <v>356.73</v>
       </c>
-      <c r="F368" s="8">
+      <c r="F368" s="12">
         <v>356.73</v>
       </c>
     </row>
@@ -9649,16 +9656,16 @@
       <c r="B369" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C369" s="2" t="s">
+      <c r="C369" s="4" t="s">
         <v>573</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="E369" s="8">
+      <c r="E369" s="12">
         <v>651.4</v>
       </c>
-      <c r="F369" s="8">
+      <c r="F369" s="12">
         <v>651.4</v>
       </c>
     </row>
@@ -9666,16 +9673,16 @@
       <c r="B370" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C370" s="2" t="s">
+      <c r="C370" s="4" t="s">
         <v>575</v>
       </c>
       <c r="D370" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="E370" s="8">
+      <c r="E370" s="12">
         <v>764.3</v>
       </c>
-      <c r="F370" s="8">
+      <c r="F370" s="12">
         <v>764.3</v>
       </c>
     </row>
@@ -9683,16 +9690,16 @@
       <c r="B371" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C371" s="2" t="s">
+      <c r="C371" s="4" t="s">
         <v>576</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="E371" s="8">
+      <c r="E371" s="12">
         <v>729.12</v>
       </c>
-      <c r="F371" s="8">
+      <c r="F371" s="12">
         <v>729.12</v>
       </c>
     </row>
@@ -9700,16 +9707,16 @@
       <c r="B372" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C372" s="2" t="s">
+      <c r="C372" s="4" t="s">
         <v>578</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="E372" s="8">
+      <c r="E372" s="12">
         <v>216.35</v>
       </c>
-      <c r="F372" s="8">
+      <c r="F372" s="12">
         <v>216.35</v>
       </c>
     </row>
@@ -9717,16 +9724,16 @@
       <c r="B373" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C373" s="2" t="s">
+      <c r="C373" s="4" t="s">
         <v>579</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="E373" s="8">
+      <c r="E373" s="12">
         <v>597.20000000000005</v>
       </c>
-      <c r="F373" s="8">
+      <c r="F373" s="12">
         <v>597.20000000000005</v>
       </c>
     </row>
@@ -9734,16 +9741,16 @@
       <c r="B374" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C374" s="2" t="s">
+      <c r="C374" s="4" t="s">
         <v>581</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="E374" s="7">
+      <c r="E374" s="11">
         <v>5600.79</v>
       </c>
-      <c r="F374" s="7">
+      <c r="F374" s="11">
         <v>5600.79</v>
       </c>
     </row>
@@ -9751,16 +9758,16 @@
       <c r="B375" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C375" s="2" t="s">
+      <c r="C375" s="4" t="s">
         <v>583</v>
       </c>
       <c r="D375" s="6" t="s">
         <v>584</v>
       </c>
-      <c r="E375" s="8">
+      <c r="E375" s="12">
         <v>652.29999999999995</v>
       </c>
-      <c r="F375" s="8">
+      <c r="F375" s="12">
         <v>652.29999999999995</v>
       </c>
     </row>
@@ -9768,16 +9775,16 @@
       <c r="B376" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C376" s="2" t="s">
+      <c r="C376" s="4" t="s">
         <v>585</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="E376" s="7">
+      <c r="E376" s="11">
         <v>2042.43</v>
       </c>
-      <c r="F376" s="7">
+      <c r="F376" s="11">
         <v>2042.43</v>
       </c>
     </row>
@@ -9785,16 +9792,16 @@
       <c r="B377" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C377" s="2" t="s">
+      <c r="C377" s="4" t="s">
         <v>587</v>
       </c>
       <c r="D377" s="6" t="s">
         <v>588</v>
       </c>
-      <c r="E377" s="8">
+      <c r="E377" s="12">
         <v>870.5</v>
       </c>
-      <c r="F377" s="8">
+      <c r="F377" s="12">
         <v>870.5</v>
       </c>
     </row>
@@ -9802,16 +9809,16 @@
       <c r="B378" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C378" s="2" t="s">
+      <c r="C378" s="4" t="s">
         <v>589</v>
       </c>
       <c r="D378" s="6" t="s">
         <v>588</v>
       </c>
-      <c r="E378" s="7">
+      <c r="E378" s="11">
         <v>1009.8</v>
       </c>
-      <c r="F378" s="7">
+      <c r="F378" s="11">
         <v>1009.8</v>
       </c>
     </row>
@@ -9819,16 +9826,16 @@
       <c r="B379" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C379" s="2" t="s">
+      <c r="C379" s="4" t="s">
         <v>590</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="E379" s="8">
+      <c r="E379" s="12">
         <v>870.5</v>
       </c>
-      <c r="F379" s="8">
+      <c r="F379" s="12">
         <v>870.5</v>
       </c>
     </row>
@@ -9836,16 +9843,16 @@
       <c r="B380" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C380" s="2" t="s">
+      <c r="C380" s="4" t="s">
         <v>592</v>
       </c>
       <c r="D380" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="E380" s="8">
+      <c r="E380" s="12">
         <v>596.72</v>
       </c>
-      <c r="F380" s="8">
+      <c r="F380" s="12">
         <v>596.72</v>
       </c>
     </row>
@@ -9853,16 +9860,16 @@
       <c r="B381" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C381" s="2" t="s">
+      <c r="C381" s="4" t="s">
         <v>594</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="E381" s="8">
+      <c r="E381" s="12">
         <v>736.72</v>
       </c>
-      <c r="F381" s="8">
+      <c r="F381" s="12">
         <v>736.72</v>
       </c>
     </row>
@@ -9870,16 +9877,16 @@
       <c r="B382" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C382" s="2" t="s">
+      <c r="C382" s="4" t="s">
         <v>596</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>597</v>
       </c>
-      <c r="E382" s="8">
+      <c r="E382" s="12">
         <v>716.1</v>
       </c>
-      <c r="F382" s="8">
+      <c r="F382" s="12">
         <v>716.1</v>
       </c>
     </row>
@@ -9887,16 +9894,16 @@
       <c r="B383" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C383" s="2" t="s">
+      <c r="C383" s="4" t="s">
         <v>598</v>
       </c>
       <c r="D383" s="6" t="s">
         <v>599</v>
       </c>
-      <c r="E383" s="8">
+      <c r="E383" s="12">
         <v>564.66</v>
       </c>
-      <c r="F383" s="8">
+      <c r="F383" s="12">
         <v>564.66</v>
       </c>
     </row>
@@ -9904,16 +9911,16 @@
       <c r="B384" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C384" s="2" t="s">
+      <c r="C384" s="4" t="s">
         <v>600</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="E384" s="8">
+      <c r="E384" s="12">
         <v>898.02</v>
       </c>
-      <c r="F384" s="8">
+      <c r="F384" s="12">
         <v>898.02</v>
       </c>
     </row>
@@ -9921,16 +9928,16 @@
       <c r="B385" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C385" s="2" t="s">
+      <c r="C385" s="4" t="s">
         <v>602</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="E385" s="8">
+      <c r="E385" s="12">
         <v>898.02</v>
       </c>
-      <c r="F385" s="8">
+      <c r="F385" s="12">
         <v>898.02</v>
       </c>
     </row>
@@ -9938,16 +9945,16 @@
       <c r="B386" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C386" s="2" t="s">
+      <c r="C386" s="4" t="s">
         <v>604</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="E386" s="8">
+      <c r="E386" s="12">
         <v>651.29999999999995</v>
       </c>
-      <c r="F386" s="8">
+      <c r="F386" s="12">
         <v>651.29999999999995</v>
       </c>
     </row>
@@ -9955,16 +9962,16 @@
       <c r="B387" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C387" s="2" t="s">
+      <c r="C387" s="4" t="s">
         <v>606</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E387" s="7">
+      <c r="E387" s="11">
         <v>-36000</v>
       </c>
-      <c r="F387" s="7">
+      <c r="F387" s="11">
         <v>-36000</v>
       </c>
     </row>
@@ -9972,16 +9979,16 @@
       <c r="B388" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="C388" s="2" t="s">
+      <c r="C388" s="4" t="s">
         <v>608</v>
       </c>
       <c r="D388" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="E388" s="8">
+      <c r="E388" s="12">
         <v>188.76</v>
       </c>
-      <c r="F388" s="8">
+      <c r="F388" s="12">
         <v>188.76</v>
       </c>
     </row>
@@ -9989,16 +9996,16 @@
       <c r="B389" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="C389" s="2" t="s">
+      <c r="C389" s="4" t="s">
         <v>609</v>
       </c>
       <c r="D389" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="E389" s="8">
+      <c r="E389" s="12">
         <v>218.02</v>
       </c>
-      <c r="F389" s="8">
+      <c r="F389" s="12">
         <v>218.02</v>
       </c>
     </row>
@@ -10006,16 +10013,16 @@
       <c r="B390" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="C390" s="2" t="s">
+      <c r="C390" s="4" t="s">
         <v>610</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="E390" s="8">
+      <c r="E390" s="12">
         <v>235.95</v>
       </c>
-      <c r="F390" s="8">
+      <c r="F390" s="12">
         <v>235.95</v>
       </c>
     </row>
@@ -10023,16 +10030,16 @@
       <c r="B391" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="C391" s="2" t="s">
+      <c r="C391" s="4" t="s">
         <v>612</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="E391" s="7">
+      <c r="E391" s="11">
         <v>9512.7099999999991</v>
       </c>
-      <c r="F391" s="7">
+      <c r="F391" s="11">
         <v>5607.64</v>
       </c>
     </row>
@@ -10040,16 +10047,16 @@
       <c r="B392" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="C392" s="2" t="s">
+      <c r="C392" s="4" t="s">
         <v>614</v>
       </c>
       <c r="D392" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="E392" s="7">
+      <c r="E392" s="11">
         <v>6835.49</v>
       </c>
-      <c r="F392" s="7">
+      <c r="F392" s="11">
         <v>6835.49</v>
       </c>
     </row>
@@ -10057,16 +10064,16 @@
       <c r="B393" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="C393" s="2" t="s">
+      <c r="C393" s="4" t="s">
         <v>616</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="E393" s="8">
+      <c r="E393" s="12">
         <v>374.52</v>
       </c>
-      <c r="F393" s="8">
+      <c r="F393" s="12">
         <v>374.52</v>
       </c>
     </row>
@@ -10074,16 +10081,16 @@
       <c r="B394" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="C394" s="2" t="s">
+      <c r="C394" s="4" t="s">
         <v>618</v>
       </c>
       <c r="D394" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="E394" s="7">
+      <c r="E394" s="11">
         <v>10694.76</v>
       </c>
-      <c r="F394" s="7">
+      <c r="F394" s="11">
         <v>10694.76</v>
       </c>
     </row>
@@ -10091,16 +10098,16 @@
       <c r="B395" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="C395" s="2" t="s">
+      <c r="C395" s="4" t="s">
         <v>620</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="E395" s="8">
+      <c r="E395" s="12">
         <v>337.41</v>
       </c>
-      <c r="F395" s="8">
+      <c r="F395" s="12">
         <v>337.41</v>
       </c>
     </row>
@@ -10108,16 +10115,16 @@
       <c r="B396" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="C396" s="2" t="s">
+      <c r="C396" s="4" t="s">
         <v>622</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="E396" s="7">
+      <c r="E396" s="11">
         <v>10808.11</v>
       </c>
-      <c r="F396" s="7">
+      <c r="F396" s="11">
         <v>6879.17</v>
       </c>
     </row>
@@ -10125,16 +10132,16 @@
       <c r="B397" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="C397" s="2" t="s">
+      <c r="C397" s="4" t="s">
         <v>623</v>
       </c>
       <c r="D397" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="E397" s="8">
+      <c r="E397" s="12">
         <v>589.9</v>
       </c>
-      <c r="F397" s="8">
+      <c r="F397" s="12">
         <v>589.9</v>
       </c>
     </row>
@@ -10142,16 +10149,16 @@
       <c r="B398" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="C398" s="2" t="s">
+      <c r="C398" s="4" t="s">
         <v>624</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E398" s="7">
+      <c r="E398" s="11">
         <v>1565.3</v>
       </c>
-      <c r="F398" s="7">
+      <c r="F398" s="11">
         <v>1565.3</v>
       </c>
     </row>
@@ -10159,16 +10166,16 @@
       <c r="B399" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="C399" s="2" t="s">
+      <c r="C399" s="4" t="s">
         <v>625</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E399" s="8">
+      <c r="E399" s="12">
         <v>752.71</v>
       </c>
-      <c r="F399" s="8">
+      <c r="F399" s="12">
         <v>752.71</v>
       </c>
     </row>
@@ -10176,16 +10183,16 @@
       <c r="B400" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="C400" s="2" t="s">
+      <c r="C400" s="4" t="s">
         <v>627</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E400" s="7">
+      <c r="E400" s="11">
         <v>2956.69</v>
       </c>
-      <c r="F400" s="7">
+      <c r="F400" s="11">
         <v>1796.36</v>
       </c>
     </row>
@@ -10193,16 +10200,16 @@
       <c r="B401" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="C401" s="2" t="s">
+      <c r="C401" s="4" t="s">
         <v>629</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="E401" s="7">
+      <c r="E401" s="11">
         <v>2026.87</v>
       </c>
-      <c r="F401" s="7">
+      <c r="F401" s="11">
         <v>2026.87</v>
       </c>
     </row>
@@ -10210,16 +10217,16 @@
       <c r="B402" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="C402" s="2" t="s">
+      <c r="C402" s="4" t="s">
         <v>630</v>
       </c>
       <c r="D402" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="E402" s="7">
+      <c r="E402" s="11">
         <v>2970.84</v>
       </c>
-      <c r="F402" s="7">
+      <c r="F402" s="11">
         <v>2970.84</v>
       </c>
     </row>
@@ -10227,16 +10234,16 @@
       <c r="B403" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="C403" s="2" t="s">
+      <c r="C403" s="4" t="s">
         <v>631</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E403" s="7">
+      <c r="E403" s="11">
         <v>1009.62</v>
       </c>
-      <c r="F403" s="7">
+      <c r="F403" s="11">
         <v>1009.62</v>
       </c>
     </row>
@@ -10244,16 +10251,16 @@
       <c r="B404" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="C404" s="2" t="s">
+      <c r="C404" s="4" t="s">
         <v>633</v>
       </c>
       <c r="D404" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="E404" s="8">
+      <c r="E404" s="12">
         <v>829.15</v>
       </c>
-      <c r="F404" s="8">
+      <c r="F404" s="12">
         <v>264.02999999999997</v>
       </c>
     </row>
@@ -10261,16 +10268,16 @@
       <c r="B405" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="C405" s="2" t="s">
+      <c r="C405" s="4" t="s">
         <v>635</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="E405" s="8">
+      <c r="E405" s="12">
         <v>569.84</v>
       </c>
-      <c r="F405" s="8">
+      <c r="F405" s="12">
         <v>569.84</v>
       </c>
     </row>
@@ -10278,16 +10285,16 @@
       <c r="B406" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="C406" s="2" t="s">
+      <c r="C406" s="4" t="s">
         <v>637</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="E406" s="8">
+      <c r="E406" s="12">
         <v>211.45</v>
       </c>
-      <c r="F406" s="8">
+      <c r="F406" s="12">
         <v>211.45</v>
       </c>
     </row>
@@ -10295,16 +10302,16 @@
       <c r="B407" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="C407" s="2" t="s">
+      <c r="C407" s="4" t="s">
         <v>639</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="E407" s="8">
+      <c r="E407" s="12">
         <v>92.34</v>
       </c>
-      <c r="F407" s="8">
+      <c r="F407" s="12">
         <v>92.34</v>
       </c>
     </row>
@@ -10312,16 +10319,16 @@
       <c r="B408" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="C408" s="2" t="s">
+      <c r="C408" s="4" t="s">
         <v>641</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="E408" s="8">
+      <c r="E408" s="12">
         <v>318.69</v>
       </c>
-      <c r="F408" s="8">
+      <c r="F408" s="12">
         <v>318.69</v>
       </c>
     </row>
@@ -10329,16 +10336,16 @@
       <c r="B409" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="C409" s="2" t="s">
+      <c r="C409" s="4" t="s">
         <v>643</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="E409" s="8">
+      <c r="E409" s="12">
         <v>501.26</v>
       </c>
-      <c r="F409" s="8">
+      <c r="F409" s="12">
         <v>501.26</v>
       </c>
     </row>
@@ -10346,16 +10353,16 @@
       <c r="B410" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="C410" s="2" t="s">
+      <c r="C410" s="4" t="s">
         <v>645</v>
       </c>
       <c r="D410" s="6" t="s">
         <v>646</v>
       </c>
-      <c r="E410" s="8">
+      <c r="E410" s="12">
         <v>798.91</v>
       </c>
-      <c r="F410" s="8">
+      <c r="F410" s="12">
         <v>711.16</v>
       </c>
     </row>
@@ -10363,16 +10370,16 @@
       <c r="B411" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="C411" s="2" t="s">
+      <c r="C411" s="4" t="s">
         <v>647</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="E411" s="7">
+      <c r="E411" s="11">
         <v>3028.65</v>
       </c>
-      <c r="F411" s="7">
+      <c r="F411" s="11">
         <v>3028.65</v>
       </c>
     </row>
@@ -10380,16 +10387,16 @@
       <c r="B412" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="C412" s="2" t="s">
+      <c r="C412" s="4" t="s">
         <v>648</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E412" s="8">
+      <c r="E412" s="12">
         <v>323.57</v>
       </c>
-      <c r="F412" s="8">
+      <c r="F412" s="12">
         <v>323.57</v>
       </c>
     </row>
@@ -10397,16 +10404,16 @@
       <c r="B413" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="C413" s="2" t="s">
+      <c r="C413" s="4" t="s">
         <v>649</v>
       </c>
       <c r="D413" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="E413" s="8">
+      <c r="E413" s="12">
         <v>401.14</v>
       </c>
-      <c r="F413" s="8">
+      <c r="F413" s="12">
         <v>401.14</v>
       </c>
     </row>
@@ -10414,16 +10421,16 @@
       <c r="B414" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="C414" s="2" t="s">
+      <c r="C414" s="4" t="s">
         <v>650</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="E414" s="7">
+      <c r="E414" s="11">
         <v>1047.43</v>
       </c>
-      <c r="F414" s="7">
+      <c r="F414" s="11">
         <v>1047.43</v>
       </c>
     </row>
@@ -10431,16 +10438,16 @@
       <c r="B415" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="C415" s="2" t="s">
+      <c r="C415" s="4" t="s">
         <v>651</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E415" s="8">
+      <c r="E415" s="12">
         <v>759.09</v>
       </c>
-      <c r="F415" s="8">
+      <c r="F415" s="12">
         <v>759.09</v>
       </c>
     </row>
@@ -10448,16 +10455,16 @@
       <c r="B416" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="C416" s="2" t="s">
+      <c r="C416" s="4" t="s">
         <v>652</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="E416" s="7">
+      <c r="E416" s="11">
         <v>2374.58</v>
       </c>
-      <c r="F416" s="7">
+      <c r="F416" s="11">
         <v>2374.58</v>
       </c>
     </row>
@@ -10465,16 +10472,16 @@
       <c r="B417" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="C417" s="2" t="s">
+      <c r="C417" s="4" t="s">
         <v>654</v>
       </c>
       <c r="D417" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="E417" s="7">
+      <c r="E417" s="11">
         <v>1688.95</v>
       </c>
-      <c r="F417" s="7">
+      <c r="F417" s="11">
         <v>1545.35</v>
       </c>
     </row>
@@ -10482,16 +10489,16 @@
       <c r="B418" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="C418" s="2" t="s">
+      <c r="C418" s="4" t="s">
         <v>655</v>
       </c>
       <c r="D418" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="E418" s="7">
+      <c r="E418" s="11">
         <v>3035.94</v>
       </c>
-      <c r="F418" s="7">
+      <c r="F418" s="11">
         <v>3035.94</v>
       </c>
     </row>
@@ -10499,16 +10506,16 @@
       <c r="B419" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="C419" s="2" t="s">
+      <c r="C419" s="4" t="s">
         <v>656</v>
       </c>
       <c r="D419" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="E419" s="7">
+      <c r="E419" s="11">
         <v>5995.83</v>
       </c>
-      <c r="F419" s="7">
+      <c r="F419" s="11">
         <v>5995.83</v>
       </c>
     </row>
@@ -10516,16 +10523,16 @@
       <c r="B420" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="C420" s="2" t="s">
+      <c r="C420" s="4" t="s">
         <v>657</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="E420" s="7">
+      <c r="E420" s="11">
         <v>2526.5300000000002</v>
       </c>
-      <c r="F420" s="7">
+      <c r="F420" s="11">
         <v>2526.5300000000002</v>
       </c>
     </row>
@@ -10533,16 +10540,16 @@
       <c r="B421" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="C421" s="2" t="s">
+      <c r="C421" s="4" t="s">
         <v>658</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="E421" s="7">
+      <c r="E421" s="11">
         <v>1992.95</v>
       </c>
-      <c r="F421" s="7">
+      <c r="F421" s="11">
         <v>1992.95</v>
       </c>
     </row>
@@ -10550,16 +10557,16 @@
       <c r="B422" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="C422" s="2" t="s">
+      <c r="C422" s="4" t="s">
         <v>659</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="E422" s="7">
+      <c r="E422" s="11">
         <v>1550.83</v>
       </c>
-      <c r="F422" s="7">
+      <c r="F422" s="11">
         <v>1550.83</v>
       </c>
     </row>
@@ -10567,16 +10574,16 @@
       <c r="B423" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="C423" s="2" t="s">
+      <c r="C423" s="4" t="s">
         <v>660</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E423" s="8">
+      <c r="E423" s="12">
         <v>188.76</v>
       </c>
-      <c r="F423" s="8">
+      <c r="F423" s="12">
         <v>188.76</v>
       </c>
     </row>
@@ -10584,16 +10591,16 @@
       <c r="B424" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="C424" s="2" t="s">
+      <c r="C424" s="4" t="s">
         <v>662</v>
       </c>
       <c r="D424" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="E424" s="7">
+      <c r="E424" s="11">
         <v>3470.57</v>
       </c>
-      <c r="F424" s="8">
+      <c r="F424" s="12">
         <v>10.98</v>
       </c>
     </row>
@@ -10601,16 +10608,16 @@
       <c r="B425" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="C425" s="2" t="s">
+      <c r="C425" s="4" t="s">
         <v>664</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E425" s="8">
+      <c r="E425" s="12">
         <v>978.53</v>
       </c>
-      <c r="F425" s="8">
+      <c r="F425" s="12">
         <v>178.53</v>
       </c>
     </row>
@@ -10618,16 +10625,16 @@
       <c r="B426" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="C426" s="2" t="s">
+      <c r="C426" s="4" t="s">
         <v>665</v>
       </c>
       <c r="D426" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="E426" s="8">
+      <c r="E426" s="12">
         <v>963.9</v>
       </c>
-      <c r="F426" s="8">
+      <c r="F426" s="12">
         <v>963.9</v>
       </c>
     </row>
@@ -10635,16 +10642,16 @@
       <c r="B427" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="C427" s="2" t="s">
+      <c r="C427" s="4" t="s">
         <v>667</v>
       </c>
       <c r="D427" s="6" t="s">
         <v>668</v>
       </c>
-      <c r="E427" s="7">
+      <c r="E427" s="11">
         <v>2732.17</v>
       </c>
-      <c r="F427" s="7">
+      <c r="F427" s="11">
         <v>1732.17</v>
       </c>
     </row>
@@ -10652,16 +10659,16 @@
       <c r="B428" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="C428" s="2" t="s">
+      <c r="C428" s="4" t="s">
         <v>669</v>
       </c>
       <c r="D428" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="E428" s="8">
+      <c r="E428" s="12">
         <v>956.4</v>
       </c>
-      <c r="F428" s="8">
+      <c r="F428" s="12">
         <v>956.4</v>
       </c>
     </row>
@@ -10669,16 +10676,16 @@
       <c r="B429" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="C429" s="2" t="s">
+      <c r="C429" s="4" t="s">
         <v>672</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E429" s="8">
+      <c r="E429" s="12">
         <v>680.06</v>
       </c>
-      <c r="F429" s="8">
+      <c r="F429" s="12">
         <v>680.06</v>
       </c>
     </row>
@@ -10686,16 +10693,16 @@
       <c r="B430" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="C430" s="2" t="s">
+      <c r="C430" s="4" t="s">
         <v>674</v>
       </c>
-      <c r="D430" s="10" t="s">
+      <c r="D430" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="E430" s="7">
+      <c r="E430" s="11">
         <v>1128.3</v>
       </c>
-      <c r="F430" s="7">
+      <c r="F430" s="11">
         <v>1128.3</v>
       </c>
     </row>
@@ -10703,16 +10710,16 @@
       <c r="B431" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="C431" s="2" t="s">
+      <c r="C431" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="D431" s="11" t="s">
+      <c r="D431" s="9" t="s">
         <v>678</v>
       </c>
-      <c r="E431" s="8">
+      <c r="E431" s="12">
         <v>628.79999999999995</v>
       </c>
-      <c r="F431" s="8">
+      <c r="F431" s="12">
         <v>262.77999999999997</v>
       </c>
     </row>
@@ -10720,16 +10727,16 @@
       <c r="B432" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C432" s="2" t="s">
+      <c r="C432" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="D432" s="11" t="s">
+      <c r="D432" s="9" t="s">
         <v>680</v>
       </c>
-      <c r="E432" s="7">
+      <c r="E432" s="11">
         <v>2644.48</v>
       </c>
-      <c r="F432" s="7">
+      <c r="F432" s="11">
         <v>2644.48</v>
       </c>
     </row>
@@ -10737,16 +10744,16 @@
       <c r="B433" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="C433" s="2" t="s">
+      <c r="C433" s="4" t="s">
         <v>682</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E433" s="7">
+      <c r="E433" s="11">
         <v>2486.83</v>
       </c>
-      <c r="F433" s="7">
+      <c r="F433" s="11">
         <v>2486.83</v>
       </c>
     </row>
@@ -10754,16 +10761,16 @@
       <c r="B434" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="C434" s="2" t="s">
+      <c r="C434" s="4" t="s">
         <v>683</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E434" s="7">
+      <c r="E434" s="11">
         <v>4991.01</v>
       </c>
-      <c r="F434" s="7">
+      <c r="F434" s="11">
         <v>4991.01</v>
       </c>
     </row>
@@ -10771,16 +10778,16 @@
       <c r="B435" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C435" s="2" t="s">
+      <c r="C435" s="4" t="s">
         <v>684</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E435" s="7">
+      <c r="E435" s="11">
         <v>6232.46</v>
       </c>
-      <c r="F435" s="7">
+      <c r="F435" s="11">
         <v>6232.46</v>
       </c>
     </row>
@@ -10788,16 +10795,16 @@
       <c r="B436" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C436" s="2" t="s">
+      <c r="C436" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="D436" s="12" t="s">
+      <c r="D436" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="E436" s="7">
+      <c r="E436" s="11">
         <v>9370.36</v>
       </c>
-      <c r="F436" s="7">
+      <c r="F436" s="11">
         <v>9370.36</v>
       </c>
     </row>
@@ -10805,16 +10812,16 @@
       <c r="B437" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="C437" s="2" t="s">
+      <c r="C437" s="4" t="s">
         <v>687</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E437" s="7">
+      <c r="E437" s="11">
         <v>1565.3</v>
       </c>
-      <c r="F437" s="7">
+      <c r="F437" s="11">
         <v>1565.3</v>
       </c>
     </row>
@@ -10822,16 +10829,16 @@
       <c r="B438" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C438" s="2" t="s">
+      <c r="C438" s="4" t="s">
         <v>688</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="E438" s="7">
+      <c r="E438" s="11">
         <v>2931.2</v>
       </c>
-      <c r="F438" s="7">
+      <c r="F438" s="11">
         <v>2931.2</v>
       </c>
     </row>
@@ -10839,16 +10846,16 @@
       <c r="B439" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C439" s="2" t="s">
+      <c r="C439" s="4" t="s">
         <v>690</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>691</v>
       </c>
-      <c r="E439" s="7">
+      <c r="E439" s="11">
         <v>2741.2</v>
       </c>
-      <c r="F439" s="7">
+      <c r="F439" s="11">
         <v>2741.2</v>
       </c>
     </row>
@@ -10856,16 +10863,16 @@
       <c r="B440" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C440" s="2" t="s">
+      <c r="C440" s="4" t="s">
         <v>692</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="E440" s="7">
+      <c r="E440" s="11">
         <v>3087.07</v>
       </c>
-      <c r="F440" s="7">
+      <c r="F440" s="11">
         <v>3087.07</v>
       </c>
     </row>
@@ -10873,16 +10880,16 @@
       <c r="B441" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C441" s="2" t="s">
+      <c r="C441" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="D441" s="12" t="s">
+      <c r="D441" s="10" t="s">
         <v>695</v>
       </c>
-      <c r="E441" s="7">
+      <c r="E441" s="11">
         <v>2201.4</v>
       </c>
-      <c r="F441" s="7">
+      <c r="F441" s="11">
         <v>2201.4</v>
       </c>
     </row>
@@ -10890,16 +10897,16 @@
       <c r="B442" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C442" s="2" t="s">
+      <c r="C442" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="D442" s="12" t="s">
+      <c r="D442" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="E442" s="7">
+      <c r="E442" s="11">
         <v>2741.2</v>
       </c>
-      <c r="F442" s="7">
+      <c r="F442" s="11">
         <v>2741.2</v>
       </c>
     </row>
@@ -10907,16 +10914,16 @@
       <c r="B443" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C443" s="2" t="s">
+      <c r="C443" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="D443" s="12" t="s">
+      <c r="D443" s="10" t="s">
         <v>698</v>
       </c>
-      <c r="E443" s="7">
+      <c r="E443" s="11">
         <v>1469.88</v>
       </c>
-      <c r="F443" s="7">
+      <c r="F443" s="11">
         <v>1469.88</v>
       </c>
     </row>

--- a/Facturi_Neincasate.xlsx
+++ b/Facturi_Neincasate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="715">
   <si>
     <t>Denumire client</t>
   </si>
@@ -2166,8 +2166,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="169" formatCode="###,###,##0.00"/>
-    <numFmt numFmtId="170" formatCode="########0.00"/>
+    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
+    <numFmt numFmtId="165" formatCode="########0.00"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -2414,10 +2414,10 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -2746,14 +2746,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E456"/>
+  <dimension ref="A1:F456"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="39.28515625" style="1" customWidth="1"/>
     <col min="2" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2769,8 +2769,11 @@
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -2786,8 +2789,11 @@
       <c r="E2" s="5">
         <v>1382.19</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" s="5">
+        <v>1382.19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -2803,8 +2809,11 @@
       <c r="E3" s="6">
         <v>970.57</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="6">
+        <v>970.57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -2820,8 +2829,11 @@
       <c r="E4" s="6">
         <v>593.46</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" s="6">
+        <v>593.46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -2837,8 +2849,11 @@
       <c r="E5" s="6">
         <v>523.6</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="6">
+        <v>523.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -2854,8 +2869,11 @@
       <c r="E6" s="6">
         <v>524.65</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="6">
+        <v>524.65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -2871,8 +2889,11 @@
       <c r="E7" s="5">
         <v>1536.44</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" s="5">
+        <v>1536.44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
@@ -2888,8 +2909,11 @@
       <c r="E8" s="5">
         <v>2508.38</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" s="5">
+        <v>2508.38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -2905,8 +2929,11 @@
       <c r="E9" s="6">
         <v>483.88</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" s="6">
+        <v>483.88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -2922,8 +2949,11 @@
       <c r="E10" s="6">
         <v>287.20999999999998</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" s="6">
+        <v>287.20999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
         <v>4</v>
       </c>
@@ -2939,8 +2969,11 @@
       <c r="E11" s="5">
         <v>1321.3</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" s="5">
+        <v>1321.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
@@ -2956,8 +2989,11 @@
       <c r="E12" s="5">
         <v>2212.12</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" s="5">
+        <v>2212.12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -2973,8 +3009,11 @@
       <c r="E13" s="5">
         <v>1990.1</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13" s="5">
+        <v>1990.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
         <v>23</v>
       </c>
@@ -2990,8 +3029,11 @@
       <c r="E14" s="6">
         <v>438.87</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" s="6">
+        <v>438.87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
@@ -3007,8 +3049,11 @@
       <c r="E15" s="6">
         <v>376.22</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" s="6">
+        <v>376.22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
@@ -3024,8 +3069,11 @@
       <c r="E16" s="6">
         <v>391.05</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" s="6">
+        <v>391.05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
         <v>30</v>
       </c>
@@ -3041,8 +3089,11 @@
       <c r="E17" s="5">
         <v>1147.69</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" s="5">
+        <v>1147.69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
         <v>30</v>
       </c>
@@ -3058,8 +3109,11 @@
       <c r="E18" s="5">
         <v>1188.72</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" s="5">
+        <v>1188.72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
@@ -3075,8 +3129,11 @@
       <c r="E19" s="6">
         <v>729.44</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" s="6">
+        <v>729.44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
         <v>36</v>
       </c>
@@ -3092,8 +3149,11 @@
       <c r="E20" s="6">
         <v>227.1</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" s="6">
+        <v>227.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
         <v>36</v>
       </c>
@@ -3109,8 +3169,11 @@
       <c r="E21" s="6">
         <v>245.39</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" s="6">
+        <v>245.39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="2" t="s">
         <v>39</v>
       </c>
@@ -3126,8 +3189,11 @@
       <c r="E22" s="6">
         <v>186.97</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" s="6">
+        <v>186.97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="2" t="s">
         <v>39</v>
       </c>
@@ -3143,8 +3209,11 @@
       <c r="E23" s="6">
         <v>799.86</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" s="6">
+        <v>799.86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="2" t="s">
         <v>39</v>
       </c>
@@ -3160,8 +3229,11 @@
       <c r="E24" s="6">
         <v>96.83</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" s="6">
+        <v>96.83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
@@ -3177,8 +3249,11 @@
       <c r="E25" s="6">
         <v>417.96</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" s="6">
+        <v>417.96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="2" t="s">
         <v>47</v>
       </c>
@@ -3194,8 +3269,11 @@
       <c r="E26" s="6">
         <v>499.33</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26" s="6">
+        <v>499.33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
         <v>47</v>
       </c>
@@ -3211,8 +3289,11 @@
       <c r="E27" s="5">
         <v>1799.67</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" s="5">
+        <v>1799.67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="2" t="s">
         <v>47</v>
       </c>
@@ -3228,8 +3309,11 @@
       <c r="E28" s="6">
         <v>371.24</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" s="6">
+        <v>371.24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
         <v>51</v>
       </c>
@@ -3245,8 +3329,11 @@
       <c r="E29" s="6">
         <v>177.94</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29" s="6">
+        <v>177.94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="2" t="s">
         <v>51</v>
       </c>
@@ -3262,8 +3349,11 @@
       <c r="E30" s="6">
         <v>393.18</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30" s="6">
+        <v>393.18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="2" t="s">
         <v>51</v>
       </c>
@@ -3279,8 +3369,11 @@
       <c r="E31" s="5">
         <v>1311.16</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31" s="5">
+        <v>1311.16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="2" t="s">
         <v>51</v>
       </c>
@@ -3296,8 +3389,11 @@
       <c r="E32" s="6">
         <v>109.38</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32" s="6">
+        <v>109.38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="2" t="s">
         <v>51</v>
       </c>
@@ -3313,8 +3409,11 @@
       <c r="E33" s="5">
         <v>1961.14</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="F33" s="5">
+        <v>1961.14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="2" t="s">
         <v>51</v>
       </c>
@@ -3330,8 +3429,11 @@
       <c r="E34" s="5">
         <v>1140.42</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F34" s="5">
+        <v>1140.42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="2" t="s">
         <v>51</v>
       </c>
@@ -3347,8 +3449,11 @@
       <c r="E35" s="6">
         <v>607.47</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="F35" s="6">
+        <v>607.47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="2" t="s">
         <v>51</v>
       </c>
@@ -3364,8 +3469,11 @@
       <c r="E36" s="6">
         <v>581.70000000000005</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="F36" s="6">
+        <v>581.70000000000005</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" s="2" t="s">
         <v>63</v>
       </c>
@@ -3381,8 +3489,11 @@
       <c r="E37" s="5">
         <v>7434.3</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="F37" s="5">
+        <v>7434.3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
         <v>63</v>
       </c>
@@ -3398,8 +3509,11 @@
       <c r="E38" s="5">
         <v>1001.25</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="F38" s="5">
+        <v>1001.25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" s="2" t="s">
         <v>63</v>
       </c>
@@ -3415,8 +3529,11 @@
       <c r="E39" s="5">
         <v>1001.25</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="F39" s="5">
+        <v>1001.25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" s="2" t="s">
         <v>68</v>
       </c>
@@ -3432,8 +3549,11 @@
       <c r="E40" s="6">
         <v>326.81</v>
       </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="F40" s="6">
+        <v>326.81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" s="2" t="s">
         <v>68</v>
       </c>
@@ -3449,8 +3569,11 @@
       <c r="E41" s="6">
         <v>631.30999999999995</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="F41" s="6">
+        <v>631.30999999999995</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" s="2" t="s">
         <v>68</v>
       </c>
@@ -3466,8 +3589,11 @@
       <c r="E42" s="5">
         <v>1260.6600000000001</v>
       </c>
-    </row>
-    <row r="43" spans="1:5">
+      <c r="F42" s="5">
+        <v>1260.6600000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" s="2" t="s">
         <v>68</v>
       </c>
@@ -3483,8 +3609,11 @@
       <c r="E43" s="6">
         <v>972.6</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="F43" s="6">
+        <v>972.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" s="2" t="s">
         <v>68</v>
       </c>
@@ -3500,8 +3629,11 @@
       <c r="E44" s="6">
         <v>911.42</v>
       </c>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="F44" s="6">
+        <v>911.42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" s="2" t="s">
         <v>75</v>
       </c>
@@ -3517,8 +3649,11 @@
       <c r="E45" s="6">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="F45" s="6">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" s="2" t="s">
         <v>75</v>
       </c>
@@ -3534,8 +3669,11 @@
       <c r="E46" s="6">
         <v>578.86</v>
       </c>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="F46" s="6">
+        <v>578.86</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="2" t="s">
         <v>75</v>
       </c>
@@ -3551,8 +3689,11 @@
       <c r="E47" s="5">
         <v>1127.1600000000001</v>
       </c>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="F47" s="5">
+        <v>1127.1600000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" s="2" t="s">
         <v>79</v>
       </c>
@@ -3568,8 +3709,11 @@
       <c r="E48" s="6">
         <v>321.92</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="F48" s="6">
+        <v>321.92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" s="2" t="s">
         <v>82</v>
       </c>
@@ -3585,8 +3729,11 @@
       <c r="E49" s="5">
         <v>1081.69</v>
       </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="F49" s="5">
+        <v>1081.69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="2" t="s">
         <v>82</v>
       </c>
@@ -3602,8 +3749,11 @@
       <c r="E50" s="5">
         <v>1632.74</v>
       </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="F50" s="5">
+        <v>1632.74</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" s="2" t="s">
         <v>82</v>
       </c>
@@ -3619,8 +3769,11 @@
       <c r="E51" s="6">
         <v>995.61</v>
       </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="F51" s="6">
+        <v>995.61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="2" t="s">
         <v>82</v>
       </c>
@@ -3636,8 +3789,11 @@
       <c r="E52" s="6">
         <v>322.64</v>
       </c>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="F52" s="6">
+        <v>322.64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" s="2" t="s">
         <v>87</v>
       </c>
@@ -3653,8 +3809,11 @@
       <c r="E53" s="6">
         <v>719.66</v>
       </c>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="F53" s="6">
+        <v>719.66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" s="2" t="s">
         <v>87</v>
       </c>
@@ -3670,8 +3829,11 @@
       <c r="E54" s="6">
         <v>774.25</v>
       </c>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="F54" s="6">
+        <v>774.25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" s="2" t="s">
         <v>87</v>
       </c>
@@ -3687,8 +3849,11 @@
       <c r="E55" s="6">
         <v>493.77</v>
       </c>
-    </row>
-    <row r="56" spans="1:5">
+      <c r="F55" s="6">
+        <v>493.77</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" s="2" t="s">
         <v>91</v>
       </c>
@@ -3704,8 +3869,11 @@
       <c r="E56" s="6">
         <v>566.28</v>
       </c>
-    </row>
-    <row r="57" spans="1:5">
+      <c r="F56" s="6">
+        <v>566.28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" s="2" t="s">
         <v>91</v>
       </c>
@@ -3721,8 +3889,11 @@
       <c r="E57" s="6">
         <v>991.24</v>
       </c>
-    </row>
-    <row r="58" spans="1:5">
+      <c r="F57" s="6">
+        <v>991.24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" s="2" t="s">
         <v>91</v>
       </c>
@@ -3738,8 +3909,11 @@
       <c r="E58" s="6">
         <v>620.66999999999996</v>
       </c>
-    </row>
-    <row r="59" spans="1:5">
+      <c r="F58" s="6">
+        <v>620.66999999999996</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" s="2" t="s">
         <v>91</v>
       </c>
@@ -3755,8 +3929,11 @@
       <c r="E59" s="6">
         <v>760.39</v>
       </c>
-    </row>
-    <row r="60" spans="1:5">
+      <c r="F59" s="6">
+        <v>760.39</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" s="2" t="s">
         <v>91</v>
       </c>
@@ -3772,8 +3949,11 @@
       <c r="E60" s="5">
         <v>2892.34</v>
       </c>
-    </row>
-    <row r="61" spans="1:5">
+      <c r="F60" s="5">
+        <v>2892.34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" s="2" t="s">
         <v>97</v>
       </c>
@@ -3789,8 +3969,11 @@
       <c r="E61" s="6">
         <v>304.39</v>
       </c>
-    </row>
-    <row r="62" spans="1:5">
+      <c r="F61" s="6">
+        <v>304.39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" s="2" t="s">
         <v>97</v>
       </c>
@@ -3806,8 +3989,11 @@
       <c r="E62" s="6">
         <v>412.14</v>
       </c>
-    </row>
-    <row r="63" spans="1:5">
+      <c r="F62" s="6">
+        <v>412.14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" s="2" t="s">
         <v>97</v>
       </c>
@@ -3823,8 +4009,11 @@
       <c r="E63" s="6">
         <v>298.94</v>
       </c>
-    </row>
-    <row r="64" spans="1:5">
+      <c r="F63" s="6">
+        <v>298.94</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" s="2" t="s">
         <v>97</v>
       </c>
@@ -3840,8 +4029,11 @@
       <c r="E64" s="6">
         <v>303.18</v>
       </c>
-    </row>
-    <row r="65" spans="1:5">
+      <c r="F64" s="6">
+        <v>303.18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" s="2" t="s">
         <v>97</v>
       </c>
@@ -3857,8 +4049,11 @@
       <c r="E65" s="6">
         <v>268.45999999999998</v>
       </c>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="F65" s="6">
+        <v>268.45999999999998</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" s="2" t="s">
         <v>97</v>
       </c>
@@ -3874,8 +4069,11 @@
       <c r="E66" s="6">
         <v>388.33</v>
       </c>
-    </row>
-    <row r="67" spans="1:5">
+      <c r="F66" s="6">
+        <v>388.33</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" s="2" t="s">
         <v>104</v>
       </c>
@@ -3891,8 +4089,11 @@
       <c r="E67" s="6">
         <v>250.3</v>
       </c>
-    </row>
-    <row r="68" spans="1:5">
+      <c r="F67" s="6">
+        <v>250.3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" s="2" t="s">
         <v>104</v>
       </c>
@@ -3908,8 +4109,11 @@
       <c r="E68" s="6">
         <v>198.84</v>
       </c>
-    </row>
-    <row r="69" spans="1:5">
+      <c r="F68" s="6">
+        <v>198.84</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" s="2" t="s">
         <v>107</v>
       </c>
@@ -3925,8 +4129,11 @@
       <c r="E69" s="6">
         <v>390.86</v>
       </c>
-    </row>
-    <row r="70" spans="1:5">
+      <c r="F69" s="6">
+        <v>390.86</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" s="2" t="s">
         <v>107</v>
       </c>
@@ -3942,8 +4149,11 @@
       <c r="E70" s="5">
         <v>4946.04</v>
       </c>
-    </row>
-    <row r="71" spans="1:5">
+      <c r="F70" s="5">
+        <v>4946.04</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" s="2" t="s">
         <v>107</v>
       </c>
@@ -3959,8 +4169,11 @@
       <c r="E71" s="5">
         <v>3164.86</v>
       </c>
-    </row>
-    <row r="72" spans="1:5">
+      <c r="F71" s="5">
+        <v>3164.86</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" s="2" t="s">
         <v>107</v>
       </c>
@@ -3976,8 +4189,11 @@
       <c r="E72" s="5">
         <v>2018.53</v>
       </c>
-    </row>
-    <row r="73" spans="1:5">
+      <c r="F72" s="5">
+        <v>2018.53</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" s="2" t="s">
         <v>107</v>
       </c>
@@ -3993,8 +4209,11 @@
       <c r="E73" s="6">
         <v>149.36000000000001</v>
       </c>
-    </row>
-    <row r="74" spans="1:5">
+      <c r="F73" s="6">
+        <v>149.36000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="2" t="s">
         <v>107</v>
       </c>
@@ -4010,8 +4229,11 @@
       <c r="E74" s="5">
         <v>1045.26</v>
       </c>
-    </row>
-    <row r="75" spans="1:5">
+      <c r="F74" s="5">
+        <v>1045.26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" s="2" t="s">
         <v>107</v>
       </c>
@@ -4027,8 +4249,11 @@
       <c r="E75" s="6">
         <v>65.459999999999994</v>
       </c>
-    </row>
-    <row r="76" spans="1:5">
+      <c r="F75" s="6">
+        <v>65.459999999999994</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" s="2" t="s">
         <v>119</v>
       </c>
@@ -4044,8 +4269,11 @@
       <c r="E76" s="6">
         <v>340.18</v>
       </c>
-    </row>
-    <row r="77" spans="1:5">
+      <c r="F76" s="6">
+        <v>340.18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" s="2" t="s">
         <v>119</v>
       </c>
@@ -4061,8 +4289,11 @@
       <c r="E77" s="6">
         <v>334.17</v>
       </c>
-    </row>
-    <row r="78" spans="1:5">
+      <c r="F77" s="6">
+        <v>334.17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="2" t="s">
         <v>119</v>
       </c>
@@ -4078,8 +4309,11 @@
       <c r="E78" s="6">
         <v>239.26</v>
       </c>
-    </row>
-    <row r="79" spans="1:5">
+      <c r="F78" s="6">
+        <v>239.26</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" s="2" t="s">
         <v>119</v>
       </c>
@@ -4095,8 +4329,11 @@
       <c r="E79" s="6">
         <v>490.77</v>
       </c>
-    </row>
-    <row r="80" spans="1:5">
+      <c r="F79" s="6">
+        <v>490.77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" s="2" t="s">
         <v>119</v>
       </c>
@@ -4112,8 +4349,11 @@
       <c r="E80" s="6">
         <v>384.88</v>
       </c>
-    </row>
-    <row r="81" spans="1:5">
+      <c r="F80" s="6">
+        <v>384.88</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" s="2" t="s">
         <v>119</v>
       </c>
@@ -4129,8 +4369,11 @@
       <c r="E81" s="6">
         <v>541.19000000000005</v>
       </c>
-    </row>
-    <row r="82" spans="1:5">
+      <c r="F81" s="6">
+        <v>541.19000000000005</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" s="2" t="s">
         <v>119</v>
       </c>
@@ -4146,8 +4389,11 @@
       <c r="E82" s="6">
         <v>411.95</v>
       </c>
-    </row>
-    <row r="83" spans="1:5">
+      <c r="F82" s="6">
+        <v>411.95</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83" s="2" t="s">
         <v>119</v>
       </c>
@@ -4163,8 +4409,11 @@
       <c r="E83" s="6">
         <v>363.47</v>
       </c>
-    </row>
-    <row r="84" spans="1:5">
+      <c r="F83" s="6">
+        <v>363.47</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" s="2" t="s">
         <v>119</v>
       </c>
@@ -4180,8 +4429,11 @@
       <c r="E84" s="5">
         <v>-1186.45</v>
       </c>
-    </row>
-    <row r="85" spans="1:5">
+      <c r="F84" s="5">
+        <v>-1186.45</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" s="2" t="s">
         <v>134</v>
       </c>
@@ -4197,8 +4449,11 @@
       <c r="E85" s="6">
         <v>952.17</v>
       </c>
-    </row>
-    <row r="86" spans="1:5">
+      <c r="F85" s="6">
+        <v>952.17</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" s="2" t="s">
         <v>137</v>
       </c>
@@ -4214,8 +4469,11 @@
       <c r="E86" s="5">
         <v>1000</v>
       </c>
-    </row>
-    <row r="87" spans="1:5">
+      <c r="F86" s="5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" s="2" t="s">
         <v>137</v>
       </c>
@@ -4231,8 +4489,11 @@
       <c r="E87" s="6">
         <v>842.01</v>
       </c>
-    </row>
-    <row r="88" spans="1:5">
+      <c r="F87" s="6">
+        <v>842.01</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" s="2" t="s">
         <v>137</v>
       </c>
@@ -4248,8 +4509,11 @@
       <c r="E88" s="6">
         <v>784.99</v>
       </c>
-    </row>
-    <row r="89" spans="1:5">
+      <c r="F88" s="6">
+        <v>784.99</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" s="2" t="s">
         <v>141</v>
       </c>
@@ -4265,8 +4529,11 @@
       <c r="E89" s="6">
         <v>777.09</v>
       </c>
-    </row>
-    <row r="90" spans="1:5">
+      <c r="F89" s="6">
+        <v>777.09</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" s="2" t="s">
         <v>143</v>
       </c>
@@ -4282,8 +4549,11 @@
       <c r="E90" s="5">
         <v>2416.3200000000002</v>
       </c>
-    </row>
-    <row r="91" spans="1:5">
+      <c r="F90" s="5">
+        <v>2416.3200000000002</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" s="2" t="s">
         <v>145</v>
       </c>
@@ -4299,8 +4569,11 @@
       <c r="E91" s="5">
         <v>1483.41</v>
       </c>
-    </row>
-    <row r="92" spans="1:5">
+      <c r="F91" s="5">
+        <v>1483.41</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" s="2" t="s">
         <v>145</v>
       </c>
@@ -4316,8 +4589,11 @@
       <c r="E92" s="6">
         <v>568.25</v>
       </c>
-    </row>
-    <row r="93" spans="1:5">
+      <c r="F92" s="6">
+        <v>568.25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" s="2" t="s">
         <v>145</v>
       </c>
@@ -4333,8 +4609,11 @@
       <c r="E93" s="6">
         <v>149.44</v>
       </c>
-    </row>
-    <row r="94" spans="1:5">
+      <c r="F93" s="6">
+        <v>149.44</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" s="2" t="s">
         <v>151</v>
       </c>
@@ -4350,8 +4629,11 @@
       <c r="E94" s="5">
         <v>1244.72</v>
       </c>
-    </row>
-    <row r="95" spans="1:5">
+      <c r="F94" s="5">
+        <v>1244.72</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" s="2" t="s">
         <v>151</v>
       </c>
@@ -4367,8 +4649,11 @@
       <c r="E95" s="6">
         <v>890.95</v>
       </c>
-    </row>
-    <row r="96" spans="1:5">
+      <c r="F95" s="6">
+        <v>890.95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" s="2" t="s">
         <v>151</v>
       </c>
@@ -4384,8 +4669,11 @@
       <c r="E96" s="6">
         <v>418.2</v>
       </c>
-    </row>
-    <row r="97" spans="1:5">
+      <c r="F96" s="6">
+        <v>418.2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="2" t="s">
         <v>151</v>
       </c>
@@ -4401,8 +4689,11 @@
       <c r="E97" s="6">
         <v>271.20999999999998</v>
       </c>
-    </row>
-    <row r="98" spans="1:5">
+      <c r="F97" s="6">
+        <v>271.20999999999998</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="2" t="s">
         <v>156</v>
       </c>
@@ -4418,8 +4709,11 @@
       <c r="E98" s="5">
         <v>4445.34</v>
       </c>
-    </row>
-    <row r="99" spans="1:5">
+      <c r="F98" s="5">
+        <v>4445.34</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="2" t="s">
         <v>156</v>
       </c>
@@ -4435,8 +4729,11 @@
       <c r="E99" s="5">
         <v>7737.85</v>
       </c>
-    </row>
-    <row r="100" spans="1:5">
+      <c r="F99" s="5">
+        <v>7737.85</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" s="2" t="s">
         <v>159</v>
       </c>
@@ -4452,8 +4749,11 @@
       <c r="E100" s="5">
         <v>5346.27</v>
       </c>
-    </row>
-    <row r="101" spans="1:5">
+      <c r="F100" s="5">
+        <v>5346.27</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101" s="2" t="s">
         <v>159</v>
       </c>
@@ -4469,8 +4769,11 @@
       <c r="E101" s="6">
         <v>301.58</v>
       </c>
-    </row>
-    <row r="102" spans="1:5">
+      <c r="F101" s="6">
+        <v>301.58</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" s="2" t="s">
         <v>159</v>
       </c>
@@ -4486,8 +4789,11 @@
       <c r="E102" s="6">
         <v>428.78</v>
       </c>
-    </row>
-    <row r="103" spans="1:5">
+      <c r="F102" s="6">
+        <v>428.78</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103" s="2" t="s">
         <v>159</v>
       </c>
@@ -4503,8 +4809,11 @@
       <c r="E103" s="5">
         <v>5152.92</v>
       </c>
-    </row>
-    <row r="104" spans="1:5">
+      <c r="F103" s="5">
+        <v>5152.92</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104" s="2" t="s">
         <v>159</v>
       </c>
@@ -4520,8 +4829,11 @@
       <c r="E104" s="6">
         <v>193.56</v>
       </c>
-    </row>
-    <row r="105" spans="1:5">
+      <c r="F104" s="6">
+        <v>193.56</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105" s="2" t="s">
         <v>159</v>
       </c>
@@ -4537,8 +4849,11 @@
       <c r="E105" s="6">
         <v>274.11</v>
       </c>
-    </row>
-    <row r="106" spans="1:5">
+      <c r="F105" s="6">
+        <v>274.11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106" s="2" t="s">
         <v>159</v>
       </c>
@@ -4554,8 +4869,11 @@
       <c r="E106" s="6">
         <v>551.74</v>
       </c>
-    </row>
-    <row r="107" spans="1:5">
+      <c r="F106" s="6">
+        <v>551.74</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
       <c r="A107" s="2" t="s">
         <v>159</v>
       </c>
@@ -4571,8 +4889,11 @@
       <c r="E107" s="5">
         <v>5257.39</v>
       </c>
-    </row>
-    <row r="108" spans="1:5">
+      <c r="F107" s="5">
+        <v>5257.39</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="2" t="s">
         <v>159</v>
       </c>
@@ -4588,8 +4909,11 @@
       <c r="E108" s="6">
         <v>190.03</v>
       </c>
-    </row>
-    <row r="109" spans="1:5">
+      <c r="F108" s="6">
+        <v>190.03</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="2" t="s">
         <v>159</v>
       </c>
@@ -4605,8 +4929,11 @@
       <c r="E109" s="5">
         <v>-10410.31</v>
       </c>
-    </row>
-    <row r="110" spans="1:5">
+      <c r="F109" s="5">
+        <v>-10410.31</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110" s="2" t="s">
         <v>178</v>
       </c>
@@ -4622,8 +4949,11 @@
       <c r="E110" s="5">
         <v>2056.79</v>
       </c>
-    </row>
-    <row r="111" spans="1:5">
+      <c r="F110" s="5">
+        <v>2056.79</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" s="2" t="s">
         <v>178</v>
       </c>
@@ -4639,8 +4969,11 @@
       <c r="E111" s="6">
         <v>684.26</v>
       </c>
-    </row>
-    <row r="112" spans="1:5">
+      <c r="F111" s="6">
+        <v>684.26</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
       <c r="A112" s="2" t="s">
         <v>178</v>
       </c>
@@ -4656,8 +4989,11 @@
       <c r="E112" s="6">
         <v>398.08</v>
       </c>
-    </row>
-    <row r="113" spans="1:5">
+      <c r="F112" s="6">
+        <v>398.08</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" s="2" t="s">
         <v>183</v>
       </c>
@@ -4673,8 +5009,11 @@
       <c r="E113" s="5">
         <v>3684.84</v>
       </c>
-    </row>
-    <row r="114" spans="1:5">
+      <c r="F113" s="5">
+        <v>3684.84</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" s="2" t="s">
         <v>183</v>
       </c>
@@ -4690,8 +5029,11 @@
       <c r="E114" s="5">
         <v>1778.88</v>
       </c>
-    </row>
-    <row r="115" spans="1:5">
+      <c r="F114" s="5">
+        <v>1778.88</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="2" t="s">
         <v>186</v>
       </c>
@@ -4707,8 +5049,11 @@
       <c r="E115" s="5">
         <v>1628.31</v>
       </c>
-    </row>
-    <row r="116" spans="1:5">
+      <c r="F115" s="5">
+        <v>1628.31</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" s="2" t="s">
         <v>186</v>
       </c>
@@ -4724,8 +5069,11 @@
       <c r="E116" s="6">
         <v>284.56</v>
       </c>
-    </row>
-    <row r="117" spans="1:5">
+      <c r="F116" s="6">
+        <v>284.56</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" s="2" t="s">
         <v>186</v>
       </c>
@@ -4741,8 +5089,11 @@
       <c r="E117" s="6">
         <v>960.11</v>
       </c>
-    </row>
-    <row r="118" spans="1:5">
+      <c r="F117" s="6">
+        <v>960.11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" s="2" t="s">
         <v>186</v>
       </c>
@@ -4758,8 +5109,11 @@
       <c r="E118" s="5">
         <v>3627.02</v>
       </c>
-    </row>
-    <row r="119" spans="1:5">
+      <c r="F118" s="5">
+        <v>3627.02</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" s="2" t="s">
         <v>191</v>
       </c>
@@ -4775,8 +5129,11 @@
       <c r="E119" s="6">
         <v>631.35</v>
       </c>
-    </row>
-    <row r="120" spans="1:5">
+      <c r="F119" s="6">
+        <v>631.35</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" s="2" t="s">
         <v>193</v>
       </c>
@@ -4792,8 +5149,11 @@
       <c r="E120" s="5">
         <v>4148.4399999999996</v>
       </c>
-    </row>
-    <row r="121" spans="1:5">
+      <c r="F120" s="5">
+        <v>4148.4399999999996</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" s="2" t="s">
         <v>193</v>
       </c>
@@ -4809,8 +5169,11 @@
       <c r="E121" s="5">
         <v>2326.6</v>
       </c>
-    </row>
-    <row r="122" spans="1:5">
+      <c r="F121" s="5">
+        <v>2326.6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" s="2" t="s">
         <v>197</v>
       </c>
@@ -4826,8 +5189,11 @@
       <c r="E122" s="6">
         <v>287.98</v>
       </c>
-    </row>
-    <row r="123" spans="1:5">
+      <c r="F122" s="6">
+        <v>287.98</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" s="2" t="s">
         <v>197</v>
       </c>
@@ -4843,8 +5209,11 @@
       <c r="E123" s="6">
         <v>461.38</v>
       </c>
-    </row>
-    <row r="124" spans="1:5">
+      <c r="F123" s="6">
+        <v>461.38</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" s="2" t="s">
         <v>197</v>
       </c>
@@ -4860,8 +5229,11 @@
       <c r="E124" s="6">
         <v>316.27</v>
       </c>
-    </row>
-    <row r="125" spans="1:5">
+      <c r="F124" s="6">
+        <v>316.27</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" s="2" t="s">
         <v>197</v>
       </c>
@@ -4877,8 +5249,11 @@
       <c r="E125" s="6">
         <v>262.48</v>
       </c>
-    </row>
-    <row r="126" spans="1:5">
+      <c r="F125" s="6">
+        <v>262.48</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" s="2" t="s">
         <v>197</v>
       </c>
@@ -4894,8 +5269,11 @@
       <c r="E126" s="6">
         <v>219.43</v>
       </c>
-    </row>
-    <row r="127" spans="1:5">
+      <c r="F126" s="6">
+        <v>219.43</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" s="2" t="s">
         <v>197</v>
       </c>
@@ -4911,8 +5289,11 @@
       <c r="E127" s="6">
         <v>261.86</v>
       </c>
-    </row>
-    <row r="128" spans="1:5">
+      <c r="F127" s="6">
+        <v>261.86</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" s="2" t="s">
         <v>197</v>
       </c>
@@ -4928,8 +5309,11 @@
       <c r="E128" s="6">
         <v>455.71</v>
       </c>
-    </row>
-    <row r="129" spans="1:5">
+      <c r="F128" s="6">
+        <v>455.71</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
       <c r="A129" s="2" t="s">
         <v>206</v>
       </c>
@@ -4945,8 +5329,11 @@
       <c r="E129" s="5">
         <v>2513.7600000000002</v>
       </c>
-    </row>
-    <row r="130" spans="1:5">
+      <c r="F129" s="5">
+        <v>2513.7600000000002</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
       <c r="A130" s="2" t="s">
         <v>206</v>
       </c>
@@ -4962,8 +5349,11 @@
       <c r="E130" s="5">
         <v>2820.19</v>
       </c>
-    </row>
-    <row r="131" spans="1:5">
+      <c r="F130" s="5">
+        <v>2820.19</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="A131" s="2" t="s">
         <v>206</v>
       </c>
@@ -4979,8 +5369,11 @@
       <c r="E131" s="5">
         <v>5665.62</v>
       </c>
-    </row>
-    <row r="132" spans="1:5">
+      <c r="F131" s="5">
+        <v>5665.62</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
       <c r="A132" s="2" t="s">
         <v>212</v>
       </c>
@@ -4996,8 +5389,11 @@
       <c r="E132" s="6">
         <v>168.97</v>
       </c>
-    </row>
-    <row r="133" spans="1:5">
+      <c r="F132" s="6">
+        <v>168.97</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
       <c r="A133" s="2" t="s">
         <v>212</v>
       </c>
@@ -5013,8 +5409,11 @@
       <c r="E133" s="5">
         <v>8875.52</v>
       </c>
-    </row>
-    <row r="134" spans="1:5">
+      <c r="F133" s="5">
+        <v>8875.52</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
       <c r="A134" s="2" t="s">
         <v>212</v>
       </c>
@@ -5030,8 +5429,11 @@
       <c r="E134" s="6">
         <v>537.76</v>
       </c>
-    </row>
-    <row r="135" spans="1:5">
+      <c r="F134" s="6">
+        <v>537.76</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
       <c r="A135" s="2" t="s">
         <v>212</v>
       </c>
@@ -5047,8 +5449,11 @@
       <c r="E135" s="6">
         <v>168.97</v>
       </c>
-    </row>
-    <row r="136" spans="1:5">
+      <c r="F135" s="6">
+        <v>168.97</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
       <c r="A136" s="2" t="s">
         <v>212</v>
       </c>
@@ -5064,8 +5469,11 @@
       <c r="E136" s="5">
         <v>6864.42</v>
       </c>
-    </row>
-    <row r="137" spans="1:5">
+      <c r="F136" s="5">
+        <v>6864.42</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="A137" s="2" t="s">
         <v>218</v>
       </c>
@@ -5081,8 +5489,11 @@
       <c r="E137" s="6">
         <v>340.09</v>
       </c>
-    </row>
-    <row r="138" spans="1:5">
+      <c r="F137" s="6">
+        <v>340.09</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="A138" s="2" t="s">
         <v>220</v>
       </c>
@@ -5098,8 +5509,11 @@
       <c r="E138" s="6">
         <v>735.97</v>
       </c>
-    </row>
-    <row r="139" spans="1:5">
+      <c r="F138" s="6">
+        <v>735.97</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="A139" s="2" t="s">
         <v>222</v>
       </c>
@@ -5115,8 +5529,11 @@
       <c r="E139" s="6">
         <v>378.31</v>
       </c>
-    </row>
-    <row r="140" spans="1:5">
+      <c r="F139" s="6">
+        <v>378.31</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
       <c r="A140" s="2" t="s">
         <v>224</v>
       </c>
@@ -5132,8 +5549,11 @@
       <c r="E140" s="5">
         <v>1214.3800000000001</v>
       </c>
-    </row>
-    <row r="141" spans="1:5">
+      <c r="F140" s="5">
+        <v>1214.3800000000001</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
       <c r="A141" s="2" t="s">
         <v>224</v>
       </c>
@@ -5149,8 +5569,11 @@
       <c r="E141" s="6">
         <v>990.84</v>
       </c>
-    </row>
-    <row r="142" spans="1:5">
+      <c r="F141" s="6">
+        <v>990.84</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="A142" s="2" t="s">
         <v>227</v>
       </c>
@@ -5166,8 +5589,11 @@
       <c r="E142" s="5">
         <v>1533.02</v>
       </c>
-    </row>
-    <row r="143" spans="1:5">
+      <c r="F142" s="5">
+        <v>1533.02</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143" s="2" t="s">
         <v>227</v>
       </c>
@@ -5183,8 +5609,11 @@
       <c r="E143" s="5">
         <v>1263.92</v>
       </c>
-    </row>
-    <row r="144" spans="1:5">
+      <c r="F143" s="5">
+        <v>1263.92</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="A144" s="2" t="s">
         <v>227</v>
       </c>
@@ -5200,8 +5629,11 @@
       <c r="E144" s="5">
         <v>1951.27</v>
       </c>
-    </row>
-    <row r="145" spans="1:5">
+      <c r="F144" s="5">
+        <v>1951.27</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
       <c r="A145" s="2" t="s">
         <v>231</v>
       </c>
@@ -5217,8 +5649,11 @@
       <c r="E145" s="6">
         <v>-36.4</v>
       </c>
-    </row>
-    <row r="146" spans="1:5">
+      <c r="F145" s="6">
+        <v>-36.4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
       <c r="A146" s="2" t="s">
         <v>231</v>
       </c>
@@ -5234,8 +5669,11 @@
       <c r="E146" s="6">
         <v>328.58</v>
       </c>
-    </row>
-    <row r="147" spans="1:5">
+      <c r="F146" s="6">
+        <v>328.58</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
       <c r="A147" s="2" t="s">
         <v>231</v>
       </c>
@@ -5251,8 +5689,11 @@
       <c r="E147" s="6">
         <v>675.45</v>
       </c>
-    </row>
-    <row r="148" spans="1:5">
+      <c r="F147" s="6">
+        <v>675.45</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
       <c r="A148" s="2" t="s">
         <v>231</v>
       </c>
@@ -5268,8 +5709,11 @@
       <c r="E148" s="6">
         <v>384.17</v>
       </c>
-    </row>
-    <row r="149" spans="1:5">
+      <c r="F148" s="6">
+        <v>384.17</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
       <c r="A149" s="2" t="s">
         <v>231</v>
       </c>
@@ -5285,8 +5729,11 @@
       <c r="E149" s="6">
         <v>483.88</v>
       </c>
-    </row>
-    <row r="150" spans="1:5">
+      <c r="F149" s="6">
+        <v>483.88</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
       <c r="A150" s="2" t="s">
         <v>231</v>
       </c>
@@ -5302,8 +5749,11 @@
       <c r="E150" s="6">
         <v>569.72</v>
       </c>
-    </row>
-    <row r="151" spans="1:5">
+      <c r="F150" s="6">
+        <v>569.72</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
       <c r="A151" s="2" t="s">
         <v>231</v>
       </c>
@@ -5319,8 +5769,11 @@
       <c r="E151" s="6">
         <v>-129.77000000000001</v>
       </c>
-    </row>
-    <row r="152" spans="1:5">
+      <c r="F151" s="6">
+        <v>-129.77000000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
       <c r="A152" s="2" t="s">
         <v>231</v>
       </c>
@@ -5336,8 +5789,11 @@
       <c r="E152" s="6">
         <v>667.9</v>
       </c>
-    </row>
-    <row r="153" spans="1:5">
+      <c r="F152" s="6">
+        <v>667.9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
       <c r="A153" s="2" t="s">
         <v>242</v>
       </c>
@@ -5353,8 +5809,11 @@
       <c r="E153" s="5">
         <v>1379.09</v>
       </c>
-    </row>
-    <row r="154" spans="1:5">
+      <c r="F153" s="5">
+        <v>1379.09</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
       <c r="A154" s="2" t="s">
         <v>244</v>
       </c>
@@ -5370,8 +5829,11 @@
       <c r="E154" s="6">
         <v>512.16999999999996</v>
       </c>
-    </row>
-    <row r="155" spans="1:5">
+      <c r="F154" s="6">
+        <v>512.16999999999996</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
       <c r="A155" s="2" t="s">
         <v>244</v>
       </c>
@@ -5387,8 +5849,11 @@
       <c r="E155" s="5">
         <v>1894.18</v>
       </c>
-    </row>
-    <row r="156" spans="1:5">
+      <c r="F155" s="5">
+        <v>1894.18</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
       <c r="A156" s="2" t="s">
         <v>244</v>
       </c>
@@ -5404,8 +5869,11 @@
       <c r="E156" s="6">
         <v>576.96</v>
       </c>
-    </row>
-    <row r="157" spans="1:5">
+      <c r="F156" s="6">
+        <v>576.96</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
       <c r="A157" s="2" t="s">
         <v>244</v>
       </c>
@@ -5421,8 +5889,11 @@
       <c r="E157" s="6">
         <v>881.9</v>
       </c>
-    </row>
-    <row r="158" spans="1:5">
+      <c r="F157" s="6">
+        <v>881.9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
       <c r="A158" s="2" t="s">
         <v>249</v>
       </c>
@@ -5438,8 +5909,11 @@
       <c r="E158" s="5">
         <v>2126.33</v>
       </c>
-    </row>
-    <row r="159" spans="1:5">
+      <c r="F158" s="5">
+        <v>2126.33</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
       <c r="A159" s="2" t="s">
         <v>249</v>
       </c>
@@ -5455,8 +5929,11 @@
       <c r="E159" s="6">
         <v>216</v>
       </c>
-    </row>
-    <row r="160" spans="1:5">
+      <c r="F159" s="6">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
       <c r="A160" s="2" t="s">
         <v>249</v>
       </c>
@@ -5472,8 +5949,11 @@
       <c r="E160" s="6">
         <v>251.63</v>
       </c>
-    </row>
-    <row r="161" spans="1:5">
+      <c r="F160" s="6">
+        <v>251.63</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
       <c r="A161" s="2" t="s">
         <v>255</v>
       </c>
@@ -5489,8 +5969,11 @@
       <c r="E161" s="6">
         <v>245.39</v>
       </c>
-    </row>
-    <row r="162" spans="1:5">
+      <c r="F161" s="6">
+        <v>245.39</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
       <c r="A162" s="2" t="s">
         <v>257</v>
       </c>
@@ -5506,8 +5989,11 @@
       <c r="E162" s="6">
         <v>395.77</v>
       </c>
-    </row>
-    <row r="163" spans="1:5">
+      <c r="F162" s="6">
+        <v>395.77</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
       <c r="A163" s="2" t="s">
         <v>257</v>
       </c>
@@ -5523,8 +6009,11 @@
       <c r="E163" s="5">
         <v>1551.64</v>
       </c>
-    </row>
-    <row r="164" spans="1:5">
+      <c r="F163" s="5">
+        <v>1551.64</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="A164" s="2" t="s">
         <v>257</v>
       </c>
@@ -5540,8 +6029,11 @@
       <c r="E164" s="6">
         <v>328.76</v>
       </c>
-    </row>
-    <row r="165" spans="1:5">
+      <c r="F164" s="6">
+        <v>328.76</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
       <c r="A165" s="2" t="s">
         <v>257</v>
       </c>
@@ -5557,8 +6049,11 @@
       <c r="E165" s="6">
         <v>466.08</v>
       </c>
-    </row>
-    <row r="166" spans="1:5">
+      <c r="F165" s="6">
+        <v>466.08</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
       <c r="A166" s="2" t="s">
         <v>262</v>
       </c>
@@ -5574,8 +6069,11 @@
       <c r="E166" s="6">
         <v>343.26</v>
       </c>
-    </row>
-    <row r="167" spans="1:5">
+      <c r="F166" s="6">
+        <v>343.26</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
       <c r="A167" s="2" t="s">
         <v>262</v>
       </c>
@@ -5591,8 +6089,11 @@
       <c r="E167" s="6">
         <v>173.03</v>
       </c>
-    </row>
-    <row r="168" spans="1:5">
+      <c r="F167" s="6">
+        <v>173.03</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="A168" s="2" t="s">
         <v>262</v>
       </c>
@@ -5608,8 +6109,11 @@
       <c r="E168" s="5">
         <v>1185.02</v>
       </c>
-    </row>
-    <row r="169" spans="1:5">
+      <c r="F168" s="5">
+        <v>1185.02</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
       <c r="A169" s="2" t="s">
         <v>262</v>
       </c>
@@ -5625,8 +6129,11 @@
       <c r="E169" s="6">
         <v>172.87</v>
       </c>
-    </row>
-    <row r="170" spans="1:5">
+      <c r="F169" s="6">
+        <v>172.87</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
       <c r="A170" s="2" t="s">
         <v>267</v>
       </c>
@@ -5642,8 +6149,11 @@
       <c r="E170" s="6">
         <v>795.21</v>
       </c>
-    </row>
-    <row r="171" spans="1:5">
+      <c r="F170" s="6">
+        <v>795.21</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
       <c r="A171" s="2" t="s">
         <v>267</v>
       </c>
@@ -5659,8 +6169,11 @@
       <c r="E171" s="6">
         <v>603.02</v>
       </c>
-    </row>
-    <row r="172" spans="1:5">
+      <c r="F171" s="6">
+        <v>603.02</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
       <c r="A172" s="2" t="s">
         <v>267</v>
       </c>
@@ -5676,8 +6189,11 @@
       <c r="E172" s="6">
         <v>316.20999999999998</v>
       </c>
-    </row>
-    <row r="173" spans="1:5">
+      <c r="F172" s="6">
+        <v>316.20999999999998</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
       <c r="A173" s="2" t="s">
         <v>267</v>
       </c>
@@ -5693,8 +6209,11 @@
       <c r="E173" s="6">
         <v>775.8</v>
       </c>
-    </row>
-    <row r="174" spans="1:5">
+      <c r="F173" s="6">
+        <v>775.8</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
       <c r="A174" s="2" t="s">
         <v>272</v>
       </c>
@@ -5710,8 +6229,11 @@
       <c r="E174" s="5">
         <v>1691.89</v>
       </c>
-    </row>
-    <row r="175" spans="1:5">
+      <c r="F174" s="5">
+        <v>1691.89</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
       <c r="A175" s="2" t="s">
         <v>272</v>
       </c>
@@ -5727,8 +6249,11 @@
       <c r="E175" s="6">
         <v>401.14</v>
       </c>
-    </row>
-    <row r="176" spans="1:5">
+      <c r="F175" s="6">
+        <v>401.14</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
       <c r="A176" s="2" t="s">
         <v>272</v>
       </c>
@@ -5744,8 +6269,11 @@
       <c r="E176" s="6">
         <v>603.80999999999995</v>
       </c>
-    </row>
-    <row r="177" spans="1:5">
+      <c r="F176" s="6">
+        <v>603.80999999999995</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
       <c r="A177" s="2" t="s">
         <v>272</v>
       </c>
@@ -5761,8 +6289,11 @@
       <c r="E177" s="6">
         <v>401.14</v>
       </c>
-    </row>
-    <row r="178" spans="1:5">
+      <c r="F177" s="6">
+        <v>401.14</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
       <c r="A178" s="2" t="s">
         <v>272</v>
       </c>
@@ -5778,8 +6309,11 @@
       <c r="E178" s="6">
         <v>429.91</v>
       </c>
-    </row>
-    <row r="179" spans="1:5">
+      <c r="F178" s="6">
+        <v>429.91</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
       <c r="A179" s="2" t="s">
         <v>278</v>
       </c>
@@ -5795,8 +6329,11 @@
       <c r="E179" s="5">
         <v>3528.34</v>
       </c>
-    </row>
-    <row r="180" spans="1:5">
+      <c r="F179" s="5">
+        <v>3528.34</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
       <c r="A180" s="2" t="s">
         <v>281</v>
       </c>
@@ -5812,8 +6349,11 @@
       <c r="E180" s="5">
         <v>10726.46</v>
       </c>
-    </row>
-    <row r="181" spans="1:5">
+      <c r="F180" s="5">
+        <v>10726.46</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
       <c r="A181" s="2" t="s">
         <v>281</v>
       </c>
@@ -5829,8 +6369,11 @@
       <c r="E181" s="5">
         <v>2086.77</v>
       </c>
-    </row>
-    <row r="182" spans="1:5">
+      <c r="F181" s="5">
+        <v>2086.77</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
       <c r="A182" s="2" t="s">
         <v>281</v>
       </c>
@@ -5846,8 +6389,11 @@
       <c r="E182" s="5">
         <v>1100.7</v>
       </c>
-    </row>
-    <row r="183" spans="1:5">
+      <c r="F182" s="5">
+        <v>1100.7</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
       <c r="A183" s="2" t="s">
         <v>281</v>
       </c>
@@ -5863,8 +6409,11 @@
       <c r="E183" s="5">
         <v>2201.4</v>
       </c>
-    </row>
-    <row r="184" spans="1:5">
+      <c r="F183" s="5">
+        <v>2201.4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
       <c r="A184" s="2" t="s">
         <v>281</v>
       </c>
@@ -5880,8 +6429,11 @@
       <c r="E184" s="6">
         <v>376.95</v>
       </c>
-    </row>
-    <row r="185" spans="1:5">
+      <c r="F184" s="6">
+        <v>376.95</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
       <c r="A185" s="2" t="s">
         <v>281</v>
       </c>
@@ -5897,8 +6449,11 @@
       <c r="E185" s="6">
         <v>295.83</v>
       </c>
-    </row>
-    <row r="186" spans="1:5">
+      <c r="F185" s="6">
+        <v>295.83</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
       <c r="A186" s="2" t="s">
         <v>288</v>
       </c>
@@ -5914,8 +6469,11 @@
       <c r="E186" s="6">
         <v>172.82</v>
       </c>
-    </row>
-    <row r="187" spans="1:5">
+      <c r="F186" s="6">
+        <v>172.82</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
       <c r="A187" s="2" t="s">
         <v>288</v>
       </c>
@@ -5931,8 +6489,11 @@
       <c r="E187" s="6">
         <v>161.83000000000001</v>
       </c>
-    </row>
-    <row r="188" spans="1:5">
+      <c r="F187" s="6">
+        <v>161.83000000000001</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
       <c r="A188" s="2" t="s">
         <v>288</v>
       </c>
@@ -5948,8 +6509,11 @@
       <c r="E188" s="6">
         <v>466.44</v>
       </c>
-    </row>
-    <row r="189" spans="1:5">
+      <c r="F188" s="6">
+        <v>466.44</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
       <c r="A189" s="2" t="s">
         <v>288</v>
       </c>
@@ -5965,8 +6529,11 @@
       <c r="E189" s="6">
         <v>311.14999999999998</v>
       </c>
-    </row>
-    <row r="190" spans="1:5">
+      <c r="F189" s="6">
+        <v>311.14999999999998</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
       <c r="A190" s="2" t="s">
         <v>288</v>
       </c>
@@ -5982,8 +6549,11 @@
       <c r="E190" s="6">
         <v>391.05</v>
       </c>
-    </row>
-    <row r="191" spans="1:5">
+      <c r="F190" s="6">
+        <v>391.05</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
       <c r="A191" s="2" t="s">
         <v>288</v>
       </c>
@@ -5999,8 +6569,11 @@
       <c r="E191" s="6">
         <v>418.15</v>
       </c>
-    </row>
-    <row r="192" spans="1:5">
+      <c r="F191" s="6">
+        <v>418.15</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
       <c r="A192" s="2" t="s">
         <v>288</v>
       </c>
@@ -6016,8 +6589,11 @@
       <c r="E192" s="6">
         <v>93.82</v>
       </c>
-    </row>
-    <row r="193" spans="1:5">
+      <c r="F192" s="6">
+        <v>93.82</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
       <c r="A193" s="2" t="s">
         <v>288</v>
       </c>
@@ -6033,8 +6609,11 @@
       <c r="E193" s="6">
         <v>404.89</v>
       </c>
-    </row>
-    <row r="194" spans="1:5">
+      <c r="F193" s="6">
+        <v>404.89</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
       <c r="A194" s="2" t="s">
         <v>288</v>
       </c>
@@ -6050,8 +6629,11 @@
       <c r="E194" s="6">
         <v>398.26</v>
       </c>
-    </row>
-    <row r="195" spans="1:5">
+      <c r="F194" s="6">
+        <v>398.26</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
       <c r="A195" s="2" t="s">
         <v>288</v>
       </c>
@@ -6067,8 +6649,11 @@
       <c r="E195" s="6">
         <v>261.86</v>
       </c>
-    </row>
-    <row r="196" spans="1:5">
+      <c r="F195" s="6">
+        <v>261.86</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
       <c r="A196" s="2" t="s">
         <v>300</v>
       </c>
@@ -6084,8 +6669,11 @@
       <c r="E196" s="5">
         <v>1583.6</v>
       </c>
-    </row>
-    <row r="197" spans="1:5">
+      <c r="F196" s="5">
+        <v>1583.6</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
       <c r="A197" s="2" t="s">
         <v>302</v>
       </c>
@@ -6101,8 +6689,11 @@
       <c r="E197" s="6">
         <v>356.1</v>
       </c>
-    </row>
-    <row r="198" spans="1:5">
+      <c r="F197" s="6">
+        <v>356.1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
       <c r="A198" s="2" t="s">
         <v>302</v>
       </c>
@@ -6118,8 +6709,11 @@
       <c r="E198" s="6">
         <v>467.44</v>
       </c>
-    </row>
-    <row r="199" spans="1:5">
+      <c r="F198" s="6">
+        <v>467.44</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
       <c r="A199" s="2" t="s">
         <v>302</v>
       </c>
@@ -6135,8 +6729,11 @@
       <c r="E199" s="6">
         <v>271.20999999999998</v>
       </c>
-    </row>
-    <row r="200" spans="1:5">
+      <c r="F199" s="6">
+        <v>271.20999999999998</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
       <c r="A200" s="2" t="s">
         <v>306</v>
       </c>
@@ -6152,8 +6749,11 @@
       <c r="E200" s="5">
         <v>3153.65</v>
       </c>
-    </row>
-    <row r="201" spans="1:5">
+      <c r="F200" s="5">
+        <v>3153.65</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
       <c r="A201" s="2" t="s">
         <v>306</v>
       </c>
@@ -6169,8 +6769,11 @@
       <c r="E201" s="5">
         <v>2741.2</v>
       </c>
-    </row>
-    <row r="202" spans="1:5">
+      <c r="F201" s="5">
+        <v>2741.2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
       <c r="A202" s="2" t="s">
         <v>306</v>
       </c>
@@ -6186,8 +6789,11 @@
       <c r="E202" s="6">
         <v>734.31</v>
       </c>
-    </row>
-    <row r="203" spans="1:5">
+      <c r="F202" s="6">
+        <v>734.31</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
       <c r="A203" s="2" t="s">
         <v>306</v>
       </c>
@@ -6203,8 +6809,11 @@
       <c r="E203" s="5">
         <v>2820.19</v>
       </c>
-    </row>
-    <row r="204" spans="1:5">
+      <c r="F203" s="5">
+        <v>2820.19</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
       <c r="A204" s="2" t="s">
         <v>306</v>
       </c>
@@ -6220,8 +6829,11 @@
       <c r="E204" s="5">
         <v>2741.2</v>
       </c>
-    </row>
-    <row r="205" spans="1:5">
+      <c r="F204" s="5">
+        <v>2741.2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
       <c r="A205" s="2" t="s">
         <v>312</v>
       </c>
@@ -6237,8 +6849,11 @@
       <c r="E205" s="5">
         <v>3744.87</v>
       </c>
-    </row>
-    <row r="206" spans="1:5">
+      <c r="F205" s="5">
+        <v>3744.87</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
       <c r="A206" s="2" t="s">
         <v>312</v>
       </c>
@@ -6254,8 +6869,11 @@
       <c r="E206" s="6">
         <v>960.45</v>
       </c>
-    </row>
-    <row r="207" spans="1:5">
+      <c r="F206" s="6">
+        <v>960.45</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
       <c r="A207" s="2" t="s">
         <v>312</v>
       </c>
@@ -6271,8 +6889,11 @@
       <c r="E207" s="6">
         <v>776.13</v>
       </c>
-    </row>
-    <row r="208" spans="1:5">
+      <c r="F207" s="6">
+        <v>776.13</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
       <c r="A208" s="2" t="s">
         <v>316</v>
       </c>
@@ -6288,8 +6909,11 @@
       <c r="E208" s="6">
         <v>836.17</v>
       </c>
-    </row>
-    <row r="209" spans="1:5">
+      <c r="F208" s="6">
+        <v>836.17</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
       <c r="A209" s="2" t="s">
         <v>316</v>
       </c>
@@ -6305,8 +6929,11 @@
       <c r="E209" s="6">
         <v>738.85</v>
       </c>
-    </row>
-    <row r="210" spans="1:5">
+      <c r="F209" s="6">
+        <v>738.85</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
       <c r="A210" s="2" t="s">
         <v>319</v>
       </c>
@@ -6322,8 +6949,11 @@
       <c r="E210" s="5">
         <v>5514.78</v>
       </c>
-    </row>
-    <row r="211" spans="1:5">
+      <c r="F210" s="5">
+        <v>5514.78</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
       <c r="A211" s="2" t="s">
         <v>319</v>
       </c>
@@ -6339,8 +6969,11 @@
       <c r="E211" s="5">
         <v>1142.45</v>
       </c>
-    </row>
-    <row r="212" spans="1:5">
+      <c r="F211" s="5">
+        <v>1142.45</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
       <c r="A212" s="2" t="s">
         <v>322</v>
       </c>
@@ -6356,8 +6989,11 @@
       <c r="E212" s="6">
         <v>139.82</v>
       </c>
-    </row>
-    <row r="213" spans="1:5">
+      <c r="F212" s="6">
+        <v>139.82</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
       <c r="A213" s="2" t="s">
         <v>322</v>
       </c>
@@ -6373,8 +7009,11 @@
       <c r="E213" s="6">
         <v>316.56</v>
       </c>
-    </row>
-    <row r="214" spans="1:5">
+      <c r="F213" s="6">
+        <v>316.56</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
       <c r="A214" s="2" t="s">
         <v>322</v>
       </c>
@@ -6390,8 +7029,11 @@
       <c r="E214" s="6">
         <v>537.76</v>
       </c>
-    </row>
-    <row r="215" spans="1:5">
+      <c r="F214" s="6">
+        <v>537.76</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
       <c r="A215" s="2" t="s">
         <v>322</v>
       </c>
@@ -6407,8 +7049,11 @@
       <c r="E215" s="6">
         <v>633.1</v>
       </c>
-    </row>
-    <row r="216" spans="1:5">
+      <c r="F215" s="6">
+        <v>633.1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
       <c r="A216" s="2" t="s">
         <v>322</v>
       </c>
@@ -6424,8 +7069,11 @@
       <c r="E216" s="6">
         <v>250.31</v>
       </c>
-    </row>
-    <row r="217" spans="1:5">
+      <c r="F216" s="6">
+        <v>250.31</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
       <c r="A217" s="2" t="s">
         <v>329</v>
       </c>
@@ -6441,8 +7089,11 @@
       <c r="E217" s="6">
         <v>173.03</v>
       </c>
-    </row>
-    <row r="218" spans="1:5">
+      <c r="F217" s="6">
+        <v>173.03</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
       <c r="A218" s="2" t="s">
         <v>329</v>
       </c>
@@ -6458,8 +7109,11 @@
       <c r="E218" s="6">
         <v>597.47</v>
       </c>
-    </row>
-    <row r="219" spans="1:5">
+      <c r="F218" s="6">
+        <v>597.47</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
       <c r="A219" s="2" t="s">
         <v>332</v>
       </c>
@@ -6475,8 +7129,11 @@
       <c r="E219" s="6">
         <v>216.29</v>
       </c>
-    </row>
-    <row r="220" spans="1:5">
+      <c r="F219" s="6">
+        <v>216.29</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
       <c r="A220" s="2" t="s">
         <v>332</v>
       </c>
@@ -6492,8 +7149,11 @@
       <c r="E220" s="5">
         <v>4007.37</v>
       </c>
-    </row>
-    <row r="221" spans="1:5">
+      <c r="F220" s="5">
+        <v>4007.37</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
       <c r="A221" s="2" t="s">
         <v>335</v>
       </c>
@@ -6509,8 +7169,11 @@
       <c r="E221" s="5">
         <v>1263.92</v>
       </c>
-    </row>
-    <row r="222" spans="1:5">
+      <c r="F221" s="5">
+        <v>1263.92</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
       <c r="A222" s="2" t="s">
         <v>335</v>
       </c>
@@ -6526,8 +7189,11 @@
       <c r="E222" s="6">
         <v>188.76</v>
       </c>
-    </row>
-    <row r="223" spans="1:5">
+      <c r="F222" s="6">
+        <v>188.76</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
       <c r="A223" s="2" t="s">
         <v>335</v>
       </c>
@@ -6543,8 +7209,11 @@
       <c r="E223" s="6">
         <v>323.64999999999998</v>
       </c>
-    </row>
-    <row r="224" spans="1:5">
+      <c r="F223" s="6">
+        <v>323.64999999999998</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
       <c r="A224" s="2" t="s">
         <v>339</v>
       </c>
@@ -6560,8 +7229,11 @@
       <c r="E224" s="5">
         <v>1566.69</v>
       </c>
-    </row>
-    <row r="225" spans="1:5">
+      <c r="F224" s="5">
+        <v>1566.69</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
       <c r="A225" s="2" t="s">
         <v>339</v>
       </c>
@@ -6577,8 +7249,11 @@
       <c r="E225" s="5">
         <v>1170.03</v>
       </c>
-    </row>
-    <row r="226" spans="1:5">
+      <c r="F225" s="5">
+        <v>1170.03</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
       <c r="A226" s="2" t="s">
         <v>339</v>
       </c>
@@ -6594,8 +7269,11 @@
       <c r="E226" s="5">
         <v>1548.06</v>
       </c>
-    </row>
-    <row r="227" spans="1:5">
+      <c r="F226" s="5">
+        <v>1548.06</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
       <c r="A227" s="2" t="s">
         <v>339</v>
       </c>
@@ -6611,8 +7289,11 @@
       <c r="E227" s="6">
         <v>162.1</v>
       </c>
-    </row>
-    <row r="228" spans="1:5">
+      <c r="F227" s="6">
+        <v>162.1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
       <c r="A228" s="2" t="s">
         <v>370</v>
       </c>
@@ -6628,8 +7309,11 @@
       <c r="E228" s="6">
         <v>911.88</v>
       </c>
-    </row>
-    <row r="229" spans="1:5">
+      <c r="F228" s="6">
+        <v>911.88</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
       <c r="A229" s="2" t="s">
         <v>370</v>
       </c>
@@ -6645,8 +7329,11 @@
       <c r="E229" s="6">
         <v>222.3</v>
       </c>
-    </row>
-    <row r="230" spans="1:5">
+      <c r="F229" s="6">
+        <v>222.3</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
       <c r="A230" s="2" t="s">
         <v>370</v>
       </c>
@@ -6662,8 +7349,11 @@
       <c r="E230" s="6">
         <v>589.88</v>
       </c>
-    </row>
-    <row r="231" spans="1:5">
+      <c r="F230" s="6">
+        <v>589.88</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
       <c r="A231" s="2" t="s">
         <v>375</v>
       </c>
@@ -6679,8 +7369,11 @@
       <c r="E231" s="5">
         <v>5995.83</v>
       </c>
-    </row>
-    <row r="232" spans="1:5">
+      <c r="F231" s="5">
+        <v>5995.83</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
       <c r="A232" s="2" t="s">
         <v>377</v>
       </c>
@@ -6696,8 +7389,11 @@
       <c r="E232" s="6">
         <v>17.61</v>
       </c>
-    </row>
-    <row r="233" spans="1:5">
+      <c r="F232" s="6">
+        <v>17.61</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
       <c r="A233" s="2" t="s">
         <v>377</v>
       </c>
@@ -6713,8 +7409,11 @@
       <c r="E233" s="6">
         <v>222.65</v>
       </c>
-    </row>
-    <row r="234" spans="1:5">
+      <c r="F233" s="6">
+        <v>222.65</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
       <c r="A234" s="2" t="s">
         <v>377</v>
       </c>
@@ -6730,8 +7429,11 @@
       <c r="E234" s="6">
         <v>351.09</v>
       </c>
-    </row>
-    <row r="235" spans="1:5">
+      <c r="F234" s="6">
+        <v>351.09</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
       <c r="A235" s="2" t="s">
         <v>382</v>
       </c>
@@ -6747,8 +7449,11 @@
       <c r="E235" s="5">
         <v>1219.77</v>
       </c>
-    </row>
-    <row r="236" spans="1:5">
+      <c r="F235" s="5">
+        <v>1219.77</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
       <c r="A236" s="2" t="s">
         <v>382</v>
       </c>
@@ -6764,8 +7469,11 @@
       <c r="E236" s="6">
         <v>838.68</v>
       </c>
-    </row>
-    <row r="237" spans="1:5">
+      <c r="F236" s="6">
+        <v>838.68</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
       <c r="A237" s="2" t="s">
         <v>382</v>
       </c>
@@ -6781,8 +7489,11 @@
       <c r="E237" s="5">
         <v>3440.81</v>
       </c>
-    </row>
-    <row r="238" spans="1:5">
+      <c r="F237" s="5">
+        <v>3440.81</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
       <c r="A238" s="2" t="s">
         <v>382</v>
       </c>
@@ -6798,8 +7509,11 @@
       <c r="E238" s="6">
         <v>353.93</v>
       </c>
-    </row>
-    <row r="239" spans="1:5">
+      <c r="F238" s="6">
+        <v>353.93</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
       <c r="A239" s="2" t="s">
         <v>382</v>
       </c>
@@ -6815,8 +7529,11 @@
       <c r="E239" s="6">
         <v>750.28</v>
       </c>
-    </row>
-    <row r="240" spans="1:5">
+      <c r="F239" s="6">
+        <v>750.28</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
       <c r="A240" s="2" t="s">
         <v>382</v>
       </c>
@@ -6832,8 +7549,11 @@
       <c r="E240" s="6">
         <v>210.36</v>
       </c>
-    </row>
-    <row r="241" spans="1:5">
+      <c r="F240" s="6">
+        <v>210.36</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
       <c r="A241" s="2" t="s">
         <v>382</v>
       </c>
@@ -6849,8 +7569,11 @@
       <c r="E241" s="6">
         <v>810.63</v>
       </c>
-    </row>
-    <row r="242" spans="1:5">
+      <c r="F241" s="6">
+        <v>810.63</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
       <c r="A242" s="2" t="s">
         <v>392</v>
       </c>
@@ -6866,8 +7589,11 @@
       <c r="E242" s="6">
         <v>377.52</v>
       </c>
-    </row>
-    <row r="243" spans="1:5">
+      <c r="F242" s="6">
+        <v>377.52</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
       <c r="A243" s="2" t="s">
         <v>394</v>
       </c>
@@ -6883,8 +7609,11 @@
       <c r="E243" s="6">
         <v>132.46</v>
       </c>
-    </row>
-    <row r="244" spans="1:5">
+      <c r="F243" s="6">
+        <v>132.46</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
       <c r="A244" s="2" t="s">
         <v>394</v>
       </c>
@@ -6900,8 +7629,11 @@
       <c r="E244" s="6">
         <v>152.68</v>
       </c>
-    </row>
-    <row r="245" spans="1:5">
+      <c r="F244" s="6">
+        <v>152.68</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
       <c r="A245" s="2" t="s">
         <v>394</v>
       </c>
@@ -6917,8 +7649,11 @@
       <c r="E245" s="6">
         <v>163.05000000000001</v>
       </c>
-    </row>
-    <row r="246" spans="1:5">
+      <c r="F245" s="6">
+        <v>163.05000000000001</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
       <c r="A246" s="2" t="s">
         <v>394</v>
       </c>
@@ -6934,8 +7669,11 @@
       <c r="E246" s="6">
         <v>220.74</v>
       </c>
-    </row>
-    <row r="247" spans="1:5">
+      <c r="F246" s="6">
+        <v>220.74</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
       <c r="A247" s="2" t="s">
         <v>394</v>
       </c>
@@ -6951,8 +7689,11 @@
       <c r="E247" s="6">
         <v>304.68</v>
       </c>
-    </row>
-    <row r="248" spans="1:5">
+      <c r="F247" s="6">
+        <v>304.68</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
       <c r="A248" s="2" t="s">
         <v>394</v>
       </c>
@@ -6968,8 +7709,11 @@
       <c r="E248" s="6">
         <v>216.59</v>
       </c>
-    </row>
-    <row r="249" spans="1:5">
+      <c r="F248" s="6">
+        <v>216.59</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
       <c r="A249" s="2" t="s">
         <v>407</v>
       </c>
@@ -6985,8 +7729,11 @@
       <c r="E249" s="5">
         <v>3826.5</v>
       </c>
-    </row>
-    <row r="250" spans="1:5">
+      <c r="F249" s="5">
+        <v>3826.5</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
       <c r="A250" s="2" t="s">
         <v>409</v>
       </c>
@@ -7002,8 +7749,11 @@
       <c r="E250" s="6">
         <v>471</v>
       </c>
-    </row>
-    <row r="251" spans="1:5">
+      <c r="F250" s="6">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
       <c r="A251" s="2" t="s">
         <v>409</v>
       </c>
@@ -7019,8 +7769,11 @@
       <c r="E251" s="5">
         <v>2931.42</v>
       </c>
-    </row>
-    <row r="252" spans="1:5">
+      <c r="F251" s="5">
+        <v>2931.42</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
       <c r="A252" s="2" t="s">
         <v>409</v>
       </c>
@@ -7036,8 +7789,11 @@
       <c r="E252" s="5">
         <v>2924.9</v>
       </c>
-    </row>
-    <row r="253" spans="1:5">
+      <c r="F252" s="5">
+        <v>2924.9</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
       <c r="A253" s="2" t="s">
         <v>409</v>
       </c>
@@ -7053,8 +7809,11 @@
       <c r="E253" s="6">
         <v>506.52</v>
       </c>
-    </row>
-    <row r="254" spans="1:5">
+      <c r="F253" s="6">
+        <v>506.52</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
       <c r="A254" s="2" t="s">
         <v>415</v>
       </c>
@@ -7070,8 +7829,11 @@
       <c r="E254" s="5">
         <v>3746.34</v>
       </c>
-    </row>
-    <row r="255" spans="1:5">
+      <c r="F254" s="5">
+        <v>3746.34</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
       <c r="A255" s="2" t="s">
         <v>415</v>
       </c>
@@ -7087,8 +7849,11 @@
       <c r="E255" s="6">
         <v>98.01</v>
       </c>
-    </row>
-    <row r="256" spans="1:5">
+      <c r="F255" s="6">
+        <v>98.01</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
       <c r="A256" s="2" t="s">
         <v>415</v>
       </c>
@@ -7104,8 +7869,11 @@
       <c r="E256" s="5">
         <v>1578.01</v>
       </c>
-    </row>
-    <row r="257" spans="1:5">
+      <c r="F256" s="5">
+        <v>1578.01</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
       <c r="A257" s="2" t="s">
         <v>415</v>
       </c>
@@ -7121,8 +7889,11 @@
       <c r="E257" s="6">
         <v>361.77</v>
       </c>
-    </row>
-    <row r="258" spans="1:5">
+      <c r="F257" s="6">
+        <v>361.77</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
       <c r="A258" s="2" t="s">
         <v>415</v>
       </c>
@@ -7138,8 +7909,11 @@
       <c r="E258" s="5">
         <v>1156.58</v>
       </c>
-    </row>
-    <row r="259" spans="1:5">
+      <c r="F258" s="5">
+        <v>1156.58</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
       <c r="A259" s="2" t="s">
         <v>423</v>
       </c>
@@ -7155,8 +7929,11 @@
       <c r="E259" s="6">
         <v>62.78</v>
       </c>
-    </row>
-    <row r="260" spans="1:5">
+      <c r="F259" s="6">
+        <v>62.78</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
       <c r="A260" s="2" t="s">
         <v>423</v>
       </c>
@@ -7172,8 +7949,11 @@
       <c r="E260" s="5">
         <v>1291.47</v>
       </c>
-    </row>
-    <row r="261" spans="1:5">
+      <c r="F260" s="5">
+        <v>1291.47</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
       <c r="A261" s="2" t="s">
         <v>423</v>
       </c>
@@ -7189,8 +7969,11 @@
       <c r="E261" s="5">
         <v>1055.2</v>
       </c>
-    </row>
-    <row r="262" spans="1:5">
+      <c r="F261" s="5">
+        <v>1055.2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
       <c r="A262" s="2" t="s">
         <v>423</v>
       </c>
@@ -7206,8 +7989,11 @@
       <c r="E262" s="6">
         <v>490.93</v>
       </c>
-    </row>
-    <row r="263" spans="1:5">
+      <c r="F262" s="6">
+        <v>490.93</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
       <c r="A263" s="2" t="s">
         <v>423</v>
       </c>
@@ -7223,8 +8009,11 @@
       <c r="E263" s="6">
         <v>800.74</v>
       </c>
-    </row>
-    <row r="264" spans="1:5">
+      <c r="F263" s="6">
+        <v>800.74</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
       <c r="A264" s="2" t="s">
         <v>423</v>
       </c>
@@ -7240,8 +8029,11 @@
       <c r="E264" s="6">
         <v>523.71</v>
       </c>
-    </row>
-    <row r="265" spans="1:5">
+      <c r="F264" s="6">
+        <v>523.71</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
       <c r="A265" s="2" t="s">
         <v>423</v>
       </c>
@@ -7257,8 +8049,11 @@
       <c r="E265" s="6">
         <v>483.88</v>
       </c>
-    </row>
-    <row r="266" spans="1:5">
+      <c r="F265" s="6">
+        <v>483.88</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
       <c r="A266" s="2" t="s">
         <v>423</v>
       </c>
@@ -7274,8 +8069,11 @@
       <c r="E266" s="6">
         <v>634.45000000000005</v>
       </c>
-    </row>
-    <row r="267" spans="1:5">
+      <c r="F266" s="6">
+        <v>634.45000000000005</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
       <c r="A267" s="2" t="s">
         <v>423</v>
       </c>
@@ -7291,8 +8089,11 @@
       <c r="E267" s="5">
         <v>1258.33</v>
       </c>
-    </row>
-    <row r="268" spans="1:5">
+      <c r="F267" s="5">
+        <v>1258.33</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
       <c r="A268" s="2" t="s">
         <v>423</v>
       </c>
@@ -7308,8 +8109,11 @@
       <c r="E268" s="6">
         <v>703.97</v>
       </c>
-    </row>
-    <row r="269" spans="1:5">
+      <c r="F268" s="6">
+        <v>703.97</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
       <c r="A269" s="2" t="s">
         <v>423</v>
       </c>
@@ -7325,8 +8129,11 @@
       <c r="E269" s="6">
         <v>522.53</v>
       </c>
-    </row>
-    <row r="270" spans="1:5">
+      <c r="F269" s="6">
+        <v>522.53</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
       <c r="A270" s="2" t="s">
         <v>423</v>
       </c>
@@ -7342,8 +8149,11 @@
       <c r="E270" s="6">
         <v>268.63</v>
       </c>
-    </row>
-    <row r="271" spans="1:5">
+      <c r="F270" s="6">
+        <v>268.63</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
       <c r="A271" s="2" t="s">
         <v>423</v>
       </c>
@@ -7359,8 +8169,11 @@
       <c r="E271" s="6">
         <v>110.33</v>
       </c>
-    </row>
-    <row r="272" spans="1:5">
+      <c r="F271" s="6">
+        <v>110.33</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
       <c r="A272" s="2" t="s">
         <v>437</v>
       </c>
@@ -7376,8 +8189,11 @@
       <c r="E272" s="6">
         <v>353.65</v>
       </c>
-    </row>
-    <row r="273" spans="1:5">
+      <c r="F272" s="6">
+        <v>353.65</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
       <c r="A273" s="2" t="s">
         <v>437</v>
       </c>
@@ -7393,8 +8209,11 @@
       <c r="E273" s="5">
         <v>1368.51</v>
       </c>
-    </row>
-    <row r="274" spans="1:5">
+      <c r="F273" s="5">
+        <v>1368.51</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
       <c r="A274" s="2" t="s">
         <v>440</v>
       </c>
@@ -7410,8 +8229,11 @@
       <c r="E274" s="6">
         <v>153.29</v>
       </c>
-    </row>
-    <row r="275" spans="1:5">
+      <c r="F274" s="6">
+        <v>153.29</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
       <c r="A275" s="2" t="s">
         <v>440</v>
       </c>
@@ -7427,8 +8249,11 @@
       <c r="E275" s="5">
         <v>1603.85</v>
       </c>
-    </row>
-    <row r="276" spans="1:5">
+      <c r="F275" s="5">
+        <v>1603.85</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
       <c r="A276" s="2" t="s">
         <v>440</v>
       </c>
@@ -7444,8 +8269,11 @@
       <c r="E276" s="6">
         <v>607.19000000000005</v>
       </c>
-    </row>
-    <row r="277" spans="1:5">
+      <c r="F276" s="6">
+        <v>607.19000000000005</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
       <c r="A277" s="2" t="s">
         <v>440</v>
       </c>
@@ -7461,8 +8289,11 @@
       <c r="E277" s="6">
         <v>250.31</v>
       </c>
-    </row>
-    <row r="278" spans="1:5">
+      <c r="F277" s="6">
+        <v>250.31</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
       <c r="A278" s="2" t="s">
         <v>440</v>
       </c>
@@ -7478,8 +8309,11 @@
       <c r="E278" s="6">
         <v>188.76</v>
       </c>
-    </row>
-    <row r="279" spans="1:5">
+      <c r="F278" s="6">
+        <v>188.76</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
       <c r="A279" s="2" t="s">
         <v>448</v>
       </c>
@@ -7495,8 +8329,11 @@
       <c r="E279" s="6">
         <v>247.1</v>
       </c>
-    </row>
-    <row r="280" spans="1:5">
+      <c r="F279" s="6">
+        <v>247.1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
       <c r="A280" s="2" t="s">
         <v>448</v>
       </c>
@@ -7512,8 +8349,11 @@
       <c r="E280" s="5">
         <v>2376.7199999999998</v>
       </c>
-    </row>
-    <row r="281" spans="1:5">
+      <c r="F280" s="5">
+        <v>2376.7199999999998</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
       <c r="A281" s="2" t="s">
         <v>448</v>
       </c>
@@ -7529,8 +8369,11 @@
       <c r="E281" s="5">
         <v>1468.04</v>
       </c>
-    </row>
-    <row r="282" spans="1:5">
+      <c r="F281" s="5">
+        <v>1468.04</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
       <c r="A282" s="2" t="s">
         <v>448</v>
       </c>
@@ -7546,8 +8389,11 @@
       <c r="E282" s="5">
         <v>3705.98</v>
       </c>
-    </row>
-    <row r="283" spans="1:5">
+      <c r="F282" s="5">
+        <v>3705.98</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
       <c r="A283" s="2" t="s">
         <v>448</v>
       </c>
@@ -7563,8 +8409,11 @@
       <c r="E283" s="6">
         <v>261.86</v>
       </c>
-    </row>
-    <row r="284" spans="1:5">
+      <c r="F283" s="6">
+        <v>261.86</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
       <c r="A284" s="2" t="s">
         <v>448</v>
       </c>
@@ -7580,8 +8429,11 @@
       <c r="E284" s="6">
         <v>772.98</v>
       </c>
-    </row>
-    <row r="285" spans="1:5">
+      <c r="F284" s="6">
+        <v>772.98</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
       <c r="A285" s="2" t="s">
         <v>448</v>
       </c>
@@ -7597,8 +8449,11 @@
       <c r="E285" s="6">
         <v>731.45</v>
       </c>
-    </row>
-    <row r="286" spans="1:5">
+      <c r="F285" s="6">
+        <v>731.45</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
       <c r="A286" s="2" t="s">
         <v>448</v>
       </c>
@@ -7614,8 +8469,11 @@
       <c r="E286" s="5">
         <v>1310.6199999999999</v>
       </c>
-    </row>
-    <row r="287" spans="1:5">
+      <c r="F286" s="5">
+        <v>1310.6199999999999</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
       <c r="A287" s="2" t="s">
         <v>448</v>
       </c>
@@ -7631,8 +8489,11 @@
       <c r="E287" s="6">
         <v>749.9</v>
       </c>
-    </row>
-    <row r="288" spans="1:5">
+      <c r="F287" s="6">
+        <v>749.9</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
       <c r="A288" s="2" t="s">
         <v>448</v>
       </c>
@@ -7648,8 +8509,11 @@
       <c r="E288" s="5">
         <v>1994.85</v>
       </c>
-    </row>
-    <row r="289" spans="1:5">
+      <c r="F288" s="5">
+        <v>1994.85</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
       <c r="A289" s="2" t="s">
         <v>448</v>
       </c>
@@ -7665,8 +8529,11 @@
       <c r="E289" s="6">
         <v>648.86</v>
       </c>
-    </row>
-    <row r="290" spans="1:5">
+      <c r="F289" s="6">
+        <v>648.86</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
       <c r="A290" s="2" t="s">
         <v>448</v>
       </c>
@@ -7682,8 +8549,11 @@
       <c r="E290" s="5">
         <v>1620.7</v>
       </c>
-    </row>
-    <row r="291" spans="1:5">
+      <c r="F290" s="5">
+        <v>1620.7</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
       <c r="A291" s="2" t="s">
         <v>134</v>
       </c>
@@ -7699,8 +8569,11 @@
       <c r="E291" s="6">
         <v>518.04999999999995</v>
       </c>
-    </row>
-    <row r="292" spans="1:5">
+      <c r="F291" s="6">
+        <v>518.04999999999995</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
       <c r="A292" s="2" t="s">
         <v>134</v>
       </c>
@@ -7716,8 +8589,11 @@
       <c r="E292" s="6">
         <v>162.1</v>
       </c>
-    </row>
-    <row r="293" spans="1:5">
+      <c r="F292" s="6">
+        <v>162.1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
       <c r="A293" s="2" t="s">
         <v>134</v>
       </c>
@@ -7733,8 +8609,11 @@
       <c r="E293" s="6">
         <v>252.08</v>
       </c>
-    </row>
-    <row r="294" spans="1:5">
+      <c r="F293" s="6">
+        <v>252.08</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
       <c r="A294" s="2" t="s">
         <v>134</v>
       </c>
@@ -7750,8 +8629,11 @@
       <c r="E294" s="6">
         <v>797.4</v>
       </c>
-    </row>
-    <row r="295" spans="1:5">
+      <c r="F294" s="6">
+        <v>797.4</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
       <c r="A295" s="2" t="s">
         <v>134</v>
       </c>
@@ -7767,8 +8649,11 @@
       <c r="E295" s="6">
         <v>349.33</v>
       </c>
-    </row>
-    <row r="296" spans="1:5">
+      <c r="F295" s="6">
+        <v>349.33</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
       <c r="A296" s="2" t="s">
         <v>134</v>
       </c>
@@ -7784,8 +8669,11 @@
       <c r="E296" s="6">
         <v>530.57000000000005</v>
       </c>
-    </row>
-    <row r="297" spans="1:5">
+      <c r="F296" s="6">
+        <v>530.57000000000005</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
       <c r="A297" s="2" t="s">
         <v>134</v>
       </c>
@@ -7801,8 +8689,11 @@
       <c r="E297" s="5">
         <v>1109.42</v>
       </c>
-    </row>
-    <row r="298" spans="1:5">
+      <c r="F297" s="5">
+        <v>1109.42</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
       <c r="A298" s="2" t="s">
         <v>134</v>
       </c>
@@ -7818,8 +8709,11 @@
       <c r="E298" s="6">
         <v>257.98</v>
       </c>
-    </row>
-    <row r="299" spans="1:5">
+      <c r="F298" s="6">
+        <v>257.98</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
       <c r="A299" s="2" t="s">
         <v>471</v>
       </c>
@@ -7835,8 +8729,11 @@
       <c r="E299" s="5">
         <v>2437.29</v>
       </c>
-    </row>
-    <row r="300" spans="1:5">
+      <c r="F299" s="5">
+        <v>2437.29</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
       <c r="A300" s="2" t="s">
         <v>471</v>
       </c>
@@ -7852,8 +8749,11 @@
       <c r="E300" s="6">
         <v>403.75</v>
       </c>
-    </row>
-    <row r="301" spans="1:5">
+      <c r="F300" s="6">
+        <v>403.75</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
       <c r="A301" s="2" t="s">
         <v>471</v>
       </c>
@@ -7869,8 +8769,11 @@
       <c r="E301" s="6">
         <v>326.95</v>
       </c>
-    </row>
-    <row r="302" spans="1:5">
+      <c r="F301" s="6">
+        <v>326.95</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
       <c r="A302" s="2" t="s">
         <v>471</v>
       </c>
@@ -7886,8 +8789,11 @@
       <c r="E302" s="6">
         <v>708.92</v>
       </c>
-    </row>
-    <row r="303" spans="1:5">
+      <c r="F302" s="6">
+        <v>708.92</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
       <c r="A303" s="2" t="s">
         <v>471</v>
       </c>
@@ -7903,8 +8809,11 @@
       <c r="E303" s="6">
         <v>170.36</v>
       </c>
-    </row>
-    <row r="304" spans="1:5">
+      <c r="F303" s="6">
+        <v>170.36</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
       <c r="A304" s="2" t="s">
         <v>471</v>
       </c>
@@ -7920,8 +8829,11 @@
       <c r="E304" s="6">
         <v>417.37</v>
       </c>
-    </row>
-    <row r="305" spans="1:5">
+      <c r="F304" s="6">
+        <v>417.37</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
       <c r="A305" s="2" t="s">
         <v>480</v>
       </c>
@@ -7937,8 +8849,11 @@
       <c r="E305" s="5">
         <v>1448.37</v>
       </c>
-    </row>
-    <row r="306" spans="1:5">
+      <c r="F305" s="5">
+        <v>1448.37</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
       <c r="A306" s="2" t="s">
         <v>482</v>
       </c>
@@ -7954,8 +8869,11 @@
       <c r="E306" s="6">
         <v>498.17</v>
       </c>
-    </row>
-    <row r="307" spans="1:5">
+      <c r="F306" s="6">
+        <v>498.17</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
       <c r="A307" s="2" t="s">
         <v>482</v>
       </c>
@@ -7971,8 +8889,11 @@
       <c r="E307" s="5">
         <v>1575.72</v>
       </c>
-    </row>
-    <row r="308" spans="1:5">
+      <c r="F307" s="5">
+        <v>1575.72</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
       <c r="A308" s="2" t="s">
         <v>482</v>
       </c>
@@ -7988,8 +8909,11 @@
       <c r="E308" s="6">
         <v>63.48</v>
       </c>
-    </row>
-    <row r="309" spans="1:5">
+      <c r="F308" s="6">
+        <v>63.48</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
       <c r="A309" s="2" t="s">
         <v>482</v>
       </c>
@@ -8005,8 +8929,11 @@
       <c r="E309" s="6">
         <v>93.8</v>
       </c>
-    </row>
-    <row r="310" spans="1:5">
+      <c r="F309" s="6">
+        <v>93.8</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
       <c r="A310" s="2" t="s">
         <v>482</v>
       </c>
@@ -8022,8 +8949,11 @@
       <c r="E310" s="6">
         <v>852.76</v>
       </c>
-    </row>
-    <row r="311" spans="1:5">
+      <c r="F310" s="6">
+        <v>852.76</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
       <c r="A311" s="2" t="s">
         <v>482</v>
       </c>
@@ -8039,8 +8969,11 @@
       <c r="E311" s="6">
         <v>119.58</v>
       </c>
-    </row>
-    <row r="312" spans="1:5">
+      <c r="F311" s="6">
+        <v>119.58</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
       <c r="A312" s="2" t="s">
         <v>482</v>
       </c>
@@ -8056,8 +8989,11 @@
       <c r="E312" s="6">
         <v>467.32</v>
       </c>
-    </row>
-    <row r="313" spans="1:5">
+      <c r="F312" s="6">
+        <v>467.32</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
       <c r="A313" s="2" t="s">
         <v>495</v>
       </c>
@@ -8073,8 +9009,11 @@
       <c r="E313" s="6">
         <v>614.36</v>
       </c>
-    </row>
-    <row r="314" spans="1:5">
+      <c r="F313" s="6">
+        <v>614.36</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
       <c r="A314" s="2" t="s">
         <v>495</v>
       </c>
@@ -8090,8 +9029,11 @@
       <c r="E314" s="5">
         <v>1172.6099999999999</v>
       </c>
-    </row>
-    <row r="315" spans="1:5">
+      <c r="F314" s="5">
+        <v>1172.6099999999999</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
       <c r="A315" s="2" t="s">
         <v>495</v>
       </c>
@@ -8107,8 +9049,11 @@
       <c r="E315" s="6">
         <v>981.7</v>
       </c>
-    </row>
-    <row r="316" spans="1:5">
+      <c r="F315" s="6">
+        <v>981.7</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
       <c r="A316" s="2" t="s">
         <v>495</v>
       </c>
@@ -8124,8 +9069,11 @@
       <c r="E316" s="6">
         <v>778.34</v>
       </c>
-    </row>
-    <row r="317" spans="1:5">
+      <c r="F316" s="6">
+        <v>778.34</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
       <c r="A317" s="2" t="s">
         <v>495</v>
       </c>
@@ -8141,8 +9089,11 @@
       <c r="E317" s="5">
         <v>1052.3699999999999</v>
       </c>
-    </row>
-    <row r="318" spans="1:5">
+      <c r="F317" s="5">
+        <v>1052.3699999999999</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
       <c r="A318" s="2" t="s">
         <v>495</v>
       </c>
@@ -8158,8 +9109,11 @@
       <c r="E318" s="5">
         <v>1352.99</v>
       </c>
-    </row>
-    <row r="319" spans="1:5">
+      <c r="F318" s="5">
+        <v>1352.99</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
       <c r="A319" s="2" t="s">
         <v>495</v>
       </c>
@@ -8175,8 +9129,11 @@
       <c r="E319" s="6">
         <v>164.08</v>
       </c>
-    </row>
-    <row r="320" spans="1:5">
+      <c r="F319" s="6">
+        <v>164.08</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
       <c r="A320" s="2" t="s">
         <v>495</v>
       </c>
@@ -8192,8 +9149,11 @@
       <c r="E320" s="6">
         <v>374.52</v>
       </c>
-    </row>
-    <row r="321" spans="1:5">
+      <c r="F320" s="6">
+        <v>374.52</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
       <c r="A321" s="2" t="s">
         <v>495</v>
       </c>
@@ -8209,8 +9169,11 @@
       <c r="E321" s="5">
         <v>1873.63</v>
       </c>
-    </row>
-    <row r="322" spans="1:5">
+      <c r="F321" s="5">
+        <v>1873.63</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
       <c r="A322" s="2" t="s">
         <v>495</v>
       </c>
@@ -8226,8 +9189,11 @@
       <c r="E322" s="6">
         <v>397.56</v>
       </c>
-    </row>
-    <row r="323" spans="1:5">
+      <c r="F322" s="6">
+        <v>397.56</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
       <c r="A323" s="2" t="s">
         <v>495</v>
       </c>
@@ -8243,8 +9209,11 @@
       <c r="E323" s="5">
         <v>1135.22</v>
       </c>
-    </row>
-    <row r="324" spans="1:5">
+      <c r="F323" s="5">
+        <v>1135.22</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
       <c r="A324" s="2" t="s">
         <v>495</v>
       </c>
@@ -8260,8 +9229,11 @@
       <c r="E324" s="6">
         <v>910.84</v>
       </c>
-    </row>
-    <row r="325" spans="1:5">
+      <c r="F324" s="6">
+        <v>910.84</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
       <c r="A325" s="2" t="s">
         <v>495</v>
       </c>
@@ -8277,8 +9249,11 @@
       <c r="E325" s="5">
         <v>1313.79</v>
       </c>
-    </row>
-    <row r="326" spans="1:5">
+      <c r="F325" s="5">
+        <v>1313.79</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
       <c r="A326" s="2" t="s">
         <v>495</v>
       </c>
@@ -8294,8 +9269,11 @@
       <c r="E326" s="6">
         <v>374.52</v>
       </c>
-    </row>
-    <row r="327" spans="1:5">
+      <c r="F326" s="6">
+        <v>374.52</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
       <c r="A327" s="2" t="s">
         <v>495</v>
       </c>
@@ -8311,8 +9289,11 @@
       <c r="E327" s="6">
         <v>633.09</v>
       </c>
-    </row>
-    <row r="328" spans="1:5">
+      <c r="F327" s="6">
+        <v>633.09</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
       <c r="A328" s="2" t="s">
         <v>495</v>
       </c>
@@ -8328,8 +9309,11 @@
       <c r="E328" s="5">
         <v>1120.5</v>
       </c>
-    </row>
-    <row r="329" spans="1:5">
+      <c r="F328" s="5">
+        <v>1120.5</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
       <c r="A329" s="2" t="s">
         <v>512</v>
       </c>
@@ -8345,8 +9329,11 @@
       <c r="E329" s="6">
         <v>736.09</v>
       </c>
-    </row>
-    <row r="330" spans="1:5">
+      <c r="F329" s="6">
+        <v>736.09</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
       <c r="A330" s="2" t="s">
         <v>512</v>
       </c>
@@ -8362,8 +9349,11 @@
       <c r="E330" s="5">
         <v>1170.74</v>
       </c>
-    </row>
-    <row r="331" spans="1:5">
+      <c r="F330" s="5">
+        <v>1170.74</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
       <c r="A331" s="2" t="s">
         <v>512</v>
       </c>
@@ -8379,8 +9369,11 @@
       <c r="E331" s="5">
         <v>1356.94</v>
       </c>
-    </row>
-    <row r="332" spans="1:5">
+      <c r="F331" s="5">
+        <v>1356.94</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
       <c r="A332" s="2" t="s">
         <v>512</v>
       </c>
@@ -8396,8 +9389,11 @@
       <c r="E332" s="5">
         <v>1873.85</v>
       </c>
-    </row>
-    <row r="333" spans="1:5">
+      <c r="F332" s="5">
+        <v>1873.85</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
       <c r="A333" s="2" t="s">
         <v>512</v>
       </c>
@@ -8413,8 +9409,11 @@
       <c r="E333" s="6">
         <v>188.76</v>
       </c>
-    </row>
-    <row r="334" spans="1:5">
+      <c r="F333" s="6">
+        <v>188.76</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
       <c r="A334" s="2" t="s">
         <v>512</v>
       </c>
@@ -8430,8 +9429,11 @@
       <c r="E334" s="5">
         <v>1565.58</v>
       </c>
-    </row>
-    <row r="335" spans="1:5">
+      <c r="F334" s="5">
+        <v>1565.58</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
       <c r="A335" s="2" t="s">
         <v>522</v>
       </c>
@@ -8447,8 +9449,11 @@
       <c r="E335" s="6">
         <v>259.48</v>
       </c>
-    </row>
-    <row r="336" spans="1:5">
+      <c r="F335" s="6">
+        <v>259.48</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
       <c r="A336" s="2" t="s">
         <v>522</v>
       </c>
@@ -8464,8 +9469,11 @@
       <c r="E336" s="6">
         <v>408.67</v>
       </c>
-    </row>
-    <row r="337" spans="1:5">
+      <c r="F336" s="6">
+        <v>408.67</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
       <c r="A337" s="2" t="s">
         <v>522</v>
       </c>
@@ -8481,8 +9489,11 @@
       <c r="E337" s="6">
         <v>188.76</v>
       </c>
-    </row>
-    <row r="338" spans="1:5">
+      <c r="F337" s="6">
+        <v>188.76</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
       <c r="A338" s="2" t="s">
         <v>526</v>
       </c>
@@ -8498,8 +9509,11 @@
       <c r="E338" s="6">
         <v>632.75</v>
       </c>
-    </row>
-    <row r="339" spans="1:5">
+      <c r="F338" s="6">
+        <v>632.75</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
       <c r="A339" s="2" t="s">
         <v>526</v>
       </c>
@@ -8515,8 +9529,11 @@
       <c r="E339" s="6">
         <v>557.41999999999996</v>
       </c>
-    </row>
-    <row r="340" spans="1:5">
+      <c r="F339" s="6">
+        <v>557.41999999999996</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
       <c r="A340" s="2" t="s">
         <v>529</v>
       </c>
@@ -8532,8 +9549,11 @@
       <c r="E340" s="6">
         <v>598.82000000000005</v>
       </c>
-    </row>
-    <row r="341" spans="1:5">
+      <c r="F340" s="6">
+        <v>598.82000000000005</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6">
       <c r="A341" s="2" t="s">
         <v>532</v>
       </c>
@@ -8549,8 +9569,11 @@
       <c r="E341" s="6">
         <v>188.76</v>
       </c>
-    </row>
-    <row r="342" spans="1:5">
+      <c r="F341" s="6">
+        <v>188.76</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6">
       <c r="A342" s="2" t="s">
         <v>532</v>
       </c>
@@ -8566,8 +9589,11 @@
       <c r="E342" s="6">
         <v>514.4</v>
       </c>
-    </row>
-    <row r="343" spans="1:5">
+      <c r="F342" s="6">
+        <v>514.4</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
       <c r="A343" s="2" t="s">
         <v>532</v>
       </c>
@@ -8583,8 +9609,11 @@
       <c r="E343" s="6">
         <v>631.80999999999995</v>
       </c>
-    </row>
-    <row r="344" spans="1:5">
+      <c r="F343" s="6">
+        <v>631.80999999999995</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6">
       <c r="A344" s="2" t="s">
         <v>536</v>
       </c>
@@ -8600,8 +9629,11 @@
       <c r="E344" s="6">
         <v>512.16999999999996</v>
       </c>
-    </row>
-    <row r="345" spans="1:5">
+      <c r="F344" s="6">
+        <v>512.16999999999996</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
       <c r="A345" s="2" t="s">
         <v>536</v>
       </c>
@@ -8617,8 +9649,11 @@
       <c r="E345" s="5">
         <v>7003.29</v>
       </c>
-    </row>
-    <row r="346" spans="1:5">
+      <c r="F345" s="5">
+        <v>7003.29</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
       <c r="A346" s="2" t="s">
         <v>539</v>
       </c>
@@ -8634,8 +9669,11 @@
       <c r="E346" s="6">
         <v>-848.73</v>
       </c>
-    </row>
-    <row r="347" spans="1:5">
+      <c r="F346" s="6">
+        <v>-848.73</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
       <c r="A347" s="2" t="s">
         <v>541</v>
       </c>
@@ -8651,8 +9689,11 @@
       <c r="E347" s="6">
         <v>436.86</v>
       </c>
-    </row>
-    <row r="348" spans="1:5">
+      <c r="F347" s="6">
+        <v>436.86</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
       <c r="A348" s="2" t="s">
         <v>541</v>
       </c>
@@ -8668,8 +9709,11 @@
       <c r="E348" s="5">
         <v>2272.1799999999998</v>
       </c>
-    </row>
-    <row r="349" spans="1:5">
+      <c r="F348" s="5">
+        <v>2272.1799999999998</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
       <c r="A349" s="2" t="s">
         <v>541</v>
       </c>
@@ -8685,8 +9729,11 @@
       <c r="E349" s="6">
         <v>164.08</v>
       </c>
-    </row>
-    <row r="350" spans="1:5">
+      <c r="F349" s="6">
+        <v>164.08</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
       <c r="A350" s="2" t="s">
         <v>541</v>
       </c>
@@ -8702,8 +9749,11 @@
       <c r="E350" s="6">
         <v>939.86</v>
       </c>
-    </row>
-    <row r="351" spans="1:5">
+      <c r="F350" s="6">
+        <v>939.86</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
       <c r="A351" s="2" t="s">
         <v>541</v>
       </c>
@@ -8719,8 +9769,11 @@
       <c r="E351" s="5">
         <v>1293.8599999999999</v>
       </c>
-    </row>
-    <row r="352" spans="1:5">
+      <c r="F351" s="5">
+        <v>1293.8599999999999</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
       <c r="A352" s="2" t="s">
         <v>547</v>
       </c>
@@ -8736,8 +9789,11 @@
       <c r="E352" s="6">
         <v>562.69000000000005</v>
       </c>
-    </row>
-    <row r="353" spans="1:5">
+      <c r="F352" s="6">
+        <v>562.69000000000005</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
       <c r="A353" s="2" t="s">
         <v>547</v>
       </c>
@@ -8753,8 +9809,11 @@
       <c r="E353" s="6">
         <v>455.71</v>
       </c>
-    </row>
-    <row r="354" spans="1:5">
+      <c r="F353" s="6">
+        <v>455.71</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
       <c r="A354" s="2" t="s">
         <v>550</v>
       </c>
@@ -8770,8 +9829,11 @@
       <c r="E354" s="5">
         <v>6553.85</v>
       </c>
-    </row>
-    <row r="355" spans="1:5">
+      <c r="F354" s="5">
+        <v>6553.85</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
       <c r="A355" s="2" t="s">
         <v>550</v>
       </c>
@@ -8787,8 +9849,11 @@
       <c r="E355" s="6">
         <v>377.52</v>
       </c>
-    </row>
-    <row r="356" spans="1:5">
+      <c r="F355" s="6">
+        <v>377.52</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
       <c r="A356" s="2" t="s">
         <v>550</v>
       </c>
@@ -8804,8 +9869,11 @@
       <c r="E356" s="6">
         <v>188.76</v>
       </c>
-    </row>
-    <row r="357" spans="1:5">
+      <c r="F356" s="6">
+        <v>188.76</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
       <c r="A357" s="2" t="s">
         <v>550</v>
       </c>
@@ -8821,8 +9889,11 @@
       <c r="E357" s="5">
         <v>6789.59</v>
       </c>
-    </row>
-    <row r="358" spans="1:5">
+      <c r="F357" s="5">
+        <v>6789.59</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6">
       <c r="A358" s="2" t="s">
         <v>555</v>
       </c>
@@ -8838,8 +9909,11 @@
       <c r="E358" s="5">
         <v>1079.05</v>
       </c>
-    </row>
-    <row r="359" spans="1:5">
+      <c r="F358" s="5">
+        <v>1079.05</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6">
       <c r="A359" s="2" t="s">
         <v>242</v>
       </c>
@@ -8855,8 +9929,11 @@
       <c r="E359" s="6">
         <v>809.77</v>
       </c>
-    </row>
-    <row r="360" spans="1:5">
+      <c r="F359" s="6">
+        <v>809.77</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
       <c r="A360" s="2" t="s">
         <v>242</v>
       </c>
@@ -8872,8 +9949,11 @@
       <c r="E360" s="5">
         <v>1551.24</v>
       </c>
-    </row>
-    <row r="361" spans="1:5">
+      <c r="F360" s="5">
+        <v>1551.24</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
       <c r="A361" s="2" t="s">
         <v>242</v>
       </c>
@@ -8889,8 +9969,11 @@
       <c r="E361" s="6">
         <v>685.68</v>
       </c>
-    </row>
-    <row r="362" spans="1:5">
+      <c r="F361" s="6">
+        <v>685.68</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
       <c r="A362" s="2" t="s">
         <v>560</v>
       </c>
@@ -8906,8 +9989,11 @@
       <c r="E362" s="6">
         <v>860.28</v>
       </c>
-    </row>
-    <row r="363" spans="1:5">
+      <c r="F362" s="6">
+        <v>860.28</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
       <c r="A363" s="2" t="s">
         <v>560</v>
       </c>
@@ -8923,8 +10009,11 @@
       <c r="E363" s="6">
         <v>313.39</v>
       </c>
-    </row>
-    <row r="364" spans="1:5">
+      <c r="F363" s="6">
+        <v>313.39</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
       <c r="A364" s="2" t="s">
         <v>563</v>
       </c>
@@ -8940,8 +10029,11 @@
       <c r="E364" s="5">
         <v>1263.92</v>
       </c>
-    </row>
-    <row r="365" spans="1:5">
+      <c r="F364" s="5">
+        <v>1263.92</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
       <c r="A365" s="2" t="s">
         <v>563</v>
       </c>
@@ -8957,8 +10049,11 @@
       <c r="E365" s="5">
         <v>1062.22</v>
       </c>
-    </row>
-    <row r="366" spans="1:5">
+      <c r="F365" s="5">
+        <v>1062.22</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
       <c r="A366" s="2" t="s">
         <v>563</v>
       </c>
@@ -8974,8 +10069,11 @@
       <c r="E366" s="5">
         <v>1401.95</v>
       </c>
-    </row>
-    <row r="367" spans="1:5">
+      <c r="F366" s="5">
+        <v>1401.95</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
       <c r="A367" s="2" t="s">
         <v>567</v>
       </c>
@@ -8991,8 +10089,11 @@
       <c r="E367" s="5">
         <v>2097.98</v>
       </c>
-    </row>
-    <row r="368" spans="1:5">
+      <c r="F367" s="5">
+        <v>2097.98</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
       <c r="A368" s="2" t="s">
         <v>567</v>
       </c>
@@ -9008,8 +10109,11 @@
       <c r="E368" s="5">
         <v>1893.12</v>
       </c>
-    </row>
-    <row r="369" spans="1:5">
+      <c r="F368" s="5">
+        <v>1893.12</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
       <c r="A369" s="2" t="s">
         <v>567</v>
       </c>
@@ -9025,8 +10129,11 @@
       <c r="E369" s="6">
         <v>473.16</v>
       </c>
-    </row>
-    <row r="370" spans="1:5">
+      <c r="F369" s="6">
+        <v>473.16</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
       <c r="A370" s="2" t="s">
         <v>567</v>
       </c>
@@ -9042,8 +10149,11 @@
       <c r="E370" s="5">
         <v>1150.99</v>
       </c>
-    </row>
-    <row r="371" spans="1:5">
+      <c r="F370" s="5">
+        <v>1150.99</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
       <c r="A371" s="2" t="s">
         <v>567</v>
       </c>
@@ -9059,8 +10169,11 @@
       <c r="E371" s="6">
         <v>981.71</v>
       </c>
-    </row>
-    <row r="372" spans="1:5">
+      <c r="F371" s="6">
+        <v>981.71</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
       <c r="A372" s="2" t="s">
         <v>567</v>
       </c>
@@ -9076,8 +10189,11 @@
       <c r="E372" s="6">
         <v>109.38</v>
       </c>
-    </row>
-    <row r="373" spans="1:5">
+      <c r="F372" s="6">
+        <v>109.38</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6">
       <c r="A373" s="2" t="s">
         <v>567</v>
       </c>
@@ -9093,8 +10209,11 @@
       <c r="E373" s="6">
         <v>981.71</v>
       </c>
-    </row>
-    <row r="374" spans="1:5">
+      <c r="F373" s="6">
+        <v>981.71</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
       <c r="A374" s="2" t="s">
         <v>576</v>
       </c>
@@ -9110,8 +10229,11 @@
       <c r="E374" s="5">
         <v>16800</v>
       </c>
-    </row>
-    <row r="375" spans="1:5">
+      <c r="F374" s="5">
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
       <c r="A375" s="2" t="s">
         <v>576</v>
       </c>
@@ -9127,8 +10249,11 @@
       <c r="E375" s="6">
         <v>594.21</v>
       </c>
-    </row>
-    <row r="376" spans="1:5">
+      <c r="F375" s="6">
+        <v>594.21</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
       <c r="A376" s="2" t="s">
         <v>576</v>
       </c>
@@ -9144,8 +10269,11 @@
       <c r="E376" s="6">
         <v>416.84</v>
       </c>
-    </row>
-    <row r="377" spans="1:5">
+      <c r="F376" s="6">
+        <v>416.84</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
       <c r="A377" s="2" t="s">
         <v>576</v>
       </c>
@@ -9161,8 +10289,11 @@
       <c r="E377" s="6">
         <v>729.12</v>
       </c>
-    </row>
-    <row r="378" spans="1:5">
+      <c r="F377" s="6">
+        <v>729.12</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
       <c r="A378" s="2" t="s">
         <v>576</v>
       </c>
@@ -9178,8 +10309,11 @@
       <c r="E378" s="6">
         <v>356.73</v>
       </c>
-    </row>
-    <row r="379" spans="1:5">
+      <c r="F378" s="6">
+        <v>356.73</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
       <c r="A379" s="2" t="s">
         <v>576</v>
       </c>
@@ -9195,8 +10329,11 @@
       <c r="E379" s="6">
         <v>651.4</v>
       </c>
-    </row>
-    <row r="380" spans="1:5">
+      <c r="F379" s="6">
+        <v>651.4</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
       <c r="A380" s="2" t="s">
         <v>576</v>
       </c>
@@ -9212,8 +10349,11 @@
       <c r="E380" s="6">
         <v>764.3</v>
       </c>
-    </row>
-    <row r="381" spans="1:5">
+      <c r="F380" s="6">
+        <v>764.3</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
       <c r="A381" s="2" t="s">
         <v>576</v>
       </c>
@@ -9229,8 +10369,11 @@
       <c r="E381" s="6">
         <v>729.12</v>
       </c>
-    </row>
-    <row r="382" spans="1:5">
+      <c r="F381" s="6">
+        <v>729.12</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
       <c r="A382" s="2" t="s">
         <v>576</v>
       </c>
@@ -9246,8 +10389,11 @@
       <c r="E382" s="6">
         <v>216.35</v>
       </c>
-    </row>
-    <row r="383" spans="1:5">
+      <c r="F382" s="6">
+        <v>216.35</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
       <c r="A383" s="2" t="s">
         <v>576</v>
       </c>
@@ -9263,8 +10409,11 @@
       <c r="E383" s="6">
         <v>597.20000000000005</v>
       </c>
-    </row>
-    <row r="384" spans="1:5">
+      <c r="F383" s="6">
+        <v>597.20000000000005</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
       <c r="A384" s="2" t="s">
         <v>576</v>
       </c>
@@ -9280,8 +10429,11 @@
       <c r="E384" s="5">
         <v>5600.79</v>
       </c>
-    </row>
-    <row r="385" spans="1:5">
+      <c r="F384" s="5">
+        <v>5600.79</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
       <c r="A385" s="2" t="s">
         <v>576</v>
       </c>
@@ -9297,8 +10449,11 @@
       <c r="E385" s="6">
         <v>652.29999999999995</v>
       </c>
-    </row>
-    <row r="386" spans="1:5">
+      <c r="F385" s="6">
+        <v>652.29999999999995</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6">
       <c r="A386" s="2" t="s">
         <v>576</v>
       </c>
@@ -9314,8 +10469,11 @@
       <c r="E386" s="5">
         <v>2042.43</v>
       </c>
-    </row>
-    <row r="387" spans="1:5">
+      <c r="F386" s="5">
+        <v>2042.43</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6">
       <c r="A387" s="2" t="s">
         <v>576</v>
       </c>
@@ -9331,8 +10489,11 @@
       <c r="E387" s="6">
         <v>870.5</v>
       </c>
-    </row>
-    <row r="388" spans="1:5">
+      <c r="F387" s="6">
+        <v>870.5</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6">
       <c r="A388" s="2" t="s">
         <v>576</v>
       </c>
@@ -9348,8 +10509,11 @@
       <c r="E388" s="5">
         <v>1009.8</v>
       </c>
-    </row>
-    <row r="389" spans="1:5">
+      <c r="F388" s="5">
+        <v>1009.8</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6">
       <c r="A389" s="2" t="s">
         <v>576</v>
       </c>
@@ -9365,8 +10529,11 @@
       <c r="E389" s="6">
         <v>870.5</v>
       </c>
-    </row>
-    <row r="390" spans="1:5">
+      <c r="F389" s="6">
+        <v>870.5</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6">
       <c r="A390" s="2" t="s">
         <v>576</v>
       </c>
@@ -9382,8 +10549,11 @@
       <c r="E390" s="6">
         <v>596.72</v>
       </c>
-    </row>
-    <row r="391" spans="1:5">
+      <c r="F390" s="6">
+        <v>596.72</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6">
       <c r="A391" s="2" t="s">
         <v>576</v>
       </c>
@@ -9399,8 +10569,11 @@
       <c r="E391" s="6">
         <v>736.72</v>
       </c>
-    </row>
-    <row r="392" spans="1:5">
+      <c r="F391" s="6">
+        <v>736.72</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6">
       <c r="A392" s="2" t="s">
         <v>576</v>
       </c>
@@ -9416,8 +10589,11 @@
       <c r="E392" s="6">
         <v>716.1</v>
       </c>
-    </row>
-    <row r="393" spans="1:5">
+      <c r="F392" s="6">
+        <v>716.1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6">
       <c r="A393" s="2" t="s">
         <v>576</v>
       </c>
@@ -9433,8 +10609,11 @@
       <c r="E393" s="6">
         <v>564.66</v>
       </c>
-    </row>
-    <row r="394" spans="1:5">
+      <c r="F393" s="6">
+        <v>564.66</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6">
       <c r="A394" s="2" t="s">
         <v>576</v>
       </c>
@@ -9450,8 +10629,11 @@
       <c r="E394" s="6">
         <v>898.02</v>
       </c>
-    </row>
-    <row r="395" spans="1:5">
+      <c r="F394" s="6">
+        <v>898.02</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6">
       <c r="A395" s="2" t="s">
         <v>576</v>
       </c>
@@ -9467,8 +10649,11 @@
       <c r="E395" s="6">
         <v>898.02</v>
       </c>
-    </row>
-    <row r="396" spans="1:5">
+      <c r="F395" s="6">
+        <v>898.02</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6">
       <c r="A396" s="2" t="s">
         <v>576</v>
       </c>
@@ -9484,8 +10669,11 @@
       <c r="E396" s="6">
         <v>651.29999999999995</v>
       </c>
-    </row>
-    <row r="397" spans="1:5">
+      <c r="F396" s="6">
+        <v>651.29999999999995</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6">
       <c r="A397" s="2" t="s">
         <v>576</v>
       </c>
@@ -9501,8 +10689,11 @@
       <c r="E397" s="5">
         <v>-36000</v>
       </c>
-    </row>
-    <row r="398" spans="1:5">
+      <c r="F397" s="5">
+        <v>-36000</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6">
       <c r="A398" s="2" t="s">
         <v>619</v>
       </c>
@@ -9518,8 +10709,11 @@
       <c r="E398" s="6">
         <v>188.76</v>
       </c>
-    </row>
-    <row r="399" spans="1:5">
+      <c r="F398" s="6">
+        <v>188.76</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6">
       <c r="A399" s="2" t="s">
         <v>619</v>
       </c>
@@ -9535,8 +10729,11 @@
       <c r="E399" s="6">
         <v>218.02</v>
       </c>
-    </row>
-    <row r="400" spans="1:5">
+      <c r="F399" s="6">
+        <v>218.02</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6">
       <c r="A400" s="2" t="s">
         <v>619</v>
       </c>
@@ -9552,8 +10749,11 @@
       <c r="E400" s="6">
         <v>235.95</v>
       </c>
-    </row>
-    <row r="401" spans="1:5">
+      <c r="F400" s="6">
+        <v>235.95</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6">
       <c r="A401" s="2" t="s">
         <v>623</v>
       </c>
@@ -9569,8 +10769,11 @@
       <c r="E401" s="5">
         <v>4607.6400000000003</v>
       </c>
-    </row>
-    <row r="402" spans="1:5">
+      <c r="F401" s="5">
+        <v>4607.6400000000003</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6">
       <c r="A402" s="2" t="s">
         <v>623</v>
       </c>
@@ -9586,8 +10789,11 @@
       <c r="E402" s="5">
         <v>6835.49</v>
       </c>
-    </row>
-    <row r="403" spans="1:5">
+      <c r="F402" s="5">
+        <v>6835.49</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6">
       <c r="A403" s="2" t="s">
         <v>623</v>
       </c>
@@ -9603,8 +10809,11 @@
       <c r="E403" s="6">
         <v>374.52</v>
       </c>
-    </row>
-    <row r="404" spans="1:5">
+      <c r="F403" s="6">
+        <v>374.52</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6">
       <c r="A404" s="2" t="s">
         <v>623</v>
       </c>
@@ -9620,8 +10829,11 @@
       <c r="E404" s="5">
         <v>10694.76</v>
       </c>
-    </row>
-    <row r="405" spans="1:5">
+      <c r="F404" s="5">
+        <v>10694.76</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6">
       <c r="A405" s="2" t="s">
         <v>631</v>
       </c>
@@ -9637,8 +10849,11 @@
       <c r="E405" s="6">
         <v>337.41</v>
       </c>
-    </row>
-    <row r="406" spans="1:5">
+      <c r="F405" s="6">
+        <v>337.41</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6">
       <c r="A406" s="2" t="s">
         <v>633</v>
       </c>
@@ -9654,8 +10869,11 @@
       <c r="E406" s="5">
         <v>3879.17</v>
       </c>
-    </row>
-    <row r="407" spans="1:5">
+      <c r="F406" s="5">
+        <v>3879.17</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6">
       <c r="A407" s="2" t="s">
         <v>633</v>
       </c>
@@ -9671,8 +10889,11 @@
       <c r="E407" s="6">
         <v>589.9</v>
       </c>
-    </row>
-    <row r="408" spans="1:5">
+      <c r="F407" s="6">
+        <v>589.9</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6">
       <c r="A408" s="2" t="s">
         <v>633</v>
       </c>
@@ -9688,8 +10909,11 @@
       <c r="E408" s="5">
         <v>1565.3</v>
       </c>
-    </row>
-    <row r="409" spans="1:5">
+      <c r="F408" s="5">
+        <v>1565.3</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6">
       <c r="A409" s="2" t="s">
         <v>633</v>
       </c>
@@ -9705,8 +10929,11 @@
       <c r="E409" s="6">
         <v>752.71</v>
       </c>
-    </row>
-    <row r="410" spans="1:5">
+      <c r="F409" s="6">
+        <v>752.71</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6">
       <c r="A410" s="2" t="s">
         <v>638</v>
       </c>
@@ -9722,8 +10949,11 @@
       <c r="E410" s="5">
         <v>1796.36</v>
       </c>
-    </row>
-    <row r="411" spans="1:5">
+      <c r="F410" s="5">
+        <v>1796.36</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6">
       <c r="A411" s="2" t="s">
         <v>640</v>
       </c>
@@ -9739,8 +10969,11 @@
       <c r="E411" s="5">
         <v>2970.84</v>
       </c>
-    </row>
-    <row r="412" spans="1:5">
+      <c r="F411" s="5">
+        <v>2970.84</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6">
       <c r="A412" s="2" t="s">
         <v>640</v>
       </c>
@@ -9756,8 +10989,11 @@
       <c r="E412" s="5">
         <v>1009.62</v>
       </c>
-    </row>
-    <row r="413" spans="1:5">
+      <c r="F412" s="5">
+        <v>1009.62</v>
+      </c>
+    </row>
+    <row r="413" spans="1:6">
       <c r="A413" s="2" t="s">
         <v>640</v>
       </c>
@@ -9773,8 +11009,11 @@
       <c r="E413" s="5">
         <v>2684.64</v>
       </c>
-    </row>
-    <row r="414" spans="1:5">
+      <c r="F413" s="5">
+        <v>2684.64</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6">
       <c r="A414" s="2" t="s">
         <v>640</v>
       </c>
@@ -9790,8 +11029,11 @@
       <c r="E414" s="6">
         <v>980.1</v>
       </c>
-    </row>
-    <row r="415" spans="1:5">
+      <c r="F414" s="6">
+        <v>980.1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6">
       <c r="A415" s="2" t="s">
         <v>645</v>
       </c>
@@ -9807,8 +11049,11 @@
       <c r="E415" s="6">
         <v>264.02999999999997</v>
       </c>
-    </row>
-    <row r="416" spans="1:5">
+      <c r="F415" s="6">
+        <v>264.02999999999997</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6">
       <c r="A416" s="2" t="s">
         <v>645</v>
       </c>
@@ -9824,8 +11069,11 @@
       <c r="E416" s="6">
         <v>569.84</v>
       </c>
-    </row>
-    <row r="417" spans="1:5">
+      <c r="F416" s="6">
+        <v>569.84</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6">
       <c r="A417" s="2" t="s">
         <v>645</v>
       </c>
@@ -9841,8 +11089,11 @@
       <c r="E417" s="6">
         <v>211.45</v>
       </c>
-    </row>
-    <row r="418" spans="1:5">
+      <c r="F417" s="6">
+        <v>211.45</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6">
       <c r="A418" s="2" t="s">
         <v>645</v>
       </c>
@@ -9858,8 +11109,11 @@
       <c r="E418" s="6">
         <v>92.34</v>
       </c>
-    </row>
-    <row r="419" spans="1:5">
+      <c r="F418" s="6">
+        <v>92.34</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6">
       <c r="A419" s="2" t="s">
         <v>645</v>
       </c>
@@ -9875,8 +11129,11 @@
       <c r="E419" s="6">
         <v>318.69</v>
       </c>
-    </row>
-    <row r="420" spans="1:5">
+      <c r="F419" s="6">
+        <v>318.69</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6">
       <c r="A420" s="2" t="s">
         <v>645</v>
       </c>
@@ -9892,8 +11149,11 @@
       <c r="E420" s="6">
         <v>501.26</v>
       </c>
-    </row>
-    <row r="421" spans="1:5">
+      <c r="F420" s="6">
+        <v>501.26</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6">
       <c r="A421" s="2" t="s">
         <v>657</v>
       </c>
@@ -9909,8 +11169,11 @@
       <c r="E421" s="6">
         <v>711.16</v>
       </c>
-    </row>
-    <row r="422" spans="1:5">
+      <c r="F421" s="6">
+        <v>711.16</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6">
       <c r="A422" s="2" t="s">
         <v>657</v>
       </c>
@@ -9926,8 +11189,11 @@
       <c r="E422" s="5">
         <v>3028.65</v>
       </c>
-    </row>
-    <row r="423" spans="1:5">
+      <c r="F422" s="5">
+        <v>3028.65</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6">
       <c r="A423" s="2" t="s">
         <v>657</v>
       </c>
@@ -9943,8 +11209,11 @@
       <c r="E423" s="6">
         <v>323.57</v>
       </c>
-    </row>
-    <row r="424" spans="1:5">
+      <c r="F423" s="6">
+        <v>323.57</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6">
       <c r="A424" s="2" t="s">
         <v>657</v>
       </c>
@@ -9960,8 +11229,11 @@
       <c r="E424" s="6">
         <v>401.14</v>
       </c>
-    </row>
-    <row r="425" spans="1:5">
+      <c r="F424" s="6">
+        <v>401.14</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6">
       <c r="A425" s="2" t="s">
         <v>657</v>
       </c>
@@ -9977,8 +11249,11 @@
       <c r="E425" s="5">
         <v>1047.43</v>
       </c>
-    </row>
-    <row r="426" spans="1:5">
+      <c r="F425" s="5">
+        <v>1047.43</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6">
       <c r="A426" s="2" t="s">
         <v>657</v>
       </c>
@@ -9994,8 +11269,11 @@
       <c r="E426" s="6">
         <v>759.09</v>
       </c>
-    </row>
-    <row r="427" spans="1:5">
+      <c r="F426" s="6">
+        <v>759.09</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6">
       <c r="A427" s="2" t="s">
         <v>657</v>
       </c>
@@ -10011,8 +11289,11 @@
       <c r="E427" s="5">
         <v>2374.58</v>
       </c>
-    </row>
-    <row r="428" spans="1:5">
+      <c r="F427" s="5">
+        <v>2374.58</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6">
       <c r="A428" s="2" t="s">
         <v>666</v>
       </c>
@@ -10028,8 +11309,11 @@
       <c r="E428" s="6">
         <v>45.35</v>
       </c>
-    </row>
-    <row r="429" spans="1:5">
+      <c r="F428" s="6">
+        <v>45.35</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6">
       <c r="A429" s="2" t="s">
         <v>666</v>
       </c>
@@ -10045,8 +11329,11 @@
       <c r="E429" s="5">
         <v>3035.94</v>
       </c>
-    </row>
-    <row r="430" spans="1:5">
+      <c r="F429" s="5">
+        <v>3035.94</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6">
       <c r="A430" s="2" t="s">
         <v>666</v>
       </c>
@@ -10062,8 +11349,11 @@
       <c r="E430" s="5">
         <v>5995.83</v>
       </c>
-    </row>
-    <row r="431" spans="1:5">
+      <c r="F430" s="5">
+        <v>5995.83</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6">
       <c r="A431" s="2" t="s">
         <v>666</v>
       </c>
@@ -10079,8 +11369,11 @@
       <c r="E431" s="5">
         <v>2526.5300000000002</v>
       </c>
-    </row>
-    <row r="432" spans="1:5">
+      <c r="F431" s="5">
+        <v>2526.5300000000002</v>
+      </c>
+    </row>
+    <row r="432" spans="1:6">
       <c r="A432" s="2" t="s">
         <v>666</v>
       </c>
@@ -10096,8 +11389,11 @@
       <c r="E432" s="5">
         <v>1992.95</v>
       </c>
-    </row>
-    <row r="433" spans="1:5">
+      <c r="F432" s="5">
+        <v>1992.95</v>
+      </c>
+    </row>
+    <row r="433" spans="1:6">
       <c r="A433" s="2" t="s">
         <v>666</v>
       </c>
@@ -10113,8 +11409,11 @@
       <c r="E433" s="5">
         <v>1550.83</v>
       </c>
-    </row>
-    <row r="434" spans="1:5">
+      <c r="F433" s="5">
+        <v>1550.83</v>
+      </c>
+    </row>
+    <row r="434" spans="1:6">
       <c r="A434" s="2" t="s">
         <v>666</v>
       </c>
@@ -10130,8 +11429,11 @@
       <c r="E434" s="6">
         <v>188.76</v>
       </c>
-    </row>
-    <row r="435" spans="1:5">
+      <c r="F434" s="6">
+        <v>188.76</v>
+      </c>
+    </row>
+    <row r="435" spans="1:6">
       <c r="A435" s="2" t="s">
         <v>666</v>
       </c>
@@ -10147,8 +11449,11 @@
       <c r="E435" s="6">
         <v>532.1</v>
       </c>
-    </row>
-    <row r="436" spans="1:5">
+      <c r="F435" s="6">
+        <v>532.1</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6">
       <c r="A436" s="2" t="s">
         <v>675</v>
       </c>
@@ -10164,8 +11469,11 @@
       <c r="E436" s="6">
         <v>10.98</v>
       </c>
-    </row>
-    <row r="437" spans="1:5">
+      <c r="F436" s="6">
+        <v>10.98</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6">
       <c r="A437" s="2" t="s">
         <v>677</v>
       </c>
@@ -10181,8 +11489,11 @@
       <c r="E437" s="6">
         <v>178.53</v>
       </c>
-    </row>
-    <row r="438" spans="1:5">
+      <c r="F437" s="6">
+        <v>178.53</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6">
       <c r="A438" s="2" t="s">
         <v>677</v>
       </c>
@@ -10198,8 +11509,11 @@
       <c r="E438" s="6">
         <v>963.9</v>
       </c>
-    </row>
-    <row r="439" spans="1:5">
+      <c r="F438" s="6">
+        <v>963.9</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6">
       <c r="A439" s="2" t="s">
         <v>680</v>
       </c>
@@ -10215,8 +11529,11 @@
       <c r="E439" s="5">
         <v>1732.17</v>
       </c>
-    </row>
-    <row r="440" spans="1:5">
+      <c r="F439" s="5">
+        <v>1732.17</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6">
       <c r="A440" s="2" t="s">
         <v>680</v>
       </c>
@@ -10232,8 +11549,11 @@
       <c r="E440" s="6">
         <v>956.4</v>
       </c>
-    </row>
-    <row r="441" spans="1:5">
+      <c r="F440" s="6">
+        <v>956.4</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6">
       <c r="A441" s="2" t="s">
         <v>685</v>
       </c>
@@ -10249,8 +11569,11 @@
       <c r="E441" s="6">
         <v>680.06</v>
       </c>
-    </row>
-    <row r="442" spans="1:5">
+      <c r="F441" s="6">
+        <v>680.06</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6">
       <c r="A442" s="2" t="s">
         <v>687</v>
       </c>
@@ -10266,8 +11589,11 @@
       <c r="E442" s="5">
         <v>2486.83</v>
       </c>
-    </row>
-    <row r="443" spans="1:5">
+      <c r="F442" s="5">
+        <v>2486.83</v>
+      </c>
+    </row>
+    <row r="443" spans="1:6">
       <c r="A443" s="2" t="s">
         <v>687</v>
       </c>
@@ -10283,8 +11609,11 @@
       <c r="E443" s="5">
         <v>4991.01</v>
       </c>
-    </row>
-    <row r="444" spans="1:5">
+      <c r="F443" s="5">
+        <v>4991.01</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6">
       <c r="A444" s="2" t="s">
         <v>156</v>
       </c>
@@ -10300,8 +11629,11 @@
       <c r="E444" s="5">
         <v>6232.46</v>
       </c>
-    </row>
-    <row r="445" spans="1:5">
+      <c r="F444" s="5">
+        <v>6232.46</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6">
       <c r="A445" s="2" t="s">
         <v>156</v>
       </c>
@@ -10317,8 +11649,11 @@
       <c r="E445" s="5">
         <v>9370.36</v>
       </c>
-    </row>
-    <row r="446" spans="1:5">
+      <c r="F445" s="5">
+        <v>9370.36</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6">
       <c r="A446" s="2" t="s">
         <v>692</v>
       </c>
@@ -10334,8 +11669,11 @@
       <c r="E446" s="5">
         <v>2472.66</v>
       </c>
-    </row>
-    <row r="447" spans="1:5">
+      <c r="F446" s="5">
+        <v>2472.66</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6">
       <c r="A447" s="2" t="s">
         <v>694</v>
       </c>
@@ -10351,8 +11689,11 @@
       <c r="E447" s="5">
         <v>1565.3</v>
       </c>
-    </row>
-    <row r="448" spans="1:5">
+      <c r="F447" s="5">
+        <v>1565.3</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6">
       <c r="A448" s="2" t="s">
         <v>306</v>
       </c>
@@ -10368,8 +11709,11 @@
       <c r="E448" s="5">
         <v>2931.2</v>
       </c>
-    </row>
-    <row r="449" spans="1:5">
+      <c r="F448" s="5">
+        <v>2931.2</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6">
       <c r="A449" s="2" t="s">
         <v>306</v>
       </c>
@@ -10385,8 +11729,11 @@
       <c r="E449" s="5">
         <v>2741.2</v>
       </c>
-    </row>
-    <row r="450" spans="1:5">
+      <c r="F449" s="5">
+        <v>2741.2</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6">
       <c r="A450" s="2" t="s">
         <v>306</v>
       </c>
@@ -10402,8 +11749,11 @@
       <c r="E450" s="5">
         <v>3087.07</v>
       </c>
-    </row>
-    <row r="451" spans="1:5">
+      <c r="F450" s="5">
+        <v>3087.07</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6">
       <c r="A451" s="2" t="s">
         <v>306</v>
       </c>
@@ -10419,8 +11769,11 @@
       <c r="E451" s="5">
         <v>2201.4</v>
       </c>
-    </row>
-    <row r="452" spans="1:5">
+      <c r="F451" s="5">
+        <v>2201.4</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6">
       <c r="A452" s="2" t="s">
         <v>306</v>
       </c>
@@ -10436,8 +11789,11 @@
       <c r="E452" s="5">
         <v>2741.2</v>
       </c>
-    </row>
-    <row r="453" spans="1:5">
+      <c r="F452" s="5">
+        <v>2741.2</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6">
       <c r="A453" s="2" t="s">
         <v>319</v>
       </c>
@@ -10453,8 +11809,11 @@
       <c r="E453" s="5">
         <v>1469.88</v>
       </c>
-    </row>
-    <row r="454" spans="1:5">
+      <c r="F453" s="5">
+        <v>1469.88</v>
+      </c>
+    </row>
+    <row r="454" spans="1:6">
       <c r="A454" s="2" t="s">
         <v>707</v>
       </c>
@@ -10470,8 +11829,11 @@
       <c r="E454" s="5">
         <v>1128.3</v>
       </c>
-    </row>
-    <row r="455" spans="1:5">
+      <c r="F454" s="5">
+        <v>1128.3</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6">
       <c r="A455" s="2" t="s">
         <v>710</v>
       </c>
@@ -10487,8 +11849,11 @@
       <c r="E455" s="6">
         <v>262.77999999999997</v>
       </c>
-    </row>
-    <row r="456" spans="1:5">
+      <c r="F455" s="6">
+        <v>262.77999999999997</v>
+      </c>
+    </row>
+    <row r="456" spans="1:6">
       <c r="A456" s="2" t="s">
         <v>306</v>
       </c>
@@ -10502,6 +11867,9 @@
         <v>2644.48</v>
       </c>
       <c r="E456" s="5">
+        <v>2644.48</v>
+      </c>
+      <c r="F456" s="5">
         <v>2644.48</v>
       </c>
     </row>
